--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01_v2.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01_v2.xlsx
@@ -21,8 +21,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Var_A_Agregovany_Dum'!$A$1:$G$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Var_A_Agregovany_Sklad'!$A$1:$G$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$118</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Var_B_Polozkovy_Dum'!$A$1:$O$188</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Var_B_Polozkovy_Dum'!$A$1:$O$189</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Var_B_Polozkovy_Sklad'!$A$1:$O$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Var_F_URS_Verification_Trail'!$A$1:$H$14</definedName>
   </definedNames>
@@ -1009,11 +1009,11 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>HSV položkově (105 ks) + PSV/TZB/VRN agregovaně (12 skupin) = 117 řádků.</t>
+          <t>HSV položkově (106 ks) + PSV/TZB/VRN agregovaně (12 skupin) = 118 řádků.</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D24" s="10" t="n"/>
       <c r="E24" s="10" t="n"/>
@@ -1027,11 +1027,11 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Plný detail (187 dum + 28 sklad = 215 položek). Cílový rozsah pro produkční pricing.</t>
+          <t>Plný detail (188 dum + 28 sklad = 216 položek). Cílový rozsah pro produkční pricing.</t>
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D25" s="10" t="n"/>
       <c r="E25" s="10" t="n"/>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>215 (187 dum + 28 sklad)</t>
+          <t>216 (188 dum + 28 sklad)</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>HSV 105 | PSV 54 | TZB 34 | VRN 22</t>
+          <t>HSV 106 | PSV 54 | TZB 34 | VRN 22</t>
         </is>
       </c>
     </row>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>0.99: 17 | 0.95: 32 | 0.90: 35 | 0.85: 41 | 0.80: 19 | 0.75: 69 | 0.70: 1 | 0.60: 1</t>
+          <t>0.99: 17 | 0.95: 32 | 0.90: 35 | 0.85: 41 | 0.80: 19 | 0.75: 69 | 0.70: 1 | 0.60: 2</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>8 WebSearch verified (3.7 %) ✓ | 5 wrong leaf flagged (2.3 %) ⚠ | 140 needs_production_lookup (65.1 %)</t>
+          <t>8 WebSearch verified (3.7 %) ✓ | 5 wrong leaf flagged (2.3 %) ⚠ | 140 needs_production_lookup (64.8 %)</t>
         </is>
       </c>
     </row>
@@ -1186,8 +1186,8 @@
       <c r="A43" s="12" t="inlineStr">
         <is>
           <t>Rozpočet generován STAVAGENT pipelinem z DSP dokumentace s DPS-grade DXF metadaty.
-215 položek celkem (187 dum + 28 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
-Confidence distribution: 17×0.99 · 32×0.95 · 35×0.90 · 41×0.85 · 19×0.80 · 69×0.75 · 1×0.70 · 1×0.60.
+216 položek celkem (188 dum + 28 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
+Confidence distribution: 17×0.99 · 32×0.95 · 35×0.90 · 41×0.85 · 19×0.80 · 69×0.75 · 1×0.70 · 2×0.60.
 25 položek vzniklo per-room expansion ze 9 aggregate parents (každá expanded položka tagged _expansion_origin).
 10 položek recalculated s exact external perimeter 38.70 m (DXF km_R_návrh_tlustá 2 closed polygon) vs prior fallback 41.0 m.
 Skladby vrstev (Sheet 8 Var_E) pochází POUZE z TZ explicit text + DXF cross-validation HATCH patterns. ŽÁDNÉ generic 'standardní RD' assumption — kde TZ silent, explicit fallback flag s ČSN default.
@@ -2576,11 +2576,11 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Krokve 100/180 á 800 mm; Kleštiny 2×60/180; Pozednice 140/160; Námětky pro přesah; … (+12 dalších)</t>
+          <t>Krokve 100/180 á 800 mm; Kleštiny 2×60/180; Pozednice 140/160; Námětky pro přesah; … (+13 dalších)</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E6" s="10" t="n"/>
       <c r="F6" s="10" t="n"/>
@@ -3138,7 +3138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J118"/>
+  <dimension ref="A1:J119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7411,37 +7411,37 @@
       </c>
       <c r="B107" s="20" t="inlineStr">
         <is>
-          <t>260217_sklad</t>
-        </is>
-      </c>
-      <c r="C107" s="21" t="inlineStr">
-        <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C107" s="8" t="inlineStr">
+        <is>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Bezpečnostní dveře RC3 sklad</t>
+          <t>Spojovací prostředky krovu — svorníky tesařských spojů — Montáž svorníků / šroubů tesařských spojů krovu délky přes 150 do 300 mm — spojení kleštin 2×60/180 mm s krokvemi (svorník cca 250 mm, M12), vč. tyče závitové + matic + podložek</t>
         </is>
       </c>
       <c r="E107" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F107" s="9" t="n">
-        <v>1</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="F107" s="23" t="n">
+        <v>50</v>
       </c>
       <c r="G107" s="10" t="n"/>
       <c r="H107" s="10" t="n"/>
       <c r="I107" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>tesar</t>
         </is>
       </c>
       <c r="J107" s="8" t="inlineStr">
         <is>
-          <t>agregát</t>
+          <t>URS-prop 762085112</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="C108" s="21" t="inlineStr">
         <is>
-          <t>PSV-77 — Podlahy</t>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D108" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
+          <t>[agregát] 1 položek: Bezpečnostní dveře RC3 sklad</t>
         </is>
       </c>
       <c r="E108" s="20" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="C109" s="21" t="inlineStr">
         <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D109" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 4 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+1 dalších)</t>
+          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
         </is>
       </c>
       <c r="E109" s="20" t="inlineStr">
@@ -7531,17 +7531,17 @@
       </c>
       <c r="B110" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="C110" s="21" t="inlineStr">
         <is>
-          <t>M-21 — Elektroinstalace silnoproudá</t>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
         </is>
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 7 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+4 dalších)</t>
+          <t>[agregát] 4 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+1 dalších)</t>
         </is>
       </c>
       <c r="E110" s="20" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="C111" s="21" t="inlineStr">
         <is>
-          <t>PSV-71 — Izolace HI + TI</t>
+          <t>M-21 — Elektroinstalace silnoproudá</t>
         </is>
       </c>
       <c r="D111" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
+          <t>[agregát] 7 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+4 dalších)</t>
         </is>
       </c>
       <c r="E111" s="20" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="C112" s="21" t="inlineStr">
         <is>
-          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
+          <t>PSV-71 — Izolace HI + TI</t>
         </is>
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
+          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
         </is>
       </c>
       <c r="E112" s="20" t="inlineStr">
@@ -7656,12 +7656,12 @@
       </c>
       <c r="C113" s="21" t="inlineStr">
         <is>
-          <t>PSV-73 — Vytápění + komín</t>
+          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
         </is>
       </c>
       <c r="D113" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
+          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
         </is>
       </c>
       <c r="E113" s="20" t="inlineStr">
@@ -7696,12 +7696,12 @@
       </c>
       <c r="C114" s="21" t="inlineStr">
         <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+          <t>PSV-73 — Vytápění + komín</t>
         </is>
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
+          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
         </is>
       </c>
       <c r="E114" s="20" t="inlineStr">
@@ -7736,12 +7736,12 @@
       </c>
       <c r="C115" s="21" t="inlineStr">
         <is>
-          <t>PSV-77 — Podlahy</t>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
+          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
         </is>
       </c>
       <c r="E115" s="20" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="C116" s="21" t="inlineStr">
         <is>
-          <t>PSV-78 — Povrchové úpravy</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D116" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
+          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
         </is>
       </c>
       <c r="E116" s="20" t="inlineStr">
@@ -7816,12 +7816,12 @@
       </c>
       <c r="C117" s="21" t="inlineStr">
         <is>
-          <t>PSV-95 — Detekce požární</t>
+          <t>PSV-78 — Povrchové úpravy</t>
         </is>
       </c>
       <c r="D117" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 2 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A</t>
+          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
         </is>
       </c>
       <c r="E117" s="20" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="C118" s="21" t="inlineStr">
         <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
+          <t>PSV-95 — Detekce požární</t>
         </is>
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
+          <t>[agregát] 2 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A</t>
         </is>
       </c>
       <c r="E118" s="20" t="inlineStr">
@@ -7885,8 +7885,48 @@
         </is>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" s="20" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C119" s="21" t="inlineStr">
+        <is>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
+        </is>
+      </c>
+      <c r="D119" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
+        </is>
+      </c>
+      <c r="E119" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F119" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G119" s="10" t="n"/>
+      <c r="H119" s="10" t="n"/>
+      <c r="I119" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J119" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J118"/>
+  <autoFilter ref="A1:J119"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7897,7 +7937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R188"/>
+  <dimension ref="A1:R189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12205,55 +12245,55 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Bourání kompletního stávajícího krovu</t>
+          <t>Spojovací prostředky krovu — svorníky tesařských spojů</t>
         </is>
       </c>
       <c r="D62" s="20" t="inlineStr">
         <is>
-          <t>962041141</t>
+          <t>762085112</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>Bourání kompletního stávajícího krovu vč. vikýřů — vaznicový s ležatou stolicí — manuálně, odvoz</t>
+          <t>Montáž svorníků / šroubů tesařských spojů krovu délky přes 150 do 300 mm — spojení kleštin 2×60/180 mm s krokvemi (svorník cca 250 mm, M12), vč. tyče závitové + matic + podložek</t>
         </is>
       </c>
       <c r="F62" s="20" t="inlineStr">
         <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="G62" s="22" t="n">
-        <v>12</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G62" s="23" t="n">
+        <v>50</v>
       </c>
       <c r="H62" s="10" t="n"/>
       <c r="I62" s="10" t="n"/>
       <c r="J62" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>tesar</t>
         </is>
       </c>
       <c r="K62" s="24" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="L62" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>matched_catalog</t>
         </is>
       </c>
       <c r="M62" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10.e — 9 t dřeva celkem; krov hlavní zdroj</t>
+          <t>KROS/ÚRS catalog (762085112 montáž svorníků tesařských spojů) + STAVAGENT MCP; TZ statika §4 krov ocelové spojky</t>
         </is>
       </c>
       <c r="N62" s="20" t="inlineStr">
         <is>
-          <t>#9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O62" s="26" t="inlineStr">
@@ -12261,10 +12301,14 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P62" s="41" t="n"/>
+      <c r="P62" s="41" t="inlineStr">
+        <is>
+          <t>Krov — spojovací prostředky</t>
+        </is>
+      </c>
       <c r="Q62" s="41" t="inlineStr">
         <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+          <t>KROV_SVORNIKY_ADD_2026-05-31</t>
         </is>
       </c>
     </row>
@@ -12279,26 +12323,26 @@
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>Bourání plechové střešní krytiny</t>
-        </is>
-      </c>
-      <c r="D63" s="27" t="inlineStr">
-        <is>
-          <t>762??? ?</t>
+          <t>Bourání kompletního stávajícího krovu</t>
+        </is>
+      </c>
+      <c r="D63" s="20" t="inlineStr">
+        <is>
+          <t>962041141</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>Bourání stávající plechové krytiny (manuálně, recyklace plechu)</t>
+          <t>Bourání kompletního stávajícího krovu vč. vikýřů — vaznicový s ležatou stolicí — manuálně, odvoz</t>
         </is>
       </c>
       <c r="F63" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="G63" s="22" t="n">
-        <v>140.9</v>
+        <v>12</v>
       </c>
       <c r="H63" s="10" t="n"/>
       <c r="I63" s="10" t="n"/>
@@ -12312,12 +12356,12 @@
       </c>
       <c r="L63" s="20" t="inlineStr">
         <is>
-          <t>wrong_leaf_disambiguation_needed</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M63" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10.e — 0.1 t kovů; stávající plech krytina</t>
+          <t>TZ B m.10.e — 9 t dřeva celkem; krov hlavní zdroj</t>
         </is>
       </c>
       <c r="N63" s="20" t="inlineStr">
@@ -12325,13 +12369,17 @@
           <t>#9</t>
         </is>
       </c>
-      <c r="O63" s="28" t="inlineStr">
-        <is>
-          <t>LEAF CHYBNÝ — viz alternatives</t>
+      <c r="O63" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
         </is>
       </c>
       <c r="P63" s="41" t="n"/>
-      <c r="Q63" s="41" t="n"/>
+      <c r="Q63" s="41" t="inlineStr">
+        <is>
+          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="20" t="n">
@@ -12344,26 +12392,26 @@
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Bourání nadezdívek nad stropem 2.NP</t>
-        </is>
-      </c>
-      <c r="D64" s="20" t="inlineStr">
-        <is>
-          <t>962031132</t>
+          <t>Bourání plechové střešní krytiny</t>
+        </is>
+      </c>
+      <c r="D64" s="27" t="inlineStr">
+        <is>
+          <t>762??? ?</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>Bourání zděných nadezdívek nad stropem 2.NP (mimo štítových stěn) — cihla pálená</t>
+          <t>Bourání stávající plechové krytiny (manuálně, recyklace plechu)</t>
         </is>
       </c>
       <c r="F64" s="20" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G64" s="22" t="n">
-        <v>6</v>
+        <v>140.9</v>
       </c>
       <c r="H64" s="10" t="n"/>
       <c r="I64" s="10" t="n"/>
@@ -12377,12 +12425,12 @@
       </c>
       <c r="L64" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>wrong_leaf_disambiguation_needed</t>
         </is>
       </c>
       <c r="M64" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3 — bourání nadezdívek mimo štítů</t>
+          <t>TZ B m.10.e — 0.1 t kovů; stávající plech krytina</t>
         </is>
       </c>
       <c r="N64" s="20" t="inlineStr">
@@ -12390,9 +12438,9 @@
           <t>#9</t>
         </is>
       </c>
-      <c r="O64" s="26" t="inlineStr">
-        <is>
-          <t>ANO</t>
+      <c r="O64" s="28" t="inlineStr">
+        <is>
+          <t>LEAF CHYBNÝ — viz alternatives</t>
         </is>
       </c>
       <c r="P64" s="41" t="n"/>
@@ -12409,26 +12457,26 @@
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>Bourání trámového stropu 2.NP/podkroví</t>
+          <t>Bourání nadezdívek nad stropem 2.NP</t>
         </is>
       </c>
       <c r="D65" s="20" t="inlineStr">
         <is>
-          <t>962041141</t>
+          <t>962031132</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>Bourání trámového stropu 2.NP/podkroví — kompletně (vč. zajištění schodiště)</t>
+          <t>Bourání zděných nadezdívek nad stropem 2.NP (mimo štítových stěn) — cihla pálená</t>
         </is>
       </c>
       <c r="F65" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="G65" s="22" t="n">
-        <v>104.4</v>
+        <v>6</v>
       </c>
       <c r="H65" s="10" t="n"/>
       <c r="I65" s="10" t="n"/>
@@ -12447,7 +12495,7 @@
       </c>
       <c r="M65" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3 — strop 2.NP/3.NP KOMPLETNĚ bourán</t>
+          <t>TZ ARS dům §3 — bourání nadezdívek mimo štítů</t>
         </is>
       </c>
       <c r="N65" s="20" t="inlineStr">
@@ -12474,17 +12522,17 @@
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Bourání lehkých příček</t>
+          <t>Bourání trámového stropu 2.NP/podkroví</t>
         </is>
       </c>
       <c r="D66" s="20" t="inlineStr">
         <is>
-          <t>962031132</t>
+          <t>962041141</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>Bourání stávajících lehkých příček (cihla, sádrokarton, dřevo)</t>
+          <t>Bourání trámového stropu 2.NP/podkroví — kompletně (vč. zajištění schodiště)</t>
         </is>
       </c>
       <c r="F66" s="20" t="inlineStr">
@@ -12493,7 +12541,7 @@
         </is>
       </c>
       <c r="G66" s="22" t="n">
-        <v>80</v>
+        <v>104.4</v>
       </c>
       <c r="H66" s="10" t="n"/>
       <c r="I66" s="10" t="n"/>
@@ -12512,7 +12560,7 @@
       </c>
       <c r="M66" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3 — lehké příčky bourány</t>
+          <t>TZ ARS dům §3 — strop 2.NP/3.NP KOMPLETNĚ bourán</t>
         </is>
       </c>
       <c r="N66" s="20" t="inlineStr">
@@ -12539,7 +12587,7 @@
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>Bourání otvorů pro nové dveře/okna</t>
+          <t>Bourání lehkých příček</t>
         </is>
       </c>
       <c r="D67" s="20" t="inlineStr">
@@ -12549,16 +12597,16 @@
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>Bourání 8 nových otvorů v nosných cihelných zdech pro dveře/okna (~1.0 × 2.1 m)</t>
+          <t>Bourání stávajících lehkých příček (cihla, sádrokarton, dřevo)</t>
         </is>
       </c>
       <c r="F67" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G67" s="23" t="n">
-        <v>8</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G67" s="22" t="n">
+        <v>80</v>
       </c>
       <c r="H67" s="10" t="n"/>
       <c r="I67" s="10" t="n"/>
@@ -12577,12 +12625,12 @@
       </c>
       <c r="M67" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS + statika — nové otvory s IPN160 překlady</t>
+          <t>TZ ARS dům §3 — lehké příčky bourány</t>
         </is>
       </c>
       <c r="N67" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#9</t>
         </is>
       </c>
       <c r="O67" s="26" t="inlineStr">
@@ -12604,26 +12652,26 @@
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>Bourání obkladů v koupelnách</t>
+          <t>Bourání otvorů pro nové dveře/okna</t>
         </is>
       </c>
       <c r="D68" s="20" t="inlineStr">
         <is>
-          <t>781473810</t>
+          <t>962031132</t>
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>Bourání keramických obkladů a zařizovacích předmětů v koupelnách 1.NP + 2.NP</t>
+          <t>Bourání 8 nových otvorů v nosných cihelných zdech pro dveře/okna (~1.0 × 2.1 m)</t>
         </is>
       </c>
       <c r="F68" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G68" s="22" t="n">
-        <v>60</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G68" s="23" t="n">
+        <v>8</v>
       </c>
       <c r="H68" s="10" t="n"/>
       <c r="I68" s="10" t="n"/>
@@ -12637,17 +12685,17 @@
       </c>
       <c r="L68" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M68" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3 — koupelny kompletně bourány</t>
+          <t>TZ ARS + statika — nové otvory s IPN160 překlady</t>
         </is>
       </c>
       <c r="N68" s="20" t="inlineStr">
         <is>
-          <t>#9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O68" s="26" t="inlineStr">
@@ -12656,11 +12704,7 @@
         </is>
       </c>
       <c r="P68" s="41" t="n"/>
-      <c r="Q68" s="41" t="inlineStr">
-        <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
-        </is>
-      </c>
+      <c r="Q68" s="41" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="20" t="n">
@@ -12673,17 +12717,17 @@
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>Bourání podlah 1.NP + 2.NP</t>
+          <t>Bourání obkladů v koupelnách</t>
         </is>
       </c>
       <c r="D69" s="20" t="inlineStr">
         <is>
-          <t>974031132</t>
+          <t>781473810</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>Sejmutí podlah 1.NP a 2.NP — vč. nášlapů, podkladních vrstev</t>
+          <t>Bourání keramických obkladů a zařizovacích předmětů v koupelnách 1.NP + 2.NP</t>
         </is>
       </c>
       <c r="F69" s="20" t="inlineStr">
@@ -12692,7 +12736,7 @@
         </is>
       </c>
       <c r="G69" s="22" t="n">
-        <v>153.51</v>
+        <v>60</v>
       </c>
       <c r="H69" s="10" t="n"/>
       <c r="I69" s="10" t="n"/>
@@ -12706,12 +12750,12 @@
       </c>
       <c r="L69" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M69" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3 — podlahy 1.NP+2.NP sejmuty</t>
+          <t>TZ ARS dům §3 — koupelny kompletně bourány</t>
         </is>
       </c>
       <c r="N69" s="20" t="inlineStr">
@@ -12725,7 +12769,11 @@
         </is>
       </c>
       <c r="P69" s="41" t="n"/>
-      <c r="Q69" s="41" t="n"/>
+      <c r="Q69" s="41" t="inlineStr">
+        <is>
+          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="20" t="n">
@@ -12738,26 +12786,26 @@
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>Záklop + zásyp — demontáž</t>
+          <t>Bourání podlah 1.NP + 2.NP</t>
         </is>
       </c>
       <c r="D70" s="20" t="inlineStr">
         <is>
-          <t>974041151</t>
+          <t>974031132</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>Demontáž záklopu a zásypů stropu 1.NP (prkenný záklop na trámech zachován)</t>
+          <t>Sejmutí podlah 1.NP a 2.NP — vč. nášlapů, podkladních vrstev</t>
         </is>
       </c>
       <c r="F70" s="20" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G70" s="22" t="n">
-        <v>5</v>
+        <v>153.51</v>
       </c>
       <c r="H70" s="10" t="n"/>
       <c r="I70" s="10" t="n"/>
@@ -12776,7 +12824,7 @@
       </c>
       <c r="M70" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3 — záklop+zásyp demontován; trámy zachovány</t>
+          <t>TZ ARS dům §3 — podlahy 1.NP+2.NP sejmuty</t>
         </is>
       </c>
       <c r="N70" s="20" t="inlineStr">
@@ -12803,26 +12851,26 @@
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>Demontáž oken a dveří</t>
+          <t>Záklop + zásyp — demontáž</t>
         </is>
       </c>
       <c r="D71" s="20" t="inlineStr">
         <is>
-          <t>968071120</t>
+          <t>974041151</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>Demontáž všech oken a dveří stávajících (recyklace)</t>
+          <t>Demontáž záklopu a zásypů stropu 1.NP (prkenný záklop na trámech zachován)</t>
         </is>
       </c>
       <c r="F71" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G71" s="23" t="n">
-        <v>25</v>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="G71" s="22" t="n">
+        <v>5</v>
       </c>
       <c r="H71" s="10" t="n"/>
       <c r="I71" s="10" t="n"/>
@@ -12841,12 +12889,12 @@
       </c>
       <c r="M71" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3 — VŠECHNY okna a dveře demontovány</t>
+          <t>TZ ARS dům §3 — záklop+zásyp demontován; trámy zachovány</t>
         </is>
       </c>
       <c r="N71" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>#9</t>
         </is>
       </c>
       <c r="O71" s="26" t="inlineStr">
@@ -12868,17 +12916,17 @@
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>Demontáž zařizovacích předmětů</t>
+          <t>Demontáž oken a dveří</t>
         </is>
       </c>
       <c r="D72" s="20" t="inlineStr">
         <is>
-          <t>725900001</t>
+          <t>968071120</t>
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>Demontáž všech sanitárních zařizovacích předmětů (WC, umyvadla, baterie, sprcha)</t>
+          <t>Demontáž všech oken a dveří stávajících (recyklace)</t>
         </is>
       </c>
       <c r="F72" s="20" t="inlineStr">
@@ -12887,7 +12935,7 @@
         </is>
       </c>
       <c r="G72" s="23" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="H72" s="10" t="n"/>
       <c r="I72" s="10" t="n"/>
@@ -12906,12 +12954,12 @@
       </c>
       <c r="M72" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3 — zařizovací předměty kompletně demontovány</t>
+          <t>TZ ARS dům §3 — VŠECHNY okna a dveře demontovány</t>
         </is>
       </c>
       <c r="N72" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O72" s="26" t="inlineStr">
@@ -12933,26 +12981,26 @@
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>Odvoz suti a likvidace</t>
+          <t>Demontáž zařizovacích předmětů</t>
         </is>
       </c>
       <c r="D73" s="20" t="inlineStr">
         <is>
-          <t>997013501</t>
+          <t>725900001</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>Odvoz a likvidace stavební suti dle vyhl. 8/2021 Sb. — celková tonáž odpadů</t>
+          <t>Demontáž všech sanitárních zařizovacích předmětů (WC, umyvadla, baterie, sprcha)</t>
         </is>
       </c>
       <c r="F73" s="20" t="inlineStr">
         <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="G73" s="22" t="n">
-        <v>56.5</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G73" s="23" t="n">
+        <v>12</v>
       </c>
       <c r="H73" s="10" t="n"/>
       <c r="I73" s="10" t="n"/>
@@ -12962,7 +13010,7 @@
         </is>
       </c>
       <c r="K73" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L73" s="20" t="inlineStr">
         <is>
@@ -12971,12 +13019,12 @@
       </c>
       <c r="M73" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10.e bilance odpadů</t>
+          <t>TZ ARS dům §3 — zařizovací předměty kompletně demontovány</t>
         </is>
       </c>
       <c r="N73" s="20" t="inlineStr">
         <is>
-          <t>#9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O73" s="26" t="inlineStr">
@@ -12998,26 +13046,26 @@
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>Demontáž oken</t>
+          <t>Odvoz suti a likvidace</t>
         </is>
       </c>
       <c r="D74" s="20" t="inlineStr">
         <is>
-          <t>978013181</t>
+          <t>997013501</t>
         </is>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
+          <t>Odvoz a likvidace stavební suti dle vyhl. 8/2021 Sb. — celková tonáž odpadů</t>
         </is>
       </c>
       <c r="F74" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G74" s="23" t="n">
-        <v>16</v>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G74" s="22" t="n">
+        <v>56.5</v>
       </c>
       <c r="H74" s="10" t="n"/>
       <c r="I74" s="10" t="n"/>
@@ -13027,34 +13075,30 @@
         </is>
       </c>
       <c r="K74" s="24" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="L74" s="20" t="inlineStr">
         <is>
-          <t>matched_websearch_verified</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M74" s="8" t="inlineStr">
         <is>
-          <t>DXF blocks okno* (Path C Tier 4) + TZ ARS — všechna okna nová</t>
+          <t>TZ B m.10.e bilance odpadů</t>
         </is>
       </c>
       <c r="N74" s="20" t="inlineStr">
         <is>
-          <t>#3</t>
-        </is>
-      </c>
-      <c r="O74" s="25" t="inlineStr">
-        <is>
-          <t>OVĚŘENO ✓</t>
+          <t>#9</t>
+        </is>
+      </c>
+      <c r="O74" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
         </is>
       </c>
       <c r="P74" s="41" t="n"/>
-      <c r="Q74" s="41" t="inlineStr">
-        <is>
-          <t>GAP_002</t>
-        </is>
-      </c>
+      <c r="Q74" s="41" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="20" t="n">
@@ -13067,7 +13111,7 @@
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>Demontáž vstupních dveří venkovních</t>
+          <t>Demontáž oken</t>
         </is>
       </c>
       <c r="D75" s="20" t="inlineStr">
@@ -13077,7 +13121,7 @@
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
+          <t>Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
         </is>
       </c>
       <c r="F75" s="20" t="inlineStr">
@@ -13086,7 +13130,7 @@
         </is>
       </c>
       <c r="G75" s="23" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H75" s="10" t="n"/>
       <c r="I75" s="10" t="n"/>
@@ -13105,7 +13149,7 @@
       </c>
       <c r="M75" s="8" t="inlineStr">
         <is>
-          <t>DXF blocks dveře (vstupní 2) + TZ ARS — 'plastové vstupní dveře' x 2</t>
+          <t>DXF blocks okno* (Path C Tier 4) + TZ ARS — všechna okna nová</t>
         </is>
       </c>
       <c r="N75" s="20" t="inlineStr">
@@ -13136,17 +13180,17 @@
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>Demontáž vnitřních dveří vč. zárubní</t>
+          <t>Demontáž vstupních dveří venkovních</t>
         </is>
       </c>
       <c r="D76" s="20" t="inlineStr">
         <is>
-          <t>968072456</t>
+          <t>978013181</t>
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
+          <t>Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
         </is>
       </c>
       <c r="F76" s="20" t="inlineStr">
@@ -13155,7 +13199,7 @@
         </is>
       </c>
       <c r="G76" s="23" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H76" s="10" t="n"/>
       <c r="I76" s="10" t="n"/>
@@ -13165,16 +13209,16 @@
         </is>
       </c>
       <c r="K76" s="24" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="L76" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>matched_websearch_verified</t>
         </is>
       </c>
       <c r="M76" s="8" t="inlineStr">
         <is>
-          <t>DXF SM__dveře polyline count → estimate (Path C Tier 4)</t>
+          <t>DXF blocks dveře (vstupní 2) + TZ ARS — 'plastové vstupní dveře' x 2</t>
         </is>
       </c>
       <c r="N76" s="20" t="inlineStr">
@@ -13182,9 +13226,9 @@
           <t>#3</t>
         </is>
       </c>
-      <c r="O76" s="26" t="inlineStr">
-        <is>
-          <t>ANO</t>
+      <c r="O76" s="25" t="inlineStr">
+        <is>
+          <t>OVĚŘENO ✓</t>
         </is>
       </c>
       <c r="P76" s="41" t="n"/>
@@ -13205,26 +13249,26 @@
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>Bourání zdiva komínu</t>
+          <t>Demontáž vnitřních dveří vč. zárubní</t>
         </is>
       </c>
       <c r="D77" s="20" t="inlineStr">
         <is>
-          <t>962024141</t>
+          <t>968072456</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
+          <t>Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
         </is>
       </c>
       <c r="F77" s="20" t="inlineStr">
         <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="G77" s="22" t="n">
-        <v>0.6</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G77" s="23" t="n">
+        <v>15</v>
       </c>
       <c r="H77" s="10" t="n"/>
       <c r="I77" s="10" t="n"/>
@@ -13234,21 +13278,21 @@
         </is>
       </c>
       <c r="K77" s="24" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="L77" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M77" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ řez A-A bourání + POZN.1.02 z půdorysů bourání</t>
+          <t>DXF SM__dveře polyline count → estimate (Path C Tier 4)</t>
         </is>
       </c>
       <c r="N77" s="20" t="inlineStr">
         <is>
-          <t>#9</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="O77" s="26" t="inlineStr">
@@ -13259,7 +13303,7 @@
       <c r="P77" s="41" t="n"/>
       <c r="Q77" s="41" t="inlineStr">
         <is>
-          <t>PER_DRAWING_GAP_POZN_1_02; URS_PHASE5B_FAMILY_VERIFIED; CHATGPT_KOMIN_QTY_FIX_2026-05-29</t>
+          <t>GAP_002</t>
         </is>
       </c>
     </row>
@@ -13274,17 +13318,17 @@
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>Bourání venkovních konstrukcí</t>
+          <t>Bourání zdiva komínu</t>
         </is>
       </c>
       <c r="D78" s="20" t="inlineStr">
         <is>
-          <t>961044111</t>
+          <t>962024141</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
+          <t>Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
         </is>
       </c>
       <c r="F78" s="20" t="inlineStr">
@@ -13293,7 +13337,7 @@
         </is>
       </c>
       <c r="G78" s="22" t="n">
-        <v>8</v>
+        <v>0.6</v>
       </c>
       <c r="H78" s="10" t="n"/>
       <c r="I78" s="10" t="n"/>
@@ -13303,7 +13347,7 @@
         </is>
       </c>
       <c r="K78" s="24" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="L78" s="20" t="inlineStr">
         <is>
@@ -13312,7 +13356,7 @@
       </c>
       <c r="M78" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ řez A-A bourání + POZN.1.03 + půdorys bourání</t>
+          <t>DXF dum_DPZ řez A-A bourání + POZN.1.02 z půdorysů bourání</t>
         </is>
       </c>
       <c r="N78" s="20" t="inlineStr">
@@ -13328,7 +13372,7 @@
       <c r="P78" s="41" t="n"/>
       <c r="Q78" s="41" t="inlineStr">
         <is>
-          <t>PER_DRAWING_GAP_POZN_1_03; URS_PHASE5B_FAMILY_VERIFIED</t>
+          <t>PER_DRAWING_GAP_POZN_1_02; URS_PHASE5B_FAMILY_VERIFIED; CHATGPT_KOMIN_QTY_FIX_2026-05-29</t>
         </is>
       </c>
     </row>
@@ -13338,55 +13382,55 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda ETICS</t>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>Příprava podkladu</t>
+          <t>Bourání venkovních konstrukcí</t>
         </is>
       </c>
       <c r="D79" s="20" t="inlineStr">
         <is>
-          <t>622401110</t>
+          <t>961044111</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>Příprava fasádního podkladu — očištění tlakovou vodou, vyspravení omítek, fungicidní nátěr</t>
+          <t>Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
         </is>
       </c>
       <c r="F79" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="G79" s="22" t="n">
-        <v>276.7</v>
+        <v>8</v>
       </c>
       <c r="H79" s="10" t="n"/>
       <c r="I79" s="10" t="n"/>
       <c r="J79" s="8" t="inlineStr">
         <is>
-          <t>fasadnik_etics</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="K79" s="24" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="L79" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M79" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — ETICS kontaktní, podklad existující omítka + DXF perimeter</t>
+          <t>DXF dum_DPZ řez A-A bourání + POZN.1.03 + půdorys bourání</t>
         </is>
       </c>
       <c r="N79" s="20" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>#9</t>
         </is>
       </c>
       <c r="O79" s="26" t="inlineStr">
@@ -13394,12 +13438,12 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P79" s="41" t="inlineStr">
-        <is>
-          <t>S01</t>
-        </is>
-      </c>
-      <c r="Q79" s="41" t="n"/>
+      <c r="P79" s="41" t="n"/>
+      <c r="Q79" s="41" t="inlineStr">
+        <is>
+          <t>PER_DRAWING_GAP_POZN_1_03; URS_PHASE5B_FAMILY_VERIFIED</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="20" t="n">
@@ -13412,17 +13456,17 @@
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>ETICS EPS 70F grey 160 mm</t>
+          <t>Příprava podkladu</t>
         </is>
       </c>
       <c r="D80" s="20" t="inlineStr">
         <is>
-          <t>622221121</t>
+          <t>622401110</t>
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>ETICS kontaktní zateplení — EPS 70F grey λ=0.032 tl. 160 mm + síťka + lepidlo + zatírací stěrka (řez S01+S12a explicit, ne 200 mm fallback)</t>
+          <t>Příprava fasádního podkladu — očištění tlakovou vodou, vyspravení omítek, fungicidní nátěr</t>
         </is>
       </c>
       <c r="F80" s="20" t="inlineStr">
@@ -13445,12 +13489,12 @@
       </c>
       <c r="L80" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M80" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 EXPLICIT 'fasádní EPS 70f grey (λ=0,032 W/mK)' + PBŘ EXPLICIT 'EPS tl. max. 200 mm' + DXF perimeter</t>
+          <t>TZ ARS dům §3.2 — ETICS kontaktní, podklad existující omítka + DXF perimeter</t>
         </is>
       </c>
       <c r="N80" s="20" t="inlineStr">
@@ -13465,14 +13509,10 @@
       </c>
       <c r="P80" s="41" t="inlineStr">
         <is>
-          <t>S01, S12a</t>
-        </is>
-      </c>
-      <c r="Q80" s="41" t="inlineStr">
-        <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
-        </is>
-      </c>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="Q80" s="41" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="20" t="n">
@@ -13485,17 +13525,17 @@
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>ETICS sokl XPS</t>
+          <t>ETICS EPS 70F grey 160 mm</t>
         </is>
       </c>
       <c r="D81" s="20" t="inlineStr">
         <is>
-          <t>622223111</t>
+          <t>622221121</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>ETICS sokl — XPS λ=0.034 tl. 120 mm + soklový profil + cihelný obklad spárovaný</t>
+          <t>ETICS kontaktní zateplení — EPS 70F grey λ=0.032 tl. 160 mm + síťka + lepidlo + zatírací stěrka (řez S01+S12a explicit, ne 200 mm fallback)</t>
         </is>
       </c>
       <c r="F81" s="20" t="inlineStr">
@@ -13504,7 +13544,7 @@
         </is>
       </c>
       <c r="G81" s="22" t="n">
-        <v>13.5</v>
+        <v>276.7</v>
       </c>
       <c r="H81" s="10" t="n"/>
       <c r="I81" s="10" t="n"/>
@@ -13523,12 +13563,12 @@
       </c>
       <c r="M81" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — sokl XPS + cihelný obklad + DXF perimeter</t>
+          <t>TZ ARS dům §3.2 EXPLICIT 'fasádní EPS 70f grey (λ=0,032 W/mK)' + PBŘ EXPLICIT 'EPS tl. max. 200 mm' + DXF perimeter</t>
         </is>
       </c>
       <c r="N81" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="O81" s="26" t="inlineStr">
@@ -13538,7 +13578,7 @@
       </c>
       <c r="P81" s="41" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>S01, S12a</t>
         </is>
       </c>
       <c r="Q81" s="41" t="inlineStr">
@@ -13558,26 +13598,26 @@
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>Špalety EPS</t>
+          <t>ETICS sokl XPS</t>
         </is>
       </c>
       <c r="D82" s="20" t="inlineStr">
         <is>
-          <t>622221221</t>
+          <t>622223111</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>Špalety oken — EPS přesah 35-40 mm + síťka + omítka</t>
+          <t>ETICS sokl — XPS λ=0.034 tl. 120 mm + soklový profil + cihelný obklad spárovaný</t>
         </is>
       </c>
       <c r="F82" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G82" s="22" t="n">
-        <v>82.2</v>
+        <v>13.5</v>
       </c>
       <c r="H82" s="10" t="n"/>
       <c r="I82" s="10" t="n"/>
@@ -13587,21 +13627,21 @@
         </is>
       </c>
       <c r="K82" s="24" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
       <c r="L82" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M82" s="8" t="inlineStr">
         <is>
-          <t>DXF okna per typ bbox + TZ ARS §3.2 EPS přesah na špaletách 35-40 mm</t>
+          <t>TZ ARS dům §3.2 — sokl XPS + cihelný obklad + DXF perimeter</t>
         </is>
       </c>
       <c r="N82" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O82" s="26" t="inlineStr">
@@ -13611,10 +13651,14 @@
       </c>
       <c r="P82" s="41" t="inlineStr">
         <is>
-          <t>S01, S12a</t>
-        </is>
-      </c>
-      <c r="Q82" s="41" t="n"/>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="Q82" s="41" t="inlineStr">
+        <is>
+          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="20" t="n">
@@ -13627,7 +13671,7 @@
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>Profilace fasády</t>
+          <t>Špalety EPS</t>
         </is>
       </c>
       <c r="D83" s="20" t="inlineStr">
@@ -13637,16 +13681,16 @@
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
+          <t>Špalety oken — EPS přesah 35-40 mm + síťka + omítka</t>
         </is>
       </c>
       <c r="F83" s="20" t="inlineStr">
         <is>
-          <t>soubor</t>
-        </is>
-      </c>
-      <c r="G83" s="23" t="n">
-        <v>1</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G83" s="22" t="n">
+        <v>82.2</v>
       </c>
       <c r="H83" s="10" t="n"/>
       <c r="I83" s="10" t="n"/>
@@ -13665,12 +13709,12 @@
       </c>
       <c r="M83" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — profilace různými tl. EPS</t>
+          <t>DXF okna per typ bbox + TZ ARS §3.2 EPS přesah na špaletách 35-40 mm</t>
         </is>
       </c>
       <c r="N83" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O83" s="26" t="inlineStr">
@@ -13696,26 +13740,26 @@
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>Tenkovrstvá omítka pastovitá</t>
+          <t>Profilace fasády</t>
         </is>
       </c>
       <c r="D84" s="20" t="inlineStr">
         <is>
-          <t>622521111</t>
+          <t>622221221</t>
         </is>
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
+          <t>Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
         </is>
       </c>
       <c r="F84" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G84" s="22" t="n">
-        <v>290.2</v>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="G84" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H84" s="10" t="n"/>
       <c r="I84" s="10" t="n"/>
@@ -13725,16 +13769,16 @@
         </is>
       </c>
       <c r="K84" s="24" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
       <c r="L84" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M84" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — pastovitá probarvená lomená bílá + DXF perimeter</t>
+          <t>TZ ARS dům §3.2 — profilace různými tl. EPS</t>
         </is>
       </c>
       <c r="N84" s="20" t="inlineStr">
@@ -13749,14 +13793,10 @@
       </c>
       <c r="P84" s="41" t="inlineStr">
         <is>
-          <t>S01, S12a, S12b</t>
-        </is>
-      </c>
-      <c r="Q84" s="41" t="inlineStr">
-        <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
-        </is>
-      </c>
+          <t>S01, S12a</t>
+        </is>
+      </c>
+      <c r="Q84" s="41" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="20" t="n">
@@ -13764,22 +13804,22 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace HI</t>
+          <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>HI pod ŽB deskou 1.NP</t>
+          <t>Tenkovrstvá omítka pastovitá</t>
         </is>
       </c>
       <c r="D85" s="20" t="inlineStr">
         <is>
-          <t>712311101</t>
+          <t>622521111</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolace pod ŽB deskou 1.NP — modifikované asfaltové pásy SBS 2× (zároveň protiradonová bariéra)</t>
+          <t>Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
         </is>
       </c>
       <c r="F85" s="20" t="inlineStr">
@@ -13788,17 +13828,17 @@
         </is>
       </c>
       <c r="G85" s="22" t="n">
-        <v>80.40000000000001</v>
+        <v>290.2</v>
       </c>
       <c r="H85" s="10" t="n"/>
       <c r="I85" s="10" t="n"/>
       <c r="J85" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>fasadnik_etics</t>
         </is>
       </c>
       <c r="K85" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L85" s="20" t="inlineStr">
         <is>
@@ -13807,12 +13847,12 @@
       </c>
       <c r="M85" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 + statika §5.5 — asfaltové pásy mod. proti radonu</t>
+          <t>TZ ARS dům §3.2 — pastovitá probarvená lomená bílá + DXF perimeter</t>
         </is>
       </c>
       <c r="N85" s="20" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O85" s="26" t="inlineStr">
@@ -13820,10 +13860,14 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P85" s="41" t="n"/>
+      <c r="P85" s="41" t="inlineStr">
+        <is>
+          <t>S01, S12a, S12b</t>
+        </is>
+      </c>
       <c r="Q85" s="41" t="inlineStr">
         <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED; URS_PHASE5B_FAMILY_VERIFIED</t>
+          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
         </is>
       </c>
     </row>
@@ -13838,26 +13882,26 @@
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>Odvětrání radonu z podloží</t>
+          <t>HI pod ŽB deskou 1.NP</t>
         </is>
       </c>
       <c r="D86" s="20" t="inlineStr">
         <is>
-          <t>712381111</t>
+          <t>712311101</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>Odvětrání radonu z podloží — perforované DN50 trubky v štěrkovém loži + výdech nad střechu</t>
+          <t>Hydroizolace pod ŽB deskou 1.NP — modifikované asfaltové pásy SBS 2× (zároveň protiradonová bariéra)</t>
         </is>
       </c>
       <c r="F86" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G86" s="22" t="n">
-        <v>12</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="H86" s="10" t="n"/>
       <c r="I86" s="10" t="n"/>
@@ -13876,12 +13920,12 @@
       </c>
       <c r="M86" s="8" t="inlineStr">
         <is>
-          <t>TZ statika §5.5 'ochrana proti radonu — modifikované asf. pásy + odvětrání'</t>
+          <t>TZ ARS dům §4 + statika §5.5 — asfaltové pásy mod. proti radonu</t>
         </is>
       </c>
       <c r="N86" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="O86" s="26" t="inlineStr">
@@ -13892,7 +13936,7 @@
       <c r="P86" s="41" t="n"/>
       <c r="Q86" s="41" t="inlineStr">
         <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+          <t>URS_PHASE5B_FAMILY_VERIFIED; URS_PHASE5B_FAMILY_VERIFIED</t>
         </is>
       </c>
     </row>
@@ -13907,26 +13951,26 @@
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>HI koupelny 1.NP + 2.NP + 3.NP</t>
-        </is>
-      </c>
-      <c r="D87" s="27" t="inlineStr">
-        <is>
-          <t>711??? ?</t>
+          <t>Odvětrání radonu z podloží</t>
+        </is>
+      </c>
+      <c r="D87" s="20" t="inlineStr">
+        <is>
+          <t>712381111</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolační stěrka koupelen 3 ks — podlaha + sokl 200 mm + sprchový kout výška 2.0 m</t>
+          <t>Odvětrání radonu z podloží — perforované DN50 trubky v štěrkovém loži + výdech nad střechu</t>
         </is>
       </c>
       <c r="F87" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G87" s="22" t="n">
-        <v>40.5</v>
+        <v>12</v>
       </c>
       <c r="H87" s="10" t="n"/>
       <c r="I87" s="10" t="n"/>
@@ -13936,7 +13980,7 @@
         </is>
       </c>
       <c r="K87" s="24" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L87" s="20" t="inlineStr">
         <is>
@@ -13945,12 +13989,12 @@
       </c>
       <c r="M87" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT labels: 3× koupelna; TZ ARS — HI vana koupelny</t>
+          <t>TZ statika §5.5 'ochrana proti radonu — modifikované asf. pásy + odvětrání'</t>
         </is>
       </c>
       <c r="N87" s="20" t="inlineStr">
         <is>
-          <t>#4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O87" s="26" t="inlineStr">
@@ -13971,22 +14015,22 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace TI</t>
+          <t>PSV-71 Izolace HI</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>Podlahový EPS 150</t>
+          <t>HI koupelny 1.NP + 2.NP + 3.NP</t>
         </is>
       </c>
       <c r="D88" s="27" t="inlineStr">
         <is>
-          <t>713121??? ?</t>
+          <t>711??? ?</t>
         </is>
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>Podlahový EPS 150 λ=0.035 tl. 120 mm — pod betonový potěr 1.NP a 3.NP</t>
+          <t>Hydroizolační stěrka koupelen 3 ks — podlaha + sokl 200 mm + sprchový kout výška 2.0 m</t>
         </is>
       </c>
       <c r="F88" s="20" t="inlineStr">
@@ -13995,17 +14039,17 @@
         </is>
       </c>
       <c r="G88" s="22" t="n">
-        <v>177.5</v>
+        <v>40.5</v>
       </c>
       <c r="H88" s="10" t="n"/>
       <c r="I88" s="10" t="n"/>
       <c r="J88" s="8" t="inlineStr">
         <is>
-          <t>izolater_TI</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K88" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L88" s="20" t="inlineStr">
         <is>
@@ -14014,7 +14058,7 @@
       </c>
       <c r="M88" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — EPS 150 λ=0.035 tl. 120 mm</t>
+          <t>DXF dum_DPZ MTEXT labels: 3× koupelna; TZ ARS — HI vana koupelny</t>
         </is>
       </c>
       <c r="N88" s="20" t="inlineStr">
@@ -14045,7 +14089,7 @@
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>Kročejová EPS nad ocelobeton</t>
+          <t>Podlahový EPS 150</t>
         </is>
       </c>
       <c r="D89" s="27" t="inlineStr">
@@ -14055,7 +14099,7 @@
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>Kročejová EPS 150 / 30 dB tl. 30 mm nad ocelobetonovým stropem 2.NP/3.NP</t>
+          <t>Podlahový EPS 150 λ=0.035 tl. 120 mm — pod betonový potěr 1.NP a 3.NP</t>
         </is>
       </c>
       <c r="F89" s="20" t="inlineStr">
@@ -14064,7 +14108,7 @@
         </is>
       </c>
       <c r="G89" s="22" t="n">
-        <v>104.4</v>
+        <v>177.5</v>
       </c>
       <c r="H89" s="10" t="n"/>
       <c r="I89" s="10" t="n"/>
@@ -14074,7 +14118,7 @@
         </is>
       </c>
       <c r="K89" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L89" s="20" t="inlineStr">
         <is>
@@ -14083,12 +14127,12 @@
       </c>
       <c r="M89" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — kročejová EPS shora ocelobeton</t>
+          <t>TZ ARS dům §4 — EPS 150 λ=0.035 tl. 120 mm</t>
         </is>
       </c>
       <c r="N89" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#4</t>
         </is>
       </c>
       <c r="O89" s="26" t="inlineStr">
@@ -14109,41 +14153,41 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Klempíř</t>
+          <t>PSV-71 Izolace TI</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>Oplechování krytiny</t>
-        </is>
-      </c>
-      <c r="D90" s="20" t="inlineStr">
-        <is>
-          <t>764312235</t>
+          <t>Kročejová EPS nad ocelobeton</t>
+        </is>
+      </c>
+      <c r="D90" s="27" t="inlineStr">
+        <is>
+          <t>713121??? ?</t>
         </is>
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>Klempířské oplechování krytiny — úžlabí, hřeben, štítové lemy (Al / Pzn lakovaný 0.55 mm)</t>
+          <t>Kročejová EPS 150 / 30 dB tl. 30 mm nad ocelobetonovým stropem 2.NP/3.NP</t>
         </is>
       </c>
       <c r="F90" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G90" s="22" t="n">
-        <v>69.5</v>
+        <v>104.4</v>
       </c>
       <c r="H90" s="10" t="n"/>
       <c r="I90" s="10" t="n"/>
       <c r="J90" s="8" t="inlineStr">
         <is>
-          <t>klempir</t>
+          <t>izolater_TI</t>
         </is>
       </c>
       <c r="K90" s="24" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="L90" s="20" t="inlineStr">
         <is>
@@ -14152,12 +14196,12 @@
       </c>
       <c r="M90" s="8" t="inlineStr">
         <is>
-          <t>DXF MA_klempíř (75.4 m) + SM__ klempířina (98.4 m) total = 173.8 m × 0.40 split heuristic — Path C Tier 3</t>
+          <t>TZ ARS dům §4 — kročejová EPS shora ocelobeton</t>
         </is>
       </c>
       <c r="N90" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O90" s="26" t="inlineStr">
@@ -14168,12 +14212,7 @@
       <c r="P90" s="41" t="n"/>
       <c r="Q90" s="41" t="inlineStr">
         <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED_CHAPTER_MATCH</t>
-        </is>
-      </c>
-      <c r="R90" s="41" t="inlineStr">
-        <is>
-          <t>PSV-76 Klempíř items sum 159.9 m vs DXF MA_klempíř + SM__ klempířina total 173.8 m, Δ -8.0 % (-13.9 m). Within ±15 % tolerance per CEV Matrix D.4 verdict (gate-3). FLAG for Karel site walkthrough — possible missing klempíř segment (small). Source: outputs/cev_matrix_d_cross_doc_consistency.json D.4.</t>
+          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
         </is>
       </c>
     </row>
@@ -14188,17 +14227,17 @@
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>Venkovní parapety oken</t>
+          <t>Oplechování krytiny</t>
         </is>
       </c>
       <c r="D91" s="20" t="inlineStr">
         <is>
-          <t>764218201</t>
+          <t>764312235</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>Venkovní parapety oken — Pzn plech lakovaný 250 mm × tl. 0.55 mm × 16 ks oken</t>
+          <t>Klempířské oplechování krytiny — úžlabí, hřeben, štítové lemy (Al / Pzn lakovaný 0.55 mm)</t>
         </is>
       </c>
       <c r="F91" s="20" t="inlineStr">
@@ -14207,7 +14246,7 @@
         </is>
       </c>
       <c r="G91" s="22" t="n">
-        <v>20.8</v>
+        <v>69.5</v>
       </c>
       <c r="H91" s="10" t="n"/>
       <c r="I91" s="10" t="n"/>
@@ -14217,7 +14256,7 @@
         </is>
       </c>
       <c r="K91" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L91" s="20" t="inlineStr">
         <is>
@@ -14226,12 +14265,12 @@
       </c>
       <c r="M91" s="8" t="inlineStr">
         <is>
-          <t>DXF okna 16 ks INSERT blocks + standard parapet width</t>
+          <t>DXF MA_klempíř (75.4 m) + SM__ klempířina (98.4 m) total = 173.8 m × 0.40 split heuristic — Path C Tier 3</t>
         </is>
       </c>
       <c r="N91" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O91" s="26" t="inlineStr">
@@ -14262,17 +14301,17 @@
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>Dešťové svody + žlaby</t>
+          <t>Venkovní parapety oken</t>
         </is>
       </c>
       <c r="D92" s="20" t="inlineStr">
         <is>
-          <t>764454802</t>
+          <t>764218201</t>
         </is>
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>Dešťové svody Pzn 100 mm + žlaby — 4 svody × ~14 m + žlaby per obvod střechy</t>
+          <t>Venkovní parapety oken — Pzn plech lakovaný 250 mm × tl. 0.55 mm × 16 ks oken</t>
         </is>
       </c>
       <c r="F92" s="20" t="inlineStr">
@@ -14281,7 +14320,7 @@
         </is>
       </c>
       <c r="G92" s="22" t="n">
-        <v>43.5</v>
+        <v>20.8</v>
       </c>
       <c r="H92" s="10" t="n"/>
       <c r="I92" s="10" t="n"/>
@@ -14291,7 +14330,7 @@
         </is>
       </c>
       <c r="K92" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L92" s="20" t="inlineStr">
         <is>
@@ -14300,7 +14339,7 @@
       </c>
       <c r="M92" s="8" t="inlineStr">
         <is>
-          <t>DXF klempířina lengths split + TZ ARS dešťové svody</t>
+          <t>DXF okna 16 ks INSERT blocks + standard parapet width</t>
         </is>
       </c>
       <c r="N92" s="20" t="inlineStr">
@@ -14336,17 +14375,17 @@
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>Vikýře + atika + závětrné lemy</t>
+          <t>Dešťové svody + žlaby</t>
         </is>
       </c>
       <c r="D93" s="20" t="inlineStr">
         <is>
-          <t>764315235</t>
+          <t>764454802</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>Klempířské doplňky vikýřů + atika + závětrné lemy (4 vikýře komplexní detail)</t>
+          <t>Dešťové svody Pzn 100 mm + žlaby — 4 svody × ~14 m + žlaby per obvod střechy</t>
         </is>
       </c>
       <c r="F93" s="20" t="inlineStr">
@@ -14355,7 +14394,7 @@
         </is>
       </c>
       <c r="G93" s="22" t="n">
-        <v>26.1</v>
+        <v>43.5</v>
       </c>
       <c r="H93" s="10" t="n"/>
       <c r="I93" s="10" t="n"/>
@@ -14374,7 +14413,7 @@
       </c>
       <c r="M93" s="8" t="inlineStr">
         <is>
-          <t>DXF klempířina geometry split + TZ ARS 4 vikýře</t>
+          <t>DXF klempířina lengths split + TZ ARS dešťové svody</t>
         </is>
       </c>
       <c r="N93" s="20" t="inlineStr">
@@ -14405,50 +14444,50 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Truhlář</t>
+          <t>PSV-76 Klempíř</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>Dřevěné stupně schodišť</t>
+          <t>Vikýře + atika + závětrné lemy</t>
         </is>
       </c>
       <c r="D94" s="20" t="inlineStr">
         <is>
-          <t>766811111</t>
+          <t>764315235</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>Dřevěné stupně ocelových schodišť (truhlářské, dub masiv tl. 40 mm)</t>
+          <t>Klempířské doplňky vikýřů + atika + závětrné lemy (4 vikýře komplexní detail)</t>
         </is>
       </c>
       <c r="F94" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G94" s="23" t="n">
-        <v>16</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G94" s="22" t="n">
+        <v>26.1</v>
       </c>
       <c r="H94" s="10" t="n"/>
       <c r="I94" s="10" t="n"/>
       <c r="J94" s="8" t="inlineStr">
         <is>
-          <t>truhlar</t>
+          <t>klempir</t>
         </is>
       </c>
       <c r="K94" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L94" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M94" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni truhlářské</t>
+          <t>DXF klempířina geometry split + TZ ARS 4 vikýře</t>
         </is>
       </c>
       <c r="N94" s="20" t="inlineStr">
@@ -14462,7 +14501,16 @@
         </is>
       </c>
       <c r="P94" s="41" t="n"/>
-      <c r="Q94" s="41" t="n"/>
+      <c r="Q94" s="41" t="inlineStr">
+        <is>
+          <t>URS_PHASE5B_FAMILY_VERIFIED_CHAPTER_MATCH</t>
+        </is>
+      </c>
+      <c r="R94" s="41" t="inlineStr">
+        <is>
+          <t>PSV-76 Klempíř items sum 159.9 m vs DXF MA_klempíř + SM__ klempířina total 173.8 m, Δ -8.0 % (-13.9 m). Within ±15 % tolerance per CEV Matrix D.4 verdict (gate-3). FLAG for Karel site walkthrough — possible missing klempíř segment (small). Source: outputs/cev_matrix_d_cross_doc_consistency.json D.4.</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="20" t="n">
@@ -14475,26 +14523,26 @@
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>Terasa garapa za opěrnou stěnou — dřevěná pochozí vrstva</t>
-        </is>
-      </c>
-      <c r="D95" s="27" t="inlineStr">
-        <is>
-          <t>762??? ?</t>
+          <t>Dřevěné stupně schodišť</t>
+        </is>
+      </c>
+      <c r="D95" s="20" t="inlineStr">
+        <is>
+          <t>766811111</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na dřevěném roštu z hranolů 50 mm na rektifikovatelných terčích (terče + podkladní skladba viz HSV1.005)</t>
+          <t>Dřevěné stupně ocelových schodišť (truhlářské, dub masiv tl. 40 mm)</t>
         </is>
       </c>
       <c r="F95" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G95" s="22" t="n">
-        <v>9.23</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G95" s="23" t="n">
+        <v>16</v>
       </c>
       <c r="H95" s="10" t="n"/>
       <c r="I95" s="10" t="n"/>
@@ -14504,16 +14552,16 @@
         </is>
       </c>
       <c r="K95" s="24" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L95" s="20" t="inlineStr">
         <is>
-          <t>family_762_leaf_lookup_required</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M95" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 + DXF dum_situace PLOT_DREVENY_04 (terasa, ne 3.NP); ŘEZ C-C potvrzuje dřevěný rošt z hranolů (NE hliníkový) + dřevěnou pochozí vrstvu</t>
+          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni truhlářské</t>
         </is>
       </c>
       <c r="N95" s="20" t="inlineStr">
@@ -14527,11 +14575,7 @@
         </is>
       </c>
       <c r="P95" s="41" t="n"/>
-      <c r="Q95" s="41" t="inlineStr">
-        <is>
-          <t>REZ_CC_TERASA_FIX_2026-05-29; SITUACE_AREA_FIX_2026-05-29</t>
-        </is>
-      </c>
+      <c r="Q95" s="41" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="20" t="n">
@@ -14539,55 +14583,55 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>PSV-76 Truhlář</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 1.NP' (ulice)</t>
-        </is>
-      </c>
-      <c r="D96" s="20" t="inlineStr">
-        <is>
-          <t>766621011</t>
+          <t>Terasa garapa za opěrnou stěnou — dřevěná pochozí vrstva</t>
+        </is>
+      </c>
+      <c r="D96" s="27" t="inlineStr">
+        <is>
+          <t>762??? ?</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP' velikost 1185×1600 mm × 2 ks (fasáda ulice)</t>
+          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na dřevěném roštu z hranolů 50 mm na rektifikovatelných terčích (terče + podkladní skladba viz HSV1.005)</t>
         </is>
       </c>
       <c r="F96" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G96" s="23" t="n">
-        <v>2</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G96" s="22" t="n">
+        <v>9.23</v>
       </c>
       <c r="H96" s="10" t="n"/>
       <c r="I96" s="10" t="n"/>
       <c r="J96" s="8" t="inlineStr">
         <is>
-          <t>okennar</t>
+          <t>truhlar</t>
         </is>
       </c>
       <c r="K96" s="24" t="n">
-        <v>0.99</v>
+        <v>0.95</v>
       </c>
       <c r="L96" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>family_762_leaf_lookup_required</t>
         </is>
       </c>
       <c r="M96" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 1.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>TZ ARS dům §4 + DXF dum_situace PLOT_DREVENY_04 (terasa, ne 3.NP); ŘEZ C-C potvrzuje dřevěný rošt z hranolů (NE hliníkový) + dřevěnou pochozí vrstvu</t>
         </is>
       </c>
       <c r="N96" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O96" s="26" t="inlineStr">
@@ -14596,7 +14640,11 @@
         </is>
       </c>
       <c r="P96" s="41" t="n"/>
-      <c r="Q96" s="41" t="n"/>
+      <c r="Q96" s="41" t="inlineStr">
+        <is>
+          <t>REZ_CC_TERASA_FIX_2026-05-29; SITUACE_AREA_FIX_2026-05-29</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="20" t="n">
@@ -14609,7 +14657,7 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada)</t>
+          <t>Plastové okno trojsklo — 'okno 1.NP' (ulice)</t>
         </is>
       </c>
       <c r="D97" s="20" t="inlineStr">
@@ -14619,7 +14667,7 @@
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP vzadu' velikost 920×1600 mm × 3 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP' velikost 1185×1600 mm × 2 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="F97" s="20" t="inlineStr">
@@ -14628,7 +14676,7 @@
         </is>
       </c>
       <c r="G97" s="23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H97" s="10" t="n"/>
       <c r="I97" s="10" t="n"/>
@@ -14642,12 +14690,12 @@
       </c>
       <c r="L97" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M97" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 1.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 1.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N97" s="20" t="inlineStr">
@@ -14674,7 +14722,7 @@
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 2.NP' (ulice)</t>
+          <t>Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada)</t>
         </is>
       </c>
       <c r="D98" s="20" t="inlineStr">
@@ -14684,7 +14732,7 @@
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 2.NP' velikost 1160×1480 mm × 4 ks (fasáda ulice)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP vzadu' velikost 920×1600 mm × 3 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="F98" s="20" t="inlineStr">
@@ -14693,7 +14741,7 @@
         </is>
       </c>
       <c r="G98" s="23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H98" s="10" t="n"/>
       <c r="I98" s="10" t="n"/>
@@ -14712,7 +14760,7 @@
       </c>
       <c r="M98" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 2.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 1.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N98" s="20" t="inlineStr">
@@ -14739,7 +14787,7 @@
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 3.NP' (ulice)</t>
+          <t>Plastové okno trojsklo — 'okno 2.NP' (ulice)</t>
         </is>
       </c>
       <c r="D99" s="20" t="inlineStr">
@@ -14749,7 +14797,7 @@
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP' velikost 1785×1241 mm × 3 ks (fasáda ulice)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 2.NP' velikost 1160×1480 mm × 4 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="F99" s="20" t="inlineStr">
@@ -14758,7 +14806,7 @@
         </is>
       </c>
       <c r="G99" s="23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H99" s="10" t="n"/>
       <c r="I99" s="10" t="n"/>
@@ -14777,7 +14825,7 @@
       </c>
       <c r="M99" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 3.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 2.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N99" s="20" t="inlineStr">
@@ -14804,7 +14852,7 @@
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 3.NP vzadu' (zahrada)</t>
+          <t>Plastové okno trojsklo — 'okno 3.NP' (ulice)</t>
         </is>
       </c>
       <c r="D100" s="20" t="inlineStr">
@@ -14814,7 +14862,7 @@
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP vzadu' velikost 2075×1241 mm × 1 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP' velikost 1785×1241 mm × 3 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="F100" s="20" t="inlineStr">
@@ -14823,7 +14871,7 @@
         </is>
       </c>
       <c r="G100" s="23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H100" s="10" t="n"/>
       <c r="I100" s="10" t="n"/>
@@ -14842,7 +14890,7 @@
       </c>
       <c r="M100" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 3.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N100" s="20" t="inlineStr">
@@ -14869,7 +14917,7 @@
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno male 3.NP vzadu' (zahrada)</t>
+          <t>Plastové okno trojsklo — 'okno 3.NP vzadu' (zahrada)</t>
         </is>
       </c>
       <c r="D101" s="20" t="inlineStr">
@@ -14879,7 +14927,7 @@
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno male 3.NP vzadu' velikost 800×1241 mm × 1 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP vzadu' velikost 2075×1241 mm × 1 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="F101" s="20" t="inlineStr">
@@ -14907,7 +14955,7 @@
       </c>
       <c r="M101" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno male 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N101" s="20" t="inlineStr">
@@ -14934,7 +14982,7 @@
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno malé vzadu' (zahrada)</t>
+          <t>Plastové okno trojsklo — 'okno male 3.NP vzadu' (zahrada)</t>
         </is>
       </c>
       <c r="D102" s="20" t="inlineStr">
@@ -14944,7 +14992,7 @@
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno malé vzadu' velikost 700×800 mm × 2 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno male 3.NP vzadu' velikost 800×1241 mm × 1 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="F102" s="20" t="inlineStr">
@@ -14953,7 +15001,7 @@
         </is>
       </c>
       <c r="G102" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H102" s="10" t="n"/>
       <c r="I102" s="10" t="n"/>
@@ -14972,7 +15020,7 @@
       </c>
       <c r="M102" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno malé vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno male 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N102" s="20" t="inlineStr">
@@ -14999,17 +15047,17 @@
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>Žaluzie kastlík purenit</t>
+          <t>Plastové okno trojsklo — 'okno malé vzadu' (zahrada)</t>
         </is>
       </c>
       <c r="D103" s="20" t="inlineStr">
         <is>
-          <t>766631211</t>
+          <t>766621011</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>Integrované stínící venkovní žaluzie v kastlíku pod omítkou s purenitovou izolací — uliční fasáda Fibichova (9 ks)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno malé vzadu' velikost 700×800 mm × 2 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="F103" s="20" t="inlineStr">
@@ -15018,17 +15066,17 @@
         </is>
       </c>
       <c r="G103" s="23" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H103" s="10" t="n"/>
       <c r="I103" s="10" t="n"/>
       <c r="J103" s="8" t="inlineStr">
         <is>
-          <t>okenni_zaluzie_kastlik_purenit</t>
+          <t>okennar</t>
         </is>
       </c>
       <c r="K103" s="24" t="n">
-        <v>0.95</v>
+        <v>0.99</v>
       </c>
       <c r="L103" s="20" t="inlineStr">
         <is>
@@ -15037,7 +15085,7 @@
       </c>
       <c r="M103" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — 'do ulice Fibichova s integrovanými stínícími žaluziemi v kastlíku pod omítkou s purenitovou izolací'</t>
+          <t>DXF dum_DPZ INSERT block 'okno malé vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N103" s="20" t="inlineStr">
@@ -15064,17 +15112,17 @@
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>Vstupní plastové dveře</t>
+          <t>Žaluzie kastlík purenit</t>
         </is>
       </c>
       <c r="D104" s="20" t="inlineStr">
         <is>
-          <t>766682111</t>
+          <t>766631211</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>Plastové vstupní dveře (ulice + zahrada) — 2 ks</t>
+          <t>Integrované stínící venkovní žaluzie v kastlíku pod omítkou s purenitovou izolací — uliční fasáda Fibichova (9 ks)</t>
         </is>
       </c>
       <c r="F104" s="20" t="inlineStr">
@@ -15083,17 +15131,17 @@
         </is>
       </c>
       <c r="G104" s="23" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H104" s="10" t="n"/>
       <c r="I104" s="10" t="n"/>
       <c r="J104" s="8" t="inlineStr">
         <is>
-          <t>okennar</t>
+          <t>okenni_zaluzie_kastlik_purenit</t>
         </is>
       </c>
       <c r="K104" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L104" s="20" t="inlineStr">
         <is>
@@ -15102,12 +15150,12 @@
       </c>
       <c r="M104" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — plastové vstupní dveře</t>
+          <t>TZ ARS dům §3.2 — 'do ulice Fibichova s integrovanými stínícími žaluziemi v kastlíku pod omítkou s purenitovou izolací'</t>
         </is>
       </c>
       <c r="N104" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O104" s="26" t="inlineStr">
@@ -15129,17 +15177,17 @@
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>Vnitřní dveře DTD laminované</t>
+          <t>Vstupní plastové dveře</t>
         </is>
       </c>
       <c r="D105" s="20" t="inlineStr">
         <is>
-          <t>766660035</t>
+          <t>766682111</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>Vnitřní dveře DTD laminované s obložkovou zárubní — odhad 15 ks</t>
+          <t>Plastové vstupní dveře (ulice + zahrada) — 2 ks</t>
         </is>
       </c>
       <c r="F105" s="20" t="inlineStr">
@@ -15148,13 +15196,13 @@
         </is>
       </c>
       <c r="G105" s="23" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H105" s="10" t="n"/>
       <c r="I105" s="10" t="n"/>
       <c r="J105" s="8" t="inlineStr">
         <is>
-          <t>truhlar</t>
+          <t>okennar</t>
         </is>
       </c>
       <c r="K105" s="24" t="n">
@@ -15167,12 +15215,12 @@
       </c>
       <c r="M105" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 + DXF MTEXT room labels</t>
+          <t>TZ ARS dům §4 — plastové vstupní dveře</t>
         </is>
       </c>
       <c r="N105" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O105" s="26" t="inlineStr">
@@ -15194,17 +15242,17 @@
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>Požárně odolné dveře EI 30 DP3</t>
+          <t>Vnitřní dveře DTD laminované</t>
         </is>
       </c>
       <c r="D106" s="20" t="inlineStr">
         <is>
-          <t>766694112</t>
+          <t>766660035</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>Požárně odolné jednokřídlové dveře EI 30 DP3 na vrcholu schodiště mezi 1.PP a 1.NP — uzavírá otvor v REI 90 stropu klenby sklepa (per PBŘ TUSPO § 'Požární uzávěry otvorů v požárních stěnách a požárních stropech: podzemní 30 DP1')</t>
+          <t>Vnitřní dveře DTD laminované s obložkovou zárubní — odhad 15 ks</t>
         </is>
       </c>
       <c r="F106" s="20" t="inlineStr">
@@ -15213,17 +15261,17 @@
         </is>
       </c>
       <c r="G106" s="23" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H106" s="10" t="n"/>
       <c r="I106" s="10" t="n"/>
       <c r="J106" s="8" t="inlineStr">
         <is>
-          <t>specialista_RC3_dvere</t>
+          <t>truhlar</t>
         </is>
       </c>
       <c r="K106" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L106" s="20" t="inlineStr">
         <is>
@@ -15232,12 +15280,12 @@
       </c>
       <c r="M106" s="8" t="inlineStr">
         <is>
-          <t>PBŘ TUSPO § Požární uzávěry otvorů 'podzemní 30DP1'; DXF schodiště 1.PP→1.NP</t>
+          <t>TZ ARS dům §4 + DXF MTEXT room labels</t>
         </is>
       </c>
       <c r="N106" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O106" s="26" t="inlineStr">
@@ -15246,11 +15294,7 @@
         </is>
       </c>
       <c r="P106" s="41" t="n"/>
-      <c r="Q106" s="41" t="inlineStr">
-        <is>
-          <t>GAP_008</t>
-        </is>
-      </c>
+      <c r="Q106" s="41" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="20" t="n">
@@ -15263,17 +15307,17 @@
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t>Oplechování venkovních parapetů Pzn — 16 ks</t>
+          <t>Požárně odolné dveře EI 30 DP3</t>
         </is>
       </c>
       <c r="D107" s="20" t="inlineStr">
         <is>
-          <t>764811112</t>
+          <t>766694112</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>Oplechování venkovních parapetů Pzn plech lakovaný 250 mm × tl. 0.55 mm, vč. okapnice + boční zakončení — 16 ks (per DXF INSERT okno × 16)</t>
+          <t>Požárně odolné jednokřídlové dveře EI 30 DP3 na vrcholu schodiště mezi 1.PP a 1.NP — uzavírá otvor v REI 90 stropu klenby sklepa (per PBŘ TUSPO § 'Požární uzávěry otvorů v požárních stěnách a požárních stropech: podzemní 30 DP1')</t>
         </is>
       </c>
       <c r="F107" s="20" t="inlineStr">
@@ -15282,17 +15326,17 @@
         </is>
       </c>
       <c r="G107" s="23" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H107" s="10" t="n"/>
       <c r="I107" s="10" t="n"/>
       <c r="J107" s="8" t="inlineStr">
         <is>
-          <t>klempir</t>
+          <t>specialista_RC3_dvere</t>
         </is>
       </c>
       <c r="K107" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L107" s="20" t="inlineStr">
         <is>
@@ -15301,7 +15345,7 @@
       </c>
       <c r="M107" s="8" t="inlineStr">
         <is>
-          <t>DXF blocks okno* 16 ks + DXF klempir_parapet 16 ks (Path C Tier 4 INSERT discovery)</t>
+          <t>PBŘ TUSPO § Požární uzávěry otvorů 'podzemní 30DP1'; DXF schodiště 1.PP→1.NP</t>
         </is>
       </c>
       <c r="N107" s="20" t="inlineStr">
@@ -15317,7 +15361,7 @@
       <c r="P107" s="41" t="n"/>
       <c r="Q107" s="41" t="inlineStr">
         <is>
-          <t>GAP_004</t>
+          <t>GAP_008</t>
         </is>
       </c>
     </row>
@@ -15327,55 +15371,55 @@
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnictví</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>Ocelové schodiště UPE200 ze zahrady</t>
+          <t>Oplechování venkovních parapetů Pzn — 16 ks</t>
         </is>
       </c>
       <c r="D108" s="20" t="inlineStr">
         <is>
-          <t>767531111</t>
+          <t>764811112</t>
         </is>
       </c>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t>Ocelové schodiště ze zahrady na mezipodestu — UPE200 schodnice + dřevěné nášlapy, kotvené do koruny opěrné stěny a zdiva (TZ statika §4)</t>
+          <t>Oplechování venkovních parapetů Pzn plech lakovaný 250 mm × tl. 0.55 mm, vč. okapnice + boční zakončení — 16 ks (per DXF INSERT okno × 16)</t>
         </is>
       </c>
       <c r="F108" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G108" s="23" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H108" s="10" t="n"/>
       <c r="I108" s="10" t="n"/>
       <c r="J108" s="8" t="inlineStr">
         <is>
-          <t>zamecnik_PSV</t>
+          <t>klempir</t>
         </is>
       </c>
       <c r="K108" s="24" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="L108" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M108" s="8" t="inlineStr">
         <is>
-          <t>TZ statika dům §4 — schodiště UPE200 + UPE100 podružné prvky</t>
+          <t>DXF blocks okno* 16 ks + DXF klempir_parapet 16 ks (Path C Tier 4 INSERT discovery)</t>
         </is>
       </c>
       <c r="N108" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O108" s="26" t="inlineStr">
@@ -15386,7 +15430,7 @@
       <c r="P108" s="41" t="n"/>
       <c r="Q108" s="41" t="inlineStr">
         <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+          <t>GAP_004</t>
         </is>
       </c>
     </row>
@@ -15401,7 +15445,7 @@
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t>Ocelové schodiště do spacího patra 3.NP</t>
+          <t>Ocelové schodiště UPE200 ze zahrady</t>
         </is>
       </c>
       <c r="D109" s="20" t="inlineStr">
@@ -15411,7 +15455,7 @@
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>Interní ocelové schodiště do spacího patra v 3.NP s dřevěnými stupni (truhlářské)</t>
+          <t>Ocelové schodiště ze zahrady na mezipodestu — UPE200 schodnice + dřevěné nášlapy, kotvené do koruny opěrné stěny a zdiva (TZ statika §4)</t>
         </is>
       </c>
       <c r="F109" s="20" t="inlineStr">
@@ -15439,12 +15483,12 @@
       </c>
       <c r="M109" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni</t>
+          <t>TZ statika dům §4 — schodiště UPE200 + UPE100 podružné prvky</t>
         </is>
       </c>
       <c r="N109" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O109" s="26" t="inlineStr">
@@ -15470,26 +15514,26 @@
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>Stříšky nad vstupy</t>
+          <t>Ocelové schodiště do spacího patra 3.NP</t>
         </is>
       </c>
       <c r="D110" s="20" t="inlineStr">
         <is>
-          <t>767532111</t>
+          <t>767531111</t>
         </is>
       </c>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t>Stříšky nad vstupy z ocelové konstrukce + Cetris desky + falcovaná krytina — 2 ks (ulice + zahrada)</t>
+          <t>Interní ocelové schodiště do spacího patra v 3.NP s dřevěnými stupni (truhlářské)</t>
         </is>
       </c>
       <c r="F110" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G110" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H110" s="10" t="n"/>
       <c r="I110" s="10" t="n"/>
@@ -15499,16 +15543,16 @@
         </is>
       </c>
       <c r="K110" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L110" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M110" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — stříšky nad vstupy ocel+Cetris+plech</t>
+          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni</t>
         </is>
       </c>
       <c r="N110" s="20" t="inlineStr">
@@ -15522,7 +15566,11 @@
         </is>
       </c>
       <c r="P110" s="41" t="n"/>
-      <c r="Q110" s="41" t="n"/>
+      <c r="Q110" s="41" t="inlineStr">
+        <is>
+          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="20" t="n">
@@ -15535,26 +15583,26 @@
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t>Zábradlí z jeklů + nerez výplň</t>
+          <t>Stříšky nad vstupy</t>
         </is>
       </c>
       <c r="D111" s="20" t="inlineStr">
         <is>
-          <t>767163115</t>
+          <t>767532111</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>Ocelové zábradlí svařované z jeklů + nerez výplň pZn antracit — schodiště interier + venkovní terasa</t>
+          <t>Stříšky nad vstupy z ocelové konstrukce + Cetris desky + falcovaná krytina — 2 ks (ulice + zahrada)</t>
         </is>
       </c>
       <c r="F111" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G111" s="22" t="n">
-        <v>18</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G111" s="23" t="n">
+        <v>2</v>
       </c>
       <c r="H111" s="10" t="n"/>
       <c r="I111" s="10" t="n"/>
@@ -15573,7 +15621,7 @@
       </c>
       <c r="M111" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — zábradlí svařované z jeklů + nerez výplň</t>
+          <t>TZ ARS dům §4 — stříšky nad vstupy ocel+Cetris+plech</t>
         </is>
       </c>
       <c r="N111" s="20" t="inlineStr">
@@ -15595,55 +15643,55 @@
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>Nášlap vinyl obytné místnosti</t>
+          <t>Zábradlí z jeklů + nerez výplň</t>
         </is>
       </c>
       <c r="D112" s="20" t="inlineStr">
         <is>
-          <t>776511820</t>
+          <t>767163115</t>
         </is>
       </c>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva vinyl tl. 4 mm na suchou skladbu — obytné místnosti (ložnice, obývák, kuchyně, chodby)</t>
+          <t>Ocelové zábradlí svařované z jeklů + nerez výplň pZn antracit — schodiště interier + venkovní terasa</t>
         </is>
       </c>
       <c r="F112" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G112" s="22" t="n">
-        <v>171.5</v>
+        <v>18</v>
       </c>
       <c r="H112" s="10" t="n"/>
       <c r="I112" s="10" t="n"/>
       <c r="J112" s="8" t="inlineStr">
         <is>
-          <t>podlahar</t>
+          <t>zamecnik_PSV</t>
         </is>
       </c>
       <c r="K112" s="24" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L112" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M112" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (kuchyně/obytná/chodba = vinyl) + TZ ARS §3.2.4 nášlapná vrstva</t>
+          <t>TZ ARS dům §4 — zábradlí svařované z jeklů + nerez výplň</t>
         </is>
       </c>
       <c r="N112" s="20" t="inlineStr">
         <is>
-          <t>#4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O112" s="26" t="inlineStr">
@@ -15652,11 +15700,7 @@
         </is>
       </c>
       <c r="P112" s="41" t="n"/>
-      <c r="Q112" s="41" t="inlineStr">
-        <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
-        </is>
-      </c>
+      <c r="Q112" s="41" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="20" t="n">
@@ -15669,17 +15713,17 @@
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t>Nášlap keramická dlažba — mokré zóny</t>
+          <t>Nášlap vinyl obytné místnosti</t>
         </is>
       </c>
       <c r="D113" s="20" t="inlineStr">
         <is>
-          <t>771274102</t>
+          <t>776511820</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva keramická dlažba lepená — koupelny + WC + spíž + komora (NÁDRŽ NP)</t>
+          <t>Nášlapná vrstva vinyl tl. 4 mm na suchou skladbu — obytné místnosti (ložnice, obývák, kuchyně, chodby)</t>
         </is>
       </c>
       <c r="F113" s="20" t="inlineStr">
@@ -15688,13 +15732,13 @@
         </is>
       </c>
       <c r="G113" s="22" t="n">
-        <v>13.5</v>
+        <v>171.5</v>
       </c>
       <c r="H113" s="10" t="n"/>
       <c r="I113" s="10" t="n"/>
       <c r="J113" s="8" t="inlineStr">
         <is>
-          <t>obkladac</t>
+          <t>podlahar</t>
         </is>
       </c>
       <c r="K113" s="24" t="n">
@@ -15702,12 +15746,12 @@
       </c>
       <c r="L113" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M113" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (koupelna/WC/spíž = dlažba mokré) + TZ ARS skladba mokrá</t>
+          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (kuchyně/obytná/chodba = vinyl) + TZ ARS §3.2.4 nášlapná vrstva</t>
         </is>
       </c>
       <c r="N113" s="20" t="inlineStr">
@@ -15721,7 +15765,11 @@
         </is>
       </c>
       <c r="P113" s="41" t="n"/>
-      <c r="Q113" s="41" t="n"/>
+      <c r="Q113" s="41" t="inlineStr">
+        <is>
+          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="20" t="n">
@@ -15734,7 +15782,7 @@
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>Nášlap keramická dlažba — 1.PP sklep</t>
+          <t>Nášlap keramická dlažba — mokré zóny</t>
         </is>
       </c>
       <c r="D114" s="20" t="inlineStr">
@@ -15744,7 +15792,7 @@
       </c>
       <c r="E114" s="8" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva keramická dlažba — 1.PP technické místnosti (sušárna + sklepy + schodiště + chodba)</t>
+          <t>Nášlapná vrstva keramická dlažba lepená — koupelny + WC + spíž + komora (NÁDRŽ NP)</t>
         </is>
       </c>
       <c r="F114" s="20" t="inlineStr">
@@ -15753,7 +15801,7 @@
         </is>
       </c>
       <c r="G114" s="22" t="n">
-        <v>32.4</v>
+        <v>13.5</v>
       </c>
       <c r="H114" s="10" t="n"/>
       <c r="I114" s="10" t="n"/>
@@ -15772,7 +15820,7 @@
       </c>
       <c r="M114" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT (návrh) — 1.PP all rooms = dlažba sklep zone</t>
+          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (koupelna/WC/spíž = dlažba mokré) + TZ ARS skladba mokrá</t>
         </is>
       </c>
       <c r="N114" s="20" t="inlineStr">
@@ -15799,17 +15847,17 @@
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t>Nášlap biodeska 3.NP spací patro</t>
+          <t>Nášlap keramická dlažba — 1.PP sklep</t>
         </is>
       </c>
       <c r="D115" s="20" t="inlineStr">
         <is>
-          <t>766411111</t>
+          <t>771274102</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva biodeska (smrk masiv) nebo OSB v 3.NP spací části nad krovem</t>
+          <t>Nášlapná vrstva keramická dlažba — 1.PP technické místnosti (sušárna + sklepy + schodiště + chodba)</t>
         </is>
       </c>
       <c r="F115" s="20" t="inlineStr">
@@ -15818,17 +15866,17 @@
         </is>
       </c>
       <c r="G115" s="22" t="n">
-        <v>25</v>
+        <v>32.4</v>
       </c>
       <c r="H115" s="10" t="n"/>
       <c r="I115" s="10" t="n"/>
       <c r="J115" s="8" t="inlineStr">
         <is>
-          <t>biodeska_konstrukcni</t>
+          <t>obkladac</t>
         </is>
       </c>
       <c r="K115" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L115" s="20" t="inlineStr">
         <is>
@@ -15837,12 +15885,12 @@
       </c>
       <c r="M115" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2.3 — biodeska patro pro přespání</t>
+          <t>DXF km_tabulka místností MTEXT (návrh) — 1.PP all rooms = dlažba sklep zone</t>
         </is>
       </c>
       <c r="N115" s="20" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>#4</t>
         </is>
       </c>
       <c r="O115" s="26" t="inlineStr">
@@ -15864,17 +15912,17 @@
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>Betonový potěr s kari nad EPS</t>
+          <t>Nášlap biodeska 3.NP spací patro</t>
         </is>
       </c>
       <c r="D116" s="20" t="inlineStr">
         <is>
-          <t>631321311</t>
+          <t>766411111</t>
         </is>
       </c>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t>Mokrá podlahová skladba — betonový potěr s kari síťkou 4/100/100 tl. 50 mm + samonivelační stěrka</t>
+          <t>Nášlapná vrstva biodeska (smrk masiv) nebo OSB v 3.NP spací části nad krovem</t>
         </is>
       </c>
       <c r="F116" s="20" t="inlineStr">
@@ -15883,17 +15931,17 @@
         </is>
       </c>
       <c r="G116" s="22" t="n">
-        <v>126.4</v>
+        <v>25</v>
       </c>
       <c r="H116" s="10" t="n"/>
       <c r="I116" s="10" t="n"/>
       <c r="J116" s="8" t="inlineStr">
         <is>
-          <t>podlahar</t>
+          <t>biodeska_konstrukcni</t>
         </is>
       </c>
       <c r="K116" s="24" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L116" s="20" t="inlineStr">
         <is>
@@ -15902,12 +15950,12 @@
       </c>
       <c r="M116" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2.4 + §3.2.x — 'kročejová izolace + betonový potěr s kari sítí'; DXF rooms areas</t>
+          <t>TZ ARS dům §3.2.3 — biodeska patro pro přespání</t>
         </is>
       </c>
       <c r="N116" s="20" t="inlineStr">
         <is>
-          <t>#4</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="O116" s="26" t="inlineStr">
@@ -15929,26 +15977,26 @@
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t>Soklíky vinyl</t>
+          <t>Betonový potěr s kari nad EPS</t>
         </is>
       </c>
       <c r="D117" s="20" t="inlineStr">
         <is>
-          <t>776511831</t>
+          <t>631321311</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>Soklíky podlahové laminátové (dub) v obytných místnostech s vinyl podlahou</t>
+          <t>Mokrá podlahová skladba — betonový potěr s kari síťkou 4/100/100 tl. 50 mm + samonivelační stěrka</t>
         </is>
       </c>
       <c r="F117" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G117" s="22" t="n">
-        <v>72.03</v>
+        <v>126.4</v>
       </c>
       <c r="H117" s="10" t="n"/>
       <c r="I117" s="10" t="n"/>
@@ -15967,12 +16015,12 @@
       </c>
       <c r="M117" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms vinyl + standard ratio per RD geometry</t>
+          <t>TZ ARS dům §3.2.4 + §3.2.x — 'kročejová izolace + betonový potěr s kari sítí'; DXF rooms areas</t>
         </is>
       </c>
       <c r="N117" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#4</t>
         </is>
       </c>
       <c r="O117" s="26" t="inlineStr">
@@ -15994,17 +16042,17 @@
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>Soklíky keramické</t>
+          <t>Soklíky vinyl</t>
         </is>
       </c>
       <c r="D118" s="20" t="inlineStr">
         <is>
-          <t>771274107</t>
+          <t>776511831</t>
         </is>
       </c>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t>Soklíky keramické v místnostech s dlažbou (koupelny + WC + spíž + 1.PP)</t>
+          <t>Soklíky podlahové laminátové (dub) v obytných místnostech s vinyl podlahou</t>
         </is>
       </c>
       <c r="F118" s="20" t="inlineStr">
@@ -16013,13 +16061,13 @@
         </is>
       </c>
       <c r="G118" s="22" t="n">
-        <v>19.28</v>
+        <v>72.03</v>
       </c>
       <c r="H118" s="10" t="n"/>
       <c r="I118" s="10" t="n"/>
       <c r="J118" s="8" t="inlineStr">
         <is>
-          <t>obkladac</t>
+          <t>podlahar</t>
         </is>
       </c>
       <c r="K118" s="24" t="n">
@@ -16032,7 +16080,7 @@
       </c>
       <c r="M118" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms dlažba + standard ratio per RD geometry</t>
+          <t>DXF rooms vinyl + standard ratio per RD geometry</t>
         </is>
       </c>
       <c r="N118" s="20" t="inlineStr">
@@ -16054,41 +16102,41 @@
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>PSV-78 Povrchové úpravy</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová + štuk 1.PP</t>
+          <t>Soklíky keramické</t>
         </is>
       </c>
       <c r="D119" s="20" t="inlineStr">
         <is>
-          <t>612311311</t>
+          <t>771274107</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.PP (stávající vyspravené + nové zděné)</t>
+          <t>Soklíky keramické v místnostech s dlažbou (koupelny + WC + spíž + 1.PP)</t>
         </is>
       </c>
       <c r="F119" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G119" s="22" t="n">
-        <v>78.2</v>
+        <v>19.28</v>
       </c>
       <c r="H119" s="10" t="n"/>
       <c r="I119" s="10" t="n"/>
       <c r="J119" s="8" t="inlineStr">
         <is>
-          <t>zednik</t>
+          <t>obkladac</t>
         </is>
       </c>
       <c r="K119" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L119" s="20" t="inlineStr">
         <is>
@@ -16097,12 +16145,12 @@
       </c>
       <c r="M119" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms 1.PP obvod + výška podlaží 2.1 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF rooms dlažba + standard ratio per RD geometry</t>
         </is>
       </c>
       <c r="N119" s="20" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O119" s="26" t="inlineStr">
@@ -16124,7 +16172,7 @@
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová + štuk 1.NP</t>
+          <t>Omítka jádrová + štuk 1.PP</t>
         </is>
       </c>
       <c r="D120" s="20" t="inlineStr">
@@ -16134,7 +16182,7 @@
       </c>
       <c r="E120" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.NP (stávající vyspravené + nové zděné)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.PP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="F120" s="20" t="inlineStr">
@@ -16143,7 +16191,7 @@
         </is>
       </c>
       <c r="G120" s="22" t="n">
-        <v>208.4</v>
+        <v>78.2</v>
       </c>
       <c r="H120" s="10" t="n"/>
       <c r="I120" s="10" t="n"/>
@@ -16162,7 +16210,7 @@
       </c>
       <c r="M120" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms 1.NP obvod + výška podlaží 2.795 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF rooms 1.PP obvod + výška podlaží 2.1 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="N120" s="20" t="inlineStr">
@@ -16189,7 +16237,7 @@
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová + štuk 2.NP</t>
+          <t>Omítka jádrová + štuk 1.NP</t>
         </is>
       </c>
       <c r="D121" s="20" t="inlineStr">
@@ -16199,7 +16247,7 @@
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 2.NP (stávající vyspravené + nové zděné)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="F121" s="20" t="inlineStr">
@@ -16208,7 +16256,7 @@
         </is>
       </c>
       <c r="G121" s="22" t="n">
-        <v>201.6</v>
+        <v>208.4</v>
       </c>
       <c r="H121" s="10" t="n"/>
       <c r="I121" s="10" t="n"/>
@@ -16227,7 +16275,7 @@
       </c>
       <c r="M121" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms 2.NP obvod + výška podlaží 2.865 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF rooms 1.NP obvod + výška podlaží 2.795 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="N121" s="20" t="inlineStr">
@@ -16254,7 +16302,7 @@
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová + štuk 3.NP</t>
+          <t>Omítka jádrová + štuk 2.NP</t>
         </is>
       </c>
       <c r="D122" s="20" t="inlineStr">
@@ -16264,7 +16312,7 @@
       </c>
       <c r="E122" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 3.NP (stávající vyspravené + nové zděné)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 2.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="F122" s="20" t="inlineStr">
@@ -16273,7 +16321,7 @@
         </is>
       </c>
       <c r="G122" s="22" t="n">
-        <v>179.1</v>
+        <v>201.6</v>
       </c>
       <c r="H122" s="10" t="n"/>
       <c r="I122" s="10" t="n"/>
@@ -16292,7 +16340,7 @@
       </c>
       <c r="M122" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms 3.NP obvod + výška podlaží 2.63 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF rooms 2.NP obvod + výška podlaží 2.865 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="N122" s="20" t="inlineStr">
@@ -16319,17 +16367,17 @@
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled — tmelení + úprava 1.NP</t>
+          <t>Omítka jádrová + štuk 3.NP</t>
         </is>
       </c>
       <c r="D123" s="20" t="inlineStr">
         <is>
-          <t>612471141</t>
+          <t>612311311</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (1.NP)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 3.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="F123" s="20" t="inlineStr">
@@ -16338,17 +16386,17 @@
         </is>
       </c>
       <c r="G123" s="22" t="n">
-        <v>59.5</v>
+        <v>179.1</v>
       </c>
       <c r="H123" s="10" t="n"/>
       <c r="I123" s="10" t="n"/>
       <c r="J123" s="8" t="inlineStr">
         <is>
-          <t>sadrokartonar</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="K123" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L123" s="20" t="inlineStr">
         <is>
@@ -16357,12 +16405,12 @@
       </c>
       <c r="M123" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT — plocha 1.NP = plocha podhledu (flat ceiling assumption)</t>
+          <t>DXF rooms 3.NP obvod + výška podlaží 2.63 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="N123" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="O123" s="26" t="inlineStr">
@@ -16384,7 +16432,7 @@
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled — tmelení + úprava 2.NP</t>
+          <t>SDK podhled — tmelení + úprava 1.NP</t>
         </is>
       </c>
       <c r="D124" s="20" t="inlineStr">
@@ -16394,7 +16442,7 @@
       </c>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (2.NP)</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (1.NP)</t>
         </is>
       </c>
       <c r="F124" s="20" t="inlineStr">
@@ -16403,7 +16451,7 @@
         </is>
       </c>
       <c r="G124" s="22" t="n">
-        <v>61.1</v>
+        <v>59.5</v>
       </c>
       <c r="H124" s="10" t="n"/>
       <c r="I124" s="10" t="n"/>
@@ -16422,7 +16470,7 @@
       </c>
       <c r="M124" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT — plocha 2.NP = plocha podhledu (flat ceiling assumption)</t>
+          <t>DXF km_tabulka místností MTEXT — plocha 1.NP = plocha podhledu (flat ceiling assumption)</t>
         </is>
       </c>
       <c r="N124" s="20" t="inlineStr">
@@ -16449,7 +16497,7 @@
       </c>
       <c r="C125" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled — tmelení + úprava 3.NP</t>
+          <t>SDK podhled — tmelení + úprava 2.NP</t>
         </is>
       </c>
       <c r="D125" s="20" t="inlineStr">
@@ -16459,7 +16507,7 @@
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (3.NP)</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (2.NP)</t>
         </is>
       </c>
       <c r="F125" s="20" t="inlineStr">
@@ -16468,7 +16516,7 @@
         </is>
       </c>
       <c r="G125" s="22" t="n">
-        <v>64.5</v>
+        <v>61.1</v>
       </c>
       <c r="H125" s="10" t="n"/>
       <c r="I125" s="10" t="n"/>
@@ -16487,7 +16535,7 @@
       </c>
       <c r="M125" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT — plocha 3.NP = plocha podhledu (flat ceiling assumption)</t>
+          <t>DXF km_tabulka místností MTEXT — plocha 2.NP = plocha podhledu (flat ceiling assumption)</t>
         </is>
       </c>
       <c r="N125" s="20" t="inlineStr">
@@ -16514,17 +16562,17 @@
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad koupelna 1.05 (1.NP)</t>
+          <t>SDK podhled — tmelení + úprava 3.NP</t>
         </is>
       </c>
       <c r="D126" s="20" t="inlineStr">
         <is>
-          <t>781447001</t>
+          <t>612471141</t>
         </is>
       </c>
       <c r="E126" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 1.05 1.NP — výška obkladu 1.6 m (z DXF km Obklady layer)</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (3.NP)</t>
         </is>
       </c>
       <c r="F126" s="20" t="inlineStr">
@@ -16533,17 +16581,17 @@
         </is>
       </c>
       <c r="G126" s="22" t="n">
-        <v>13.4</v>
+        <v>64.5</v>
       </c>
       <c r="H126" s="10" t="n"/>
       <c r="I126" s="10" t="n"/>
       <c r="J126" s="8" t="inlineStr">
         <is>
-          <t>obkladac</t>
+          <t>sadrokartonar</t>
         </is>
       </c>
       <c r="K126" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L126" s="20" t="inlineStr">
         <is>
@@ -16552,7 +16600,7 @@
       </c>
       <c r="M126" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms PIP perimeter 1.05 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
+          <t>DXF km_tabulka místností MTEXT — plocha 3.NP = plocha podhledu (flat ceiling assumption)</t>
         </is>
       </c>
       <c r="N126" s="20" t="inlineStr">
@@ -16579,7 +16627,7 @@
       </c>
       <c r="C127" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad koupelna 2.03 (2.NP)</t>
+          <t>Keramický obklad koupelna 1.05 (1.NP)</t>
         </is>
       </c>
       <c r="D127" s="20" t="inlineStr">
@@ -16589,7 +16637,7 @@
       </c>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 2.03 2.NP — výška obkladu 2.45 m (z DXF km Obklady layer)</t>
+          <t>Keramický obklad stěn koupelny 1.05 1.NP — výška obkladu 1.6 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="F127" s="20" t="inlineStr">
@@ -16598,7 +16646,7 @@
         </is>
       </c>
       <c r="G127" s="22" t="n">
-        <v>15.2</v>
+        <v>13.4</v>
       </c>
       <c r="H127" s="10" t="n"/>
       <c r="I127" s="10" t="n"/>
@@ -16617,7 +16665,7 @@
       </c>
       <c r="M127" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms PIP perimeter 2.03 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
+          <t>DXF rooms PIP perimeter 1.05 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
         </is>
       </c>
       <c r="N127" s="20" t="inlineStr">
@@ -16644,7 +16692,7 @@
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad koupelna 3.04 (3.NP)</t>
+          <t>Keramický obklad koupelna 2.03 (2.NP)</t>
         </is>
       </c>
       <c r="D128" s="20" t="inlineStr">
@@ -16654,7 +16702,7 @@
       </c>
       <c r="E128" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 3.04 3.NP — výška obkladu 2.7 m (z DXF km Obklady layer)</t>
+          <t>Keramický obklad stěn koupelny 2.03 2.NP — výška obkladu 2.45 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="F128" s="20" t="inlineStr">
@@ -16663,7 +16711,7 @@
         </is>
       </c>
       <c r="G128" s="22" t="n">
-        <v>24.3</v>
+        <v>15.2</v>
       </c>
       <c r="H128" s="10" t="n"/>
       <c r="I128" s="10" t="n"/>
@@ -16682,7 +16730,7 @@
       </c>
       <c r="M128" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms PIP perimeter 3.04 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
+          <t>DXF rooms PIP perimeter 2.03 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
         </is>
       </c>
       <c r="N128" s="20" t="inlineStr">
@@ -16709,7 +16757,7 @@
       </c>
       <c r="C129" s="8" t="inlineStr">
         <is>
-          <t>Obklad za kuchyňskou linkou</t>
+          <t>Keramický obklad koupelna 3.04 (3.NP)</t>
         </is>
       </c>
       <c r="D129" s="20" t="inlineStr">
@@ -16719,7 +16767,7 @@
       </c>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad za kuchyňskou linkou nad pracovní deskou — 2 kuchyně × ~5 m² (1.06 byt rodičů + 3.05 byt 3.NP)</t>
+          <t>Keramický obklad stěn koupelny 3.04 3.NP — výška obkladu 2.7 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="F129" s="20" t="inlineStr">
@@ -16728,7 +16776,7 @@
         </is>
       </c>
       <c r="G129" s="22" t="n">
-        <v>10</v>
+        <v>24.3</v>
       </c>
       <c r="H129" s="10" t="n"/>
       <c r="I129" s="10" t="n"/>
@@ -16738,7 +16786,7 @@
         </is>
       </c>
       <c r="K129" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L129" s="20" t="inlineStr">
         <is>
@@ -16747,7 +16795,7 @@
       </c>
       <c r="M129" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ 2× kuchyně MTEXT + TZ ARS</t>
+          <t>DXF rooms PIP perimeter 3.04 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
         </is>
       </c>
       <c r="N129" s="20" t="inlineStr">
@@ -16774,17 +16822,17 @@
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba</t>
+          <t>Obklad za kuchyňskou linkou</t>
         </is>
       </c>
       <c r="D130" s="20" t="inlineStr">
         <is>
-          <t>784121011</t>
+          <t>781447001</t>
         </is>
       </c>
       <c r="E130" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba akrylátová bílá 2× — všechny stěny + podhledy mimo obklad</t>
+          <t>Keramický obklad za kuchyňskou linkou nad pracovní deskou — 2 kuchyně × ~5 m² (1.06 byt rodičů + 3.05 byt 3.NP)</t>
         </is>
       </c>
       <c r="F130" s="20" t="inlineStr">
@@ -16793,17 +16841,17 @@
         </is>
       </c>
       <c r="G130" s="22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H130" s="10" t="n"/>
       <c r="I130" s="10" t="n"/>
       <c r="J130" s="8" t="inlineStr">
         <is>
-          <t>malir</t>
+          <t>obkladac</t>
         </is>
       </c>
       <c r="K130" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L130" s="20" t="inlineStr">
         <is>
@@ -16812,7 +16860,7 @@
       </c>
       <c r="M130" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS — interiérová výmalba (aggregate, no TZ per-room directive)</t>
+          <t>DXF dum_DPZ 2× kuchyně MTEXT + TZ ARS</t>
         </is>
       </c>
       <c r="N130" s="20" t="inlineStr">
@@ -16826,11 +16874,7 @@
         </is>
       </c>
       <c r="P130" s="41" t="n"/>
-      <c r="Q130" s="41" t="inlineStr">
-        <is>
-          <t>GAP_007_deprecated</t>
-        </is>
-      </c>
+      <c r="Q130" s="41" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="20" t="n">
@@ -16843,7 +16887,7 @@
       </c>
       <c r="C131" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.NP</t>
+          <t>Interiérová výmalba</t>
         </is>
       </c>
       <c r="D131" s="20" t="inlineStr">
@@ -16853,7 +16897,7 @@
       </c>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.NP — stěny + SDK podhled − obklad koupelny 1.05 (1.6 m výška)</t>
+          <t>Interiérová výmalba akrylátová bílá 2× — všechny stěny + podhledy mimo obklad</t>
         </is>
       </c>
       <c r="F131" s="20" t="inlineStr">
@@ -16862,7 +16906,7 @@
         </is>
       </c>
       <c r="G131" s="22" t="n">
-        <v>254.5</v>
+        <v>0</v>
       </c>
       <c r="H131" s="10" t="n"/>
       <c r="I131" s="10" t="n"/>
@@ -16872,7 +16916,7 @@
         </is>
       </c>
       <c r="K131" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L131" s="20" t="inlineStr">
         <is>
@@ -16881,7 +16925,7 @@
       </c>
       <c r="M131" s="8" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.002 + SDK podhled PSV78.005</t>
+          <t>TZ ARS — interiérová výmalba (aggregate, no TZ per-room directive)</t>
         </is>
       </c>
       <c r="N131" s="20" t="inlineStr">
@@ -16897,7 +16941,7 @@
       <c r="P131" s="41" t="n"/>
       <c r="Q131" s="41" t="inlineStr">
         <is>
-          <t>GAP_007</t>
+          <t>GAP_007_deprecated</t>
         </is>
       </c>
     </row>
@@ -16912,7 +16956,7 @@
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.PP</t>
+          <t>Interiérová výmalba 1.NP</t>
         </is>
       </c>
       <c r="D132" s="20" t="inlineStr">
@@ -16922,7 +16966,7 @@
       </c>
       <c r="E132" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.PP — sklep stěny + klenba bílá vápenná 2×</t>
+          <t>Interiérová výmalba 1.NP — stěny + SDK podhled − obklad koupelny 1.05 (1.6 m výška)</t>
         </is>
       </c>
       <c r="F132" s="20" t="inlineStr">
@@ -16931,7 +16975,7 @@
         </is>
       </c>
       <c r="G132" s="22" t="n">
-        <v>78.2</v>
+        <v>254.5</v>
       </c>
       <c r="H132" s="10" t="n"/>
       <c r="I132" s="10" t="n"/>
@@ -16950,7 +16994,7 @@
       </c>
       <c r="M132" s="8" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.001 + SDK podhled PSV78.—</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.002 + SDK podhled PSV78.005</t>
         </is>
       </c>
       <c r="N132" s="20" t="inlineStr">
@@ -16981,7 +17025,7 @@
       </c>
       <c r="C133" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 2.NP</t>
+          <t>Interiérová výmalba 1.PP</t>
         </is>
       </c>
       <c r="D133" s="20" t="inlineStr">
@@ -16991,7 +17035,7 @@
       </c>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 2.NP — stěny + SDK podhled − obklad koupelny 2.03 (2.45 m výška)</t>
+          <t>Interiérová výmalba 1.PP — sklep stěny + klenba bílá vápenná 2×</t>
         </is>
       </c>
       <c r="F133" s="20" t="inlineStr">
@@ -17000,7 +17044,7 @@
         </is>
       </c>
       <c r="G133" s="22" t="n">
-        <v>247.5</v>
+        <v>78.2</v>
       </c>
       <c r="H133" s="10" t="n"/>
       <c r="I133" s="10" t="n"/>
@@ -17019,7 +17063,7 @@
       </c>
       <c r="M133" s="8" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.003 + SDK podhled PSV78.006</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.001 + SDK podhled PSV78.—</t>
         </is>
       </c>
       <c r="N133" s="20" t="inlineStr">
@@ -17050,7 +17094,7 @@
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 3.NP</t>
+          <t>Interiérová výmalba 2.NP</t>
         </is>
       </c>
       <c r="D134" s="20" t="inlineStr">
@@ -17060,7 +17104,7 @@
       </c>
       <c r="E134" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 3.NP — stěny + SDK podhled − obklad koupelny 3.04 (2.7 m výška)</t>
+          <t>Interiérová výmalba 2.NP — stěny + SDK podhled − obklad koupelny 2.03 (2.45 m výška)</t>
         </is>
       </c>
       <c r="F134" s="20" t="inlineStr">
@@ -17069,7 +17113,7 @@
         </is>
       </c>
       <c r="G134" s="22" t="n">
-        <v>219.3</v>
+        <v>247.5</v>
       </c>
       <c r="H134" s="10" t="n"/>
       <c r="I134" s="10" t="n"/>
@@ -17088,7 +17132,7 @@
       </c>
       <c r="M134" s="8" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.004 + SDK podhled PSV78.007</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.003 + SDK podhled PSV78.006</t>
         </is>
       </c>
       <c r="N134" s="20" t="inlineStr">
@@ -17114,37 +17158,37 @@
       </c>
       <c r="B135" s="8" t="inlineStr">
         <is>
-          <t>PSV-95 Detekce požární</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="C135" s="8" t="inlineStr">
         <is>
-          <t>Autonomní hlásič kouře</t>
+          <t>Interiérová výmalba 3.NP</t>
         </is>
       </c>
       <c r="D135" s="20" t="inlineStr">
         <is>
-          <t>375211101</t>
+          <t>784121011</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>Autonomní hlásič kouře dle ČSN EN 14604 — 4 ks v místnostech 1.01, 1.02, 2.04, 3.03 dle PBŘ</t>
+          <t>Interiérová výmalba 3.NP — stěny + SDK podhled − obklad koupelny 3.04 (2.7 m výška)</t>
         </is>
       </c>
       <c r="F135" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G135" s="23" t="n">
-        <v>4</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G135" s="22" t="n">
+        <v>219.3</v>
       </c>
       <c r="H135" s="10" t="n"/>
       <c r="I135" s="10" t="n"/>
       <c r="J135" s="8" t="inlineStr">
         <is>
-          <t>elektroinstalater</t>
+          <t>malir</t>
         </is>
       </c>
       <c r="K135" s="24" t="n">
@@ -17152,12 +17196,12 @@
       </c>
       <c r="L135" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M135" s="8" t="inlineStr">
         <is>
-          <t>TZ PBŘ dům — ČSN EN 14604 autonomní hlásič kouře 4 ks</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.004 + SDK podhled PSV78.007</t>
         </is>
       </c>
       <c r="N135" s="20" t="inlineStr">
@@ -17173,7 +17217,7 @@
       <c r="P135" s="41" t="n"/>
       <c r="Q135" s="41" t="inlineStr">
         <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+          <t>GAP_007</t>
         </is>
       </c>
     </row>
@@ -17188,17 +17232,17 @@
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>Přenosný hasicí přístroj 34A</t>
+          <t>Autonomní hlásič kouře</t>
         </is>
       </c>
       <c r="D136" s="20" t="inlineStr">
         <is>
-          <t>966067121</t>
+          <t>375211101</t>
         </is>
       </c>
       <c r="E136" s="8" t="inlineStr">
         <is>
-          <t>Přenosný hasicí přístroj 34A dle PBŘ — min. 1 ks na společné chodbě</t>
+          <t>Autonomní hlásič kouře dle ČSN EN 14604 — 4 ks v místnostech 1.01, 1.02, 2.04, 3.03 dle PBŘ</t>
         </is>
       </c>
       <c r="F136" s="20" t="inlineStr">
@@ -17207,13 +17251,13 @@
         </is>
       </c>
       <c r="G136" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H136" s="10" t="n"/>
       <c r="I136" s="10" t="n"/>
       <c r="J136" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>elektroinstalater</t>
         </is>
       </c>
       <c r="K136" s="24" t="n">
@@ -17221,12 +17265,12 @@
       </c>
       <c r="L136" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M136" s="8" t="inlineStr">
         <is>
-          <t>TZ PBŘ dům — PHP 34A 1 ks minimum</t>
+          <t>TZ PBŘ dům — ČSN EN 14604 autonomní hlásič kouře 4 ks</t>
         </is>
       </c>
       <c r="N136" s="20" t="inlineStr">
@@ -17240,7 +17284,11 @@
         </is>
       </c>
       <c r="P136" s="41" t="n"/>
-      <c r="Q136" s="41" t="n"/>
+      <c r="Q136" s="41" t="inlineStr">
+        <is>
+          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="20" t="n">
@@ -17248,27 +17296,27 @@
       </c>
       <c r="B137" s="8" t="inlineStr">
         <is>
-          <t>M-21 ELI silnoproud</t>
+          <t>PSV-95 Detekce požární</t>
         </is>
       </c>
       <c r="C137" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávající ELI</t>
+          <t>Přenosný hasicí přístroj 34A</t>
         </is>
       </c>
       <c r="D137" s="20" t="inlineStr">
         <is>
-          <t>210010011</t>
+          <t>966067121</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávající elektroinstalace v celém domě (vodiče, rozvaděč, zásuvky, svítidla) — recyklace mědi</t>
+          <t>Přenosný hasicí přístroj 34A dle PBŘ — min. 1 ks na společné chodbě</t>
         </is>
       </c>
       <c r="F137" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G137" s="23" t="n">
@@ -17278,7 +17326,7 @@
       <c r="I137" s="10" t="n"/>
       <c r="J137" s="8" t="inlineStr">
         <is>
-          <t>elektroinstalater</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K137" s="24" t="n">
@@ -17291,12 +17339,12 @@
       </c>
       <c r="M137" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — kompletně nová ELI</t>
+          <t>TZ PBŘ dům — PHP 34A 1 ks minimum</t>
         </is>
       </c>
       <c r="N137" s="20" t="inlineStr">
         <is>
-          <t>#7</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O137" s="26" t="inlineStr">
@@ -17318,26 +17366,26 @@
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t>Pojistková skříň + 3× podružný rozvaděč</t>
+          <t>Demontáž stávající ELI</t>
         </is>
       </c>
       <c r="D138" s="20" t="inlineStr">
         <is>
-          <t>210110023</t>
+          <t>210010011</t>
         </is>
       </c>
       <c r="E138" s="8" t="inlineStr">
         <is>
-          <t>Nová pojistková skříň + 3× podružný rozvaděč pro každé patro (1.NP, 2.NP, 3.NP) s podružným měřením</t>
+          <t>Demontáž stávající elektroinstalace v celém domě (vodiče, rozvaděč, zásuvky, svítidla) — recyklace mědi</t>
         </is>
       </c>
       <c r="F138" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G138" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H138" s="10" t="n"/>
       <c r="I138" s="10" t="n"/>
@@ -17356,7 +17404,7 @@
       </c>
       <c r="M138" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — 'nová pojistková skříň s podružným měřením pro každé patro'</t>
+          <t>TZ ARS dům §4 — kompletně nová ELI</t>
         </is>
       </c>
       <c r="N138" s="20" t="inlineStr">
@@ -17383,26 +17431,26 @@
       </c>
       <c r="C139" s="8" t="inlineStr">
         <is>
-          <t>Rozvody silnoproud</t>
+          <t>Pojistková skříň + 3× podružný rozvaděč</t>
         </is>
       </c>
       <c r="D139" s="20" t="inlineStr">
         <is>
-          <t>210800012</t>
+          <t>210110023</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
         <is>
-          <t>Nové silnoproudé rozvody — vodiče CYKY 3×1.5 / 3×2.5 / 5×2.5 / 5×6 + krabice + instalační trubky</t>
+          <t>Nová pojistková skříň + 3× podružný rozvaděč pro každé patro (1.NP, 2.NP, 3.NP) s podružným měřením</t>
         </is>
       </c>
       <c r="F139" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G139" s="22" t="n">
-        <v>700</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G139" s="23" t="n">
+        <v>4</v>
       </c>
       <c r="H139" s="10" t="n"/>
       <c r="I139" s="10" t="n"/>
@@ -17412,7 +17460,7 @@
         </is>
       </c>
       <c r="K139" s="24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L139" s="20" t="inlineStr">
         <is>
@@ -17421,7 +17469,7 @@
       </c>
       <c r="M139" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD 3-byt. dispozice</t>
+          <t>TZ ARS dům §4 — 'nová pojistková skříň s podružným měřením pro každé patro'</t>
         </is>
       </c>
       <c r="N139" s="20" t="inlineStr">
@@ -17448,26 +17496,26 @@
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>Zásuvky a vypínače</t>
+          <t>Rozvody silnoproud</t>
         </is>
       </c>
       <c r="D140" s="20" t="inlineStr">
         <is>
-          <t>210810050</t>
+          <t>210800012</t>
         </is>
       </c>
       <c r="E140" s="8" t="inlineStr">
         <is>
-          <t>Zásuvky a vypínače dodávka + montáž — ~70 ks (60-80 dle vyjasnění #7)</t>
+          <t>Nové silnoproudé rozvody — vodiče CYKY 3×1.5 / 3×2.5 / 5×2.5 / 5×6 + krabice + instalační trubky</t>
         </is>
       </c>
       <c r="F140" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G140" s="23" t="n">
-        <v>70</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G140" s="22" t="n">
+        <v>700</v>
       </c>
       <c r="H140" s="10" t="n"/>
       <c r="I140" s="10" t="n"/>
@@ -17486,7 +17534,7 @@
       </c>
       <c r="M140" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD 220 m² 3-byt.</t>
+          <t>TZ ARS + B4_productivity standard RD 3-byt. dispozice</t>
         </is>
       </c>
       <c r="N140" s="20" t="inlineStr">
@@ -17513,17 +17561,17 @@
       </c>
       <c r="C141" s="8" t="inlineStr">
         <is>
-          <t>Svítidla</t>
+          <t>Zásuvky a vypínače</t>
         </is>
       </c>
       <c r="D141" s="20" t="inlineStr">
         <is>
-          <t>210820002</t>
+          <t>210810050</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
         <is>
-          <t>Svítidla dodávka + montáž — ~35 ks (30-40 dle vyjasnění #7) interiér + venkovní u vstupů</t>
+          <t>Zásuvky a vypínače dodávka + montáž — ~70 ks (60-80 dle vyjasnění #7)</t>
         </is>
       </c>
       <c r="F141" s="20" t="inlineStr">
@@ -17532,7 +17580,7 @@
         </is>
       </c>
       <c r="G141" s="23" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="H141" s="10" t="n"/>
       <c r="I141" s="10" t="n"/>
@@ -17551,7 +17599,7 @@
       </c>
       <c r="M141" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD</t>
+          <t>TZ ARS + B4_productivity standard RD 220 m² 3-byt.</t>
         </is>
       </c>
       <c r="N141" s="20" t="inlineStr">
@@ -17578,26 +17626,26 @@
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>Příprava FVE</t>
+          <t>Svítidla</t>
         </is>
       </c>
       <c r="D142" s="20" t="inlineStr">
         <is>
-          <t>210800099</t>
+          <t>210820002</t>
         </is>
       </c>
       <c r="E142" s="8" t="inlineStr">
         <is>
-          <t>Příprava na osazení FVE — rezerva v rozvaděči (jistič + zásuvka pro střídač) + trasy do střechy</t>
+          <t>Svítidla dodávka + montáž — ~35 ks (30-40 dle vyjasnění #7) interiér + venkovní u vstupů</t>
         </is>
       </c>
       <c r="F142" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G142" s="23" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="H142" s="10" t="n"/>
       <c r="I142" s="10" t="n"/>
@@ -17607,7 +17655,7 @@
         </is>
       </c>
       <c r="K142" s="24" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="L142" s="20" t="inlineStr">
         <is>
@@ -17616,7 +17664,7 @@
       </c>
       <c r="M142" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — FVE příprava (bez panelů samotných)</t>
+          <t>TZ ARS + B4_productivity standard RD</t>
         </is>
       </c>
       <c r="N142" s="20" t="inlineStr">
@@ -17643,17 +17691,17 @@
       </c>
       <c r="C143" s="8" t="inlineStr">
         <is>
-          <t>Revize ELI při kolaudaci</t>
+          <t>Příprava FVE</t>
         </is>
       </c>
       <c r="D143" s="20" t="inlineStr">
         <is>
-          <t>996019011</t>
+          <t>210800099</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
         <is>
-          <t>Výchozí revize elektrické instalace dle ČSN 33 2000-6 + revizní zpráva pro kolaudaci</t>
+          <t>Příprava na osazení FVE — rezerva v rozvaděči (jistič + zásuvka pro střídač) + trasy do střechy</t>
         </is>
       </c>
       <c r="F143" s="20" t="inlineStr">
@@ -17668,11 +17716,11 @@
       <c r="I143" s="10" t="n"/>
       <c r="J143" s="8" t="inlineStr">
         <is>
-          <t>revize_specialista</t>
+          <t>elektroinstalater</t>
         </is>
       </c>
       <c r="K143" s="24" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="L143" s="20" t="inlineStr">
         <is>
@@ -17681,12 +17729,12 @@
       </c>
       <c r="M143" s="8" t="inlineStr">
         <is>
-          <t>Povinná revize ELI dle ČSN 33 2000-6 + kolaudace</t>
+          <t>TZ ARS dům §4 — FVE příprava (bez panelů samotných)</t>
         </is>
       </c>
       <c r="N143" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#7</t>
         </is>
       </c>
       <c r="O143" s="26" t="inlineStr">
@@ -17703,22 +17751,22 @@
       </c>
       <c r="B144" s="8" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>M-21 ELI silnoproud</t>
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>Revize stávajících přípojek</t>
+          <t>Revize ELI při kolaudaci</t>
         </is>
       </c>
       <c r="D144" s="20" t="inlineStr">
         <is>
-          <t>722290515</t>
+          <t>996019011</t>
         </is>
       </c>
       <c r="E144" s="8" t="inlineStr">
         <is>
-          <t>Revize stávajícího napojení vodovodu + kanalizace na pozemku — kontrola stavu, čištění, tlaková zkouška</t>
+          <t>Výchozí revize elektrické instalace dle ČSN 33 2000-6 + revizní zpráva pro kolaudaci</t>
         </is>
       </c>
       <c r="F144" s="20" t="inlineStr">
@@ -17733,25 +17781,25 @@
       <c r="I144" s="10" t="n"/>
       <c r="J144" s="8" t="inlineStr">
         <is>
-          <t>vodar</t>
+          <t>revize_specialista</t>
         </is>
       </c>
       <c r="K144" s="24" t="n">
-        <v>0.85</v>
+        <v>0.99</v>
       </c>
       <c r="L144" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M144" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — vodovod + kanalizace stávající, bez změny</t>
+          <t>Povinná revize ELI dle ČSN 33 2000-6 + kolaudace</t>
         </is>
       </c>
       <c r="N144" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O144" s="26" t="inlineStr">
@@ -17760,11 +17808,7 @@
         </is>
       </c>
       <c r="P144" s="41" t="n"/>
-      <c r="Q144" s="41" t="inlineStr">
-        <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
-        </is>
-      </c>
+      <c r="Q144" s="41" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="20" t="n">
@@ -17777,26 +17821,26 @@
       </c>
       <c r="C145" s="8" t="inlineStr">
         <is>
-          <t>Nové rozvody vody do 3.NP</t>
+          <t>Revize stávajících přípojek</t>
         </is>
       </c>
       <c r="D145" s="20" t="inlineStr">
         <is>
-          <t>722172011</t>
+          <t>722290515</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
         <is>
-          <t>Nové rozvody studené + teplé vody do koupelen 1.NP + 2.NP + 3.NP a kuchyní (PEX/Cu, dimenze DN15-25)</t>
+          <t>Revize stávajícího napojení vodovodu + kanalizace na pozemku — kontrola stavu, čištění, tlaková zkouška</t>
         </is>
       </c>
       <c r="F145" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G145" s="22" t="n">
-        <v>80</v>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G145" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H145" s="10" t="n"/>
       <c r="I145" s="10" t="n"/>
@@ -17806,7 +17850,7 @@
         </is>
       </c>
       <c r="K145" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L145" s="20" t="inlineStr">
         <is>
@@ -17815,7 +17859,7 @@
       </c>
       <c r="M145" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — nové koupelny + kuchyně, vyjasnění #6 working assumption</t>
+          <t>TZ ARS dům §4 — vodovod + kanalizace stávající, bez změny</t>
         </is>
       </c>
       <c r="N145" s="20" t="inlineStr">
@@ -17846,17 +17890,17 @@
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>Nové odpadní rozvody</t>
+          <t>Nové rozvody vody do 3.NP</t>
         </is>
       </c>
       <c r="D146" s="20" t="inlineStr">
         <is>
-          <t>721174021</t>
+          <t>722172011</t>
         </is>
       </c>
       <c r="E146" s="8" t="inlineStr">
         <is>
-          <t>Nové odpadní rozvody PVC-HT DN40-DN110 ke koupelnám 1.NP, 2.NP, 3.NP a kuchyním + napojení na stávající</t>
+          <t>Nové rozvody studené + teplé vody do koupelen 1.NP + 2.NP + 3.NP a kuchyní (PEX/Cu, dimenze DN15-25)</t>
         </is>
       </c>
       <c r="F146" s="20" t="inlineStr">
@@ -17865,7 +17909,7 @@
         </is>
       </c>
       <c r="G146" s="22" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H146" s="10" t="n"/>
       <c r="I146" s="10" t="n"/>
@@ -17879,12 +17923,12 @@
       </c>
       <c r="L146" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M146" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — nové koupelny + kuchyně, odpad do stávající kanalizace</t>
+          <t>TZ ARS dům §4 — nové koupelny + kuchyně, vyjasnění #6 working assumption</t>
         </is>
       </c>
       <c r="N146" s="20" t="inlineStr">
@@ -17898,7 +17942,11 @@
         </is>
       </c>
       <c r="P146" s="41" t="n"/>
-      <c r="Q146" s="41" t="n"/>
+      <c r="Q146" s="41" t="inlineStr">
+        <is>
+          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="20" t="n">
@@ -17911,26 +17959,26 @@
       </c>
       <c r="C147" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP)</t>
+          <t>Nové odpadní rozvody</t>
         </is>
       </c>
       <c r="D147" s="20" t="inlineStr">
         <is>
-          <t>725291131</t>
+          <t>721174021</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 1.05 1.NP: 1× vana (DXF) + 1× umyvadlo (DXF) + 1× WC (TZ standard)</t>
+          <t>Nové odpadní rozvody PVC-HT DN40-DN110 ke koupelnám 1.NP, 2.NP, 3.NP a kuchyním + napojení na stávající</t>
         </is>
       </c>
       <c r="F147" s="20" t="inlineStr">
         <is>
-          <t>set</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G147" s="22" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H147" s="10" t="n"/>
       <c r="I147" s="10" t="n"/>
@@ -17949,7 +17997,7 @@
       </c>
       <c r="M147" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 1.05 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>TZ ARS dům §4 — nové koupelny + kuchyně, odpad do stávající kanalizace</t>
         </is>
       </c>
       <c r="N147" s="20" t="inlineStr">
@@ -17963,11 +18011,7 @@
         </is>
       </c>
       <c r="P147" s="41" t="n"/>
-      <c r="Q147" s="41" t="inlineStr">
-        <is>
-          <t>GAP_005_deprecated</t>
-        </is>
-      </c>
+      <c r="Q147" s="41" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="20" t="n">
@@ -17980,26 +18024,26 @@
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture A</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP)</t>
         </is>
       </c>
       <c r="D148" s="20" t="inlineStr">
         <is>
-          <t>725211101</t>
+          <t>725291131</t>
         </is>
       </c>
       <c r="E148" s="8" t="inlineStr">
         <is>
-          <t>Vana koupelnová obdélníková 170×70 cm — koupelna 1.05 1.NP</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 1.05 1.NP: 1× vana (DXF) + 1× umyvadlo (DXF) + 1× WC (TZ standard)</t>
         </is>
       </c>
       <c r="F148" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G148" s="23" t="n">
-        <v>1</v>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="G148" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H148" s="10" t="n"/>
       <c r="I148" s="10" t="n"/>
@@ -18009,7 +18053,7 @@
         </is>
       </c>
       <c r="K148" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L148" s="20" t="inlineStr">
         <is>
@@ -18018,12 +18062,12 @@
       </c>
       <c r="M148" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 1.05 1.NP + TZ ARS koupelna kompletace</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 1.05 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="N148" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O148" s="26" t="inlineStr">
@@ -18034,7 +18078,7 @@
       <c r="P148" s="41" t="n"/>
       <c r="Q148" s="41" t="inlineStr">
         <is>
-          <t>GAP_005</t>
+          <t>GAP_005_deprecated</t>
         </is>
       </c>
     </row>
@@ -18049,17 +18093,17 @@
       </c>
       <c r="C149" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture B</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture A</t>
         </is>
       </c>
       <c r="D149" s="20" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725211101</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 1.05 1.NP</t>
+          <t>Vana koupelnová obdélníková 170×70 cm — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="F149" s="20" t="inlineStr">
@@ -18118,17 +18162,17 @@
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture C</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture B</t>
         </is>
       </c>
       <c r="D150" s="20" t="inlineStr">
         <is>
-          <t>725111101</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="E150" s="8" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 1.05 1.NP</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="F150" s="20" t="inlineStr">
@@ -18187,26 +18231,26 @@
       </c>
       <c r="C151" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP)</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture C</t>
         </is>
       </c>
       <c r="D151" s="20" t="inlineStr">
         <is>
-          <t>725291131</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 2.03 2.NP: 1× umyvadlo (DXF) + 1× WC (TZ standard) + 1× sprcha (TZ standard)</t>
+          <t>WC kombi keramické bílé — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="F151" s="20" t="inlineStr">
         <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="G151" s="22" t="n">
-        <v>0</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G151" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H151" s="10" t="n"/>
       <c r="I151" s="10" t="n"/>
@@ -18216,7 +18260,7 @@
         </is>
       </c>
       <c r="K151" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L151" s="20" t="inlineStr">
         <is>
@@ -18225,12 +18269,12 @@
       </c>
       <c r="M151" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 2.03 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>DXF dum_DPZ MTEXT room 1.05 1.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="N151" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O151" s="26" t="inlineStr">
@@ -18241,7 +18285,7 @@
       <c r="P151" s="41" t="n"/>
       <c r="Q151" s="41" t="inlineStr">
         <is>
-          <t>GAP_005_deprecated</t>
+          <t>GAP_005</t>
         </is>
       </c>
     </row>
@@ -18256,26 +18300,26 @@
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture A</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP)</t>
         </is>
       </c>
       <c r="D152" s="20" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725291131</t>
         </is>
       </c>
       <c r="E152" s="8" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 2.03 2.NP</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 2.03 2.NP: 1× umyvadlo (DXF) + 1× WC (TZ standard) + 1× sprcha (TZ standard)</t>
         </is>
       </c>
       <c r="F152" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G152" s="23" t="n">
-        <v>1</v>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="G152" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H152" s="10" t="n"/>
       <c r="I152" s="10" t="n"/>
@@ -18285,7 +18329,7 @@
         </is>
       </c>
       <c r="K152" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L152" s="20" t="inlineStr">
         <is>
@@ -18294,12 +18338,12 @@
       </c>
       <c r="M152" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 2.03 2.NP + TZ ARS koupelna kompletace</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 2.03 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="N152" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O152" s="26" t="inlineStr">
@@ -18310,7 +18354,7 @@
       <c r="P152" s="41" t="n"/>
       <c r="Q152" s="41" t="inlineStr">
         <is>
-          <t>GAP_005</t>
+          <t>GAP_005_deprecated</t>
         </is>
       </c>
     </row>
@@ -18325,17 +18369,17 @@
       </c>
       <c r="C153" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture B</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture A</t>
         </is>
       </c>
       <c r="D153" s="20" t="inlineStr">
         <is>
-          <t>725221201</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
         <is>
-          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 2.03 2.NP</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="F153" s="20" t="inlineStr">
@@ -18394,17 +18438,17 @@
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture C</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture B</t>
         </is>
       </c>
       <c r="D154" s="20" t="inlineStr">
         <is>
-          <t>725111101</t>
+          <t>725221201</t>
         </is>
       </c>
       <c r="E154" s="8" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 2.03 2.NP</t>
+          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="F154" s="20" t="inlineStr">
@@ -18463,26 +18507,26 @@
       </c>
       <c r="C155" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP)</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture C</t>
         </is>
       </c>
       <c r="D155" s="20" t="inlineStr">
         <is>
-          <t>725291131</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 3.04 3.NP: 1× WC (DXF) + 1× umyvadlo (TZ standard) + 1× sprcha (TZ standard)</t>
+          <t>WC kombi keramické bílé — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="F155" s="20" t="inlineStr">
         <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="G155" s="22" t="n">
-        <v>0</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G155" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H155" s="10" t="n"/>
       <c r="I155" s="10" t="n"/>
@@ -18492,7 +18536,7 @@
         </is>
       </c>
       <c r="K155" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L155" s="20" t="inlineStr">
         <is>
@@ -18501,12 +18545,12 @@
       </c>
       <c r="M155" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 3.04 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>DXF dum_DPZ MTEXT room 2.03 2.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="N155" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O155" s="26" t="inlineStr">
@@ -18517,7 +18561,7 @@
       <c r="P155" s="41" t="n"/>
       <c r="Q155" s="41" t="inlineStr">
         <is>
-          <t>GAP_005_deprecated</t>
+          <t>GAP_005</t>
         </is>
       </c>
     </row>
@@ -18532,26 +18576,26 @@
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture A</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP)</t>
         </is>
       </c>
       <c r="D156" s="20" t="inlineStr">
         <is>
-          <t>725111101</t>
+          <t>725291131</t>
         </is>
       </c>
       <c r="E156" s="8" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 3.04 3.NP</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 3.04 3.NP: 1× WC (DXF) + 1× umyvadlo (TZ standard) + 1× sprcha (TZ standard)</t>
         </is>
       </c>
       <c r="F156" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G156" s="23" t="n">
-        <v>1</v>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="G156" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H156" s="10" t="n"/>
       <c r="I156" s="10" t="n"/>
@@ -18561,7 +18605,7 @@
         </is>
       </c>
       <c r="K156" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L156" s="20" t="inlineStr">
         <is>
@@ -18570,12 +18614,12 @@
       </c>
       <c r="M156" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 3.04 3.NP + TZ ARS koupelna kompletace</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 3.04 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="N156" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O156" s="26" t="inlineStr">
@@ -18586,7 +18630,7 @@
       <c r="P156" s="41" t="n"/>
       <c r="Q156" s="41" t="inlineStr">
         <is>
-          <t>GAP_005</t>
+          <t>GAP_005_deprecated</t>
         </is>
       </c>
     </row>
@@ -18601,17 +18645,17 @@
       </c>
       <c r="C157" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture B</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture A</t>
         </is>
       </c>
       <c r="D157" s="20" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 3.04 3.NP</t>
+          <t>WC kombi keramické bílé — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="F157" s="20" t="inlineStr">
@@ -18670,17 +18714,17 @@
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture C</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture B</t>
         </is>
       </c>
       <c r="D158" s="20" t="inlineStr">
         <is>
-          <t>725221201</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="E158" s="8" t="inlineStr">
         <is>
-          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 3.04 3.NP</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="F158" s="20" t="inlineStr">
@@ -18739,17 +18783,17 @@
       </c>
       <c r="C159" s="8" t="inlineStr">
         <is>
-          <t>Kuchyňský dřez 2 ks (1.06 + 3.05)</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture C</t>
         </is>
       </c>
       <c r="D159" s="20" t="inlineStr">
         <is>
-          <t>725840111</t>
+          <t>725221201</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
         <is>
-          <t>Kuchyňský dřez nerez + montáž — 2 ks (kuchyně 1.06 byt rodičů + kuchyně 3.05 byt 3.NP)</t>
+          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="F159" s="20" t="inlineStr">
@@ -18758,7 +18802,7 @@
         </is>
       </c>
       <c r="G159" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H159" s="10" t="n"/>
       <c r="I159" s="10" t="n"/>
@@ -18768,7 +18812,7 @@
         </is>
       </c>
       <c r="K159" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L159" s="20" t="inlineStr">
         <is>
@@ -18777,12 +18821,12 @@
       </c>
       <c r="M159" s="8" t="inlineStr">
         <is>
-          <t>DXF kuchyně MTEXT 2× + TZ ARS — dispozice byty</t>
+          <t>DXF dum_DPZ MTEXT room 3.04 3.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="N159" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O159" s="26" t="inlineStr">
@@ -18791,7 +18835,11 @@
         </is>
       </c>
       <c r="P159" s="41" t="n"/>
-      <c r="Q159" s="41" t="n"/>
+      <c r="Q159" s="41" t="inlineStr">
+        <is>
+          <t>GAP_005</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="20" t="n">
@@ -18804,17 +18852,17 @@
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>Vodovodní baterie + drobnosti</t>
+          <t>Kuchyňský dřez 2 ks (1.06 + 3.05)</t>
         </is>
       </c>
       <c r="D160" s="20" t="inlineStr">
         <is>
-          <t>725822611</t>
+          <t>725840111</t>
         </is>
       </c>
       <c r="E160" s="8" t="inlineStr">
         <is>
-          <t>Vodovodní baterie (WC ventil + páková umyvadlová + sprchové + dřezové + termostat sprchové) — ~15 ks + drobné instalační materiály</t>
+          <t>Kuchyňský dřez nerez + montáž — 2 ks (kuchyně 1.06 byt rodičů + kuchyně 3.05 byt 3.NP)</t>
         </is>
       </c>
       <c r="F160" s="20" t="inlineStr">
@@ -18823,7 +18871,7 @@
         </is>
       </c>
       <c r="G160" s="23" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H160" s="10" t="n"/>
       <c r="I160" s="10" t="n"/>
@@ -18833,7 +18881,7 @@
         </is>
       </c>
       <c r="K160" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L160" s="20" t="inlineStr">
         <is>
@@ -18842,7 +18890,7 @@
       </c>
       <c r="M160" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS — kompletní baterie nové</t>
+          <t>DXF kuchyně MTEXT 2× + TZ ARS — dispozice byty</t>
         </is>
       </c>
       <c r="N160" s="20" t="inlineStr">
@@ -18869,17 +18917,17 @@
       </c>
       <c r="C161" s="8" t="inlineStr">
         <is>
-          <t>Akumulační zásobník TUV v suterénu</t>
+          <t>Vodovodní baterie + drobnosti</t>
         </is>
       </c>
       <c r="D161" s="20" t="inlineStr">
         <is>
-          <t>732419411</t>
+          <t>725822611</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
         <is>
-          <t>Akumulační zásobník TUV ~300 l v 1.PP napojený na topný systém (sporáková kamna + krb + elektrokotel) — nepřímotop</t>
+          <t>Vodovodní baterie (WC ventil + páková umyvadlová + sprchové + dřezové + termostat sprchové) — ~15 ks + drobné instalační materiály</t>
         </is>
       </c>
       <c r="F161" s="20" t="inlineStr">
@@ -18888,17 +18936,17 @@
         </is>
       </c>
       <c r="G161" s="23" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H161" s="10" t="n"/>
       <c r="I161" s="10" t="n"/>
       <c r="J161" s="8" t="inlineStr">
         <is>
-          <t>instalater_TUV_akumulacni_zasobnik</t>
+          <t>vodar</t>
         </is>
       </c>
       <c r="K161" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L161" s="20" t="inlineStr">
         <is>
@@ -18907,7 +18955,7 @@
       </c>
       <c r="M161" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — kombi akumulační zásobník napojený na multivariantní topný systém</t>
+          <t>TZ ARS — kompletní baterie nové</t>
         </is>
       </c>
       <c r="N161" s="20" t="inlineStr">
@@ -18934,17 +18982,17 @@
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t>Elektrický bojler 3.NP</t>
+          <t>Akumulační zásobník TUV v suterénu</t>
         </is>
       </c>
       <c r="D162" s="20" t="inlineStr">
         <is>
-          <t>732429211</t>
+          <t>732419411</t>
         </is>
       </c>
       <c r="E162" s="8" t="inlineStr">
         <is>
-          <t>Elektrický bojler ~80 l v koupelně 3.NP (nezávislý zdroj pro samostatný byt)</t>
+          <t>Akumulační zásobník TUV ~300 l v 1.PP napojený na topný systém (sporáková kamna + krb + elektrokotel) — nepřímotop</t>
         </is>
       </c>
       <c r="F162" s="20" t="inlineStr">
@@ -18959,7 +19007,7 @@
       <c r="I162" s="10" t="n"/>
       <c r="J162" s="8" t="inlineStr">
         <is>
-          <t>vodar</t>
+          <t>instalater_TUV_akumulacni_zasobnik</t>
         </is>
       </c>
       <c r="K162" s="24" t="n">
@@ -18972,7 +19020,7 @@
       </c>
       <c r="M162" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — elektrický bojler v 3.NP koupelně, vyjasnění #6 odhad 80 l</t>
+          <t>TZ ARS dům §4 — kombi akumulační zásobník napojený na multivariantní topný systém</t>
         </is>
       </c>
       <c r="N162" s="20" t="inlineStr">
@@ -18994,22 +19042,22 @@
       </c>
       <c r="B163" s="8" t="inlineStr">
         <is>
-          <t>PSV-73 Vytápění</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="C163" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna na tuhá paliva</t>
+          <t>Elektrický bojler 3.NP</t>
         </is>
       </c>
       <c r="D163" s="20" t="inlineStr">
         <is>
-          <t>733241011</t>
+          <t>732429211</t>
         </is>
       </c>
       <c r="E163" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna na tuhá paliva ~10 kW s akumulačním zásobníkem TUV — dodávka</t>
+          <t>Elektrický bojler ~80 l v koupelně 3.NP (nezávislý zdroj pro samostatný byt)</t>
         </is>
       </c>
       <c r="F163" s="20" t="inlineStr">
@@ -19024,7 +19072,7 @@
       <c r="I163" s="10" t="n"/>
       <c r="J163" s="8" t="inlineStr">
         <is>
-          <t>topenar</t>
+          <t>vodar</t>
         </is>
       </c>
       <c r="K163" s="24" t="n">
@@ -19037,7 +19085,7 @@
       </c>
       <c r="M163" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — primární zdroj 1.NP/2.NP, ~10 kW odhad standard RD</t>
+          <t>TZ ARS dům §4 — elektrický bojler v 3.NP koupelně, vyjasnění #6 odhad 80 l</t>
         </is>
       </c>
       <c r="N163" s="20" t="inlineStr">
@@ -19064,22 +19112,22 @@
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna — montáž</t>
+          <t>Sporáková kamna na tuhá paliva</t>
         </is>
       </c>
       <c r="D164" s="20" t="inlineStr">
         <is>
-          <t>733281011</t>
+          <t>733241011</t>
         </is>
       </c>
       <c r="E164" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna — montáž vč. napojení na komín + akumulační zásobník (cca 8 Nh)</t>
+          <t>Sporáková kamna na tuhá paliva ~10 kW s akumulačním zásobníkem TUV — dodávka</t>
         </is>
       </c>
       <c r="F164" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G164" s="23" t="n">
@@ -19093,7 +19141,7 @@
         </is>
       </c>
       <c r="K164" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L164" s="20" t="inlineStr">
         <is>
@@ -19102,12 +19150,12 @@
       </c>
       <c r="M164" s="8" t="inlineStr">
         <is>
-          <t>Standard montáž kamen s napojením na zásobník</t>
+          <t>TZ ARS dům §4 — primární zdroj 1.NP/2.NP, ~10 kW odhad standard RD</t>
         </is>
       </c>
       <c r="N164" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O164" s="26" t="inlineStr">
@@ -19129,22 +19177,22 @@
       </c>
       <c r="C165" s="8" t="inlineStr">
         <is>
-          <t>Elektrokotel 3.NP</t>
+          <t>Sporáková kamna — montáž</t>
         </is>
       </c>
       <c r="D165" s="20" t="inlineStr">
         <is>
-          <t>733131221</t>
+          <t>733281011</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
         <is>
-          <t>Elektrokotel ~8 kW pro 3.NP samostatný byt — dodávka + montáž + napojení</t>
+          <t>Sporáková kamna — montáž vč. napojení na komín + akumulační zásobník (cca 8 Nh)</t>
         </is>
       </c>
       <c r="F165" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G165" s="23" t="n">
@@ -19158,7 +19206,7 @@
         </is>
       </c>
       <c r="K165" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L165" s="20" t="inlineStr">
         <is>
@@ -19167,12 +19215,12 @@
       </c>
       <c r="M165" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — 'Nově navržené 3.NP bude vytápěno elektrokotlem'; ~8 kW odhad</t>
+          <t>Standard montáž kamen s napojením na zásobník</t>
         </is>
       </c>
       <c r="N165" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O165" s="26" t="inlineStr">
@@ -19194,17 +19242,17 @@
       </c>
       <c r="C166" s="8" t="inlineStr">
         <is>
-          <t>Krb na tuhá paliva 3.NP</t>
+          <t>Elektrokotel 3.NP</t>
         </is>
       </c>
       <c r="D166" s="20" t="inlineStr">
         <is>
-          <t>733241011</t>
+          <t>733131221</t>
         </is>
       </c>
       <c r="E166" s="8" t="inlineStr">
         <is>
-          <t>Krb na tuhá paliva v 3.NP ~6 kW — dodávka + montáž s napojením na samostatný komín</t>
+          <t>Elektrokotel ~8 kW pro 3.NP samostatný byt — dodávka + montáž + napojení</t>
         </is>
       </c>
       <c r="F166" s="20" t="inlineStr">
@@ -19232,7 +19280,7 @@
       </c>
       <c r="M166" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — krb v 3.NP, ~6 kW odhad</t>
+          <t>TZ ARS dům §4 — 'Nově navržené 3.NP bude vytápěno elektrokotlem'; ~8 kW odhad</t>
         </is>
       </c>
       <c r="N166" s="20" t="inlineStr">
@@ -19259,17 +19307,17 @@
       </c>
       <c r="C167" s="8" t="inlineStr">
         <is>
-          <t>Multisplit TČ — venkovní jednotka</t>
+          <t>Krb na tuhá paliva 3.NP</t>
         </is>
       </c>
       <c r="D167" s="20" t="inlineStr">
         <is>
-          <t>733425211</t>
+          <t>733241011</t>
         </is>
       </c>
       <c r="E167" s="8" t="inlineStr">
         <is>
-          <t>Multisplit tepelné čerpadlo vzduch-vzduch — 1× venkovní jednotka ~10 kW (silent mode hl. tlaku ≤49 dBA)</t>
+          <t>Krb na tuhá paliva v 3.NP ~6 kW — dodávka + montáž s napojením na samostatný komín</t>
         </is>
       </c>
       <c r="F167" s="20" t="inlineStr">
@@ -19284,7 +19332,7 @@
       <c r="I167" s="10" t="n"/>
       <c r="J167" s="8" t="inlineStr">
         <is>
-          <t>specialista_TC_multisplit</t>
+          <t>topenar</t>
         </is>
       </c>
       <c r="K167" s="24" t="n">
@@ -19297,7 +19345,7 @@
       </c>
       <c r="M167" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — multisplit TČ s akustikou hl. tlaku ≤49 dBA, NV 272/2011</t>
+          <t>TZ ARS dům §4 — krb v 3.NP, ~6 kW odhad</t>
         </is>
       </c>
       <c r="N167" s="20" t="inlineStr">
@@ -19324,17 +19372,17 @@
       </c>
       <c r="C168" s="8" t="inlineStr">
         <is>
-          <t>Multisplit TČ — vnitřní jednotky</t>
+          <t>Multisplit TČ — venkovní jednotka</t>
         </is>
       </c>
       <c r="D168" s="20" t="inlineStr">
         <is>
-          <t>733425221</t>
+          <t>733425211</t>
         </is>
       </c>
       <c r="E168" s="8" t="inlineStr">
         <is>
-          <t>Multisplit TČ — 5× vnitřní jednotka v obytných místnostech (1.NP, 2.NP, 3.NP — chlazení + vytápění)</t>
+          <t>Multisplit tepelné čerpadlo vzduch-vzduch — 1× venkovní jednotka ~10 kW (silent mode hl. tlaku ≤49 dBA)</t>
         </is>
       </c>
       <c r="F168" s="20" t="inlineStr">
@@ -19343,7 +19391,7 @@
         </is>
       </c>
       <c r="G168" s="23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H168" s="10" t="n"/>
       <c r="I168" s="10" t="n"/>
@@ -19353,7 +19401,7 @@
         </is>
       </c>
       <c r="K168" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L168" s="20" t="inlineStr">
         <is>
@@ -19362,7 +19410,7 @@
       </c>
       <c r="M168" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — vnitřní jednotky multisplit, vyjasnění #6 odhad 5 ks</t>
+          <t>TZ ARS dům §4 — multisplit TČ s akustikou hl. tlaku ≤49 dBA, NV 272/2011</t>
         </is>
       </c>
       <c r="N168" s="20" t="inlineStr">
@@ -19389,36 +19437,36 @@
       </c>
       <c r="C169" s="8" t="inlineStr">
         <is>
-          <t>Revize komínu</t>
+          <t>Multisplit TČ — vnitřní jednotky</t>
         </is>
       </c>
       <c r="D169" s="20" t="inlineStr">
         <is>
-          <t>734262122</t>
+          <t>733425221</t>
         </is>
       </c>
       <c r="E169" s="8" t="inlineStr">
         <is>
-          <t>Revize stávajícího komínu — kontrola, čištění, vystrojení vložkou nerez DN160 pro kamna + krb 3.NP</t>
+          <t>Multisplit TČ — 5× vnitřní jednotka v obytných místnostech (1.NP, 2.NP, 3.NP — chlazení + vytápění)</t>
         </is>
       </c>
       <c r="F169" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G169" s="23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H169" s="10" t="n"/>
       <c r="I169" s="10" t="n"/>
       <c r="J169" s="8" t="inlineStr">
         <is>
-          <t>kominik</t>
+          <t>specialista_TC_multisplit</t>
         </is>
       </c>
       <c r="K169" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L169" s="20" t="inlineStr">
         <is>
@@ -19427,7 +19475,7 @@
       </c>
       <c r="M169" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — komín stávající, vystrojení vložkou pro kamna + krb</t>
+          <t>TZ ARS dům §4 — vnitřní jednotky multisplit, vyjasnění #6 odhad 5 ks</t>
         </is>
       </c>
       <c r="N169" s="20" t="inlineStr">
@@ -19454,36 +19502,36 @@
       </c>
       <c r="C170" s="8" t="inlineStr">
         <is>
-          <t>Rozvody otopné soustavy</t>
+          <t>Revize komínu</t>
         </is>
       </c>
       <c r="D170" s="20" t="inlineStr">
         <is>
-          <t>733111021</t>
+          <t>734262122</t>
         </is>
       </c>
       <c r="E170" s="8" t="inlineStr">
         <is>
-          <t>Rozvody otopné soustavy Cu/PEX k vnitřním jednotkám TČ + radiátorům pro doplňkové (cca 100 bm odhad)</t>
+          <t>Revize stávajícího komínu — kontrola, čištění, vystrojení vložkou nerez DN160 pro kamna + krb 3.NP</t>
         </is>
       </c>
       <c r="F170" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G170" s="22" t="n">
-        <v>100</v>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G170" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H170" s="10" t="n"/>
       <c r="I170" s="10" t="n"/>
       <c r="J170" s="8" t="inlineStr">
         <is>
-          <t>topenar</t>
+          <t>kominik</t>
         </is>
       </c>
       <c r="K170" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L170" s="20" t="inlineStr">
         <is>
@@ -19492,7 +19540,7 @@
       </c>
       <c r="M170" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — rozvody otopné soustavy</t>
+          <t>TZ ARS dům §4 — komín stávající, vystrojení vložkou pro kamna + krb</t>
         </is>
       </c>
       <c r="N170" s="20" t="inlineStr">
@@ -19514,41 +19562,41 @@
       </c>
       <c r="B171" s="8" t="inlineStr">
         <is>
-          <t>VRN — BOZP</t>
+          <t>PSV-73 Vytápění</t>
         </is>
       </c>
       <c r="C171" s="8" t="inlineStr">
         <is>
-          <t>Koordinace BOZP</t>
+          <t>Rozvody otopné soustavy</t>
         </is>
       </c>
       <c r="D171" s="20" t="inlineStr">
         <is>
-          <t>030091000</t>
+          <t>733111021</t>
         </is>
       </c>
       <c r="E171" s="8" t="inlineStr">
         <is>
-          <t>Koordinátor BOZP na staveništi dle zákona 309/2006 Sb. — pro stavbu s více než jedním zhotovitelem</t>
+          <t>Rozvody otopné soustavy Cu/PEX k vnitřním jednotkám TČ + radiátorům pro doplňkové (cca 100 bm odhad)</t>
         </is>
       </c>
       <c r="F171" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G171" s="23" t="n">
-        <v>1</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G171" s="22" t="n">
+        <v>100</v>
       </c>
       <c r="H171" s="10" t="n"/>
       <c r="I171" s="10" t="n"/>
       <c r="J171" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>topenar</t>
         </is>
       </c>
       <c r="K171" s="24" t="n">
-        <v>0.99</v>
+        <v>0.75</v>
       </c>
       <c r="L171" s="20" t="inlineStr">
         <is>
@@ -19557,12 +19605,12 @@
       </c>
       <c r="M171" s="8" t="inlineStr">
         <is>
-          <t>Zákon 309/2006 Sb. — povinný BOZP koordinátor pro vícezhotovitelskou stavbu</t>
+          <t>TZ ARS dům §4 — rozvody otopné soustavy</t>
         </is>
       </c>
       <c r="N171" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O171" s="26" t="inlineStr">
@@ -19579,22 +19627,22 @@
       </c>
       <c r="B172" s="8" t="inlineStr">
         <is>
-          <t>VRN — Dokumentace</t>
+          <t>VRN — BOZP</t>
         </is>
       </c>
       <c r="C172" s="8" t="inlineStr">
         <is>
-          <t>Předávací protokoly + DSP</t>
+          <t>Koordinace BOZP</t>
         </is>
       </c>
       <c r="D172" s="20" t="inlineStr">
         <is>
-          <t>030151000</t>
+          <t>030091000</t>
         </is>
       </c>
       <c r="E172" s="8" t="inlineStr">
         <is>
-          <t>Předávací protokoly + Dokumentace skutečného provedení (DSP) — sestavení, vázání, dodávka 2× tiskem + elektronická verze</t>
+          <t>Koordinátor BOZP na staveništi dle zákona 309/2006 Sb. — pro stavbu s více než jedním zhotovitelem</t>
         </is>
       </c>
       <c r="F172" s="20" t="inlineStr">
@@ -19622,12 +19670,12 @@
       </c>
       <c r="M172" s="8" t="inlineStr">
         <is>
-          <t>Vyhláška 499/2006 Sb. + ČKAIT — DSP povinná pro kolaudaci</t>
+          <t>Zákon 309/2006 Sb. — povinný BOZP koordinátor pro vícezhotovitelskou stavbu</t>
         </is>
       </c>
       <c r="N172" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#10</t>
         </is>
       </c>
       <c r="O172" s="26" t="inlineStr">
@@ -19644,41 +19692,41 @@
       </c>
       <c r="B173" s="8" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>VRN — Dokumentace</t>
         </is>
       </c>
       <c r="C173" s="8" t="inlineStr">
         <is>
-          <t>Kontejnery suti tříděné</t>
+          <t>Předávací protokoly + DSP</t>
         </is>
       </c>
       <c r="D173" s="20" t="inlineStr">
         <is>
-          <t>997013211</t>
+          <t>030151000</t>
         </is>
       </c>
       <c r="E173" s="8" t="inlineStr">
         <is>
-          <t>Kontejnery na suť tříděnou velkoobjemové (beton/cihly, dřevo, kovy, EPS, sádra, směs) — pronájem + svozy</t>
+          <t>Předávací protokoly + Dokumentace skutečného provedení (DSP) — sestavení, vázání, dodávka 2× tiskem + elektronická verze</t>
         </is>
       </c>
       <c r="F173" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G173" s="23" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H173" s="10" t="n"/>
       <c r="I173" s="10" t="n"/>
       <c r="J173" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K173" s="24" t="n">
-        <v>0.85</v>
+        <v>0.99</v>
       </c>
       <c r="L173" s="20" t="inlineStr">
         <is>
@@ -19687,12 +19735,12 @@
       </c>
       <c r="M173" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10.e: beton/cihly 46 t + dřevo 9 t + kovy 0.1 + EPS 0.1 + sádra 0.2 + směs 1.0</t>
+          <t>Vyhláška 499/2006 Sb. + ČKAIT — DSP povinná pro kolaudaci</t>
         </is>
       </c>
       <c r="N173" s="20" t="inlineStr">
         <is>
-          <t>#9, #10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O173" s="26" t="inlineStr">
@@ -19714,36 +19762,36 @@
       </c>
       <c r="C174" s="8" t="inlineStr">
         <is>
-          <t>Doprava materiálu</t>
+          <t>Kontejnery suti tříděné</t>
         </is>
       </c>
       <c r="D174" s="20" t="inlineStr">
         <is>
-          <t>031031000</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="E174" s="8" t="inlineStr">
         <is>
-          <t>Doprava materiálu na stavbu (centrální koordinace) — paušál ~2-3 % z PN materiál</t>
+          <t>Kontejnery na suť tříděnou velkoobjemové (beton/cihly, dřevo, kovy, EPS, sádra, směs) — pronájem + svozy</t>
         </is>
       </c>
       <c r="F174" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G174" s="23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H174" s="10" t="n"/>
       <c r="I174" s="10" t="n"/>
       <c r="J174" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="K174" s="24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L174" s="20" t="inlineStr">
         <is>
@@ -19752,12 +19800,12 @@
       </c>
       <c r="M174" s="8" t="inlineStr">
         <is>
-          <t>B4_productivity — standard doprava RD městská zástavba</t>
+          <t>TZ B m.10.e: beton/cihly 46 t + dřevo 9 t + kovy 0.1 + EPS 0.1 + sádra 0.2 + směs 1.0</t>
         </is>
       </c>
       <c r="N174" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>#9, #10</t>
         </is>
       </c>
       <c r="O174" s="26" t="inlineStr">
@@ -19779,36 +19827,36 @@
       </c>
       <c r="C175" s="8" t="inlineStr">
         <is>
-          <t>Likvidace odpadů 56.9 t</t>
+          <t>Doprava materiálu</t>
         </is>
       </c>
       <c r="D175" s="20" t="inlineStr">
         <is>
-          <t>997013211</t>
+          <t>031031000</t>
         </is>
       </c>
       <c r="E175" s="8" t="inlineStr">
         <is>
-          <t>Likvidace stavební suti dle vyhl. 8/2021 Sb. — skládkovné + recyklace + třídění (56.9 t celkem per TZ B m.10.e)</t>
+          <t>Doprava materiálu na stavbu (centrální koordinace) — paušál ~2-3 % z PN materiál</t>
         </is>
       </c>
       <c r="F175" s="20" t="inlineStr">
         <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="G175" s="22" t="n">
-        <v>56.9</v>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="G175" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H175" s="10" t="n"/>
       <c r="I175" s="10" t="n"/>
       <c r="J175" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K175" s="24" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="L175" s="20" t="inlineStr">
         <is>
@@ -19817,12 +19865,12 @@
       </c>
       <c r="M175" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10.e bilance odpadů celkem dům</t>
+          <t>B4_productivity — standard doprava RD městská zástavba</t>
         </is>
       </c>
       <c r="N175" s="20" t="inlineStr">
         <is>
-          <t>#9, #10</t>
+          <t>#10</t>
         </is>
       </c>
       <c r="O175" s="26" t="inlineStr">
@@ -19839,41 +19887,41 @@
       </c>
       <c r="B176" s="8" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="C176" s="8" t="inlineStr">
         <is>
-          <t>Geodetické zaměření před + po realizaci</t>
+          <t>Likvidace odpadů 56.9 t</t>
         </is>
       </c>
       <c r="D176" s="20" t="inlineStr">
         <is>
-          <t>030141000</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="E176" s="8" t="inlineStr">
         <is>
-          <t>Geodetické zaměření před realizací (verifikace polohopis + výškopis) + po dokončení (zaměření skutečného provedení pro kolaudaci)</t>
+          <t>Likvidace stavební suti dle vyhl. 8/2021 Sb. — skládkovné + recyklace + třídění (56.9 t celkem per TZ B m.10.e)</t>
         </is>
       </c>
       <c r="F176" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G176" s="23" t="n">
-        <v>2</v>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G176" s="22" t="n">
+        <v>56.9</v>
       </c>
       <c r="H176" s="10" t="n"/>
       <c r="I176" s="10" t="n"/>
       <c r="J176" s="8" t="inlineStr">
         <is>
-          <t>geodet</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="K176" s="24" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="L176" s="20" t="inlineStr">
         <is>
@@ -19882,12 +19930,12 @@
       </c>
       <c r="M176" s="8" t="inlineStr">
         <is>
-          <t>Standard — geodet před+po pro každou stavbu</t>
+          <t>TZ B m.10.e bilance odpadů celkem dům</t>
         </is>
       </c>
       <c r="N176" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#9, #10</t>
         </is>
       </c>
       <c r="O176" s="26" t="inlineStr">
@@ -19904,37 +19952,37 @@
       </c>
       <c r="B177" s="8" t="inlineStr">
         <is>
-          <t>VRN — Kolaudace</t>
+          <t>VRN — Geodet</t>
         </is>
       </c>
       <c r="C177" s="8" t="inlineStr">
         <is>
-          <t>Kolaudační řízení</t>
+          <t>Geodetické zaměření před + po realizaci</t>
         </is>
       </c>
       <c r="D177" s="20" t="inlineStr">
         <is>
-          <t>030171000</t>
+          <t>030141000</t>
         </is>
       </c>
       <c r="E177" s="8" t="inlineStr">
         <is>
-          <t>Kolaudační řízení — paušál (správní poplatky + součinnost) dle zákona 183/2006 Sb.</t>
+          <t>Geodetické zaměření před realizací (verifikace polohopis + výškopis) + po dokončení (zaměření skutečného provedení pro kolaudaci)</t>
         </is>
       </c>
       <c r="F177" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G177" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H177" s="10" t="n"/>
       <c r="I177" s="10" t="n"/>
       <c r="J177" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>geodet</t>
         </is>
       </c>
       <c r="K177" s="24" t="n">
@@ -19947,7 +19995,7 @@
       </c>
       <c r="M177" s="8" t="inlineStr">
         <is>
-          <t>Zákon 183/2006 Sb. + vyhl. 499/2006 Sb.</t>
+          <t>Standard — geodet před+po pro každou stavbu</t>
         </is>
       </c>
       <c r="N177" s="20" t="inlineStr">
@@ -19969,31 +20017,31 @@
       </c>
       <c r="B178" s="8" t="inlineStr">
         <is>
-          <t>VRN — Lešení</t>
+          <t>VRN — Kolaudace</t>
         </is>
       </c>
       <c r="C178" s="8" t="inlineStr">
         <is>
-          <t>Fasádní lešení (ETICS + krov + klempířina)</t>
+          <t>Kolaudační řízení</t>
         </is>
       </c>
       <c r="D178" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>030171000</t>
         </is>
       </c>
       <c r="E178" s="8" t="inlineStr">
         <is>
-          <t>Fasádní lešení trubkové/rámové vč. montáže + pronájmu + demontáže — pro provedení ETICS fasády, krovu a klempířiny po obvodu domu (výška 13 m)</t>
+          <t>Kolaudační řízení — paušál (správní poplatky + součinnost) dle zákona 183/2006 Sb.</t>
         </is>
       </c>
       <c r="F178" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G178" s="22" t="n">
-        <v>503.1</v>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="G178" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H178" s="10" t="n"/>
       <c r="I178" s="10" t="n"/>
@@ -20003,7 +20051,7 @@
         </is>
       </c>
       <c r="K178" s="24" t="n">
-        <v>0.8</v>
+        <v>0.99</v>
       </c>
       <c r="L178" s="20" t="inlineStr">
         <is>
@@ -20012,7 +20060,7 @@
       </c>
       <c r="M178" s="8" t="inlineStr">
         <is>
-          <t>anchor checklist PM02 — technical necessity (ETICS 276.7 m² nelze provést bez lešení, 941xxx URS família) + DXF obvod 38.7 m + řez výška 13 m</t>
+          <t>Zákon 183/2006 Sb. + vyhl. 499/2006 Sb.</t>
         </is>
       </c>
       <c r="N178" s="20" t="inlineStr">
@@ -20026,11 +20074,7 @@
         </is>
       </c>
       <c r="P178" s="41" t="n"/>
-      <c r="Q178" s="41" t="inlineStr">
-        <is>
-          <t>ANCHOR_CHECKLIST_PM02</t>
-        </is>
-      </c>
+      <c r="Q178" s="41" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="20" t="n">
@@ -20038,31 +20082,31 @@
       </c>
       <c r="B179" s="8" t="inlineStr">
         <is>
-          <t>VRN — Pojištění + zábory</t>
+          <t>VRN — Lešení</t>
         </is>
       </c>
       <c r="C179" s="8" t="inlineStr">
         <is>
-          <t>Pojištění stavby (montážní + odpovědnostní)</t>
+          <t>Fasádní lešení (ETICS + krov + klempířina)</t>
         </is>
       </c>
       <c r="D179" s="20" t="inlineStr">
         <is>
-          <t>030081000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E179" s="8" t="inlineStr">
         <is>
-          <t>Montážní pojištění stavby (CAR) + pojištění odpovědnosti za škodu (zhotovitel) — paušál cca 0.3-0.5 % z PN</t>
+          <t>Fasádní lešení trubkové/rámové vč. montáže + pronájmu + demontáže — pro provedení ETICS fasády, krovu a klempířiny po obvodu domu (výška 13 m)</t>
         </is>
       </c>
       <c r="F179" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
-        </is>
-      </c>
-      <c r="G179" s="23" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G179" s="22" t="n">
+        <v>503.1</v>
       </c>
       <c r="H179" s="10" t="n"/>
       <c r="I179" s="10" t="n"/>
@@ -20072,7 +20116,7 @@
         </is>
       </c>
       <c r="K179" s="24" t="n">
-        <v>0.99</v>
+        <v>0.8</v>
       </c>
       <c r="L179" s="20" t="inlineStr">
         <is>
@@ -20081,12 +20125,12 @@
       </c>
       <c r="M179" s="8" t="inlineStr">
         <is>
-          <t>Standard zhotovitel — pojistná povinnost</t>
+          <t>anchor checklist PM02 — technical necessity (ETICS 276.7 m² nelze provést bez lešení, 941xxx URS família) + DXF obvod 38.7 m + řez výška 13 m</t>
         </is>
       </c>
       <c r="N179" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O179" s="26" t="inlineStr">
@@ -20095,7 +20139,11 @@
         </is>
       </c>
       <c r="P179" s="41" t="n"/>
-      <c r="Q179" s="41" t="n"/>
+      <c r="Q179" s="41" t="inlineStr">
+        <is>
+          <t>ANCHOR_CHECKLIST_PM02</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="20" t="n">
@@ -20108,22 +20156,22 @@
       </c>
       <c r="C180" s="8" t="inlineStr">
         <is>
-          <t>Krátkodobé zábory ul. Fibichova</t>
+          <t>Pojištění stavby (montážní + odpovědnostní)</t>
         </is>
       </c>
       <c r="D180" s="20" t="inlineStr">
         <is>
-          <t>030083000</t>
+          <t>030081000</t>
         </is>
       </c>
       <c r="E180" s="8" t="inlineStr">
         <is>
-          <t>Krátkodobé zábory ulice Fibichova pro materiál a kontejnery (povolení MU Jáchymov + DI) — odhad 30 dnů kumulativně</t>
+          <t>Montážní pojištění stavby (CAR) + pojištění odpovědnosti za škodu (zhotovitel) — paušál cca 0.3-0.5 % z PN</t>
         </is>
       </c>
       <c r="F180" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>paušál</t>
         </is>
       </c>
       <c r="G180" s="23" t="n">
@@ -20137,7 +20185,7 @@
         </is>
       </c>
       <c r="K180" s="24" t="n">
-        <v>0.75</v>
+        <v>0.99</v>
       </c>
       <c r="L180" s="20" t="inlineStr">
         <is>
@@ -20146,7 +20194,7 @@
       </c>
       <c r="M180" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10 + situace — řadovka ul. Fibichova</t>
+          <t>Standard zhotovitel — pojistná povinnost</t>
         </is>
       </c>
       <c r="N180" s="20" t="inlineStr">
@@ -20168,22 +20216,22 @@
       </c>
       <c r="B181" s="8" t="inlineStr">
         <is>
-          <t>VRN — Průzkumy</t>
+          <t>VRN — Pojištění + zábory</t>
         </is>
       </c>
       <c r="C181" s="8" t="inlineStr">
         <is>
-          <t>Mykologický průzkum dřeva při bourání</t>
+          <t>Krátkodobé zábory ul. Fibichova</t>
         </is>
       </c>
       <c r="D181" s="20" t="inlineStr">
         <is>
-          <t>030131000</t>
+          <t>030083000</t>
         </is>
       </c>
       <c r="E181" s="8" t="inlineStr">
         <is>
-          <t>Mykologický průzkum + průzkum výskytu dřevokazného hmyzu stávajícího krovu a dřevěných trámů zhlaví — pro vyloučení narušení dřevěných konstrukcí; provádí autorizovaný mykolog při bourání</t>
+          <t>Krátkodobé zábory ulice Fibichova pro materiál a kontejnery (povolení MU Jáchymov + DI) — odhad 30 dnů kumulativně</t>
         </is>
       </c>
       <c r="F181" s="20" t="inlineStr">
@@ -20198,11 +20246,11 @@
       <c r="I181" s="10" t="n"/>
       <c r="J181" s="8" t="inlineStr">
         <is>
-          <t>mykolog</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K181" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L181" s="20" t="inlineStr">
         <is>
@@ -20211,7 +20259,7 @@
       </c>
       <c r="M181" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2.3 + POZN.2.05 z půdorysů návrh + řez A-A návrh (explicit dřevokazný hmyz scope per drawing wording)</t>
+          <t>TZ B m.10 + situace — řadovka ul. Fibichova</t>
         </is>
       </c>
       <c r="N181" s="20" t="inlineStr">
@@ -20225,11 +20273,7 @@
         </is>
       </c>
       <c r="P181" s="41" t="n"/>
-      <c r="Q181" s="41" t="inlineStr">
-        <is>
-          <t>PER_DRAWING_ENRICHMENT_POZN_2_05</t>
-        </is>
-      </c>
+      <c r="Q181" s="41" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="20" t="n">
@@ -20242,17 +20286,17 @@
       </c>
       <c r="C182" s="8" t="inlineStr">
         <is>
-          <t>Azbestový průzkum podrobný před demolicí</t>
+          <t>Mykologický průzkum dřeva při bourání</t>
         </is>
       </c>
       <c r="D182" s="20" t="inlineStr">
         <is>
-          <t>030133000</t>
+          <t>030131000</t>
         </is>
       </c>
       <c r="E182" s="8" t="inlineStr">
         <is>
-          <t>Azbestový průzkum podrobný před demolicí — laboratorní vzorky a posudek (B kap. m.7.a předběžně negativní, ale podrobný před bouráním povinný)</t>
+          <t>Mykologický průzkum + průzkum výskytu dřevokazného hmyzu stávajícího krovu a dřevěných trámů zhlaví — pro vyloučení narušení dřevěných konstrukcí; provádí autorizovaný mykolog při bourání</t>
         </is>
       </c>
       <c r="F182" s="20" t="inlineStr">
@@ -20267,7 +20311,7 @@
       <c r="I182" s="10" t="n"/>
       <c r="J182" s="8" t="inlineStr">
         <is>
-          <t>azbestovy_specialista</t>
+          <t>mykolog</t>
         </is>
       </c>
       <c r="K182" s="24" t="n">
@@ -20280,7 +20324,7 @@
       </c>
       <c r="M182" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.7.a + ARS §3.2 — azbestový průzkum povinný před demolicí</t>
+          <t>TZ ARS dům §3.2.3 + POZN.2.05 z půdorysů návrh + řez A-A návrh (explicit dřevokazný hmyz scope per drawing wording)</t>
         </is>
       </c>
       <c r="N182" s="20" t="inlineStr">
@@ -20294,7 +20338,11 @@
         </is>
       </c>
       <c r="P182" s="41" t="n"/>
-      <c r="Q182" s="41" t="n"/>
+      <c r="Q182" s="41" t="inlineStr">
+        <is>
+          <t>PER_DRAWING_ENRICHMENT_POZN_2_05</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="20" t="n">
@@ -20302,41 +20350,41 @@
       </c>
       <c r="B183" s="8" t="inlineStr">
         <is>
-          <t>VRN — Přesun hmot</t>
+          <t>VRN — Průzkumy</t>
         </is>
       </c>
       <c r="C183" s="8" t="inlineStr">
         <is>
-          <t>Přesun hmot pro budovu</t>
+          <t>Azbestový průzkum podrobný před demolicí</t>
         </is>
       </c>
       <c r="D183" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>030133000</t>
         </is>
       </c>
       <c r="E183" s="8" t="inlineStr">
         <is>
-          <t>Přesun hmot pro budovu — vnitrostaveništní vertikální + horizontální doprava materiálu a hmot (rekonstrukce vícepodlažní RD + nástavba 3.NP)</t>
+          <t>Azbestový průzkum podrobný před demolicí — laboratorní vzorky a posudek (B kap. m.7.a předběžně negativní, ale podrobný před bouráním povinný)</t>
         </is>
       </c>
       <c r="F183" s="20" t="inlineStr">
         <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="G183" s="22" t="n">
-        <v>0</v>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G183" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H183" s="10" t="n"/>
       <c r="I183" s="10" t="n"/>
       <c r="J183" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>azbestovy_specialista</t>
         </is>
       </c>
       <c r="K183" s="24" t="n">
-        <v>0.6</v>
+        <v>0.85</v>
       </c>
       <c r="L183" s="20" t="inlineStr">
         <is>
@@ -20345,12 +20393,12 @@
       </c>
       <c r="M183" s="8" t="inlineStr">
         <is>
-          <t>anchor checklist PM01 — technical necessity (povinná položka každého rozpočtu, 998xxx URS família)</t>
+          <t>TZ B m.7.a + ARS §3.2 — azbestový průzkum povinný před demolicí</t>
         </is>
       </c>
       <c r="N183" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#10</t>
         </is>
       </c>
       <c r="O183" s="26" t="inlineStr">
@@ -20359,11 +20407,7 @@
         </is>
       </c>
       <c r="P183" s="41" t="n"/>
-      <c r="Q183" s="41" t="inlineStr">
-        <is>
-          <t>ANCHOR_CHECKLIST_PM01</t>
-        </is>
-      </c>
+      <c r="Q183" s="41" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="20" t="n">
@@ -20371,41 +20415,41 @@
       </c>
       <c r="B184" s="8" t="inlineStr">
         <is>
-          <t>VRN — Revize</t>
+          <t>VRN — Přesun hmot</t>
         </is>
       </c>
       <c r="C184" s="8" t="inlineStr">
         <is>
-          <t>Revize hydrantu vnějšího</t>
+          <t>Přesun hmot pro budovu</t>
         </is>
       </c>
       <c r="D184" s="20" t="inlineStr">
         <is>
-          <t>030161000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E184" s="8" t="inlineStr">
         <is>
-          <t>Revize vnějšího hydrantu pro požární zabezpečení (DN min. 80, vzdálenost 100 m dle TZ PBŘ) — periodická kontrola</t>
+          <t>Přesun hmot pro budovu — vnitrostaveništní vertikální + horizontální doprava materiálu a hmot (rekonstrukce vícepodlažní RD + nástavba 3.NP)</t>
         </is>
       </c>
       <c r="F184" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G184" s="23" t="n">
-        <v>1</v>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G184" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H184" s="10" t="n"/>
       <c r="I184" s="10" t="n"/>
       <c r="J184" s="8" t="inlineStr">
         <is>
-          <t>revize_specialista</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K184" s="24" t="n">
-        <v>0.85</v>
+        <v>0.6</v>
       </c>
       <c r="L184" s="20" t="inlineStr">
         <is>
@@ -20414,7 +20458,7 @@
       </c>
       <c r="M184" s="8" t="inlineStr">
         <is>
-          <t>TZ PBŘ dům — vnější odběrné místo požární vody, revize před kolaudací</t>
+          <t>anchor checklist PM01 — technical necessity (povinná položka každého rozpočtu, 998xxx URS família)</t>
         </is>
       </c>
       <c r="N184" s="20" t="inlineStr">
@@ -20428,7 +20472,11 @@
         </is>
       </c>
       <c r="P184" s="41" t="n"/>
-      <c r="Q184" s="41" t="n"/>
+      <c r="Q184" s="41" t="inlineStr">
+        <is>
+          <t>ANCHOR_CHECKLIST_PM01</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="20" t="n">
@@ -20436,41 +20484,41 @@
       </c>
       <c r="B185" s="8" t="inlineStr">
         <is>
-          <t>VRN — Zařízení staveniště</t>
+          <t>VRN — Revize</t>
         </is>
       </c>
       <c r="C185" s="8" t="inlineStr">
         <is>
-          <t>Buňky kancelář + sociální</t>
+          <t>Revize hydrantu vnějšího</t>
         </is>
       </c>
       <c r="D185" s="20" t="inlineStr">
         <is>
-          <t>030011000</t>
+          <t>030161000</t>
         </is>
       </c>
       <c r="E185" s="8" t="inlineStr">
         <is>
-          <t>Zařízení staveniště — buňka kancelář + sociální buňka (WC + šatna), pronájem ~8 měsíců</t>
+          <t>Revize vnějšího hydrantu pro požární zabezpečení (DN min. 80, vzdálenost 100 m dle TZ PBŘ) — periodická kontrola</t>
         </is>
       </c>
       <c r="F185" s="20" t="inlineStr">
         <is>
-          <t>kpl-měs</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G185" s="23" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H185" s="10" t="n"/>
       <c r="I185" s="10" t="n"/>
       <c r="J185" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>revize_specialista</t>
         </is>
       </c>
       <c r="K185" s="24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L185" s="20" t="inlineStr">
         <is>
@@ -20479,12 +20527,12 @@
       </c>
       <c r="M185" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.1.m realizace 2026-2027 + standard staveniště RD městská zástavba</t>
+          <t>TZ PBŘ dům — vnější odběrné místo požární vody, revize před kolaudací</t>
         </is>
       </c>
       <c r="N185" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O185" s="26" t="inlineStr">
@@ -20506,22 +20554,22 @@
       </c>
       <c r="C186" s="8" t="inlineStr">
         <is>
-          <t>Mobilní WC</t>
+          <t>Buňky kancelář + sociální</t>
         </is>
       </c>
       <c r="D186" s="20" t="inlineStr">
         <is>
-          <t>030013000</t>
+          <t>030011000</t>
         </is>
       </c>
       <c r="E186" s="8" t="inlineStr">
         <is>
-          <t>Mobilní chemické WC TOI TOI pro pracovníky — pronájem ~8 měsíců</t>
+          <t>Zařízení staveniště — buňka kancelář + sociální buňka (WC + šatna), pronájem ~8 měsíců</t>
         </is>
       </c>
       <c r="F186" s="20" t="inlineStr">
         <is>
-          <t>ks-měs</t>
+          <t>kpl-měs</t>
         </is>
       </c>
       <c r="G186" s="23" t="n">
@@ -20544,7 +20592,7 @@
       </c>
       <c r="M186" s="8" t="inlineStr">
         <is>
-          <t>BOZP — mobilní WC povinné pro stavbu RD</t>
+          <t>TZ B m.1.m realizace 2026-2027 + standard staveniště RD městská zástavba</t>
         </is>
       </c>
       <c r="N186" s="20" t="inlineStr">
@@ -20571,26 +20619,26 @@
       </c>
       <c r="C187" s="8" t="inlineStr">
         <is>
-          <t>El. odběr + vodovodní odběr stavby</t>
+          <t>Mobilní WC</t>
         </is>
       </c>
       <c r="D187" s="20" t="inlineStr">
         <is>
-          <t>031011000</t>
+          <t>030013000</t>
         </is>
       </c>
       <c r="E187" s="8" t="inlineStr">
         <is>
-          <t>El. odběr stavby (zřízení staveništního rozvaděče + měřič) + vodovodní odběr (zřízení staveništní přípojky + vodoměr) — ~8 měsíců</t>
+          <t>Mobilní chemické WC TOI TOI pro pracovníky — pronájem ~8 měsíců</t>
         </is>
       </c>
       <c r="F187" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks-měs</t>
         </is>
       </c>
       <c r="G187" s="23" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H187" s="10" t="n"/>
       <c r="I187" s="10" t="n"/>
@@ -20609,7 +20657,7 @@
       </c>
       <c r="M187" s="8" t="inlineStr">
         <is>
-          <t>Standard staveniště — el. + voda zřízení a odběr po dobu stavby</t>
+          <t>BOZP — mobilní WC povinné pro stavbu RD</t>
         </is>
       </c>
       <c r="N187" s="20" t="inlineStr">
@@ -20636,17 +20684,17 @@
       </c>
       <c r="C188" s="8" t="inlineStr">
         <is>
-          <t>Voda staveniště</t>
+          <t>El. odběr + vodovodní odběr stavby</t>
         </is>
       </c>
       <c r="D188" s="20" t="inlineStr">
         <is>
-          <t>012103101</t>
+          <t>031011000</t>
         </is>
       </c>
       <c r="E188" s="8" t="inlineStr">
         <is>
-          <t>Voda staveniště — napojení na stávající vodovodní přípojku, dočasné rozvody na staveništi (mísení malt, čištění, soc. zázemí), paušál pro dobu výstavby ~18 měs.</t>
+          <t>El. odběr stavby (zřízení staveništního rozvaděče + měřič) + vodovodní odběr (zřízení staveništní přípojky + vodoměr) — ~8 měsíců</t>
         </is>
       </c>
       <c r="F188" s="20" t="inlineStr">
@@ -20665,38 +20713,103 @@
         </is>
       </c>
       <c r="K188" s="24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L188" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M188" s="8" t="inlineStr">
+        <is>
+          <t>Standard staveniště — el. + voda zřízení a odběr po dobu stavby</t>
+        </is>
+      </c>
+      <c r="N188" s="20" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
+      <c r="O188" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P188" s="41" t="n"/>
+      <c r="Q188" s="41" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="20" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Zařízení staveniště</t>
+        </is>
+      </c>
+      <c r="C189" s="8" t="inlineStr">
+        <is>
+          <t>Voda staveniště</t>
+        </is>
+      </c>
+      <c r="D189" s="20" t="inlineStr">
+        <is>
+          <t>012103101</t>
+        </is>
+      </c>
+      <c r="E189" s="8" t="inlineStr">
+        <is>
+          <t>Voda staveniště — napojení na stávající vodovodní přípojku, dočasné rozvody na staveništi (mísení malt, čištění, soc. zázemí), paušál pro dobu výstavby ~18 měs.</t>
+        </is>
+      </c>
+      <c r="F189" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G189" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H189" s="10" t="n"/>
+      <c r="I189" s="10" t="n"/>
+      <c r="J189" s="8" t="inlineStr">
+        <is>
+          <t>VRN_management</t>
+        </is>
+      </c>
+      <c r="K189" s="24" t="n">
         <v>0.9</v>
       </c>
-      <c r="L188" s="20" t="inlineStr">
+      <c r="L189" s="20" t="inlineStr">
         <is>
           <t>needs_production_lookup</t>
         </is>
       </c>
-      <c r="M188" s="8" t="inlineStr">
+      <c r="M189" s="8" t="inlineStr">
         <is>
           <t>TZ B Souhrnná m.5 — 'Stávající vodovodní přípojka z veřejného vodovodu'</t>
         </is>
       </c>
-      <c r="N188" s="20" t="inlineStr">
+      <c r="N189" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O188" s="26" t="inlineStr">
+      <c r="O189" s="26" t="inlineStr">
         <is>
           <t>ANO</t>
         </is>
       </c>
-      <c r="P188" s="41" t="n"/>
-      <c r="Q188" s="41" t="inlineStr">
+      <c r="P189" s="41" t="n"/>
+      <c r="Q189" s="41" t="inlineStr">
         <is>
           <t>GAP_003</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O188"/>
-  <conditionalFormatting sqref="K2:K188">
+  <autoFilter ref="A1:O189"/>
+  <conditionalFormatting sqref="K2:K189">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0" stopIfTrue="1">
       <formula>0.70</formula>
     </cfRule>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01_v2.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01_v2.xlsx
@@ -26609,7 +26609,7 @@
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>Podlahový EPS 150 λ=0.035 tl. 120 mm — pod betonový potěr 1.NP a 3.NP…</t>
+          <t>Hydroizolace pod ŽB deskou 1.NP — modifikované asfaltové pásy SBS 2× (zároveň pr…</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01_v2.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01_v2.xlsx
@@ -19,11 +19,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross_verification" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Var_A_Agregovany_Dum'!$A$1:$G$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Var_A_Agregovany_Dum'!$A$1:$G$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Var_A_Agregovany_Sklad'!$A$1:$G$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$131</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Var_B_Polozkovy_Dum'!$A$1:$O$201</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Var_B_Polozkovy_Sklad'!$A$1:$O$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$133</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Var_B_Polozkovy_Dum'!$A$1:$O$204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Var_B_Polozkovy_Sklad'!$A$1:$O$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Var_F_URS_Verification_Trail'!$A$1:$H$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -991,11 +991,11 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>GROUP BY kapitola per objekt (24 souhrnných řádků). Pro orientační cenovku.</t>
+          <t>GROUP BY kapitola per objekt (25 souhrnných řádků). Pro orientační cenovku.</t>
         </is>
       </c>
       <c r="C23" s="9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D23" s="10" t="n"/>
       <c r="E23" s="10" t="n"/>
@@ -1009,11 +1009,11 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>HSV položkově (118 ks) + PSV/TZB/VRN agregovaně (12 skupin) = 130 řádků.</t>
+          <t>HSV položkově (119 ks) + PSV/TZB/VRN agregovaně (13 skupin) = 132 řádků.</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D24" s="10" t="n"/>
       <c r="E24" s="10" t="n"/>
@@ -1027,11 +1027,11 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Plný detail (200 dum + 28 sklad = 228 položek). Cílový rozsah pro produkční pricing.</t>
+          <t>Plný detail (203 dum + 31 sklad = 234 položek). Cílový rozsah pro produkční pricing.</t>
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="D25" s="10" t="n"/>
       <c r="E25" s="10" t="n"/>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>228 (200 dum + 28 sklad)</t>
+          <t>234 (203 dum + 31 sklad)</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>HSV 118 | PSV 54 | TZB 34 | VRN 22</t>
+          <t>HSV 119 | M 2 | PSV 56 | TZB 34 | VRN 23</t>
         </is>
       </c>
     </row>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>0.99: 17 | 0.95: 32 | 0.90: 35 | 0.85: 41 | 0.80: 19 | 0.75: 72 | 0.70: 2 | 0.60: 2 | 0.50: 4 | 0.00: 4</t>
+          <t>0.99: 17 | 0.95: 32 | 0.90: 35 | 0.85: 41 | 0.80: 21 | 0.75: 72 | 0.70: 4 | 0.60: 3 | 0.50: 4 | 0.00: 5</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>8 WebSearch verified (3.5 %) ✓ | 5 wrong leaf flagged (2.2 %) ⚠ | 150 needs_production_lookup (65.8 %)</t>
+          <t>8 WebSearch verified (3.4 %) ✓ | 5 wrong leaf flagged (2.1 %) ⚠ | 156 needs_production_lookup (66.7 %)</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>28 items (viz Otazky_pro_Karla docx)</t>
+          <t>29 items (viz Otazky_pro_Karla docx)</t>
         </is>
       </c>
     </row>
@@ -1186,8 +1186,8 @@
       <c r="A43" s="12" t="inlineStr">
         <is>
           <t>Rozpočet generován STAVAGENT pipelinem z DSP dokumentace s DPS-grade DXF metadaty.
-228 položek celkem (200 dum + 28 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
-Confidence distribution: 17×0.99 · 32×0.95 · 35×0.90 · 41×0.85 · 19×0.80 · 72×0.75 · 2×0.70 · 2×0.60 · 4×0.50 · 4×0.00.
+234 položek celkem (203 dum + 31 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
+Confidence distribution: 17×0.99 · 32×0.95 · 35×0.90 · 41×0.85 · 21×0.80 · 72×0.75 · 4×0.70 · 3×0.60 · 4×0.50 · 5×0.00.
 25 položek vzniklo per-room expansion ze 9 aggregate parents (každá expanded položka tagged _expansion_origin).
 10 položek recalculated s exact external perimeter 38.70 m (DXF km_R_návrh_tlustá 2 closed polygon) vs prior fallback 41.0 m.
 Skladby vrstev (Sheet 8 Var_E) pochází POUZE z TZ explicit text + DXF cross-validation HATCH patterns. ŽÁDNÉ generic 'standardní RD' assumption — kde TZ silent, explicit fallback flag s ČSN default.
@@ -2416,7 +2416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2651,11 +2651,11 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; Zásuvky a vypínače; … (+3 dalších)</t>
+          <t>Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; Zásuvky a vypínače; … (+4 dalších)</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" s="10" t="n"/>
       <c r="F9" s="10" t="n"/>
@@ -2671,16 +2671,16 @@
       </c>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t>PSV-71 — Izolace HI + TI</t>
+          <t>M-24</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; Podlahový EPS 150; … (+1 dalších)</t>
+          <t>Lokální odtah digestoří kuchyní</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E10" s="10" t="n"/>
       <c r="F10" s="10" t="n"/>
@@ -2696,16 +2696,16 @@
       </c>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
+          <t>PSV-71 — Izolace HI + TI</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; Sanitární keramika koupelna 1.05 (1.NP); … (+15 dalších)</t>
+          <t>HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; Podlahový EPS 150; … (+1 dalších)</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E11" s="10" t="n"/>
       <c r="F11" s="10" t="n"/>
@@ -2721,16 +2721,16 @@
       </c>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t>PSV-73 — Vytápění + komín</t>
+          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; Krb na tuhá paliva 3.NP; … (+4 dalších)</t>
+          <t>Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; Sanitární keramika koupelna 1.05 (1.NP); … (+15 dalších)</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E12" s="10" t="n"/>
       <c r="F12" s="10" t="n"/>
@@ -2746,16 +2746,16 @@
       </c>
       <c r="B13" s="21" t="inlineStr">
         <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+          <t>PSV-73 — Vytápění + komín</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); Plastové okno trojsklo — 'okno 3.NP' (ulice); … (+18 dalších)</t>
+          <t>Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; Krb na tuhá paliva 3.NP; … (+4 dalších)</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E13" s="10" t="n"/>
       <c r="F13" s="10" t="n"/>
@@ -2771,16 +2771,16 @@
       </c>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t>PSV-77 — Podlahy</t>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; Nášlap biodeska 3.NP spací patro; … (+3 dalších)</t>
+          <t>Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); Plastové okno trojsklo — 'okno 3.NP' (ulice); … (+18 dalších)</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E14" s="10" t="n"/>
       <c r="F14" s="10" t="n"/>
@@ -2796,16 +2796,16 @@
       </c>
       <c r="B15" s="21" t="inlineStr">
         <is>
-          <t>PSV-78 — Povrchové úpravy</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; Omítka jádrová + štuk 3.NP; … (+12 dalších)</t>
+          <t>Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; Nášlap biodeska 3.NP spací patro; … (+3 dalších)</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E15" s="10" t="n"/>
       <c r="F15" s="10" t="n"/>
@@ -2821,16 +2821,16 @@
       </c>
       <c r="B16" s="21" t="inlineStr">
         <is>
-          <t>PSV-95 — Detekce požární</t>
+          <t>PSV-78 — Povrchové úpravy</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Autonomní hlásič kouře; Přenosný hasicí přístroj 34A</t>
+          <t>Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; Omítka jádrová + štuk 3.NP; … (+12 dalších)</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E16" s="10" t="n"/>
       <c r="F16" s="10" t="n"/>
@@ -2846,16 +2846,16 @@
       </c>
       <c r="B17" s="21" t="inlineStr">
         <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
+          <t>PSV-95 — Detekce požární</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; Kontejnery suti tříděné; … (+14 dalších)</t>
+          <t>Autonomní hlásič kouře; Přenosný hasicí přístroj 34A; Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="E17" s="10" t="n"/>
       <c r="F17" s="10" t="n"/>
@@ -2865,8 +2865,33 @@
         </is>
       </c>
     </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="20" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; Kontejnery suti tříděné; … (+14 dalších)</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="E18" s="10" t="n"/>
+      <c r="F18" s="10" t="n"/>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>agregát — detail viz List B</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G17"/>
+  <autoFilter ref="A1:G18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3037,11 +3062,11 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Sklad mezipodesta schodiště prefa</t>
+          <t>Sklad mezipodesta schodiště prefa; Vjezd Dvořákova — napojení na komunikaci</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" s="10" t="n"/>
       <c r="F6" s="10" t="n"/>
@@ -3062,11 +3087,11 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Bezpečnostní dveře RC3 sklad</t>
+          <t>Bezpečnostní dveře RC3 sklad; Vjezdová brána</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="10" t="n"/>
       <c r="F7" s="10" t="n"/>
@@ -3112,11 +3137,11 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; Podíl na obecných VRN dům</t>
+          <t>Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; Podíl na obecných VRN dům; … (+1 dalších)</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E9" s="10" t="n"/>
       <c r="F9" s="10" t="n"/>
@@ -3138,7 +3163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J131"/>
+  <dimension ref="A1:J133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7926,34 +7951,32 @@
           <t>260217_sklad</t>
         </is>
       </c>
-      <c r="C120" s="21" t="inlineStr">
-        <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+      <c r="C120" s="8" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + vjezd</t>
         </is>
       </c>
       <c r="D120" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Bezpečnostní dveře RC3 sklad</t>
+          <t>Vjezd Dvořákova — napojení na komunikaci — Napojení vjezdu na ulici Dvořákova — vydláždění z betonových dlaždic + spádování na pozemek investora + odvodnění dešťové vody na pozemek (ne na komunikaci)</t>
         </is>
       </c>
       <c r="E120" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F120" s="9" t="n">
-        <v>1</v>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F120" s="22" t="n"/>
       <c r="G120" s="10" t="n"/>
       <c r="H120" s="10" t="n"/>
       <c r="I120" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>komunikace</t>
         </is>
       </c>
       <c r="J120" s="8" t="inlineStr">
         <is>
-          <t>agregát</t>
+          <t>URS-prop —</t>
         </is>
       </c>
     </row>
@@ -7968,12 +7991,12 @@
       </c>
       <c r="C121" s="21" t="inlineStr">
         <is>
-          <t>PSV-77 — Podlahy</t>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D121" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
+          <t>[agregát] 2 položek: Bezpečnostní dveře RC3 sklad; Vjezdová brána</t>
         </is>
       </c>
       <c r="E121" s="20" t="inlineStr">
@@ -8008,12 +8031,12 @@
       </c>
       <c r="C122" s="21" t="inlineStr">
         <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 4 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+1 dalších)</t>
+          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
         </is>
       </c>
       <c r="E122" s="20" t="inlineStr">
@@ -8043,17 +8066,17 @@
       </c>
       <c r="B123" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="C123" s="21" t="inlineStr">
         <is>
-          <t>M-21 — Elektroinstalace silnoproudá</t>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
         </is>
       </c>
       <c r="D123" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 7 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+4 dalších)</t>
+          <t>[agregát] 5 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+2 dalších)</t>
         </is>
       </c>
       <c r="E123" s="20" t="inlineStr">
@@ -8088,12 +8111,12 @@
       </c>
       <c r="C124" s="21" t="inlineStr">
         <is>
-          <t>PSV-71 — Izolace HI + TI</t>
+          <t>M-21 — Elektroinstalace silnoproudá</t>
         </is>
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
+          <t>[agregát] 8 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+5 dalších)</t>
         </is>
       </c>
       <c r="E124" s="20" t="inlineStr">
@@ -8128,12 +8151,12 @@
       </c>
       <c r="C125" s="21" t="inlineStr">
         <is>
-          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
+          <t>M-24</t>
         </is>
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
+          <t>[agregát] 1 položek: Lokální odtah digestoří kuchyní</t>
         </is>
       </c>
       <c r="E125" s="20" t="inlineStr">
@@ -8168,12 +8191,12 @@
       </c>
       <c r="C126" s="21" t="inlineStr">
         <is>
-          <t>PSV-73 — Vytápění + komín</t>
+          <t>PSV-71 — Izolace HI + TI</t>
         </is>
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
+          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
         </is>
       </c>
       <c r="E126" s="20" t="inlineStr">
@@ -8208,12 +8231,12 @@
       </c>
       <c r="C127" s="21" t="inlineStr">
         <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
         </is>
       </c>
       <c r="D127" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
+          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
         </is>
       </c>
       <c r="E127" s="20" t="inlineStr">
@@ -8248,12 +8271,12 @@
       </c>
       <c r="C128" s="21" t="inlineStr">
         <is>
-          <t>PSV-77 — Podlahy</t>
+          <t>PSV-73 — Vytápění + komín</t>
         </is>
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
+          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
         </is>
       </c>
       <c r="E128" s="20" t="inlineStr">
@@ -8288,12 +8311,12 @@
       </c>
       <c r="C129" s="21" t="inlineStr">
         <is>
-          <t>PSV-78 — Povrchové úpravy</t>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
+          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
         </is>
       </c>
       <c r="E129" s="20" t="inlineStr">
@@ -8328,12 +8351,12 @@
       </c>
       <c r="C130" s="21" t="inlineStr">
         <is>
-          <t>PSV-95 — Detekce požární</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 2 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A</t>
+          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
         </is>
       </c>
       <c r="E130" s="20" t="inlineStr">
@@ -8368,12 +8391,12 @@
       </c>
       <c r="C131" s="21" t="inlineStr">
         <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
+          <t>PSV-78 — Povrchové úpravy</t>
         </is>
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
+          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
         </is>
       </c>
       <c r="E131" s="20" t="inlineStr">
@@ -8397,8 +8420,88 @@
         </is>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" s="20" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C132" s="21" t="inlineStr">
+        <is>
+          <t>PSV-95 — Detekce požární</t>
+        </is>
+      </c>
+      <c r="D132" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 3 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A; Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
+        </is>
+      </c>
+      <c r="E132" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F132" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G132" s="10" t="n"/>
+      <c r="H132" s="10" t="n"/>
+      <c r="I132" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J132" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="20" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C133" s="21" t="inlineStr">
+        <is>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
+        </is>
+      </c>
+      <c r="D133" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
+        </is>
+      </c>
+      <c r="E133" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F133" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G133" s="10" t="n"/>
+      <c r="H133" s="10" t="n"/>
+      <c r="I133" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J133" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J131"/>
+  <autoFilter ref="A1:J133"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8409,7 +8512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R201"/>
+  <dimension ref="A1:R204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -18705,27 +18808,27 @@
       </c>
       <c r="B150" s="8" t="inlineStr">
         <is>
-          <t>M-21 ELI silnoproud</t>
+          <t>PSV-95 Detekce požární</t>
         </is>
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávající ELI</t>
+          <t>Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
         </is>
       </c>
       <c r="D150" s="20" t="inlineStr">
         <is>
-          <t>210010011</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E150" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávající elektroinstalace v celém domě (vodiče, rozvaděč, zásuvky, svítidla) — recyklace mědi</t>
+          <t>Předávací protokol krbu na tuhá paliva + kontrola bezpečných vzdáleností (800 mm směr sálání / 400 mm strany, nehořlavá zóna podlahy) dle PBŘ</t>
         </is>
       </c>
       <c r="F150" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>soubor</t>
         </is>
       </c>
       <c r="G150" s="23" t="n">
@@ -18735,11 +18838,11 @@
       <c r="I150" s="10" t="n"/>
       <c r="J150" s="8" t="inlineStr">
         <is>
-          <t>elektroinstalater</t>
+          <t>topenar</t>
         </is>
       </c>
       <c r="K150" s="24" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="L150" s="20" t="inlineStr">
         <is>
@@ -18748,12 +18851,12 @@
       </c>
       <c r="M150" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — kompletně nová ELI</t>
+          <t>PBŘ D.3</t>
         </is>
       </c>
       <c r="N150" s="20" t="inlineStr">
         <is>
-          <t>#7</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O150" s="26" t="inlineStr">
@@ -18761,8 +18864,12 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P150" s="41" t="n"/>
-      <c r="Q150" s="41" t="n"/>
+      <c r="P150" s="41" t="inlineStr"/>
+      <c r="Q150" s="41" t="inlineStr">
+        <is>
+          <t>DODATEK_PBR_GAPS_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="20" t="n">
@@ -18775,26 +18882,26 @@
       </c>
       <c r="C151" s="8" t="inlineStr">
         <is>
-          <t>Pojistková skříň + 3× podružný rozvaděč</t>
+          <t>Demontáž stávající ELI</t>
         </is>
       </c>
       <c r="D151" s="20" t="inlineStr">
         <is>
-          <t>210110023</t>
+          <t>210010011</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t>Nová pojistková skříň + 3× podružný rozvaděč pro každé patro (1.NP, 2.NP, 3.NP) s podružným měřením</t>
+          <t>Demontáž stávající elektroinstalace v celém domě (vodiče, rozvaděč, zásuvky, svítidla) — recyklace mědi</t>
         </is>
       </c>
       <c r="F151" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G151" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H151" s="10" t="n"/>
       <c r="I151" s="10" t="n"/>
@@ -18813,7 +18920,7 @@
       </c>
       <c r="M151" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — 'nová pojistková skříň s podružným měřením pro každé patro'</t>
+          <t>TZ ARS dům §4 — kompletně nová ELI</t>
         </is>
       </c>
       <c r="N151" s="20" t="inlineStr">
@@ -18840,26 +18947,26 @@
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>Rozvody silnoproud</t>
+          <t>Pojistková skříň + 3× podružný rozvaděč</t>
         </is>
       </c>
       <c r="D152" s="20" t="inlineStr">
         <is>
-          <t>210800012</t>
+          <t>210110023</t>
         </is>
       </c>
       <c r="E152" s="8" t="inlineStr">
         <is>
-          <t>Nové silnoproudé rozvody — vodiče CYKY 3×1.5 / 3×2.5 / 5×2.5 / 5×6 + krabice + instalační trubky</t>
+          <t>Nová pojistková skříň + 3× podružný rozvaděč pro každé patro (1.NP, 2.NP, 3.NP) s podružným měřením</t>
         </is>
       </c>
       <c r="F152" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G152" s="22" t="n">
-        <v>700</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G152" s="23" t="n">
+        <v>4</v>
       </c>
       <c r="H152" s="10" t="n"/>
       <c r="I152" s="10" t="n"/>
@@ -18869,7 +18976,7 @@
         </is>
       </c>
       <c r="K152" s="24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L152" s="20" t="inlineStr">
         <is>
@@ -18878,7 +18985,7 @@
       </c>
       <c r="M152" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD 3-byt. dispozice</t>
+          <t>TZ ARS dům §4 — 'nová pojistková skříň s podružným měřením pro každé patro'</t>
         </is>
       </c>
       <c r="N152" s="20" t="inlineStr">
@@ -18905,26 +19012,26 @@
       </c>
       <c r="C153" s="8" t="inlineStr">
         <is>
-          <t>Zásuvky a vypínače</t>
+          <t>Rozvody silnoproud</t>
         </is>
       </c>
       <c r="D153" s="20" t="inlineStr">
         <is>
-          <t>210810050</t>
+          <t>210800012</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
         <is>
-          <t>Zásuvky a vypínače dodávka + montáž — ~70 ks (60-80 dle vyjasnění #7)</t>
+          <t>Nové silnoproudé rozvody — vodiče CYKY 3×1.5 / 3×2.5 / 5×2.5 / 5×6 + krabice + instalační trubky</t>
         </is>
       </c>
       <c r="F153" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G153" s="23" t="n">
-        <v>70</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G153" s="22" t="n">
+        <v>700</v>
       </c>
       <c r="H153" s="10" t="n"/>
       <c r="I153" s="10" t="n"/>
@@ -18943,7 +19050,7 @@
       </c>
       <c r="M153" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD 220 m² 3-byt.</t>
+          <t>TZ ARS + B4_productivity standard RD 3-byt. dispozice</t>
         </is>
       </c>
       <c r="N153" s="20" t="inlineStr">
@@ -18970,17 +19077,17 @@
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>Svítidla</t>
+          <t>Zásuvky a vypínače</t>
         </is>
       </c>
       <c r="D154" s="20" t="inlineStr">
         <is>
-          <t>210820002</t>
+          <t>210810050</t>
         </is>
       </c>
       <c r="E154" s="8" t="inlineStr">
         <is>
-          <t>Svítidla dodávka + montáž — ~35 ks (30-40 dle vyjasnění #7) interiér + venkovní u vstupů</t>
+          <t>Zásuvky a vypínače dodávka + montáž — ~70 ks (60-80 dle vyjasnění #7)</t>
         </is>
       </c>
       <c r="F154" s="20" t="inlineStr">
@@ -18989,7 +19096,7 @@
         </is>
       </c>
       <c r="G154" s="23" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="H154" s="10" t="n"/>
       <c r="I154" s="10" t="n"/>
@@ -19008,7 +19115,7 @@
       </c>
       <c r="M154" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD</t>
+          <t>TZ ARS + B4_productivity standard RD 220 m² 3-byt.</t>
         </is>
       </c>
       <c r="N154" s="20" t="inlineStr">
@@ -19035,26 +19142,26 @@
       </c>
       <c r="C155" s="8" t="inlineStr">
         <is>
-          <t>Příprava FVE</t>
+          <t>Svítidla</t>
         </is>
       </c>
       <c r="D155" s="20" t="inlineStr">
         <is>
-          <t>210800099</t>
+          <t>210820002</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
         <is>
-          <t>Příprava na osazení FVE — rezerva v rozvaděči (jistič + zásuvka pro střídač) + trasy do střechy</t>
+          <t>Svítidla dodávka + montáž — ~35 ks (30-40 dle vyjasnění #7) interiér + venkovní u vstupů</t>
         </is>
       </c>
       <c r="F155" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G155" s="23" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="H155" s="10" t="n"/>
       <c r="I155" s="10" t="n"/>
@@ -19064,7 +19171,7 @@
         </is>
       </c>
       <c r="K155" s="24" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="L155" s="20" t="inlineStr">
         <is>
@@ -19073,7 +19180,7 @@
       </c>
       <c r="M155" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — FVE příprava (bez panelů samotných)</t>
+          <t>TZ ARS + B4_productivity standard RD</t>
         </is>
       </c>
       <c r="N155" s="20" t="inlineStr">
@@ -19100,17 +19207,17 @@
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>Revize ELI při kolaudaci</t>
+          <t>Příprava FVE</t>
         </is>
       </c>
       <c r="D156" s="20" t="inlineStr">
         <is>
-          <t>996019011</t>
+          <t>210800099</t>
         </is>
       </c>
       <c r="E156" s="8" t="inlineStr">
         <is>
-          <t>Výchozí revize elektrické instalace dle ČSN 33 2000-6 + revizní zpráva pro kolaudaci</t>
+          <t>Příprava na osazení FVE — rezerva v rozvaděči (jistič + zásuvka pro střídač) + trasy do střechy</t>
         </is>
       </c>
       <c r="F156" s="20" t="inlineStr">
@@ -19125,11 +19232,11 @@
       <c r="I156" s="10" t="n"/>
       <c r="J156" s="8" t="inlineStr">
         <is>
-          <t>revize_specialista</t>
+          <t>elektroinstalater</t>
         </is>
       </c>
       <c r="K156" s="24" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="L156" s="20" t="inlineStr">
         <is>
@@ -19138,12 +19245,12 @@
       </c>
       <c r="M156" s="8" t="inlineStr">
         <is>
-          <t>Povinná revize ELI dle ČSN 33 2000-6 + kolaudace</t>
+          <t>TZ ARS dům §4 — FVE příprava (bez panelů samotných)</t>
         </is>
       </c>
       <c r="N156" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#7</t>
         </is>
       </c>
       <c r="O156" s="26" t="inlineStr">
@@ -19160,22 +19267,22 @@
       </c>
       <c r="B157" s="8" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>M-21 ELI silnoproud</t>
         </is>
       </c>
       <c r="C157" s="8" t="inlineStr">
         <is>
-          <t>Revize stávajících přípojek</t>
+          <t>Revize ELI při kolaudaci</t>
         </is>
       </c>
       <c r="D157" s="20" t="inlineStr">
         <is>
-          <t>722290515</t>
+          <t>996019011</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
         <is>
-          <t>Revize stávajícího napojení vodovodu + kanalizace na pozemku — kontrola stavu, čištění, tlaková zkouška</t>
+          <t>Výchozí revize elektrické instalace dle ČSN 33 2000-6 + revizní zpráva pro kolaudaci</t>
         </is>
       </c>
       <c r="F157" s="20" t="inlineStr">
@@ -19190,25 +19297,25 @@
       <c r="I157" s="10" t="n"/>
       <c r="J157" s="8" t="inlineStr">
         <is>
-          <t>vodar</t>
+          <t>revize_specialista</t>
         </is>
       </c>
       <c r="K157" s="24" t="n">
-        <v>0.85</v>
+        <v>0.99</v>
       </c>
       <c r="L157" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M157" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — vodovod + kanalizace stávající, bez změny</t>
+          <t>Povinná revize ELI dle ČSN 33 2000-6 + kolaudace</t>
         </is>
       </c>
       <c r="N157" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O157" s="26" t="inlineStr">
@@ -19217,11 +19324,7 @@
         </is>
       </c>
       <c r="P157" s="41" t="n"/>
-      <c r="Q157" s="41" t="inlineStr">
-        <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
-        </is>
-      </c>
+      <c r="Q157" s="41" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="20" t="n">
@@ -19234,26 +19337,26 @@
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>Nové rozvody vody do 3.NP</t>
+          <t>Revize stávajících přípojek</t>
         </is>
       </c>
       <c r="D158" s="20" t="inlineStr">
         <is>
-          <t>722172011</t>
+          <t>722290515</t>
         </is>
       </c>
       <c r="E158" s="8" t="inlineStr">
         <is>
-          <t>Nové rozvody studené + teplé vody do koupelen 1.NP + 2.NP + 3.NP a kuchyní (PEX/Cu, dimenze DN15-25)</t>
+          <t>Revize stávajícího napojení vodovodu + kanalizace na pozemku — kontrola stavu, čištění, tlaková zkouška</t>
         </is>
       </c>
       <c r="F158" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G158" s="22" t="n">
-        <v>80</v>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G158" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H158" s="10" t="n"/>
       <c r="I158" s="10" t="n"/>
@@ -19263,7 +19366,7 @@
         </is>
       </c>
       <c r="K158" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L158" s="20" t="inlineStr">
         <is>
@@ -19272,7 +19375,7 @@
       </c>
       <c r="M158" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — nové koupelny + kuchyně, vyjasnění #6 working assumption</t>
+          <t>TZ ARS dům §4 — vodovod + kanalizace stávající, bez změny</t>
         </is>
       </c>
       <c r="N158" s="20" t="inlineStr">
@@ -19303,17 +19406,17 @@
       </c>
       <c r="C159" s="8" t="inlineStr">
         <is>
-          <t>Nové odpadní rozvody</t>
+          <t>Nové rozvody vody do 3.NP</t>
         </is>
       </c>
       <c r="D159" s="20" t="inlineStr">
         <is>
-          <t>721174021</t>
+          <t>722172011</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
         <is>
-          <t>Nové odpadní rozvody PVC-HT DN40-DN110 ke koupelnám 1.NP, 2.NP, 3.NP a kuchyním + napojení na stávající</t>
+          <t>Nové rozvody studené + teplé vody do koupelen 1.NP + 2.NP + 3.NP a kuchyní (PEX/Cu, dimenze DN15-25)</t>
         </is>
       </c>
       <c r="F159" s="20" t="inlineStr">
@@ -19322,7 +19425,7 @@
         </is>
       </c>
       <c r="G159" s="22" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H159" s="10" t="n"/>
       <c r="I159" s="10" t="n"/>
@@ -19336,12 +19439,12 @@
       </c>
       <c r="L159" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M159" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — nové koupelny + kuchyně, odpad do stávající kanalizace</t>
+          <t>TZ ARS dům §4 — nové koupelny + kuchyně, vyjasnění #6 working assumption</t>
         </is>
       </c>
       <c r="N159" s="20" t="inlineStr">
@@ -19355,7 +19458,11 @@
         </is>
       </c>
       <c r="P159" s="41" t="n"/>
-      <c r="Q159" s="41" t="n"/>
+      <c r="Q159" s="41" t="inlineStr">
+        <is>
+          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="20" t="n">
@@ -19368,26 +19475,26 @@
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP)</t>
+          <t>Nové odpadní rozvody</t>
         </is>
       </c>
       <c r="D160" s="20" t="inlineStr">
         <is>
-          <t>725291131</t>
+          <t>721174021</t>
         </is>
       </c>
       <c r="E160" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 1.05 1.NP: 1× vana (DXF) + 1× umyvadlo (DXF) + 1× WC (TZ standard)</t>
+          <t>Nové odpadní rozvody PVC-HT DN40-DN110 ke koupelnám 1.NP, 2.NP, 3.NP a kuchyním + napojení na stávající</t>
         </is>
       </c>
       <c r="F160" s="20" t="inlineStr">
         <is>
-          <t>set</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G160" s="22" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H160" s="10" t="n"/>
       <c r="I160" s="10" t="n"/>
@@ -19406,7 +19513,7 @@
       </c>
       <c r="M160" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 1.05 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>TZ ARS dům §4 — nové koupelny + kuchyně, odpad do stávající kanalizace</t>
         </is>
       </c>
       <c r="N160" s="20" t="inlineStr">
@@ -19420,11 +19527,7 @@
         </is>
       </c>
       <c r="P160" s="41" t="n"/>
-      <c r="Q160" s="41" t="inlineStr">
-        <is>
-          <t>GAP_005_deprecated</t>
-        </is>
-      </c>
+      <c r="Q160" s="41" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="20" t="n">
@@ -19437,26 +19540,26 @@
       </c>
       <c r="C161" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture A</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP)</t>
         </is>
       </c>
       <c r="D161" s="20" t="inlineStr">
         <is>
-          <t>725211101</t>
+          <t>725291131</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
         <is>
-          <t>Vana koupelnová obdélníková 170×70 cm — koupelna 1.05 1.NP</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 1.05 1.NP: 1× vana (DXF) + 1× umyvadlo (DXF) + 1× WC (TZ standard)</t>
         </is>
       </c>
       <c r="F161" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G161" s="23" t="n">
-        <v>1</v>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="G161" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H161" s="10" t="n"/>
       <c r="I161" s="10" t="n"/>
@@ -19466,7 +19569,7 @@
         </is>
       </c>
       <c r="K161" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L161" s="20" t="inlineStr">
         <is>
@@ -19475,12 +19578,12 @@
       </c>
       <c r="M161" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 1.05 1.NP + TZ ARS koupelna kompletace</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 1.05 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="N161" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O161" s="26" t="inlineStr">
@@ -19491,7 +19594,7 @@
       <c r="P161" s="41" t="n"/>
       <c r="Q161" s="41" t="inlineStr">
         <is>
-          <t>GAP_005</t>
+          <t>GAP_005_deprecated</t>
         </is>
       </c>
     </row>
@@ -19506,17 +19609,17 @@
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture B</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture A</t>
         </is>
       </c>
       <c r="D162" s="20" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725211101</t>
         </is>
       </c>
       <c r="E162" s="8" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 1.05 1.NP</t>
+          <t>Vana koupelnová obdélníková 170×70 cm — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="F162" s="20" t="inlineStr">
@@ -19575,17 +19678,17 @@
       </c>
       <c r="C163" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture C</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture B</t>
         </is>
       </c>
       <c r="D163" s="20" t="inlineStr">
         <is>
-          <t>725111101</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="E163" s="8" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 1.05 1.NP</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="F163" s="20" t="inlineStr">
@@ -19644,26 +19747,26 @@
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP)</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture C</t>
         </is>
       </c>
       <c r="D164" s="20" t="inlineStr">
         <is>
-          <t>725291131</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="E164" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 2.03 2.NP: 1× umyvadlo (DXF) + 1× WC (TZ standard) + 1× sprcha (TZ standard)</t>
+          <t>WC kombi keramické bílé — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="F164" s="20" t="inlineStr">
         <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="G164" s="22" t="n">
-        <v>0</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G164" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H164" s="10" t="n"/>
       <c r="I164" s="10" t="n"/>
@@ -19673,7 +19776,7 @@
         </is>
       </c>
       <c r="K164" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L164" s="20" t="inlineStr">
         <is>
@@ -19682,12 +19785,12 @@
       </c>
       <c r="M164" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 2.03 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>DXF dum_DPZ MTEXT room 1.05 1.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="N164" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O164" s="26" t="inlineStr">
@@ -19698,7 +19801,7 @@
       <c r="P164" s="41" t="n"/>
       <c r="Q164" s="41" t="inlineStr">
         <is>
-          <t>GAP_005_deprecated</t>
+          <t>GAP_005</t>
         </is>
       </c>
     </row>
@@ -19713,26 +19816,26 @@
       </c>
       <c r="C165" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture A</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP)</t>
         </is>
       </c>
       <c r="D165" s="20" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725291131</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 2.03 2.NP</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 2.03 2.NP: 1× umyvadlo (DXF) + 1× WC (TZ standard) + 1× sprcha (TZ standard)</t>
         </is>
       </c>
       <c r="F165" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G165" s="23" t="n">
-        <v>1</v>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="G165" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H165" s="10" t="n"/>
       <c r="I165" s="10" t="n"/>
@@ -19742,7 +19845,7 @@
         </is>
       </c>
       <c r="K165" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L165" s="20" t="inlineStr">
         <is>
@@ -19751,12 +19854,12 @@
       </c>
       <c r="M165" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 2.03 2.NP + TZ ARS koupelna kompletace</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 2.03 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="N165" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O165" s="26" t="inlineStr">
@@ -19767,7 +19870,7 @@
       <c r="P165" s="41" t="n"/>
       <c r="Q165" s="41" t="inlineStr">
         <is>
-          <t>GAP_005</t>
+          <t>GAP_005_deprecated</t>
         </is>
       </c>
     </row>
@@ -19782,17 +19885,17 @@
       </c>
       <c r="C166" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture B</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture A</t>
         </is>
       </c>
       <c r="D166" s="20" t="inlineStr">
         <is>
-          <t>725221201</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="E166" s="8" t="inlineStr">
         <is>
-          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 2.03 2.NP</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="F166" s="20" t="inlineStr">
@@ -19851,17 +19954,17 @@
       </c>
       <c r="C167" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture C</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture B</t>
         </is>
       </c>
       <c r="D167" s="20" t="inlineStr">
         <is>
-          <t>725111101</t>
+          <t>725221201</t>
         </is>
       </c>
       <c r="E167" s="8" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 2.03 2.NP</t>
+          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="F167" s="20" t="inlineStr">
@@ -19920,26 +20023,26 @@
       </c>
       <c r="C168" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP)</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture C</t>
         </is>
       </c>
       <c r="D168" s="20" t="inlineStr">
         <is>
-          <t>725291131</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="E168" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 3.04 3.NP: 1× WC (DXF) + 1× umyvadlo (TZ standard) + 1× sprcha (TZ standard)</t>
+          <t>WC kombi keramické bílé — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="F168" s="20" t="inlineStr">
         <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="G168" s="22" t="n">
-        <v>0</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G168" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H168" s="10" t="n"/>
       <c r="I168" s="10" t="n"/>
@@ -19949,7 +20052,7 @@
         </is>
       </c>
       <c r="K168" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L168" s="20" t="inlineStr">
         <is>
@@ -19958,12 +20061,12 @@
       </c>
       <c r="M168" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 3.04 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>DXF dum_DPZ MTEXT room 2.03 2.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="N168" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O168" s="26" t="inlineStr">
@@ -19974,7 +20077,7 @@
       <c r="P168" s="41" t="n"/>
       <c r="Q168" s="41" t="inlineStr">
         <is>
-          <t>GAP_005_deprecated</t>
+          <t>GAP_005</t>
         </is>
       </c>
     </row>
@@ -19989,26 +20092,26 @@
       </c>
       <c r="C169" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture A</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP)</t>
         </is>
       </c>
       <c r="D169" s="20" t="inlineStr">
         <is>
-          <t>725111101</t>
+          <t>725291131</t>
         </is>
       </c>
       <c r="E169" s="8" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 3.04 3.NP</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 3.04 3.NP: 1× WC (DXF) + 1× umyvadlo (TZ standard) + 1× sprcha (TZ standard)</t>
         </is>
       </c>
       <c r="F169" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G169" s="23" t="n">
-        <v>1</v>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="G169" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H169" s="10" t="n"/>
       <c r="I169" s="10" t="n"/>
@@ -20018,7 +20121,7 @@
         </is>
       </c>
       <c r="K169" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L169" s="20" t="inlineStr">
         <is>
@@ -20027,12 +20130,12 @@
       </c>
       <c r="M169" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 3.04 3.NP + TZ ARS koupelna kompletace</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 3.04 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="N169" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O169" s="26" t="inlineStr">
@@ -20043,7 +20146,7 @@
       <c r="P169" s="41" t="n"/>
       <c r="Q169" s="41" t="inlineStr">
         <is>
-          <t>GAP_005</t>
+          <t>GAP_005_deprecated</t>
         </is>
       </c>
     </row>
@@ -20058,17 +20161,17 @@
       </c>
       <c r="C170" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture B</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture A</t>
         </is>
       </c>
       <c r="D170" s="20" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="E170" s="8" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 3.04 3.NP</t>
+          <t>WC kombi keramické bílé — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="F170" s="20" t="inlineStr">
@@ -20127,17 +20230,17 @@
       </c>
       <c r="C171" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture C</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture B</t>
         </is>
       </c>
       <c r="D171" s="20" t="inlineStr">
         <is>
-          <t>725221201</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="E171" s="8" t="inlineStr">
         <is>
-          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 3.04 3.NP</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="F171" s="20" t="inlineStr">
@@ -20196,17 +20299,17 @@
       </c>
       <c r="C172" s="8" t="inlineStr">
         <is>
-          <t>Kuchyňský dřez 2 ks (1.06 + 3.05)</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture C</t>
         </is>
       </c>
       <c r="D172" s="20" t="inlineStr">
         <is>
-          <t>725840111</t>
+          <t>725221201</t>
         </is>
       </c>
       <c r="E172" s="8" t="inlineStr">
         <is>
-          <t>Kuchyňský dřez nerez + montáž — 2 ks (kuchyně 1.06 byt rodičů + kuchyně 3.05 byt 3.NP)</t>
+          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="F172" s="20" t="inlineStr">
@@ -20215,7 +20318,7 @@
         </is>
       </c>
       <c r="G172" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H172" s="10" t="n"/>
       <c r="I172" s="10" t="n"/>
@@ -20225,7 +20328,7 @@
         </is>
       </c>
       <c r="K172" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L172" s="20" t="inlineStr">
         <is>
@@ -20234,12 +20337,12 @@
       </c>
       <c r="M172" s="8" t="inlineStr">
         <is>
-          <t>DXF kuchyně MTEXT 2× + TZ ARS — dispozice byty</t>
+          <t>DXF dum_DPZ MTEXT room 3.04 3.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="N172" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O172" s="26" t="inlineStr">
@@ -20248,7 +20351,11 @@
         </is>
       </c>
       <c r="P172" s="41" t="n"/>
-      <c r="Q172" s="41" t="n"/>
+      <c r="Q172" s="41" t="inlineStr">
+        <is>
+          <t>GAP_005</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="20" t="n">
@@ -20261,17 +20368,17 @@
       </c>
       <c r="C173" s="8" t="inlineStr">
         <is>
-          <t>Vodovodní baterie + drobnosti</t>
+          <t>Kuchyňský dřez 2 ks (1.06 + 3.05)</t>
         </is>
       </c>
       <c r="D173" s="20" t="inlineStr">
         <is>
-          <t>725822611</t>
+          <t>725840111</t>
         </is>
       </c>
       <c r="E173" s="8" t="inlineStr">
         <is>
-          <t>Vodovodní baterie (WC ventil + páková umyvadlová + sprchové + dřezové + termostat sprchové) — ~15 ks + drobné instalační materiály</t>
+          <t>Kuchyňský dřez nerez + montáž — 2 ks (kuchyně 1.06 byt rodičů + kuchyně 3.05 byt 3.NP)</t>
         </is>
       </c>
       <c r="F173" s="20" t="inlineStr">
@@ -20280,7 +20387,7 @@
         </is>
       </c>
       <c r="G173" s="23" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H173" s="10" t="n"/>
       <c r="I173" s="10" t="n"/>
@@ -20290,7 +20397,7 @@
         </is>
       </c>
       <c r="K173" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L173" s="20" t="inlineStr">
         <is>
@@ -20299,7 +20406,7 @@
       </c>
       <c r="M173" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS — kompletní baterie nové</t>
+          <t>DXF kuchyně MTEXT 2× + TZ ARS — dispozice byty</t>
         </is>
       </c>
       <c r="N173" s="20" t="inlineStr">
@@ -20326,17 +20433,17 @@
       </c>
       <c r="C174" s="8" t="inlineStr">
         <is>
-          <t>Akumulační zásobník TUV v suterénu</t>
+          <t>Vodovodní baterie + drobnosti</t>
         </is>
       </c>
       <c r="D174" s="20" t="inlineStr">
         <is>
-          <t>732419411</t>
+          <t>725822611</t>
         </is>
       </c>
       <c r="E174" s="8" t="inlineStr">
         <is>
-          <t>Akumulační zásobník TUV ~300 l v 1.PP napojený na topný systém (sporáková kamna + krb + elektrokotel) — nepřímotop</t>
+          <t>Vodovodní baterie (WC ventil + páková umyvadlová + sprchové + dřezové + termostat sprchové) — ~15 ks + drobné instalační materiály</t>
         </is>
       </c>
       <c r="F174" s="20" t="inlineStr">
@@ -20345,17 +20452,17 @@
         </is>
       </c>
       <c r="G174" s="23" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H174" s="10" t="n"/>
       <c r="I174" s="10" t="n"/>
       <c r="J174" s="8" t="inlineStr">
         <is>
-          <t>instalater_TUV_akumulacni_zasobnik</t>
+          <t>vodar</t>
         </is>
       </c>
       <c r="K174" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L174" s="20" t="inlineStr">
         <is>
@@ -20364,7 +20471,7 @@
       </c>
       <c r="M174" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — kombi akumulační zásobník napojený na multivariantní topný systém</t>
+          <t>TZ ARS — kompletní baterie nové</t>
         </is>
       </c>
       <c r="N174" s="20" t="inlineStr">
@@ -20391,17 +20498,17 @@
       </c>
       <c r="C175" s="8" t="inlineStr">
         <is>
-          <t>Elektrický bojler 3.NP</t>
+          <t>Akumulační zásobník TUV v suterénu</t>
         </is>
       </c>
       <c r="D175" s="20" t="inlineStr">
         <is>
-          <t>732429211</t>
+          <t>732419411</t>
         </is>
       </c>
       <c r="E175" s="8" t="inlineStr">
         <is>
-          <t>Elektrický bojler ~80 l v koupelně 3.NP (nezávislý zdroj pro samostatný byt)</t>
+          <t>Akumulační zásobník TUV ~300 l v 1.PP napojený na topný systém (sporáková kamna + krb + elektrokotel) — nepřímotop</t>
         </is>
       </c>
       <c r="F175" s="20" t="inlineStr">
@@ -20416,7 +20523,7 @@
       <c r="I175" s="10" t="n"/>
       <c r="J175" s="8" t="inlineStr">
         <is>
-          <t>vodar</t>
+          <t>instalater_TUV_akumulacni_zasobnik</t>
         </is>
       </c>
       <c r="K175" s="24" t="n">
@@ -20429,7 +20536,7 @@
       </c>
       <c r="M175" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — elektrický bojler v 3.NP koupelně, vyjasnění #6 odhad 80 l</t>
+          <t>TZ ARS dům §4 — kombi akumulační zásobník napojený na multivariantní topný systém</t>
         </is>
       </c>
       <c r="N175" s="20" t="inlineStr">
@@ -20451,22 +20558,22 @@
       </c>
       <c r="B176" s="8" t="inlineStr">
         <is>
-          <t>PSV-73 Vytápění</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="C176" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna na tuhá paliva</t>
+          <t>Elektrický bojler 3.NP</t>
         </is>
       </c>
       <c r="D176" s="20" t="inlineStr">
         <is>
-          <t>733241011</t>
+          <t>732429211</t>
         </is>
       </c>
       <c r="E176" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna na tuhá paliva ~10 kW s akumulačním zásobníkem TUV — dodávka</t>
+          <t>Elektrický bojler ~80 l v koupelně 3.NP (nezávislý zdroj pro samostatný byt)</t>
         </is>
       </c>
       <c r="F176" s="20" t="inlineStr">
@@ -20481,7 +20588,7 @@
       <c r="I176" s="10" t="n"/>
       <c r="J176" s="8" t="inlineStr">
         <is>
-          <t>topenar</t>
+          <t>vodar</t>
         </is>
       </c>
       <c r="K176" s="24" t="n">
@@ -20494,7 +20601,7 @@
       </c>
       <c r="M176" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — primární zdroj 1.NP/2.NP, ~10 kW odhad standard RD</t>
+          <t>TZ ARS dům §4 — elektrický bojler v 3.NP koupelně, vyjasnění #6 odhad 80 l</t>
         </is>
       </c>
       <c r="N176" s="20" t="inlineStr">
@@ -20521,22 +20628,22 @@
       </c>
       <c r="C177" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna — montáž</t>
+          <t>Sporáková kamna na tuhá paliva</t>
         </is>
       </c>
       <c r="D177" s="20" t="inlineStr">
         <is>
-          <t>733281011</t>
+          <t>733241011</t>
         </is>
       </c>
       <c r="E177" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna — montáž vč. napojení na komín + akumulační zásobník (cca 8 Nh)</t>
+          <t>Sporáková kamna na tuhá paliva ~10 kW s akumulačním zásobníkem TUV — dodávka</t>
         </is>
       </c>
       <c r="F177" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G177" s="23" t="n">
@@ -20550,7 +20657,7 @@
         </is>
       </c>
       <c r="K177" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L177" s="20" t="inlineStr">
         <is>
@@ -20559,12 +20666,12 @@
       </c>
       <c r="M177" s="8" t="inlineStr">
         <is>
-          <t>Standard montáž kamen s napojením na zásobník</t>
+          <t>TZ ARS dům §4 — primární zdroj 1.NP/2.NP, ~10 kW odhad standard RD</t>
         </is>
       </c>
       <c r="N177" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O177" s="26" t="inlineStr">
@@ -20586,22 +20693,22 @@
       </c>
       <c r="C178" s="8" t="inlineStr">
         <is>
-          <t>Elektrokotel 3.NP</t>
+          <t>Sporáková kamna — montáž</t>
         </is>
       </c>
       <c r="D178" s="20" t="inlineStr">
         <is>
-          <t>733131221</t>
+          <t>733281011</t>
         </is>
       </c>
       <c r="E178" s="8" t="inlineStr">
         <is>
-          <t>Elektrokotel ~8 kW pro 3.NP samostatný byt — dodávka + montáž + napojení</t>
+          <t>Sporáková kamna — montáž vč. napojení na komín + akumulační zásobník (cca 8 Nh)</t>
         </is>
       </c>
       <c r="F178" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G178" s="23" t="n">
@@ -20615,7 +20722,7 @@
         </is>
       </c>
       <c r="K178" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L178" s="20" t="inlineStr">
         <is>
@@ -20624,12 +20731,12 @@
       </c>
       <c r="M178" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — 'Nově navržené 3.NP bude vytápěno elektrokotlem'; ~8 kW odhad</t>
+          <t>Standard montáž kamen s napojením na zásobník</t>
         </is>
       </c>
       <c r="N178" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O178" s="26" t="inlineStr">
@@ -20651,17 +20758,17 @@
       </c>
       <c r="C179" s="8" t="inlineStr">
         <is>
-          <t>Krb na tuhá paliva 3.NP</t>
+          <t>Elektrokotel 3.NP</t>
         </is>
       </c>
       <c r="D179" s="20" t="inlineStr">
         <is>
-          <t>733241011</t>
+          <t>733131221</t>
         </is>
       </c>
       <c r="E179" s="8" t="inlineStr">
         <is>
-          <t>Krb na tuhá paliva v 3.NP ~6 kW — dodávka + montáž s napojením na samostatný komín</t>
+          <t>Elektrokotel ~8 kW pro 3.NP samostatný byt — dodávka + montáž + napojení</t>
         </is>
       </c>
       <c r="F179" s="20" t="inlineStr">
@@ -20689,7 +20796,7 @@
       </c>
       <c r="M179" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — krb v 3.NP, ~6 kW odhad</t>
+          <t>TZ ARS dům §4 — 'Nově navržené 3.NP bude vytápěno elektrokotlem'; ~8 kW odhad</t>
         </is>
       </c>
       <c r="N179" s="20" t="inlineStr">
@@ -20716,17 +20823,17 @@
       </c>
       <c r="C180" s="8" t="inlineStr">
         <is>
-          <t>Multisplit TČ — venkovní jednotka</t>
+          <t>Krb na tuhá paliva 3.NP</t>
         </is>
       </c>
       <c r="D180" s="20" t="inlineStr">
         <is>
-          <t>733425211</t>
+          <t>733241011</t>
         </is>
       </c>
       <c r="E180" s="8" t="inlineStr">
         <is>
-          <t>Multisplit tepelné čerpadlo vzduch-vzduch — 1× venkovní jednotka ~10 kW (silent mode hl. tlaku ≤49 dBA)</t>
+          <t>Krb na tuhá paliva v 3.NP ~6 kW — dodávka + montáž s napojením na samostatný komín</t>
         </is>
       </c>
       <c r="F180" s="20" t="inlineStr">
@@ -20741,7 +20848,7 @@
       <c r="I180" s="10" t="n"/>
       <c r="J180" s="8" t="inlineStr">
         <is>
-          <t>specialista_TC_multisplit</t>
+          <t>topenar</t>
         </is>
       </c>
       <c r="K180" s="24" t="n">
@@ -20754,7 +20861,7 @@
       </c>
       <c r="M180" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — multisplit TČ s akustikou hl. tlaku ≤49 dBA, NV 272/2011</t>
+          <t>TZ ARS dům §4 — krb v 3.NP, ~6 kW odhad</t>
         </is>
       </c>
       <c r="N180" s="20" t="inlineStr">
@@ -20781,17 +20888,17 @@
       </c>
       <c r="C181" s="8" t="inlineStr">
         <is>
-          <t>Multisplit TČ — vnitřní jednotky</t>
+          <t>Multisplit TČ — venkovní jednotka</t>
         </is>
       </c>
       <c r="D181" s="20" t="inlineStr">
         <is>
-          <t>733425221</t>
+          <t>733425211</t>
         </is>
       </c>
       <c r="E181" s="8" t="inlineStr">
         <is>
-          <t>Multisplit TČ — 5× vnitřní jednotka v obytných místnostech (1.NP, 2.NP, 3.NP — chlazení + vytápění)</t>
+          <t>Multisplit tepelné čerpadlo vzduch-vzduch — 1× venkovní jednotka ~10 kW (silent mode hl. tlaku ≤49 dBA)</t>
         </is>
       </c>
       <c r="F181" s="20" t="inlineStr">
@@ -20800,7 +20907,7 @@
         </is>
       </c>
       <c r="G181" s="23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H181" s="10" t="n"/>
       <c r="I181" s="10" t="n"/>
@@ -20810,7 +20917,7 @@
         </is>
       </c>
       <c r="K181" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L181" s="20" t="inlineStr">
         <is>
@@ -20819,7 +20926,7 @@
       </c>
       <c r="M181" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — vnitřní jednotky multisplit, vyjasnění #6 odhad 5 ks</t>
+          <t>TZ ARS dům §4 — multisplit TČ s akustikou hl. tlaku ≤49 dBA, NV 272/2011</t>
         </is>
       </c>
       <c r="N181" s="20" t="inlineStr">
@@ -20846,36 +20953,36 @@
       </c>
       <c r="C182" s="8" t="inlineStr">
         <is>
-          <t>Revize komínu</t>
+          <t>Multisplit TČ — vnitřní jednotky</t>
         </is>
       </c>
       <c r="D182" s="20" t="inlineStr">
         <is>
-          <t>734262122</t>
+          <t>733425221</t>
         </is>
       </c>
       <c r="E182" s="8" t="inlineStr">
         <is>
-          <t>Revize stávajícího komínu — kontrola, čištění, vystrojení vložkou nerez DN160 pro kamna + krb 3.NP</t>
+          <t>Multisplit TČ — 5× vnitřní jednotka v obytných místnostech (1.NP, 2.NP, 3.NP — chlazení + vytápění)</t>
         </is>
       </c>
       <c r="F182" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G182" s="23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H182" s="10" t="n"/>
       <c r="I182" s="10" t="n"/>
       <c r="J182" s="8" t="inlineStr">
         <is>
-          <t>kominik</t>
+          <t>specialista_TC_multisplit</t>
         </is>
       </c>
       <c r="K182" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L182" s="20" t="inlineStr">
         <is>
@@ -20884,7 +20991,7 @@
       </c>
       <c r="M182" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — komín stávající, vystrojení vložkou pro kamna + krb</t>
+          <t>TZ ARS dům §4 — vnitřní jednotky multisplit, vyjasnění #6 odhad 5 ks</t>
         </is>
       </c>
       <c r="N182" s="20" t="inlineStr">
@@ -20911,36 +21018,36 @@
       </c>
       <c r="C183" s="8" t="inlineStr">
         <is>
-          <t>Rozvody otopné soustavy</t>
+          <t>Revize komínu</t>
         </is>
       </c>
       <c r="D183" s="20" t="inlineStr">
         <is>
-          <t>733111021</t>
+          <t>734262122</t>
         </is>
       </c>
       <c r="E183" s="8" t="inlineStr">
         <is>
-          <t>Rozvody otopné soustavy Cu/PEX k vnitřním jednotkám TČ + radiátorům pro doplňkové (cca 100 bm odhad)</t>
+          <t>Revize stávajícího komínu — kontrola, čištění, vystrojení vložkou nerez DN160 pro kamna + krb 3.NP</t>
         </is>
       </c>
       <c r="F183" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G183" s="22" t="n">
-        <v>100</v>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G183" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H183" s="10" t="n"/>
       <c r="I183" s="10" t="n"/>
       <c r="J183" s="8" t="inlineStr">
         <is>
-          <t>topenar</t>
+          <t>kominik</t>
         </is>
       </c>
       <c r="K183" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L183" s="20" t="inlineStr">
         <is>
@@ -20949,7 +21056,7 @@
       </c>
       <c r="M183" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — rozvody otopné soustavy</t>
+          <t>TZ ARS dům §4 — komín stávající, vystrojení vložkou pro kamna + krb</t>
         </is>
       </c>
       <c r="N183" s="20" t="inlineStr">
@@ -20971,41 +21078,41 @@
       </c>
       <c r="B184" s="8" t="inlineStr">
         <is>
-          <t>VRN — BOZP</t>
+          <t>PSV-73 Vytápění</t>
         </is>
       </c>
       <c r="C184" s="8" t="inlineStr">
         <is>
-          <t>Koordinace BOZP</t>
+          <t>Rozvody otopné soustavy</t>
         </is>
       </c>
       <c r="D184" s="20" t="inlineStr">
         <is>
-          <t>030091000</t>
+          <t>733111021</t>
         </is>
       </c>
       <c r="E184" s="8" t="inlineStr">
         <is>
-          <t>Koordinátor BOZP na staveništi dle zákona 309/2006 Sb. — pro stavbu s více než jedním zhotovitelem</t>
+          <t>Rozvody otopné soustavy Cu/PEX k vnitřním jednotkám TČ + radiátorům pro doplňkové (cca 100 bm odhad)</t>
         </is>
       </c>
       <c r="F184" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G184" s="23" t="n">
-        <v>1</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G184" s="22" t="n">
+        <v>100</v>
       </c>
       <c r="H184" s="10" t="n"/>
       <c r="I184" s="10" t="n"/>
       <c r="J184" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>topenar</t>
         </is>
       </c>
       <c r="K184" s="24" t="n">
-        <v>0.99</v>
+        <v>0.75</v>
       </c>
       <c r="L184" s="20" t="inlineStr">
         <is>
@@ -21014,12 +21121,12 @@
       </c>
       <c r="M184" s="8" t="inlineStr">
         <is>
-          <t>Zákon 309/2006 Sb. — povinný BOZP koordinátor pro vícezhotovitelskou stavbu</t>
+          <t>TZ ARS dům §4 — rozvody otopné soustavy</t>
         </is>
       </c>
       <c r="N184" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O184" s="26" t="inlineStr">
@@ -21036,22 +21143,22 @@
       </c>
       <c r="B185" s="8" t="inlineStr">
         <is>
-          <t>VRN — Dokumentace</t>
+          <t>VRN — BOZP</t>
         </is>
       </c>
       <c r="C185" s="8" t="inlineStr">
         <is>
-          <t>Předávací protokoly + DSP</t>
+          <t>Koordinace BOZP</t>
         </is>
       </c>
       <c r="D185" s="20" t="inlineStr">
         <is>
-          <t>030151000</t>
+          <t>030091000</t>
         </is>
       </c>
       <c r="E185" s="8" t="inlineStr">
         <is>
-          <t>Předávací protokoly + Dokumentace skutečného provedení (DSP) — sestavení, vázání, dodávka 2× tiskem + elektronická verze</t>
+          <t>Koordinátor BOZP na staveništi dle zákona 309/2006 Sb. — pro stavbu s více než jedním zhotovitelem</t>
         </is>
       </c>
       <c r="F185" s="20" t="inlineStr">
@@ -21079,12 +21186,12 @@
       </c>
       <c r="M185" s="8" t="inlineStr">
         <is>
-          <t>Vyhláška 499/2006 Sb. + ČKAIT — DSP povinná pro kolaudaci</t>
+          <t>Zákon 309/2006 Sb. — povinný BOZP koordinátor pro vícezhotovitelskou stavbu</t>
         </is>
       </c>
       <c r="N185" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#10</t>
         </is>
       </c>
       <c r="O185" s="26" t="inlineStr">
@@ -21101,41 +21208,41 @@
       </c>
       <c r="B186" s="8" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>VRN — Dokumentace</t>
         </is>
       </c>
       <c r="C186" s="8" t="inlineStr">
         <is>
-          <t>Kontejnery suti tříděné</t>
+          <t>Předávací protokoly + DSP</t>
         </is>
       </c>
       <c r="D186" s="20" t="inlineStr">
         <is>
-          <t>997013211</t>
+          <t>030151000</t>
         </is>
       </c>
       <c r="E186" s="8" t="inlineStr">
         <is>
-          <t>Kontejnery na suť tříděnou velkoobjemové (beton/cihly, dřevo, kovy, EPS, sádra, směs) — pronájem + svozy</t>
+          <t>Předávací protokoly + Dokumentace skutečného provedení (DSP) — sestavení, vázání, dodávka 2× tiskem + elektronická verze</t>
         </is>
       </c>
       <c r="F186" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G186" s="23" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H186" s="10" t="n"/>
       <c r="I186" s="10" t="n"/>
       <c r="J186" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K186" s="24" t="n">
-        <v>0.85</v>
+        <v>0.99</v>
       </c>
       <c r="L186" s="20" t="inlineStr">
         <is>
@@ -21144,12 +21251,12 @@
       </c>
       <c r="M186" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10.e: beton/cihly 46 t + dřevo 9 t + kovy 0.1 + EPS 0.1 + sádra 0.2 + směs 1.0</t>
+          <t>Vyhláška 499/2006 Sb. + ČKAIT — DSP povinná pro kolaudaci</t>
         </is>
       </c>
       <c r="N186" s="20" t="inlineStr">
         <is>
-          <t>#9, #10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O186" s="26" t="inlineStr">
@@ -21171,36 +21278,36 @@
       </c>
       <c r="C187" s="8" t="inlineStr">
         <is>
-          <t>Doprava materiálu</t>
+          <t>Kontejnery suti tříděné</t>
         </is>
       </c>
       <c r="D187" s="20" t="inlineStr">
         <is>
-          <t>031031000</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="E187" s="8" t="inlineStr">
         <is>
-          <t>Doprava materiálu na stavbu (centrální koordinace) — paušál ~2-3 % z PN materiál</t>
+          <t>Kontejnery na suť tříděnou velkoobjemové (beton/cihly, dřevo, kovy, EPS, sádra, směs) — pronájem + svozy</t>
         </is>
       </c>
       <c r="F187" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G187" s="23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H187" s="10" t="n"/>
       <c r="I187" s="10" t="n"/>
       <c r="J187" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="K187" s="24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L187" s="20" t="inlineStr">
         <is>
@@ -21209,12 +21316,12 @@
       </c>
       <c r="M187" s="8" t="inlineStr">
         <is>
-          <t>B4_productivity — standard doprava RD městská zástavba</t>
+          <t>TZ B m.10.e: beton/cihly 46 t + dřevo 9 t + kovy 0.1 + EPS 0.1 + sádra 0.2 + směs 1.0</t>
         </is>
       </c>
       <c r="N187" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>#9, #10</t>
         </is>
       </c>
       <c r="O187" s="26" t="inlineStr">
@@ -21236,36 +21343,36 @@
       </c>
       <c r="C188" s="8" t="inlineStr">
         <is>
-          <t>Likvidace odpadů 56.9 t</t>
+          <t>Doprava materiálu</t>
         </is>
       </c>
       <c r="D188" s="20" t="inlineStr">
         <is>
-          <t>997013211</t>
+          <t>031031000</t>
         </is>
       </c>
       <c r="E188" s="8" t="inlineStr">
         <is>
-          <t>Likvidace stavební suti dle vyhl. 8/2021 Sb. — skládkovné + recyklace + třídění (56.9 t celkem per TZ B m.10.e)</t>
+          <t>Doprava materiálu na stavbu (centrální koordinace) — paušál ~2-3 % z PN materiál</t>
         </is>
       </c>
       <c r="F188" s="20" t="inlineStr">
         <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="G188" s="22" t="n">
-        <v>56.9</v>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="G188" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H188" s="10" t="n"/>
       <c r="I188" s="10" t="n"/>
       <c r="J188" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K188" s="24" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="L188" s="20" t="inlineStr">
         <is>
@@ -21274,12 +21381,12 @@
       </c>
       <c r="M188" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10.e bilance odpadů celkem dům</t>
+          <t>B4_productivity — standard doprava RD městská zástavba</t>
         </is>
       </c>
       <c r="N188" s="20" t="inlineStr">
         <is>
-          <t>#9, #10</t>
+          <t>#10</t>
         </is>
       </c>
       <c r="O188" s="26" t="inlineStr">
@@ -21296,41 +21403,41 @@
       </c>
       <c r="B189" s="8" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="C189" s="8" t="inlineStr">
         <is>
-          <t>Geodetické zaměření před + po realizaci</t>
+          <t>Likvidace odpadů 56.9 t</t>
         </is>
       </c>
       <c r="D189" s="20" t="inlineStr">
         <is>
-          <t>030141000</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="E189" s="8" t="inlineStr">
         <is>
-          <t>Geodetické zaměření před realizací (verifikace polohopis + výškopis) + po dokončení (zaměření skutečného provedení pro kolaudaci)</t>
+          <t>Likvidace stavební suti dle vyhl. 8/2021 Sb. — skládkovné + recyklace + třídění (56.9 t celkem per TZ B m.10.e)</t>
         </is>
       </c>
       <c r="F189" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G189" s="23" t="n">
-        <v>2</v>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G189" s="22" t="n">
+        <v>56.9</v>
       </c>
       <c r="H189" s="10" t="n"/>
       <c r="I189" s="10" t="n"/>
       <c r="J189" s="8" t="inlineStr">
         <is>
-          <t>geodet</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="K189" s="24" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="L189" s="20" t="inlineStr">
         <is>
@@ -21339,12 +21446,12 @@
       </c>
       <c r="M189" s="8" t="inlineStr">
         <is>
-          <t>Standard — geodet před+po pro každou stavbu</t>
+          <t>TZ B m.10.e bilance odpadů celkem dům</t>
         </is>
       </c>
       <c r="N189" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#9, #10</t>
         </is>
       </c>
       <c r="O189" s="26" t="inlineStr">
@@ -21361,37 +21468,37 @@
       </c>
       <c r="B190" s="8" t="inlineStr">
         <is>
-          <t>VRN — Kolaudace</t>
+          <t>VRN — Geodet</t>
         </is>
       </c>
       <c r="C190" s="8" t="inlineStr">
         <is>
-          <t>Kolaudační řízení</t>
+          <t>Geodetické zaměření před + po realizaci</t>
         </is>
       </c>
       <c r="D190" s="20" t="inlineStr">
         <is>
-          <t>030171000</t>
+          <t>030141000</t>
         </is>
       </c>
       <c r="E190" s="8" t="inlineStr">
         <is>
-          <t>Kolaudační řízení — paušál (správní poplatky + součinnost) dle zákona 183/2006 Sb.</t>
+          <t>Geodetické zaměření před realizací (verifikace polohopis + výškopis) + po dokončení (zaměření skutečného provedení pro kolaudaci)</t>
         </is>
       </c>
       <c r="F190" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G190" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H190" s="10" t="n"/>
       <c r="I190" s="10" t="n"/>
       <c r="J190" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>geodet</t>
         </is>
       </c>
       <c r="K190" s="24" t="n">
@@ -21404,7 +21511,7 @@
       </c>
       <c r="M190" s="8" t="inlineStr">
         <is>
-          <t>Zákon 183/2006 Sb. + vyhl. 499/2006 Sb.</t>
+          <t>Standard — geodet před+po pro každou stavbu</t>
         </is>
       </c>
       <c r="N190" s="20" t="inlineStr">
@@ -21426,31 +21533,31 @@
       </c>
       <c r="B191" s="8" t="inlineStr">
         <is>
-          <t>VRN — Lešení</t>
+          <t>VRN — Kolaudace</t>
         </is>
       </c>
       <c r="C191" s="8" t="inlineStr">
         <is>
-          <t>Fasádní lešení (ETICS + krov + klempířina)</t>
+          <t>Kolaudační řízení</t>
         </is>
       </c>
       <c r="D191" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>030171000</t>
         </is>
       </c>
       <c r="E191" s="8" t="inlineStr">
         <is>
-          <t>Fasádní lešení trubkové/rámové vč. montáže + pronájmu + demontáže — pro provedení ETICS fasády, krovu a klempířiny po obvodu domu (výška 13 m)</t>
+          <t>Kolaudační řízení — paušál (správní poplatky + součinnost) dle zákona 183/2006 Sb.</t>
         </is>
       </c>
       <c r="F191" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G191" s="22" t="n">
-        <v>503.1</v>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="G191" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H191" s="10" t="n"/>
       <c r="I191" s="10" t="n"/>
@@ -21460,7 +21567,7 @@
         </is>
       </c>
       <c r="K191" s="24" t="n">
-        <v>0.8</v>
+        <v>0.99</v>
       </c>
       <c r="L191" s="20" t="inlineStr">
         <is>
@@ -21469,7 +21576,7 @@
       </c>
       <c r="M191" s="8" t="inlineStr">
         <is>
-          <t>anchor checklist PM02 — technical necessity (ETICS 276.7 m² nelze provést bez lešení, 941xxx URS família) + DXF obvod 38.7 m + řez výška 13 m</t>
+          <t>Zákon 183/2006 Sb. + vyhl. 499/2006 Sb.</t>
         </is>
       </c>
       <c r="N191" s="20" t="inlineStr">
@@ -21483,11 +21590,7 @@
         </is>
       </c>
       <c r="P191" s="41" t="n"/>
-      <c r="Q191" s="41" t="inlineStr">
-        <is>
-          <t>ANCHOR_CHECKLIST_PM02</t>
-        </is>
-      </c>
+      <c r="Q191" s="41" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="20" t="n">
@@ -21495,31 +21598,31 @@
       </c>
       <c r="B192" s="8" t="inlineStr">
         <is>
-          <t>VRN — Pojištění + zábory</t>
+          <t>VRN — Lešení</t>
         </is>
       </c>
       <c r="C192" s="8" t="inlineStr">
         <is>
-          <t>Pojištění stavby (montážní + odpovědnostní)</t>
+          <t>Fasádní lešení (ETICS + krov + klempířina)</t>
         </is>
       </c>
       <c r="D192" s="20" t="inlineStr">
         <is>
-          <t>030081000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E192" s="8" t="inlineStr">
         <is>
-          <t>Montážní pojištění stavby (CAR) + pojištění odpovědnosti za škodu (zhotovitel) — paušál cca 0.3-0.5 % z PN</t>
+          <t>Fasádní lešení trubkové/rámové vč. montáže + pronájmu + demontáže — pro provedení ETICS fasády, krovu a klempířiny po obvodu domu (výška 13 m)</t>
         </is>
       </c>
       <c r="F192" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
-        </is>
-      </c>
-      <c r="G192" s="23" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G192" s="22" t="n">
+        <v>503.1</v>
       </c>
       <c r="H192" s="10" t="n"/>
       <c r="I192" s="10" t="n"/>
@@ -21529,7 +21632,7 @@
         </is>
       </c>
       <c r="K192" s="24" t="n">
-        <v>0.99</v>
+        <v>0.8</v>
       </c>
       <c r="L192" s="20" t="inlineStr">
         <is>
@@ -21538,12 +21641,12 @@
       </c>
       <c r="M192" s="8" t="inlineStr">
         <is>
-          <t>Standard zhotovitel — pojistná povinnost</t>
+          <t>anchor checklist PM02 — technical necessity (ETICS 276.7 m² nelze provést bez lešení, 941xxx URS família) + DXF obvod 38.7 m + řez výška 13 m</t>
         </is>
       </c>
       <c r="N192" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O192" s="26" t="inlineStr">
@@ -21552,7 +21655,11 @@
         </is>
       </c>
       <c r="P192" s="41" t="n"/>
-      <c r="Q192" s="41" t="n"/>
+      <c r="Q192" s="41" t="inlineStr">
+        <is>
+          <t>ANCHOR_CHECKLIST_PM02</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="20" t="n">
@@ -21565,22 +21672,22 @@
       </c>
       <c r="C193" s="8" t="inlineStr">
         <is>
-          <t>Krátkodobé zábory ul. Fibichova</t>
+          <t>Pojištění stavby (montážní + odpovědnostní)</t>
         </is>
       </c>
       <c r="D193" s="20" t="inlineStr">
         <is>
-          <t>030083000</t>
+          <t>030081000</t>
         </is>
       </c>
       <c r="E193" s="8" t="inlineStr">
         <is>
-          <t>Krátkodobé zábory ulice Fibichova pro materiál a kontejnery (povolení MU Jáchymov + DI) — odhad 30 dnů kumulativně</t>
+          <t>Montážní pojištění stavby (CAR) + pojištění odpovědnosti za škodu (zhotovitel) — paušál cca 0.3-0.5 % z PN</t>
         </is>
       </c>
       <c r="F193" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>paušál</t>
         </is>
       </c>
       <c r="G193" s="23" t="n">
@@ -21594,7 +21701,7 @@
         </is>
       </c>
       <c r="K193" s="24" t="n">
-        <v>0.75</v>
+        <v>0.99</v>
       </c>
       <c r="L193" s="20" t="inlineStr">
         <is>
@@ -21603,7 +21710,7 @@
       </c>
       <c r="M193" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10 + situace — řadovka ul. Fibichova</t>
+          <t>Standard zhotovitel — pojistná povinnost</t>
         </is>
       </c>
       <c r="N193" s="20" t="inlineStr">
@@ -21625,22 +21732,22 @@
       </c>
       <c r="B194" s="8" t="inlineStr">
         <is>
-          <t>VRN — Průzkumy</t>
+          <t>VRN — Pojištění + zábory</t>
         </is>
       </c>
       <c r="C194" s="8" t="inlineStr">
         <is>
-          <t>Mykologický průzkum dřeva při bourání</t>
+          <t>Krátkodobé zábory ul. Fibichova</t>
         </is>
       </c>
       <c r="D194" s="20" t="inlineStr">
         <is>
-          <t>030131000</t>
+          <t>030083000</t>
         </is>
       </c>
       <c r="E194" s="8" t="inlineStr">
         <is>
-          <t>Mykologický průzkum + průzkum výskytu dřevokazného hmyzu stávajícího krovu a dřevěných trámů zhlaví — pro vyloučení narušení dřevěných konstrukcí; provádí autorizovaný mykolog při bourání</t>
+          <t>Krátkodobé zábory ulice Fibichova pro materiál a kontejnery (povolení MU Jáchymov + DI) — odhad 30 dnů kumulativně</t>
         </is>
       </c>
       <c r="F194" s="20" t="inlineStr">
@@ -21655,11 +21762,11 @@
       <c r="I194" s="10" t="n"/>
       <c r="J194" s="8" t="inlineStr">
         <is>
-          <t>mykolog</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K194" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L194" s="20" t="inlineStr">
         <is>
@@ -21668,7 +21775,7 @@
       </c>
       <c r="M194" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2.3 + POZN.2.05 z půdorysů návrh + řez A-A návrh (explicit dřevokazný hmyz scope per drawing wording)</t>
+          <t>TZ B m.10 + situace — řadovka ul. Fibichova</t>
         </is>
       </c>
       <c r="N194" s="20" t="inlineStr">
@@ -21682,11 +21789,7 @@
         </is>
       </c>
       <c r="P194" s="41" t="n"/>
-      <c r="Q194" s="41" t="inlineStr">
-        <is>
-          <t>PER_DRAWING_ENRICHMENT_POZN_2_05</t>
-        </is>
-      </c>
+      <c r="Q194" s="41" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="20" t="n">
@@ -21699,17 +21802,17 @@
       </c>
       <c r="C195" s="8" t="inlineStr">
         <is>
-          <t>Azbestový průzkum podrobný před demolicí</t>
+          <t>Mykologický průzkum dřeva při bourání</t>
         </is>
       </c>
       <c r="D195" s="20" t="inlineStr">
         <is>
-          <t>030133000</t>
+          <t>030131000</t>
         </is>
       </c>
       <c r="E195" s="8" t="inlineStr">
         <is>
-          <t>Azbestový průzkum podrobný před demolicí — laboratorní vzorky a posudek (B kap. m.7.a předběžně negativní, ale podrobný před bouráním povinný)</t>
+          <t>Mykologický průzkum + průzkum výskytu dřevokazného hmyzu stávajícího krovu a dřevěných trámů zhlaví — pro vyloučení narušení dřevěných konstrukcí; provádí autorizovaný mykolog při bourání</t>
         </is>
       </c>
       <c r="F195" s="20" t="inlineStr">
@@ -21724,7 +21827,7 @@
       <c r="I195" s="10" t="n"/>
       <c r="J195" s="8" t="inlineStr">
         <is>
-          <t>azbestovy_specialista</t>
+          <t>mykolog</t>
         </is>
       </c>
       <c r="K195" s="24" t="n">
@@ -21737,7 +21840,7 @@
       </c>
       <c r="M195" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.7.a + ARS §3.2 — azbestový průzkum povinný před demolicí</t>
+          <t>TZ ARS dům §3.2.3 + POZN.2.05 z půdorysů návrh + řez A-A návrh (explicit dřevokazný hmyz scope per drawing wording)</t>
         </is>
       </c>
       <c r="N195" s="20" t="inlineStr">
@@ -21751,7 +21854,11 @@
         </is>
       </c>
       <c r="P195" s="41" t="n"/>
-      <c r="Q195" s="41" t="n"/>
+      <c r="Q195" s="41" t="inlineStr">
+        <is>
+          <t>PER_DRAWING_ENRICHMENT_POZN_2_05</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="20" t="n">
@@ -21759,41 +21866,41 @@
       </c>
       <c r="B196" s="8" t="inlineStr">
         <is>
-          <t>VRN — Přesun hmot</t>
+          <t>VRN — Průzkumy</t>
         </is>
       </c>
       <c r="C196" s="8" t="inlineStr">
         <is>
-          <t>Přesun hmot pro budovu</t>
+          <t>Azbestový průzkum podrobný před demolicí</t>
         </is>
       </c>
       <c r="D196" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>030133000</t>
         </is>
       </c>
       <c r="E196" s="8" t="inlineStr">
         <is>
-          <t>Přesun hmot pro budovu — vnitrostaveništní vertikální + horizontální doprava materiálu a hmot (rekonstrukce vícepodlažní RD + nástavba 3.NP)</t>
+          <t>Azbestový průzkum podrobný před demolicí — laboratorní vzorky a posudek (B kap. m.7.a předběžně negativní, ale podrobný před bouráním povinný)</t>
         </is>
       </c>
       <c r="F196" s="20" t="inlineStr">
         <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="G196" s="22" t="n">
-        <v>0</v>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G196" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H196" s="10" t="n"/>
       <c r="I196" s="10" t="n"/>
       <c r="J196" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>azbestovy_specialista</t>
         </is>
       </c>
       <c r="K196" s="24" t="n">
-        <v>0.6</v>
+        <v>0.85</v>
       </c>
       <c r="L196" s="20" t="inlineStr">
         <is>
@@ -21802,12 +21909,12 @@
       </c>
       <c r="M196" s="8" t="inlineStr">
         <is>
-          <t>anchor checklist PM01 — technical necessity (povinná položka každého rozpočtu, 998xxx URS família)</t>
+          <t>TZ B m.7.a + ARS §3.2 — azbestový průzkum povinný před demolicí</t>
         </is>
       </c>
       <c r="N196" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#10</t>
         </is>
       </c>
       <c r="O196" s="26" t="inlineStr">
@@ -21816,11 +21923,7 @@
         </is>
       </c>
       <c r="P196" s="41" t="n"/>
-      <c r="Q196" s="41" t="inlineStr">
-        <is>
-          <t>ANCHOR_CHECKLIST_PM01</t>
-        </is>
-      </c>
+      <c r="Q196" s="41" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="20" t="n">
@@ -21828,41 +21931,41 @@
       </c>
       <c r="B197" s="8" t="inlineStr">
         <is>
-          <t>VRN — Revize</t>
+          <t>VRN — Přesun hmot</t>
         </is>
       </c>
       <c r="C197" s="8" t="inlineStr">
         <is>
-          <t>Revize hydrantu vnějšího</t>
+          <t>Přesun hmot pro budovu</t>
         </is>
       </c>
       <c r="D197" s="20" t="inlineStr">
         <is>
-          <t>030161000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E197" s="8" t="inlineStr">
         <is>
-          <t>Revize vnějšího hydrantu pro požární zabezpečení (DN min. 80, vzdálenost 100 m dle TZ PBŘ) — periodická kontrola</t>
+          <t>Přesun hmot pro budovu — vnitrostaveništní vertikální + horizontální doprava materiálu a hmot (rekonstrukce vícepodlažní RD + nástavba 3.NP)</t>
         </is>
       </c>
       <c r="F197" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G197" s="23" t="n">
-        <v>1</v>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G197" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H197" s="10" t="n"/>
       <c r="I197" s="10" t="n"/>
       <c r="J197" s="8" t="inlineStr">
         <is>
-          <t>revize_specialista</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K197" s="24" t="n">
-        <v>0.85</v>
+        <v>0.6</v>
       </c>
       <c r="L197" s="20" t="inlineStr">
         <is>
@@ -21871,7 +21974,7 @@
       </c>
       <c r="M197" s="8" t="inlineStr">
         <is>
-          <t>TZ PBŘ dům — vnější odběrné místo požární vody, revize před kolaudací</t>
+          <t>anchor checklist PM01 — technical necessity (povinná položka každého rozpočtu, 998xxx URS família)</t>
         </is>
       </c>
       <c r="N197" s="20" t="inlineStr">
@@ -21885,7 +21988,11 @@
         </is>
       </c>
       <c r="P197" s="41" t="n"/>
-      <c r="Q197" s="41" t="n"/>
+      <c r="Q197" s="41" t="inlineStr">
+        <is>
+          <t>ANCHOR_CHECKLIST_PM01</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="20" t="n">
@@ -21893,41 +22000,41 @@
       </c>
       <c r="B198" s="8" t="inlineStr">
         <is>
-          <t>VRN — Zařízení staveniště</t>
+          <t>VRN — Revize</t>
         </is>
       </c>
       <c r="C198" s="8" t="inlineStr">
         <is>
-          <t>Buňky kancelář + sociální</t>
+          <t>Revize hydrantu vnějšího</t>
         </is>
       </c>
       <c r="D198" s="20" t="inlineStr">
         <is>
-          <t>030011000</t>
+          <t>030161000</t>
         </is>
       </c>
       <c r="E198" s="8" t="inlineStr">
         <is>
-          <t>Zařízení staveniště — buňka kancelář + sociální buňka (WC + šatna), pronájem ~8 měsíců</t>
+          <t>Revize vnějšího hydrantu pro požární zabezpečení (DN min. 80, vzdálenost 100 m dle TZ PBŘ) — periodická kontrola</t>
         </is>
       </c>
       <c r="F198" s="20" t="inlineStr">
         <is>
-          <t>kpl-měs</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G198" s="23" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H198" s="10" t="n"/>
       <c r="I198" s="10" t="n"/>
       <c r="J198" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>revize_specialista</t>
         </is>
       </c>
       <c r="K198" s="24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L198" s="20" t="inlineStr">
         <is>
@@ -21936,12 +22043,12 @@
       </c>
       <c r="M198" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.1.m realizace 2026-2027 + standard staveniště RD městská zástavba</t>
+          <t>TZ PBŘ dům — vnější odběrné místo požární vody, revize před kolaudací</t>
         </is>
       </c>
       <c r="N198" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O198" s="26" t="inlineStr">
@@ -21963,22 +22070,22 @@
       </c>
       <c r="C199" s="8" t="inlineStr">
         <is>
-          <t>Mobilní WC</t>
+          <t>Buňky kancelář + sociální</t>
         </is>
       </c>
       <c r="D199" s="20" t="inlineStr">
         <is>
-          <t>030013000</t>
+          <t>030011000</t>
         </is>
       </c>
       <c r="E199" s="8" t="inlineStr">
         <is>
-          <t>Mobilní chemické WC TOI TOI pro pracovníky — pronájem ~8 měsíců</t>
+          <t>Zařízení staveniště — buňka kancelář + sociální buňka (WC + šatna), pronájem ~8 měsíců</t>
         </is>
       </c>
       <c r="F199" s="20" t="inlineStr">
         <is>
-          <t>ks-měs</t>
+          <t>kpl-měs</t>
         </is>
       </c>
       <c r="G199" s="23" t="n">
@@ -22001,7 +22108,7 @@
       </c>
       <c r="M199" s="8" t="inlineStr">
         <is>
-          <t>BOZP — mobilní WC povinné pro stavbu RD</t>
+          <t>TZ B m.1.m realizace 2026-2027 + standard staveniště RD městská zástavba</t>
         </is>
       </c>
       <c r="N199" s="20" t="inlineStr">
@@ -22028,26 +22135,26 @@
       </c>
       <c r="C200" s="8" t="inlineStr">
         <is>
-          <t>El. odběr + vodovodní odběr stavby</t>
+          <t>Mobilní WC</t>
         </is>
       </c>
       <c r="D200" s="20" t="inlineStr">
         <is>
-          <t>031011000</t>
+          <t>030013000</t>
         </is>
       </c>
       <c r="E200" s="8" t="inlineStr">
         <is>
-          <t>El. odběr stavby (zřízení staveništního rozvaděče + měřič) + vodovodní odběr (zřízení staveništní přípojky + vodoměr) — ~8 měsíců</t>
+          <t>Mobilní chemické WC TOI TOI pro pracovníky — pronájem ~8 měsíců</t>
         </is>
       </c>
       <c r="F200" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks-měs</t>
         </is>
       </c>
       <c r="G200" s="23" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H200" s="10" t="n"/>
       <c r="I200" s="10" t="n"/>
@@ -22066,7 +22173,7 @@
       </c>
       <c r="M200" s="8" t="inlineStr">
         <is>
-          <t>Standard staveniště — el. + voda zřízení a odběr po dobu stavby</t>
+          <t>BOZP — mobilní WC povinné pro stavbu RD</t>
         </is>
       </c>
       <c r="N200" s="20" t="inlineStr">
@@ -22093,17 +22200,17 @@
       </c>
       <c r="C201" s="8" t="inlineStr">
         <is>
-          <t>Voda staveniště</t>
+          <t>El. odběr + vodovodní odběr stavby</t>
         </is>
       </c>
       <c r="D201" s="20" t="inlineStr">
         <is>
-          <t>012103101</t>
+          <t>031011000</t>
         </is>
       </c>
       <c r="E201" s="8" t="inlineStr">
         <is>
-          <t>Voda staveniště — napojení na stávající vodovodní přípojku, dočasné rozvody na staveništi (mísení malt, čištění, soc. zázemí), paušál pro dobu výstavby ~18 měs.</t>
+          <t>El. odběr stavby (zřízení staveništního rozvaděče + měřič) + vodovodní odběr (zřízení staveništní přípojky + vodoměr) — ~8 měsíců</t>
         </is>
       </c>
       <c r="F201" s="20" t="inlineStr">
@@ -22122,38 +22229,241 @@
         </is>
       </c>
       <c r="K201" s="24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L201" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M201" s="8" t="inlineStr">
+        <is>
+          <t>Standard staveniště — el. + voda zřízení a odběr po dobu stavby</t>
+        </is>
+      </c>
+      <c r="N201" s="20" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
+      <c r="O201" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P201" s="41" t="n"/>
+      <c r="Q201" s="41" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="20" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Zařízení staveniště</t>
+        </is>
+      </c>
+      <c r="C202" s="8" t="inlineStr">
+        <is>
+          <t>Voda staveniště</t>
+        </is>
+      </c>
+      <c r="D202" s="20" t="inlineStr">
+        <is>
+          <t>012103101</t>
+        </is>
+      </c>
+      <c r="E202" s="8" t="inlineStr">
+        <is>
+          <t>Voda staveniště — napojení na stávající vodovodní přípojku, dočasné rozvody na staveništi (mísení malt, čištění, soc. zázemí), paušál pro dobu výstavby ~18 měs.</t>
+        </is>
+      </c>
+      <c r="F202" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G202" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H202" s="10" t="n"/>
+      <c r="I202" s="10" t="n"/>
+      <c r="J202" s="8" t="inlineStr">
+        <is>
+          <t>VRN_management</t>
+        </is>
+      </c>
+      <c r="K202" s="24" t="n">
         <v>0.9</v>
       </c>
-      <c r="L201" s="20" t="inlineStr">
+      <c r="L202" s="20" t="inlineStr">
         <is>
           <t>needs_production_lookup</t>
         </is>
       </c>
-      <c r="M201" s="8" t="inlineStr">
+      <c r="M202" s="8" t="inlineStr">
         <is>
           <t>TZ B Souhrnná m.5 — 'Stávající vodovodní přípojka z veřejného vodovodu'</t>
         </is>
       </c>
-      <c r="N201" s="20" t="inlineStr">
+      <c r="N202" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O201" s="26" t="inlineStr">
+      <c r="O202" s="26" t="inlineStr">
         <is>
           <t>ANO</t>
         </is>
       </c>
-      <c r="P201" s="41" t="n"/>
-      <c r="Q201" s="41" t="inlineStr">
+      <c r="P202" s="41" t="n"/>
+      <c r="Q202" s="41" t="inlineStr">
         <is>
           <t>GAP_003</t>
         </is>
       </c>
     </row>
+    <row r="203">
+      <c r="A203" s="20" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" s="8" t="inlineStr">
+        <is>
+          <t>M-21 ELI silnoproud</t>
+        </is>
+      </c>
+      <c r="C203" s="8" t="inlineStr">
+        <is>
+          <t>Hlavní vypínač TOTAL STOP + požární značení</t>
+        </is>
+      </c>
+      <c r="D203" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E203" s="8" t="inlineStr">
+        <is>
+          <t>Hlavní vypínač elektrické energie TOTAL STOP + požární značení rozvodného zařízení a uzávěrů (voda/elektro)</t>
+        </is>
+      </c>
+      <c r="F203" s="20" t="inlineStr">
+        <is>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="G203" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H203" s="10" t="n"/>
+      <c r="I203" s="10" t="n"/>
+      <c r="J203" s="8" t="inlineStr">
+        <is>
+          <t>elektrikar</t>
+        </is>
+      </c>
+      <c r="K203" s="24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L203" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M203" s="8" t="inlineStr">
+        <is>
+          <t>PBŘ D.3 §16.05/16.06</t>
+        </is>
+      </c>
+      <c r="N203" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O203" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P203" s="41" t="inlineStr"/>
+      <c r="Q203" s="41" t="inlineStr">
+        <is>
+          <t>DODATEK_PBR_GAPS_2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="20" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" s="8" t="inlineStr">
+        <is>
+          <t>M-24 VZT</t>
+        </is>
+      </c>
+      <c r="C204" s="8" t="inlineStr">
+        <is>
+          <t>Lokální odtah digestoří kuchyní</t>
+        </is>
+      </c>
+      <c r="D204" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E204" s="8" t="inlineStr">
+        <is>
+          <t>Lokální odtah digestoří kuchyní (1.NP + 3.NP) — dodávka + montáž digestoře + prostup fasádou/střechou + zpětná klapka</t>
+        </is>
+      </c>
+      <c r="F204" s="20" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G204" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H204" s="10" t="n"/>
+      <c r="I204" s="10" t="n"/>
+      <c r="J204" s="8" t="inlineStr">
+        <is>
+          <t>vzduchotechnik</t>
+        </is>
+      </c>
+      <c r="K204" s="24" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L204" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M204" s="8" t="inlineStr">
+        <is>
+          <t>B zpráva — VZT: obytné místnosti větrání okny, kuchyně lokální odtah digestoří</t>
+        </is>
+      </c>
+      <c r="N204" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O204" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P204" s="41" t="inlineStr"/>
+      <c r="Q204" s="41" t="inlineStr">
+        <is>
+          <t>DODATEK_PBR_GAPS_2026-06-01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O201"/>
-  <conditionalFormatting sqref="K2:K201">
+  <autoFilter ref="A1:O204"/>
+  <conditionalFormatting sqref="K2:K204">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0" stopIfTrue="1">
       <formula>0.70</formula>
     </cfRule>
@@ -22171,12 +22481,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R29"/>
+  <dimension ref="A1:R32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="47" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
@@ -23801,41 +24111,39 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>HSV-5 Komunikace + vjezd</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Bezpečnostní dveře RC3 sklad</t>
+          <t>Vjezd Dvořákova — napojení na komunikaci</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>766682111</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
+          <t>Napojení vjezdu na ulici Dvořákova — vydláždění z betonových dlaždic + spádování na pozemek investora + odvodnění dešťové vody na pozemek (ne na komunikaci)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G24" s="23" t="n">
-        <v>1</v>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="n"/>
       <c r="H24" s="10" t="n"/>
       <c r="I24" s="10" t="n"/>
       <c r="J24" s="8" t="inlineStr">
         <is>
-          <t>specialista_RC3_dvere</t>
+          <t>komunikace</t>
         </is>
       </c>
       <c r="K24" s="24" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="L24" s="20" t="inlineStr">
         <is>
@@ -23844,7 +24152,7 @@
       </c>
       <c r="M24" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §1.4 — RC3 bezpečnostní dveře v ocelové zárubni</t>
+          <t>Dodatek PD č.1 (E.01) / DI PČR požadavek</t>
         </is>
       </c>
       <c r="N24" s="20" t="inlineStr">
@@ -23857,8 +24165,12 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P24" s="41" t="n"/>
-      <c r="Q24" s="41" t="n"/>
+      <c r="P24" s="41" t="inlineStr"/>
+      <c r="Q24" s="41" t="inlineStr">
+        <is>
+          <t>DODATEK_PBR_GAPS_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="20" t="n">
@@ -23866,50 +24178,50 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Betonová dlažba sklad</t>
-        </is>
-      </c>
-      <c r="D25" s="27" t="inlineStr">
-        <is>
-          <t>596??? ?</t>
+          <t>Bezpečnostní dveře RC3 sklad</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>766682111</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>Betonová dlažba do pískového lože — povrch podlahy skladu (~21 m²)</t>
+          <t>Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G25" s="22" t="n">
-        <v>17.6</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G25" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H25" s="10" t="n"/>
       <c r="I25" s="10" t="n"/>
       <c r="J25" s="8" t="inlineStr">
         <is>
-          <t>podlahar</t>
+          <t>specialista_RC3_dvere</t>
         </is>
       </c>
       <c r="K25" s="24" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="L25" s="20" t="inlineStr">
         <is>
-          <t>wrong_leaf_disambiguation_needed</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ km_tabulka místností + Phase 3.5 sklad qty crosscheck (Pattern 17 Phase 0a Layer 2 + Pattern 31 CEV Matrix D.2)</t>
+          <t>TZ statika sklad §1.4 — RC3 bezpečnostní dveře v ocelové zárubni</t>
         </is>
       </c>
       <c r="N25" s="20" t="inlineStr">
@@ -23917,21 +24229,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O25" s="28" t="inlineStr">
-        <is>
-          <t>LEAF CHYBNÝ — viz alternatives</t>
-        </is>
-      </c>
-      <c r="P25" s="41" t="inlineStr">
-        <is>
-          <t>S01_sklad</t>
-        </is>
-      </c>
-      <c r="Q25" s="41" t="inlineStr">
-        <is>
-          <t>PHASE_3_5_SKLAD_QTY_DXF_VERIFY</t>
-        </is>
-      </c>
+      <c r="O25" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P25" s="41" t="n"/>
+      <c r="Q25" s="41" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="20" t="n">
@@ -23939,27 +24243,27 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Doprava prefa H-BLOK auto s hyd. rukou</t>
+          <t>Vjezdová brána</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>031032000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>Doprava prefa H-BLOK Standard z výrobny Herkul (Obrnice) auto s hydraulickou rukou — celkem ~60 ks bloků</t>
+          <t>Vjezdová brána na pozemku investora (ocelová) — dodávka + montáž</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G26" s="23" t="n">
@@ -23969,11 +24273,11 @@
       <c r="I26" s="10" t="n"/>
       <c r="J26" s="8" t="inlineStr">
         <is>
-          <t>prefa_bloky_specialista</t>
+          <t>zamecnik</t>
         </is>
       </c>
       <c r="K26" s="24" t="n">
-        <v>0.85</v>
+        <v>0.6</v>
       </c>
       <c r="L26" s="20" t="inlineStr">
         <is>
@@ -23982,7 +24286,7 @@
       </c>
       <c r="M26" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 + ARS — auto s hyd. rukou pro osazení H-BLOK</t>
+          <t>Dodatek PD č.1 (E.01)</t>
         </is>
       </c>
       <c r="N26" s="20" t="inlineStr">
@@ -23995,8 +24299,12 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P26" s="41" t="n"/>
-      <c r="Q26" s="41" t="n"/>
+      <c r="P26" s="41" t="inlineStr"/>
+      <c r="Q26" s="41" t="inlineStr">
+        <is>
+          <t>DODATEK_PBR_GAPS_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="20" t="n">
@@ -24004,50 +24312,50 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Likvidace odpadu sklad</t>
-        </is>
-      </c>
-      <c r="D27" s="20" t="inlineStr">
-        <is>
-          <t>997013211</t>
+          <t>Betonová dlažba sklad</t>
+        </is>
+      </c>
+      <c r="D27" s="27" t="inlineStr">
+        <is>
+          <t>596??? ?</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
+          <t>Betonová dlažba do pískového lože — povrch podlahy skladu (~21 m²)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G27" s="22" t="n">
-        <v>8</v>
+        <v>17.6</v>
       </c>
       <c r="H27" s="10" t="n"/>
       <c r="I27" s="10" t="n"/>
       <c r="J27" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>podlahar</t>
         </is>
       </c>
       <c r="K27" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L27" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>wrong_leaf_disambiguation_needed</t>
         </is>
       </c>
       <c r="M27" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS sklad §3 — kamenné zídky + schodiště odstraneny</t>
+          <t>DXF sklad_DPZ km_tabulka místností + Phase 3.5 sklad qty crosscheck (Pattern 17 Phase 0a Layer 2 + Pattern 31 CEV Matrix D.2)</t>
         </is>
       </c>
       <c r="N27" s="20" t="inlineStr">
@@ -24055,13 +24363,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O27" s="26" t="inlineStr">
-        <is>
-          <t>ANO</t>
-        </is>
-      </c>
-      <c r="P27" s="41" t="n"/>
-      <c r="Q27" s="41" t="n"/>
+      <c r="O27" s="28" t="inlineStr">
+        <is>
+          <t>LEAF CHYBNÝ — viz alternatives</t>
+        </is>
+      </c>
+      <c r="P27" s="41" t="inlineStr">
+        <is>
+          <t>S01_sklad</t>
+        </is>
+      </c>
+      <c r="Q27" s="41" t="inlineStr">
+        <is>
+          <t>PHASE_3_5_SKLAD_QTY_DXF_VERIFY</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="20" t="n">
@@ -24069,22 +24385,22 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Geodetické vytýčení sklad</t>
+          <t>Doprava prefa H-BLOK auto s hyd. rukou</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>030141000</t>
+          <t>031032000</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
+          <t>Doprava prefa H-BLOK Standard z výrobny Herkul (Obrnice) auto s hydraulickou rukou — celkem ~60 ks bloků</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -24099,11 +24415,11 @@
       <c r="I28" s="10" t="n"/>
       <c r="J28" s="8" t="inlineStr">
         <is>
-          <t>geodet</t>
+          <t>prefa_bloky_specialista</t>
         </is>
       </c>
       <c r="K28" s="24" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="L28" s="20" t="inlineStr">
         <is>
@@ -24112,7 +24428,7 @@
       </c>
       <c r="M28" s="8" t="inlineStr">
         <is>
-          <t>Standard — geodet vytýčení pro každý nový objekt</t>
+          <t>TZ statika sklad §4 + ARS — auto s hyd. rukou pro osazení H-BLOK</t>
         </is>
       </c>
       <c r="N28" s="20" t="inlineStr">
@@ -24134,41 +24450,41 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>VRN — Společné</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Podíl na obecných VRN dům</t>
+          <t>Likvidace odpadu sklad</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
         <is>
-          <t>030001000</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+          <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
-        </is>
-      </c>
-      <c r="G29" s="23" t="n">
-        <v>1</v>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G29" s="22" t="n">
+        <v>8</v>
       </c>
       <c r="H29" s="10" t="n"/>
       <c r="I29" s="10" t="n"/>
       <c r="J29" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="K29" s="24" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="L29" s="20" t="inlineStr">
         <is>
@@ -24177,7 +24493,7 @@
       </c>
       <c r="M29" s="8" t="inlineStr">
         <is>
-          <t>Standard zhotovitel — alokace VRN pro paralelně realizovaný sklad</t>
+          <t>TZ ARS sklad §3 — kamenné zídky + schodiště odstraneny</t>
         </is>
       </c>
       <c r="N29" s="20" t="inlineStr">
@@ -24193,9 +24509,208 @@
       <c r="P29" s="41" t="n"/>
       <c r="Q29" s="41" t="n"/>
     </row>
+    <row r="30">
+      <c r="A30" s="20" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Geodet</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Geodetické vytýčení sklad</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>030141000</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
+        </is>
+      </c>
+      <c r="F30" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G30" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="10" t="n"/>
+      <c r="I30" s="10" t="n"/>
+      <c r="J30" s="8" t="inlineStr">
+        <is>
+          <t>geodet</t>
+        </is>
+      </c>
+      <c r="K30" s="24" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L30" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M30" s="8" t="inlineStr">
+        <is>
+          <t>Standard — geodet vytýčení pro každý nový objekt</t>
+        </is>
+      </c>
+      <c r="N30" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O30" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P30" s="41" t="n"/>
+      <c r="Q30" s="41" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Geodet / PČR</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Rozhledové trojúhelníky — vytyčení + kontrola</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>Vytyčení + kontrola rozhledových trojúhelníků (Vn=40 km/h, Dz=25 m) dle požadavku DI PČR</t>
+        </is>
+      </c>
+      <c r="F31" s="20" t="inlineStr">
+        <is>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="G31" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="10" t="n"/>
+      <c r="I31" s="10" t="n"/>
+      <c r="J31" s="8" t="inlineStr">
+        <is>
+          <t>geodet</t>
+        </is>
+      </c>
+      <c r="K31" s="24" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L31" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M31" s="8" t="inlineStr">
+        <is>
+          <t>Dodatek PD č.1 (E.01) / DI PČR</t>
+        </is>
+      </c>
+      <c r="N31" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O31" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P31" s="41" t="inlineStr"/>
+      <c r="Q31" s="41" t="inlineStr">
+        <is>
+          <t>DODATEK_PBR_GAPS_2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="20" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Společné</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Podíl na obecných VRN dům</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>030001000</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+        </is>
+      </c>
+      <c r="F32" s="20" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="G32" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="10" t="n"/>
+      <c r="I32" s="10" t="n"/>
+      <c r="J32" s="8" t="inlineStr">
+        <is>
+          <t>VRN_management</t>
+        </is>
+      </c>
+      <c r="K32" s="24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L32" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M32" s="8" t="inlineStr">
+        <is>
+          <t>Standard zhotovitel — alokace VRN pro paralelně realizovaný sklad</t>
+        </is>
+      </c>
+      <c r="N32" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O32" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P32" s="41" t="n"/>
+      <c r="Q32" s="41" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O29"/>
-  <conditionalFormatting sqref="K2:K29">
+  <autoFilter ref="A1:O32"/>
+  <conditionalFormatting sqref="K2:K32">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0" stopIfTrue="1">
       <formula>0.70</formula>
     </cfRule>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01_v2.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01_v2.xlsx
@@ -21,8 +21,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Var_A_Agregovany_Dum'!$A$1:$G$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Var_A_Agregovany_Sklad'!$A$1:$G$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$133</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Var_B_Polozkovy_Dum'!$A$1:$O$204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$132</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Var_B_Polozkovy_Dum'!$A$1:$O$203</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Var_B_Polozkovy_Sklad'!$A$1:$O$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Var_F_URS_Verification_Trail'!$A$1:$H$14</definedName>
   </definedNames>
@@ -1009,11 +1009,11 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>HSV položkově (119 ks) + PSV/TZB/VRN agregovaně (13 skupin) = 132 řádků.</t>
+          <t>HSV položkově (118 ks) + PSV/TZB/VRN agregovaně (13 skupin) = 131 řádků.</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D24" s="10" t="n"/>
       <c r="E24" s="10" t="n"/>
@@ -1027,11 +1027,11 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Plný detail (203 dum + 31 sklad = 234 položek). Cílový rozsah pro produkční pricing.</t>
+          <t>Plný detail (202 dum + 31 sklad = 233 položek). Cílový rozsah pro produkční pricing.</t>
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D25" s="10" t="n"/>
       <c r="E25" s="10" t="n"/>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>234 (203 dum + 31 sklad)</t>
+          <t>233 (202 dum + 31 sklad)</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>HSV 119 | M 2 | PSV 56 | TZB 34 | VRN 23</t>
+          <t>HSV 118 | M 2 | PSV 56 | TZB 34 | VRN 23</t>
         </is>
       </c>
     </row>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>0.99: 17 | 0.95: 32 | 0.90: 35 | 0.85: 41 | 0.80: 21 | 0.75: 72 | 0.70: 4 | 0.60: 3 | 0.50: 4 | 0.00: 5</t>
+          <t>0.99: 17 | 0.95: 32 | 0.90: 35 | 0.85: 41 | 0.80: 21 | 0.75: 71 | 0.70: 4 | 0.60: 3 | 0.50: 4 | 0.00: 5</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>8 WebSearch verified (3.4 %) ✓ | 5 wrong leaf flagged (2.1 %) ⚠ | 156 needs_production_lookup (66.7 %)</t>
+          <t>8 WebSearch verified (3.4 %) ✓ | 5 wrong leaf flagged (2.1 %) ⚠ | 155 needs_production_lookup (66.5 %)</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>29 items (viz Otazky_pro_Karla docx)</t>
+          <t>30 items (viz Otazky_pro_Karla docx)</t>
         </is>
       </c>
     </row>
@@ -1186,8 +1186,8 @@
       <c r="A43" s="12" t="inlineStr">
         <is>
           <t>Rozpočet generován STAVAGENT pipelinem z DSP dokumentace s DPS-grade DXF metadaty.
-234 položek celkem (203 dum + 31 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
-Confidence distribution: 17×0.99 · 32×0.95 · 35×0.90 · 41×0.85 · 21×0.80 · 72×0.75 · 4×0.70 · 3×0.60 · 4×0.50 · 5×0.00.
+233 položek celkem (202 dum + 31 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
+Confidence distribution: 17×0.99 · 32×0.95 · 35×0.90 · 41×0.85 · 21×0.80 · 71×0.75 · 4×0.70 · 3×0.60 · 4×0.50 · 5×0.00.
 25 položek vzniklo per-room expansion ze 9 aggregate parents (každá expanded položka tagged _expansion_origin).
 10 položek recalculated s exact external perimeter 38.70 m (DXF km_R_návrh_tlustá 2 closed polygon) vs prior fallback 41.0 m.
 Skladby vrstev (Sheet 8 Var_E) pochází POUZE z TZ explicit text + DXF cross-validation HATCH patterns. ŽÁDNÉ generic 'standardní RD' assumption — kde TZ silent, explicit fallback flag s ČSN default.
@@ -2601,11 +2601,11 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Bourání kompletního stávajícího krovu; Bourání plechové střešní krytiny; Bourání nadezdívek nad stropem 2.NP; Bourání trámového stropu 2.NP/podkroví; … (+14 dalších)</t>
+          <t>Bourání kompletního stávajícího krovu; Bourání plechové střešní krytiny; Bourání nadezdívek nad stropem 2.NP; Bourání trámového stropu 2.NP/podkroví; … (+13 dalších)</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E7" s="10" t="n"/>
       <c r="F7" s="10" t="n"/>
@@ -3163,7 +3163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J133"/>
+  <dimension ref="A1:J132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6766,7 +6766,7 @@
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>Demontáž oken a dveří — Demontáž všech oken a dveří stávajících (recyklace)</t>
+          <t>Demontáž zařizovacích předmětů — Demontáž všech sanitárních zařizovacích předmětů (WC, umyvadla, baterie, sprcha)</t>
         </is>
       </c>
       <c r="E90" s="20" t="inlineStr">
@@ -6775,7 +6775,7 @@
         </is>
       </c>
       <c r="F90" s="23" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="G90" s="10" t="n"/>
       <c r="H90" s="10" t="n"/>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="J90" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 968071120</t>
+          <t>URS-prop 725900001</t>
         </is>
       </c>
     </row>
@@ -6806,16 +6806,16 @@
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>Demontáž zařizovacích předmětů — Demontáž všech sanitárních zařizovacích předmětů (WC, umyvadla, baterie, sprcha)</t>
+          <t>Odvoz suti a likvidace — Odvoz a likvidace stavební suti dle vyhl. 8/2021 Sb. — celková tonáž odpadů</t>
         </is>
       </c>
       <c r="E91" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="F91" s="23" t="n">
-        <v>12</v>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="F91" s="22" t="n">
+        <v>56.5</v>
       </c>
       <c r="G91" s="10" t="n"/>
       <c r="H91" s="10" t="n"/>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="J91" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 725900001</t>
+          <t>URS-prop 997013501</t>
         </is>
       </c>
     </row>
@@ -6841,32 +6841,32 @@
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>Odvoz suti a likvidace — Odvoz a likvidace stavební suti dle vyhl. 8/2021 Sb. — celková tonáž odpadů</t>
+          <t>Příprava podkladu — Příprava fasádního podkladu — očištění tlakovou vodou, vyspravení omítek, fungicidní nátěr</t>
         </is>
       </c>
       <c r="E92" s="20" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F92" s="22" t="n">
-        <v>56.5</v>
+        <v>276.7</v>
       </c>
       <c r="G92" s="10" t="n"/>
       <c r="H92" s="10" t="n"/>
       <c r="I92" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>fasadnik_etics</t>
         </is>
       </c>
       <c r="J92" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 997013501</t>
+          <t>URS-prop 622401110</t>
         </is>
       </c>
     </row>
@@ -6886,7 +6886,7 @@
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>Příprava podkladu — Příprava fasádního podkladu — očištění tlakovou vodou, vyspravení omítek, fungicidní nátěr</t>
+          <t>ETICS EPS 70F grey 160 mm — ETICS kontaktní zateplení — EPS 70F grey λ=0.032 tl. 160 mm + síťka + lepidlo + zatírací stěrka (řez S01+S12a explicit, ne 200 mm fallback)</t>
         </is>
       </c>
       <c r="E93" s="20" t="inlineStr">
@@ -6906,7 +6906,7 @@
       </c>
       <c r="J93" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 622401110</t>
+          <t>URS-prop 622221121</t>
         </is>
       </c>
     </row>
@@ -6926,7 +6926,7 @@
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>ETICS EPS 70F grey 160 mm — ETICS kontaktní zateplení — EPS 70F grey λ=0.032 tl. 160 mm + síťka + lepidlo + zatírací stěrka (řez S01+S12a explicit, ne 200 mm fallback)</t>
+          <t>ETICS sokl XPS — ETICS sokl — XPS λ=0.034 tl. 120 mm + soklový profil + cihelný obklad spárovaný</t>
         </is>
       </c>
       <c r="E94" s="20" t="inlineStr">
@@ -6935,7 +6935,7 @@
         </is>
       </c>
       <c r="F94" s="22" t="n">
-        <v>276.7</v>
+        <v>13.5</v>
       </c>
       <c r="G94" s="10" t="n"/>
       <c r="H94" s="10" t="n"/>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="J94" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 622221121</t>
+          <t>URS-prop 622223111</t>
         </is>
       </c>
     </row>
@@ -6966,16 +6966,16 @@
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>ETICS sokl XPS — ETICS sokl — XPS λ=0.034 tl. 120 mm + soklový profil + cihelný obklad spárovaný</t>
+          <t>Špalety EPS — Špalety oken — EPS přesah 35-40 mm + síťka + omítka</t>
         </is>
       </c>
       <c r="E95" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="F95" s="22" t="n">
-        <v>13.5</v>
+        <v>82.2</v>
       </c>
       <c r="G95" s="10" t="n"/>
       <c r="H95" s="10" t="n"/>
@@ -6986,7 +6986,7 @@
       </c>
       <c r="J95" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 622223111</t>
+          <t>URS-prop 622221221</t>
         </is>
       </c>
     </row>
@@ -7006,16 +7006,16 @@
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>Špalety EPS — Špalety oken — EPS přesah 35-40 mm + síťka + omítka</t>
+          <t>Profilace fasády — Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
         </is>
       </c>
       <c r="E96" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="F96" s="22" t="n">
-        <v>82.2</v>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="F96" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="G96" s="10" t="n"/>
       <c r="H96" s="10" t="n"/>
@@ -7046,16 +7046,16 @@
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>Profilace fasády — Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
+          <t>Tenkovrstvá omítka pastovitá — Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
         </is>
       </c>
       <c r="E97" s="20" t="inlineStr">
         <is>
-          <t>soubor</t>
-        </is>
-      </c>
-      <c r="F97" s="23" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F97" s="22" t="n">
+        <v>290.2</v>
       </c>
       <c r="G97" s="10" t="n"/>
       <c r="H97" s="10" t="n"/>
@@ -7066,7 +7066,7 @@
       </c>
       <c r="J97" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 622221221</t>
+          <t>URS-prop 622521111</t>
         </is>
       </c>
     </row>
@@ -7081,32 +7081,32 @@
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda ETICS</t>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>Tenkovrstvá omítka pastovitá — Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
+          <t>Demontáž oken — Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
         </is>
       </c>
       <c r="E98" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F98" s="22" t="n">
-        <v>290.2</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="F98" s="23" t="n">
+        <v>16</v>
       </c>
       <c r="G98" s="10" t="n"/>
       <c r="H98" s="10" t="n"/>
       <c r="I98" s="8" t="inlineStr">
         <is>
-          <t>fasadnik_etics</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="J98" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 622521111</t>
+          <t>URS-prop 978013181</t>
         </is>
       </c>
     </row>
@@ -7126,7 +7126,7 @@
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>Demontáž oken — Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
+          <t>Demontáž vstupních dveří venkovních — Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
         </is>
       </c>
       <c r="E99" s="20" t="inlineStr">
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="F99" s="23" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G99" s="10" t="n"/>
       <c r="H99" s="10" t="n"/>
@@ -7166,7 +7166,7 @@
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>Demontáž vstupních dveří venkovních — Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
+          <t>Demontáž vnitřních dveří vč. zárubní — Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
         </is>
       </c>
       <c r="E100" s="20" t="inlineStr">
@@ -7175,7 +7175,7 @@
         </is>
       </c>
       <c r="F100" s="23" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="G100" s="10" t="n"/>
       <c r="H100" s="10" t="n"/>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="J100" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 978013181</t>
+          <t>URS-prop 968072456</t>
         </is>
       </c>
     </row>
@@ -7206,16 +7206,16 @@
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>Demontáž vnitřních dveří vč. zárubní — Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
+          <t>Bourání zdiva komínu — Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
         </is>
       </c>
       <c r="E101" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="F101" s="23" t="n">
-        <v>15</v>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F101" s="22" t="n">
+        <v>0.6</v>
       </c>
       <c r="G101" s="10" t="n"/>
       <c r="H101" s="10" t="n"/>
@@ -7226,7 +7226,7 @@
       </c>
       <c r="J101" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 968072456</t>
+          <t>URS-prop 962024141</t>
         </is>
       </c>
     </row>
@@ -7246,7 +7246,7 @@
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>Bourání zdiva komínu — Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
+          <t>Bourání venkovních konstrukcí — Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
         </is>
       </c>
       <c r="E102" s="20" t="inlineStr">
@@ -7255,7 +7255,7 @@
         </is>
       </c>
       <c r="F102" s="22" t="n">
-        <v>0.6</v>
+        <v>8</v>
       </c>
       <c r="G102" s="10" t="n"/>
       <c r="H102" s="10" t="n"/>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="J102" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 962024141</t>
+          <t>URS-prop 961044111</t>
         </is>
       </c>
     </row>
@@ -7281,32 +7281,32 @@
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>HSV-1 Zemní práce</t>
         </is>
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>Bourání venkovních konstrukcí — Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
+          <t>Drenáž za bílou vanou — Drenáž za opěrnou stěnou (bílou vanou) — drenážní trubka DN100 vlnitá perforovaná + štěrkový obsyp 16/32 + geotextilie + napojení do dešťové kanalizace, L po obvodu BV</t>
         </is>
       </c>
       <c r="E103" s="20" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F103" s="22" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G103" s="10" t="n"/>
       <c r="H103" s="10" t="n"/>
       <c r="I103" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="J103" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 961044111</t>
+          <t>URS-prop 877315111</t>
         </is>
       </c>
     </row>
@@ -7316,37 +7316,37 @@
       </c>
       <c r="B104" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>HSV-1 Zemní práce</t>
+          <t>HSV-5 Komunikace + schodiště</t>
         </is>
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>Drenáž za bílou vanou — Drenáž za opěrnou stěnou (bílou vanou) — drenážní trubka DN100 vlnitá perforovaná + štěrkový obsyp 16/32 + geotextilie + napojení do dešťové kanalizace, L po obvodu BV</t>
+          <t>Sklad mezipodesta schodiště prefa — Sklad mezipodesta schodiště — prefa betonové stupně (9 ks × 179.5×250 mm) + kladecí vrstva zavlhlého betonu nad ŽB podkladní deskou (S05 sklad skladba)</t>
         </is>
       </c>
       <c r="E104" s="20" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F104" s="22" t="n">
-        <v>12</v>
+        <v>5.5</v>
       </c>
       <c r="G104" s="10" t="n"/>
       <c r="H104" s="10" t="n"/>
       <c r="I104" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>betonar</t>
         </is>
       </c>
       <c r="J104" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 877315111</t>
+          <t>URS-prop 121301101</t>
         </is>
       </c>
     </row>
@@ -7356,37 +7356,37 @@
       </c>
       <c r="B105" s="20" t="inlineStr">
         <is>
-          <t>260217_sklad</t>
+          <t>260219_dum</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + schodiště</t>
+          <t>HSV-1 Zemní práce</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>Sklad mezipodesta schodiště prefa — Sklad mezipodesta schodiště — prefa betonové stupně (9 ks × 179.5×250 mm) + kladecí vrstva zavlhlého betonu nad ŽB podkladní deskou (S05 sklad skladba)</t>
+          <t>Venkovní schody na terénu (zahrada za opěrnou stěnou) — Venkovní schody na terénu z betonových dílců do betonového lože — rameno 1: 8×175×280 mm + rameno 2: 5×175×280 mm (13 stupňů), zahrada za opěrnou stěnou</t>
         </is>
       </c>
       <c r="E105" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F105" s="22" t="n">
-        <v>5.5</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="F105" s="23" t="n">
+        <v>13</v>
       </c>
       <c r="G105" s="10" t="n"/>
       <c r="H105" s="10" t="n"/>
       <c r="I105" s="8" t="inlineStr">
         <is>
-          <t>betonar</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="J105" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 121301101</t>
+          <t>URS-prop —</t>
         </is>
       </c>
     </row>
@@ -7401,12 +7401,12 @@
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>HSV-1 Zemní práce</t>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t>Venkovní schody na terénu (zahrada za opěrnou stěnou) — Venkovní schody na terénu z betonových dílců do betonového lože — rameno 1: 8×175×280 mm + rameno 2: 5×175×280 mm (13 stupňů), zahrada za opěrnou stěnou</t>
+          <t>Spojovací prostředky krovu — svorníky tesařských spojů — Montáž svorníků / šroubů tesařských spojů krovu délky přes 150 do 300 mm — spojení kleštin 2×60/180 mm s krokvemi (svorník cca 250 mm, M12), vč. tyče závitové + matic + podložek</t>
         </is>
       </c>
       <c r="E106" s="20" t="inlineStr">
@@ -7415,18 +7415,18 @@
         </is>
       </c>
       <c r="F106" s="23" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="G106" s="10" t="n"/>
       <c r="H106" s="10" t="n"/>
       <c r="I106" s="8" t="inlineStr">
         <is>
-          <t>zednik</t>
+          <t>tesar</t>
         </is>
       </c>
       <c r="J106" s="8" t="inlineStr">
         <is>
-          <t>URS-prop —</t>
+          <t>URS-prop 762085112</t>
         </is>
       </c>
     </row>
@@ -7441,32 +7441,32 @@
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Krov + střecha</t>
+          <t>HSV-4 Vodorovné</t>
         </is>
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t>Spojovací prostředky krovu — svorníky tesařských spojů — Montáž svorníků / šroubů tesařských spojů krovu délky přes 150 do 300 mm — spojení kleštin 2×60/180 mm s krokvemi (svorník cca 250 mm, M12), vč. tyče závitové + matic + podložek</t>
+          <t>Strop 1.NP/2.NP — kročejová izolace (S07) — Desky kročejové izolace (Isover T-P) tl. 30 mm — trámový strop 1.NP/2.NP</t>
         </is>
       </c>
       <c r="E107" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="F107" s="23" t="n">
-        <v>50</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F107" s="22" t="n">
+        <v>59.5</v>
       </c>
       <c r="G107" s="10" t="n"/>
       <c r="H107" s="10" t="n"/>
       <c r="I107" s="8" t="inlineStr">
         <is>
-          <t>tesar</t>
+          <t>izolater_TI</t>
         </is>
       </c>
       <c r="J107" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 762085112</t>
+          <t>URS-prop 713191</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D108" s="8" t="inlineStr">
         <is>
-          <t>Strop 1.NP/2.NP — kročejová izolace (S07) — Desky kročejové izolace (Isover T-P) tl. 30 mm — trámový strop 1.NP/2.NP</t>
+          <t>Strop 1.NP/2.NP — separační geotextilie (S07) — Separační geotextilie pod suchý podsyp — trámový strop 1.NP/2.NP</t>
         </is>
       </c>
       <c r="E108" s="20" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="J108" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 713191</t>
+          <t>URS-prop —</t>
         </is>
       </c>
     </row>
@@ -7526,7 +7526,7 @@
       </c>
       <c r="D109" s="8" t="inlineStr">
         <is>
-          <t>Strop 1.NP/2.NP — separační geotextilie (S07) — Separační geotextilie pod suchý podsyp — trámový strop 1.NP/2.NP</t>
+          <t>Strop 2.NP/3.NP — min. vata výplň mezi nosníky (S09) — Tepelná/akustická izolace minerální vata výplň mezi ocelové nosníky stropu 2.NP/3.NP, tl. 180/200 mm</t>
         </is>
       </c>
       <c r="E109" s="20" t="inlineStr">
@@ -7535,7 +7535,7 @@
         </is>
       </c>
       <c r="F109" s="22" t="n">
-        <v>59.5</v>
+        <v>104.4</v>
       </c>
       <c r="G109" s="10" t="n"/>
       <c r="H109" s="10" t="n"/>
@@ -7546,7 +7546,7 @@
       </c>
       <c r="J109" s="8" t="inlineStr">
         <is>
-          <t>URS-prop —</t>
+          <t>URS-prop 713121</t>
         </is>
       </c>
     </row>
@@ -7566,7 +7566,7 @@
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
-          <t>Strop 2.NP/3.NP — min. vata výplň mezi nosníky (S09) — Tepelná/akustická izolace minerální vata výplň mezi ocelové nosníky stropu 2.NP/3.NP, tl. 180/200 mm</t>
+          <t>Strop klemba mezi patry — Fermacell (S08) — Roznášecí sádrovláknité dílce Fermacell 2E22 tl. 25 mm — suchá skladba nad cihelnou klembou S08</t>
         </is>
       </c>
       <c r="E110" s="20" t="inlineStr">
@@ -7574,19 +7574,17 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="F110" s="22" t="n">
-        <v>104.4</v>
-      </c>
+      <c r="F110" s="22" t="n"/>
       <c r="G110" s="10" t="n"/>
       <c r="H110" s="10" t="n"/>
       <c r="I110" s="8" t="inlineStr">
         <is>
-          <t>izolater_TI</t>
+          <t>suchá_vystavba</t>
         </is>
       </c>
       <c r="J110" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 713121</t>
+          <t>URS-prop —</t>
         </is>
       </c>
     </row>
@@ -7606,7 +7604,7 @@
       </c>
       <c r="D111" s="8" t="inlineStr">
         <is>
-          <t>Strop klemba mezi patry — Fermacell (S08) — Roznášecí sádrovláknité dílce Fermacell 2E22 tl. 25 mm — suchá skladba nad cihelnou klembou S08</t>
+          <t>Strop klemba mezi patry — kročejová izolace (S08) — Desky kročejové izolace (Isover T-P) tl. 30 mm — suchá skladba nad klembou S08</t>
         </is>
       </c>
       <c r="E111" s="20" t="inlineStr">
@@ -7619,12 +7617,12 @@
       <c r="H111" s="10" t="n"/>
       <c r="I111" s="8" t="inlineStr">
         <is>
-          <t>suchá_vystavba</t>
+          <t>izolater_TI</t>
         </is>
       </c>
       <c r="J111" s="8" t="inlineStr">
         <is>
-          <t>URS-prop —</t>
+          <t>URS-prop 713191</t>
         </is>
       </c>
     </row>
@@ -7644,7 +7642,7 @@
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
-          <t>Strop klemba mezi patry — kročejová izolace (S08) — Desky kročejové izolace (Isover T-P) tl. 30 mm — suchá skladba nad klembou S08</t>
+          <t>Strop klemba mezi patry — suchý podsyp + dřevěný rošt (S08) — Vyrovnávací suchý podsyp keramzit/liapor + dřevěný rošt tl. 50 mm — nad klembou S08</t>
         </is>
       </c>
       <c r="E112" s="20" t="inlineStr">
@@ -7657,12 +7655,12 @@
       <c r="H112" s="10" t="n"/>
       <c r="I112" s="8" t="inlineStr">
         <is>
-          <t>izolater_TI</t>
+          <t>suchá_vystavba</t>
         </is>
       </c>
       <c r="J112" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 713191</t>
+          <t>URS-prop —</t>
         </is>
       </c>
     </row>
@@ -7682,7 +7680,7 @@
       </c>
       <c r="D113" s="8" t="inlineStr">
         <is>
-          <t>Strop klemba mezi patry — suchý podsyp + dřevěný rošt (S08) — Vyrovnávací suchý podsyp keramzit/liapor + dřevěný rošt tl. 50 mm — nad klembou S08</t>
+          <t>Strop klemba mezi patry — separační vrstva (S08) — Separační vrstva pod suchý podsyp — nad cihelnou klembou S08</t>
         </is>
       </c>
       <c r="E113" s="20" t="inlineStr">
@@ -7715,12 +7713,12 @@
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>HSV-4 Vodorovné</t>
+          <t>HSV-7 Fasáda + zateplení</t>
         </is>
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t>Strop klemba mezi patry — separační vrstva (S08) — Separační vrstva pod suchý podsyp — nad cihelnou klembou S08</t>
+          <t>Sokl suterénu — sanační zateplení (S03) — Sanační zateplení soklu — sanační izolační deska Styrcon 200 + lepící tmel (Lepstyr plus) + armovací vrstva s tkaninou + penetrace</t>
         </is>
       </c>
       <c r="E114" s="20" t="inlineStr">
@@ -7728,12 +7726,14 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="F114" s="22" t="n"/>
+      <c r="F114" s="22" t="n">
+        <v>23</v>
+      </c>
       <c r="G114" s="10" t="n"/>
       <c r="H114" s="10" t="n"/>
       <c r="I114" s="8" t="inlineStr">
         <is>
-          <t>suchá_vystavba</t>
+          <t>fasader</t>
         </is>
       </c>
       <c r="J114" s="8" t="inlineStr">
@@ -7758,7 +7758,7 @@
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
-          <t>Sokl suterénu — sanační zateplení (S03) — Sanační zateplení soklu — sanační izolační deska Styrcon 200 + lepící tmel (Lepstyr plus) + armovací vrstva s tkaninou + penetrace</t>
+          <t>Sokl pod terénem — drenážní nopová folie (S03a) — Drenážní vrstva — nopová folie tl. 20 mm na suterénní stěnu pod úrovní terénu</t>
         </is>
       </c>
       <c r="E115" s="20" t="inlineStr">
@@ -7773,7 +7773,7 @@
       <c r="H115" s="10" t="n"/>
       <c r="I115" s="8" t="inlineStr">
         <is>
-          <t>fasader</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="J115" s="8" t="inlineStr">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="D116" s="8" t="inlineStr">
         <is>
-          <t>Sokl pod terénem — drenážní nopová folie (S03a) — Drenážní vrstva — nopová folie tl. 20 mm na suterénní stěnu pod úrovní terénu</t>
+          <t>Sokl nad terénem — provětraný obklad (S03b) — Provětrávaná mezera s kotevním roštem 40 mm + keramický obklad 20 mm — sokl nad úrovní terénu</t>
         </is>
       </c>
       <c r="E116" s="20" t="inlineStr">
@@ -7813,7 +7813,7 @@
       <c r="H116" s="10" t="n"/>
       <c r="I116" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>obkladac</t>
         </is>
       </c>
       <c r="J116" s="8" t="inlineStr">
@@ -7833,12 +7833,12 @@
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda + zateplení</t>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="D117" s="8" t="inlineStr">
         <is>
-          <t>Sokl nad terénem — provětraný obklad (S03b) — Provětrávaná mezera s kotevním roštem 40 mm + keramický obklad 20 mm — sokl nad úrovní terénu</t>
+          <t>Střecha — pojistná HI folie pod Al krytinu (S10) — Pojistná hydroizolační folie pod hliníkovou falcovanou krytinu (nad celoplošným bedněním)</t>
         </is>
       </c>
       <c r="E117" s="20" t="inlineStr">
@@ -7847,13 +7847,13 @@
         </is>
       </c>
       <c r="F117" s="22" t="n">
-        <v>23</v>
+        <v>140.94</v>
       </c>
       <c r="G117" s="10" t="n"/>
       <c r="H117" s="10" t="n"/>
       <c r="I117" s="8" t="inlineStr">
         <is>
-          <t>obkladac</t>
+          <t>pokryvac</t>
         </is>
       </c>
       <c r="J117" s="8" t="inlineStr">
@@ -7873,12 +7873,12 @@
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Krov + střecha</t>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t>Střecha — pojistná HI folie pod Al krytinu (S10) — Pojistná hydroizolační folie pod hliníkovou falcovanou krytinu (nad celoplošným bedněním)</t>
+          <t>Demontáž vnějšího keram. obkladu suterénu (S03 stávající) — Demontáž stávajícího vnějšího keramického obkladu suterénní stěny (sokl) tl. 20 mm</t>
         </is>
       </c>
       <c r="E118" s="20" t="inlineStr">
@@ -7887,13 +7887,13 @@
         </is>
       </c>
       <c r="F118" s="22" t="n">
-        <v>140.94</v>
+        <v>23</v>
       </c>
       <c r="G118" s="10" t="n"/>
       <c r="H118" s="10" t="n"/>
       <c r="I118" s="8" t="inlineStr">
         <is>
-          <t>pokryvac</t>
+          <t>bourac</t>
         </is>
       </c>
       <c r="J118" s="8" t="inlineStr">
@@ -7908,17 +7908,17 @@
       </c>
       <c r="B119" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>HSV-5 Komunikace + vjezd</t>
         </is>
       </c>
       <c r="D119" s="8" t="inlineStr">
         <is>
-          <t>Demontáž vnějšího keram. obkladu suterénu (S03 stávající) — Demontáž stávajícího vnějšího keramického obkladu suterénní stěny (sokl) tl. 20 mm</t>
+          <t>Vjezd Dvořákova — napojení na komunikaci — Napojení vjezdu na ulici Dvořákova — vydláždění z betonových dlaždic + spádování na pozemek investora + odvodnění dešťové vody na pozemek (ne na komunikaci)</t>
         </is>
       </c>
       <c r="E119" s="20" t="inlineStr">
@@ -7926,14 +7926,12 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="F119" s="22" t="n">
-        <v>23</v>
-      </c>
+      <c r="F119" s="22" t="n"/>
       <c r="G119" s="10" t="n"/>
       <c r="H119" s="10" t="n"/>
       <c r="I119" s="8" t="inlineStr">
         <is>
-          <t>bourac</t>
+          <t>komunikace</t>
         </is>
       </c>
       <c r="J119" s="8" t="inlineStr">
@@ -7951,32 +7949,34 @@
           <t>260217_sklad</t>
         </is>
       </c>
-      <c r="C120" s="8" t="inlineStr">
-        <is>
-          <t>HSV-5 Komunikace + vjezd</t>
+      <c r="C120" s="21" t="inlineStr">
+        <is>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D120" s="8" t="inlineStr">
         <is>
-          <t>Vjezd Dvořákova — napojení na komunikaci — Napojení vjezdu na ulici Dvořákova — vydláždění z betonových dlaždic + spádování na pozemek investora + odvodnění dešťové vody na pozemek (ne na komunikaci)</t>
+          <t>[agregát] 2 položek: Bezpečnostní dveře RC3 sklad; Vjezdová brána</t>
         </is>
       </c>
       <c r="E120" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F120" s="22" t="n"/>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F120" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="G120" s="10" t="n"/>
       <c r="H120" s="10" t="n"/>
       <c r="I120" s="8" t="inlineStr">
         <is>
-          <t>komunikace</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J120" s="8" t="inlineStr">
         <is>
-          <t>URS-prop —</t>
+          <t>agregát</t>
         </is>
       </c>
     </row>
@@ -7991,12 +7991,12 @@
       </c>
       <c r="C121" s="21" t="inlineStr">
         <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D121" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 2 položek: Bezpečnostní dveře RC3 sklad; Vjezdová brána</t>
+          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
         </is>
       </c>
       <c r="E121" s="20" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="C122" s="21" t="inlineStr">
         <is>
-          <t>PSV-77 — Podlahy</t>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
+          <t>[agregát] 5 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+2 dalších)</t>
         </is>
       </c>
       <c r="E122" s="20" t="inlineStr">
@@ -8066,17 +8066,17 @@
       </c>
       <c r="B123" s="20" t="inlineStr">
         <is>
-          <t>260217_sklad</t>
+          <t>260219_dum</t>
         </is>
       </c>
       <c r="C123" s="21" t="inlineStr">
         <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
+          <t>M-21 — Elektroinstalace silnoproudá</t>
         </is>
       </c>
       <c r="D123" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 5 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+2 dalších)</t>
+          <t>[agregát] 8 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+5 dalších)</t>
         </is>
       </c>
       <c r="E123" s="20" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="C124" s="21" t="inlineStr">
         <is>
-          <t>M-21 — Elektroinstalace silnoproudá</t>
+          <t>M-24</t>
         </is>
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 8 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+5 dalších)</t>
+          <t>[agregát] 1 položek: Lokální odtah digestoří kuchyní</t>
         </is>
       </c>
       <c r="E124" s="20" t="inlineStr">
@@ -8151,12 +8151,12 @@
       </c>
       <c r="C125" s="21" t="inlineStr">
         <is>
-          <t>M-24</t>
+          <t>PSV-71 — Izolace HI + TI</t>
         </is>
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Lokální odtah digestoří kuchyní</t>
+          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
         </is>
       </c>
       <c r="E125" s="20" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="C126" s="21" t="inlineStr">
         <is>
-          <t>PSV-71 — Izolace HI + TI</t>
+          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
         </is>
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
+          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
         </is>
       </c>
       <c r="E126" s="20" t="inlineStr">
@@ -8231,12 +8231,12 @@
       </c>
       <c r="C127" s="21" t="inlineStr">
         <is>
-          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
+          <t>PSV-73 — Vytápění + komín</t>
         </is>
       </c>
       <c r="D127" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
+          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
         </is>
       </c>
       <c r="E127" s="20" t="inlineStr">
@@ -8271,12 +8271,12 @@
       </c>
       <c r="C128" s="21" t="inlineStr">
         <is>
-          <t>PSV-73 — Vytápění + komín</t>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
+          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
         </is>
       </c>
       <c r="E128" s="20" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="C129" s="21" t="inlineStr">
         <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
+          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
         </is>
       </c>
       <c r="E129" s="20" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="C130" s="21" t="inlineStr">
         <is>
-          <t>PSV-77 — Podlahy</t>
+          <t>PSV-78 — Povrchové úpravy</t>
         </is>
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
+          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
         </is>
       </c>
       <c r="E130" s="20" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="C131" s="21" t="inlineStr">
         <is>
-          <t>PSV-78 — Povrchové úpravy</t>
+          <t>PSV-95 — Detekce požární</t>
         </is>
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
+          <t>[agregát] 3 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A; Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
         </is>
       </c>
       <c r="E131" s="20" t="inlineStr">
@@ -8431,12 +8431,12 @@
       </c>
       <c r="C132" s="21" t="inlineStr">
         <is>
-          <t>PSV-95 — Detekce požární</t>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
         </is>
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 3 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A; Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
+          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
         </is>
       </c>
       <c r="E132" s="20" t="inlineStr">
@@ -8460,48 +8460,8 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="20" t="n">
-        <v>132</v>
-      </c>
-      <c r="B133" s="20" t="inlineStr">
-        <is>
-          <t>260219_dum</t>
-        </is>
-      </c>
-      <c r="C133" s="21" t="inlineStr">
-        <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
-        </is>
-      </c>
-      <c r="D133" s="8" t="inlineStr">
-        <is>
-          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
-        </is>
-      </c>
-      <c r="E133" s="20" t="inlineStr">
-        <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F133" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G133" s="10" t="n"/>
-      <c r="H133" s="10" t="n"/>
-      <c r="I133" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J133" s="8" t="inlineStr">
-        <is>
-          <t>agregát</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J133"/>
+  <autoFilter ref="A1:J132"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8512,7 +8472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R204"/>
+  <dimension ref="A1:R203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -14067,17 +14027,17 @@
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>Demontáž oken a dveří</t>
+          <t>Demontáž zařizovacích předmětů</t>
         </is>
       </c>
       <c r="D80" s="20" t="inlineStr">
         <is>
-          <t>968071120</t>
+          <t>725900001</t>
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>Demontáž všech oken a dveří stávajících (recyklace)</t>
+          <t>Demontáž všech sanitárních zařizovacích předmětů (WC, umyvadla, baterie, sprcha)</t>
         </is>
       </c>
       <c r="F80" s="20" t="inlineStr">
@@ -14086,7 +14046,7 @@
         </is>
       </c>
       <c r="G80" s="23" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="H80" s="10" t="n"/>
       <c r="I80" s="10" t="n"/>
@@ -14105,12 +14065,12 @@
       </c>
       <c r="M80" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3 — VŠECHNY okna a dveře demontovány</t>
+          <t>TZ ARS dům §3 — zařizovací předměty kompletně demontovány</t>
         </is>
       </c>
       <c r="N80" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O80" s="26" t="inlineStr">
@@ -14132,26 +14092,26 @@
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>Demontáž zařizovacích předmětů</t>
+          <t>Odvoz suti a likvidace</t>
         </is>
       </c>
       <c r="D81" s="20" t="inlineStr">
         <is>
-          <t>725900001</t>
+          <t>997013501</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>Demontáž všech sanitárních zařizovacích předmětů (WC, umyvadla, baterie, sprcha)</t>
+          <t>Odvoz a likvidace stavební suti dle vyhl. 8/2021 Sb. — celková tonáž odpadů</t>
         </is>
       </c>
       <c r="F81" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G81" s="23" t="n">
-        <v>12</v>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G81" s="22" t="n">
+        <v>56.5</v>
       </c>
       <c r="H81" s="10" t="n"/>
       <c r="I81" s="10" t="n"/>
@@ -14161,7 +14121,7 @@
         </is>
       </c>
       <c r="K81" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L81" s="20" t="inlineStr">
         <is>
@@ -14170,12 +14130,12 @@
       </c>
       <c r="M81" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3 — zařizovací předměty kompletně demontovány</t>
+          <t>TZ B m.10.e bilance odpadů</t>
         </is>
       </c>
       <c r="N81" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#9</t>
         </is>
       </c>
       <c r="O81" s="26" t="inlineStr">
@@ -14197,26 +14157,26 @@
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>Odvoz suti a likvidace</t>
+          <t>Demontáž oken</t>
         </is>
       </c>
       <c r="D82" s="20" t="inlineStr">
         <is>
-          <t>997013501</t>
+          <t>978013181</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>Odvoz a likvidace stavební suti dle vyhl. 8/2021 Sb. — celková tonáž odpadů</t>
+          <t>Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
         </is>
       </c>
       <c r="F82" s="20" t="inlineStr">
         <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="G82" s="22" t="n">
-        <v>56.5</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G82" s="23" t="n">
+        <v>16</v>
       </c>
       <c r="H82" s="10" t="n"/>
       <c r="I82" s="10" t="n"/>
@@ -14226,30 +14186,34 @@
         </is>
       </c>
       <c r="K82" s="24" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="L82" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>matched_websearch_verified</t>
         </is>
       </c>
       <c r="M82" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10.e bilance odpadů</t>
+          <t>DXF blocks okno* (Path C Tier 4) + TZ ARS — všechna okna nová</t>
         </is>
       </c>
       <c r="N82" s="20" t="inlineStr">
         <is>
-          <t>#9</t>
-        </is>
-      </c>
-      <c r="O82" s="26" t="inlineStr">
-        <is>
-          <t>ANO</t>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="O82" s="25" t="inlineStr">
+        <is>
+          <t>OVĚŘENO ✓</t>
         </is>
       </c>
       <c r="P82" s="41" t="n"/>
-      <c r="Q82" s="41" t="n"/>
+      <c r="Q82" s="41" t="inlineStr">
+        <is>
+          <t>F2_DEDUP_DEMONTAZ_OKEN_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="20" t="n">
@@ -14262,7 +14226,7 @@
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>Demontáž oken</t>
+          <t>Demontáž vstupních dveří venkovních</t>
         </is>
       </c>
       <c r="D83" s="20" t="inlineStr">
@@ -14272,7 +14236,7 @@
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
+          <t>Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
         </is>
       </c>
       <c r="F83" s="20" t="inlineStr">
@@ -14281,7 +14245,7 @@
         </is>
       </c>
       <c r="G83" s="23" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="H83" s="10" t="n"/>
       <c r="I83" s="10" t="n"/>
@@ -14300,7 +14264,7 @@
       </c>
       <c r="M83" s="8" t="inlineStr">
         <is>
-          <t>DXF blocks okno* (Path C Tier 4) + TZ ARS — všechna okna nová</t>
+          <t>DXF blocks dveře (vstupní 2) + TZ ARS — 'plastové vstupní dveře' x 2</t>
         </is>
       </c>
       <c r="N83" s="20" t="inlineStr">
@@ -14331,17 +14295,17 @@
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>Demontáž vstupních dveří venkovních</t>
+          <t>Demontáž vnitřních dveří vč. zárubní</t>
         </is>
       </c>
       <c r="D84" s="20" t="inlineStr">
         <is>
-          <t>978013181</t>
+          <t>968072456</t>
         </is>
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
+          <t>Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
         </is>
       </c>
       <c r="F84" s="20" t="inlineStr">
@@ -14350,7 +14314,7 @@
         </is>
       </c>
       <c r="G84" s="23" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H84" s="10" t="n"/>
       <c r="I84" s="10" t="n"/>
@@ -14360,16 +14324,16 @@
         </is>
       </c>
       <c r="K84" s="24" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="L84" s="20" t="inlineStr">
         <is>
-          <t>matched_websearch_verified</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M84" s="8" t="inlineStr">
         <is>
-          <t>DXF blocks dveře (vstupní 2) + TZ ARS — 'plastové vstupní dveře' x 2</t>
+          <t>DXF SM__dveře polyline count → estimate (Path C Tier 4)</t>
         </is>
       </c>
       <c r="N84" s="20" t="inlineStr">
@@ -14377,9 +14341,9 @@
           <t>#3</t>
         </is>
       </c>
-      <c r="O84" s="25" t="inlineStr">
-        <is>
-          <t>OVĚŘENO ✓</t>
+      <c r="O84" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
         </is>
       </c>
       <c r="P84" s="41" t="n"/>
@@ -14400,26 +14364,26 @@
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>Demontáž vnitřních dveří vč. zárubní</t>
+          <t>Bourání zdiva komínu</t>
         </is>
       </c>
       <c r="D85" s="20" t="inlineStr">
         <is>
-          <t>968072456</t>
+          <t>962024141</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
+          <t>Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
         </is>
       </c>
       <c r="F85" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G85" s="23" t="n">
-        <v>15</v>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="G85" s="22" t="n">
+        <v>0.6</v>
       </c>
       <c r="H85" s="10" t="n"/>
       <c r="I85" s="10" t="n"/>
@@ -14429,21 +14393,21 @@
         </is>
       </c>
       <c r="K85" s="24" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="L85" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M85" s="8" t="inlineStr">
         <is>
-          <t>DXF SM__dveře polyline count → estimate (Path C Tier 4)</t>
+          <t>DXF dum_DPZ řez A-A bourání + POZN.1.02 z půdorysů bourání</t>
         </is>
       </c>
       <c r="N85" s="20" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>#9</t>
         </is>
       </c>
       <c r="O85" s="26" t="inlineStr">
@@ -14454,7 +14418,7 @@
       <c r="P85" s="41" t="n"/>
       <c r="Q85" s="41" t="inlineStr">
         <is>
-          <t>GAP_002</t>
+          <t>PER_DRAWING_GAP_POZN_1_02; URS_PHASE5B_FAMILY_VERIFIED; CHATGPT_KOMIN_QTY_FIX_2026-05-29</t>
         </is>
       </c>
     </row>
@@ -14469,17 +14433,17 @@
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>Bourání zdiva komínu</t>
+          <t>Bourání venkovních konstrukcí</t>
         </is>
       </c>
       <c r="D86" s="20" t="inlineStr">
         <is>
-          <t>962024141</t>
+          <t>961044111</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
+          <t>Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
         </is>
       </c>
       <c r="F86" s="20" t="inlineStr">
@@ -14488,7 +14452,7 @@
         </is>
       </c>
       <c r="G86" s="22" t="n">
-        <v>0.6</v>
+        <v>8</v>
       </c>
       <c r="H86" s="10" t="n"/>
       <c r="I86" s="10" t="n"/>
@@ -14498,7 +14462,7 @@
         </is>
       </c>
       <c r="K86" s="24" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="L86" s="20" t="inlineStr">
         <is>
@@ -14507,7 +14471,7 @@
       </c>
       <c r="M86" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ řez A-A bourání + POZN.1.02 z půdorysů bourání</t>
+          <t>DXF dum_DPZ řez A-A bourání + POZN.1.03 + půdorys bourání</t>
         </is>
       </c>
       <c r="N86" s="20" t="inlineStr">
@@ -14523,7 +14487,7 @@
       <c r="P86" s="41" t="n"/>
       <c r="Q86" s="41" t="inlineStr">
         <is>
-          <t>PER_DRAWING_GAP_POZN_1_02; URS_PHASE5B_FAMILY_VERIFIED; CHATGPT_KOMIN_QTY_FIX_2026-05-29</t>
+          <t>PER_DRAWING_GAP_POZN_1_03; URS_PHASE5B_FAMILY_VERIFIED</t>
         </is>
       </c>
     </row>
@@ -14538,50 +14502,50 @@
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>Bourání venkovních konstrukcí</t>
+          <t>Demontáž vnějšího keram. obkladu suterénu (S03 stávající)</t>
         </is>
       </c>
       <c r="D87" s="20" t="inlineStr">
         <is>
-          <t>961044111</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
+          <t>Demontáž stávajícího vnějšího keramického obkladu suterénní stěny (sokl) tl. 20 mm</t>
         </is>
       </c>
       <c r="F87" s="20" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G87" s="22" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H87" s="10" t="n"/>
       <c r="I87" s="10" t="n"/>
       <c r="J87" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>bourac</t>
         </is>
       </c>
       <c r="K87" s="24" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="L87" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M87" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ řez A-A bourání + POZN.1.03 + půdorys bourání</t>
+          <t>skladba S03 stávající (vnější keram. obklad) + Řez A-A sokl</t>
         </is>
       </c>
       <c r="N87" s="20" t="inlineStr">
         <is>
-          <t>#9</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O87" s="26" t="inlineStr">
@@ -14589,10 +14553,14 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P87" s="41" t="n"/>
+      <c r="P87" s="41" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
       <c r="Q87" s="41" t="inlineStr">
         <is>
-          <t>PER_DRAWING_GAP_POZN_1_03; URS_PHASE5B_FAMILY_VERIFIED</t>
+          <t>SKLADBY_GAPS_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -14602,12 +14570,12 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>HSV-7 Fasáda + zateplení</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>Demontáž vnějšího keram. obkladu suterénu (S03 stávající)</t>
+          <t>Sokl suterénu — sanační zateplení (S03)</t>
         </is>
       </c>
       <c r="D88" s="20" t="inlineStr">
@@ -14617,7 +14585,7 @@
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávajícího vnějšího keramického obkladu suterénní stěny (sokl) tl. 20 mm</t>
+          <t>Sanační zateplení soklu — sanační izolační deska Styrcon 200 + lepící tmel (Lepstyr plus) + armovací vrstva s tkaninou + penetrace</t>
         </is>
       </c>
       <c r="F88" s="20" t="inlineStr">
@@ -14632,7 +14600,7 @@
       <c r="I88" s="10" t="n"/>
       <c r="J88" s="8" t="inlineStr">
         <is>
-          <t>bourac</t>
+          <t>fasader</t>
         </is>
       </c>
       <c r="K88" s="24" t="n">
@@ -14645,7 +14613,7 @@
       </c>
       <c r="M88" s="8" t="inlineStr">
         <is>
-          <t>skladba S03 stávající (vnější keram. obklad) + Řez A-A sokl</t>
+          <t>Řez A-A sokl tags (S03b -0.200/-0.975) + obvod ETICS</t>
         </is>
       </c>
       <c r="N88" s="20" t="inlineStr">
@@ -14680,7 +14648,7 @@
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>Sokl suterénu — sanační zateplení (S03)</t>
+          <t>Sokl pod terénem — drenážní nopová folie (S03a)</t>
         </is>
       </c>
       <c r="D89" s="20" t="inlineStr">
@@ -14690,7 +14658,7 @@
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>Sanační zateplení soklu — sanační izolační deska Styrcon 200 + lepící tmel (Lepstyr plus) + armovací vrstva s tkaninou + penetrace</t>
+          <t>Drenážní vrstva — nopová folie tl. 20 mm na suterénní stěnu pod úrovní terénu</t>
         </is>
       </c>
       <c r="F89" s="20" t="inlineStr">
@@ -14705,7 +14673,7 @@
       <c r="I89" s="10" t="n"/>
       <c r="J89" s="8" t="inlineStr">
         <is>
-          <t>fasader</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K89" s="24" t="n">
@@ -14718,7 +14686,7 @@
       </c>
       <c r="M89" s="8" t="inlineStr">
         <is>
-          <t>Řez A-A sokl tags (S03b -0.200/-0.975) + obvod ETICS</t>
+          <t>Řez A-A/C-C sokl + obvod ETICS</t>
         </is>
       </c>
       <c r="N89" s="20" t="inlineStr">
@@ -14753,7 +14721,7 @@
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>Sokl pod terénem — drenážní nopová folie (S03a)</t>
+          <t>Sokl nad terénem — provětraný obklad (S03b)</t>
         </is>
       </c>
       <c r="D90" s="20" t="inlineStr">
@@ -14763,7 +14731,7 @@
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>Drenážní vrstva — nopová folie tl. 20 mm na suterénní stěnu pod úrovní terénu</t>
+          <t>Provětrávaná mezera s kotevním roštem 40 mm + keramický obklad 20 mm — sokl nad úrovní terénu</t>
         </is>
       </c>
       <c r="F90" s="20" t="inlineStr">
@@ -14778,7 +14746,7 @@
       <c r="I90" s="10" t="n"/>
       <c r="J90" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>obkladac</t>
         </is>
       </c>
       <c r="K90" s="24" t="n">
@@ -14791,7 +14759,7 @@
       </c>
       <c r="M90" s="8" t="inlineStr">
         <is>
-          <t>Řez A-A/C-C sokl + obvod ETICS</t>
+          <t>Řez A-A sokl tags S03b + obvod ETICS</t>
         </is>
       </c>
       <c r="N90" s="20" t="inlineStr">
@@ -14821,22 +14789,22 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda + zateplení</t>
+          <t>HSV-7 Fasáda ETICS</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>Sokl nad terénem — provětraný obklad (S03b)</t>
+          <t>Příprava podkladu</t>
         </is>
       </c>
       <c r="D91" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>622401110</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>Provětrávaná mezera s kotevním roštem 40 mm + keramický obklad 20 mm — sokl nad úrovní terénu</t>
+          <t>Příprava fasádního podkladu — očištění tlakovou vodou, vyspravení omítek, fungicidní nátěr</t>
         </is>
       </c>
       <c r="F91" s="20" t="inlineStr">
@@ -14845,17 +14813,17 @@
         </is>
       </c>
       <c r="G91" s="22" t="n">
-        <v>23</v>
+        <v>276.7</v>
       </c>
       <c r="H91" s="10" t="n"/>
       <c r="I91" s="10" t="n"/>
       <c r="J91" s="8" t="inlineStr">
         <is>
-          <t>obkladac</t>
+          <t>fasadnik_etics</t>
         </is>
       </c>
       <c r="K91" s="24" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="L91" s="20" t="inlineStr">
         <is>
@@ -14864,12 +14832,12 @@
       </c>
       <c r="M91" s="8" t="inlineStr">
         <is>
-          <t>Řez A-A sokl tags S03b + obvod ETICS</t>
+          <t>TZ ARS dům §3.2 — ETICS kontaktní, podklad existující omítka + DXF perimeter</t>
         </is>
       </c>
       <c r="N91" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="O91" s="26" t="inlineStr">
@@ -14879,14 +14847,10 @@
       </c>
       <c r="P91" s="41" t="inlineStr">
         <is>
-          <t>S03</t>
-        </is>
-      </c>
-      <c r="Q91" s="41" t="inlineStr">
-        <is>
-          <t>SKLADBY_GAPS_2026-06-01</t>
-        </is>
-      </c>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="Q91" s="41" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="20" t="n">
@@ -14899,17 +14863,17 @@
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>Příprava podkladu</t>
+          <t>ETICS EPS 70F grey 160 mm</t>
         </is>
       </c>
       <c r="D92" s="20" t="inlineStr">
         <is>
-          <t>622401110</t>
+          <t>622221121</t>
         </is>
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>Příprava fasádního podkladu — očištění tlakovou vodou, vyspravení omítek, fungicidní nátěr</t>
+          <t>ETICS kontaktní zateplení — EPS 70F grey λ=0.032 tl. 160 mm + síťka + lepidlo + zatírací stěrka (řez S01+S12a explicit, ne 200 mm fallback)</t>
         </is>
       </c>
       <c r="F92" s="20" t="inlineStr">
@@ -14932,12 +14896,12 @@
       </c>
       <c r="L92" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M92" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — ETICS kontaktní, podklad existující omítka + DXF perimeter</t>
+          <t>TZ ARS dům §3.2 EXPLICIT 'fasádní EPS 70f grey (λ=0,032 W/mK)' + PBŘ EXPLICIT 'EPS tl. max. 200 mm' + DXF perimeter</t>
         </is>
       </c>
       <c r="N92" s="20" t="inlineStr">
@@ -14952,10 +14916,14 @@
       </c>
       <c r="P92" s="41" t="inlineStr">
         <is>
-          <t>S01</t>
-        </is>
-      </c>
-      <c r="Q92" s="41" t="n"/>
+          <t>S01, S12a</t>
+        </is>
+      </c>
+      <c r="Q92" s="41" t="inlineStr">
+        <is>
+          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="20" t="n">
@@ -14968,17 +14936,17 @@
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>ETICS EPS 70F grey 160 mm</t>
+          <t>ETICS sokl XPS</t>
         </is>
       </c>
       <c r="D93" s="20" t="inlineStr">
         <is>
-          <t>622221121</t>
+          <t>622223111</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>ETICS kontaktní zateplení — EPS 70F grey λ=0.032 tl. 160 mm + síťka + lepidlo + zatírací stěrka (řez S01+S12a explicit, ne 200 mm fallback)</t>
+          <t>ETICS sokl — XPS λ=0.034 tl. 120 mm + soklový profil + cihelný obklad spárovaný</t>
         </is>
       </c>
       <c r="F93" s="20" t="inlineStr">
@@ -14987,7 +14955,7 @@
         </is>
       </c>
       <c r="G93" s="22" t="n">
-        <v>276.7</v>
+        <v>13.5</v>
       </c>
       <c r="H93" s="10" t="n"/>
       <c r="I93" s="10" t="n"/>
@@ -15006,12 +14974,12 @@
       </c>
       <c r="M93" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 EXPLICIT 'fasádní EPS 70f grey (λ=0,032 W/mK)' + PBŘ EXPLICIT 'EPS tl. max. 200 mm' + DXF perimeter</t>
+          <t>TZ ARS dům §3.2 — sokl XPS + cihelný obklad + DXF perimeter</t>
         </is>
       </c>
       <c r="N93" s="20" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O93" s="26" t="inlineStr">
@@ -15021,7 +14989,7 @@
       </c>
       <c r="P93" s="41" t="inlineStr">
         <is>
-          <t>S01, S12a</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="Q93" s="41" t="inlineStr">
@@ -15041,26 +15009,26 @@
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>ETICS sokl XPS</t>
+          <t>Špalety EPS</t>
         </is>
       </c>
       <c r="D94" s="20" t="inlineStr">
         <is>
-          <t>622223111</t>
+          <t>622221221</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>ETICS sokl — XPS λ=0.034 tl. 120 mm + soklový profil + cihelný obklad spárovaný</t>
+          <t>Špalety oken — EPS přesah 35-40 mm + síťka + omítka</t>
         </is>
       </c>
       <c r="F94" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G94" s="22" t="n">
-        <v>13.5</v>
+        <v>82.2</v>
       </c>
       <c r="H94" s="10" t="n"/>
       <c r="I94" s="10" t="n"/>
@@ -15070,21 +15038,21 @@
         </is>
       </c>
       <c r="K94" s="24" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
       <c r="L94" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M94" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — sokl XPS + cihelný obklad + DXF perimeter</t>
+          <t>DXF okna per typ bbox + TZ ARS §3.2 EPS přesah na špaletách 35-40 mm</t>
         </is>
       </c>
       <c r="N94" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O94" s="26" t="inlineStr">
@@ -15094,14 +15062,10 @@
       </c>
       <c r="P94" s="41" t="inlineStr">
         <is>
-          <t>S01</t>
-        </is>
-      </c>
-      <c r="Q94" s="41" t="inlineStr">
-        <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
-        </is>
-      </c>
+          <t>S01, S12a</t>
+        </is>
+      </c>
+      <c r="Q94" s="41" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="20" t="n">
@@ -15114,7 +15078,7 @@
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>Špalety EPS</t>
+          <t>Profilace fasády</t>
         </is>
       </c>
       <c r="D95" s="20" t="inlineStr">
@@ -15124,16 +15088,16 @@
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>Špalety oken — EPS přesah 35-40 mm + síťka + omítka</t>
+          <t>Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
         </is>
       </c>
       <c r="F95" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G95" s="22" t="n">
-        <v>82.2</v>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="G95" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H95" s="10" t="n"/>
       <c r="I95" s="10" t="n"/>
@@ -15152,12 +15116,12 @@
       </c>
       <c r="M95" s="8" t="inlineStr">
         <is>
-          <t>DXF okna per typ bbox + TZ ARS §3.2 EPS přesah na špaletách 35-40 mm</t>
+          <t>TZ ARS dům §3.2 — profilace různými tl. EPS</t>
         </is>
       </c>
       <c r="N95" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O95" s="26" t="inlineStr">
@@ -15183,26 +15147,26 @@
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>Profilace fasády</t>
+          <t>Tenkovrstvá omítka pastovitá</t>
         </is>
       </c>
       <c r="D96" s="20" t="inlineStr">
         <is>
-          <t>622221221</t>
+          <t>622521111</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
+          <t>Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
         </is>
       </c>
       <c r="F96" s="20" t="inlineStr">
         <is>
-          <t>soubor</t>
-        </is>
-      </c>
-      <c r="G96" s="23" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G96" s="22" t="n">
+        <v>290.2</v>
       </c>
       <c r="H96" s="10" t="n"/>
       <c r="I96" s="10" t="n"/>
@@ -15212,16 +15176,16 @@
         </is>
       </c>
       <c r="K96" s="24" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
       <c r="L96" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M96" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — profilace různými tl. EPS</t>
+          <t>TZ ARS dům §3.2 — pastovitá probarvená lomená bílá + DXF perimeter</t>
         </is>
       </c>
       <c r="N96" s="20" t="inlineStr">
@@ -15236,10 +15200,14 @@
       </c>
       <c r="P96" s="41" t="inlineStr">
         <is>
-          <t>S01, S12a</t>
-        </is>
-      </c>
-      <c r="Q96" s="41" t="n"/>
+          <t>S01, S12a, S12b</t>
+        </is>
+      </c>
+      <c r="Q96" s="41" t="inlineStr">
+        <is>
+          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="20" t="n">
@@ -15247,22 +15215,22 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda ETICS</t>
+          <t>PSV-71 Izolace HI</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>Tenkovrstvá omítka pastovitá</t>
+          <t>HI pod ŽB deskou 1.NP</t>
         </is>
       </c>
       <c r="D97" s="20" t="inlineStr">
         <is>
-          <t>622521111</t>
+          <t>712311101</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
+          <t>Hydroizolace pod ŽB deskou 1.NP — modifikované asfaltové pásy SBS 2× (zároveň protiradonová bariéra)</t>
         </is>
       </c>
       <c r="F97" s="20" t="inlineStr">
@@ -15271,17 +15239,17 @@
         </is>
       </c>
       <c r="G97" s="22" t="n">
-        <v>290.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="H97" s="10" t="n"/>
       <c r="I97" s="10" t="n"/>
       <c r="J97" s="8" t="inlineStr">
         <is>
-          <t>fasadnik_etics</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K97" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L97" s="20" t="inlineStr">
         <is>
@@ -15290,12 +15258,12 @@
       </c>
       <c r="M97" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — pastovitá probarvená lomená bílá + DXF perimeter</t>
+          <t>TZ ARS dům §4 + statika §5.5 — asfaltové pásy mod. proti radonu</t>
         </is>
       </c>
       <c r="N97" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="O97" s="26" t="inlineStr">
@@ -15303,14 +15271,10 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P97" s="41" t="inlineStr">
-        <is>
-          <t>S01, S12a, S12b</t>
-        </is>
-      </c>
+      <c r="P97" s="41" t="n"/>
       <c r="Q97" s="41" t="inlineStr">
         <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+          <t>URS_PHASE5B_FAMILY_VERIFIED; URS_PHASE5B_FAMILY_VERIFIED</t>
         </is>
       </c>
     </row>
@@ -15325,26 +15289,26 @@
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>HI pod ŽB deskou 1.NP</t>
+          <t>Odvětrání radonu z podloží</t>
         </is>
       </c>
       <c r="D98" s="20" t="inlineStr">
         <is>
-          <t>712311101</t>
+          <t>712381111</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolace pod ŽB deskou 1.NP — modifikované asfaltové pásy SBS 2× (zároveň protiradonová bariéra)</t>
+          <t>Odvětrání radonu z podloží — perforované DN50 trubky v štěrkovém loži + výdech nad střechu</t>
         </is>
       </c>
       <c r="F98" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G98" s="22" t="n">
-        <v>80.40000000000001</v>
+        <v>12</v>
       </c>
       <c r="H98" s="10" t="n"/>
       <c r="I98" s="10" t="n"/>
@@ -15363,12 +15327,12 @@
       </c>
       <c r="M98" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 + statika §5.5 — asfaltové pásy mod. proti radonu</t>
+          <t>TZ statika §5.5 'ochrana proti radonu — modifikované asf. pásy + odvětrání'</t>
         </is>
       </c>
       <c r="N98" s="20" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O98" s="26" t="inlineStr">
@@ -15379,7 +15343,7 @@
       <c r="P98" s="41" t="n"/>
       <c r="Q98" s="41" t="inlineStr">
         <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED; URS_PHASE5B_FAMILY_VERIFIED</t>
+          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
         </is>
       </c>
     </row>
@@ -15394,26 +15358,26 @@
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>Odvětrání radonu z podloží</t>
-        </is>
-      </c>
-      <c r="D99" s="20" t="inlineStr">
-        <is>
-          <t>712381111</t>
+          <t>HI koupelny 1.NP + 2.NP + 3.NP</t>
+        </is>
+      </c>
+      <c r="D99" s="27" t="inlineStr">
+        <is>
+          <t>711??? ?</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>Odvětrání radonu z podloží — perforované DN50 trubky v štěrkovém loži + výdech nad střechu</t>
+          <t>Hydroizolační stěrka koupelen 3 ks — podlaha + sokl 200 mm + sprchový kout výška 2.0 m</t>
         </is>
       </c>
       <c r="F99" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G99" s="22" t="n">
-        <v>12</v>
+        <v>40.5</v>
       </c>
       <c r="H99" s="10" t="n"/>
       <c r="I99" s="10" t="n"/>
@@ -15423,7 +15387,7 @@
         </is>
       </c>
       <c r="K99" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L99" s="20" t="inlineStr">
         <is>
@@ -15432,12 +15396,12 @@
       </c>
       <c r="M99" s="8" t="inlineStr">
         <is>
-          <t>TZ statika §5.5 'ochrana proti radonu — modifikované asf. pásy + odvětrání'</t>
+          <t>DXF dum_DPZ MTEXT labels: 3× koupelna; TZ ARS — HI vana koupelny</t>
         </is>
       </c>
       <c r="N99" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#4</t>
         </is>
       </c>
       <c r="O99" s="26" t="inlineStr">
@@ -15458,22 +15422,22 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace HI</t>
+          <t>PSV-71 Izolace TI</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>HI koupelny 1.NP + 2.NP + 3.NP</t>
+          <t>Podlahový EPS 150</t>
         </is>
       </c>
       <c r="D100" s="27" t="inlineStr">
         <is>
-          <t>711??? ?</t>
+          <t>713121??? ?</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolační stěrka koupelen 3 ks — podlaha + sokl 200 mm + sprchový kout výška 2.0 m</t>
+          <t>Podlahový EPS 150 λ=0.035 tl. 120 mm — pod betonový potěr 1.NP a 3.NP</t>
         </is>
       </c>
       <c r="F100" s="20" t="inlineStr">
@@ -15482,17 +15446,17 @@
         </is>
       </c>
       <c r="G100" s="22" t="n">
-        <v>40.5</v>
+        <v>177.5</v>
       </c>
       <c r="H100" s="10" t="n"/>
       <c r="I100" s="10" t="n"/>
       <c r="J100" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>izolater_TI</t>
         </is>
       </c>
       <c r="K100" s="24" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L100" s="20" t="inlineStr">
         <is>
@@ -15501,7 +15465,7 @@
       </c>
       <c r="M100" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT labels: 3× koupelna; TZ ARS — HI vana koupelny</t>
+          <t>TZ ARS dům §4 — EPS 150 λ=0.035 tl. 120 mm</t>
         </is>
       </c>
       <c r="N100" s="20" t="inlineStr">
@@ -15532,7 +15496,7 @@
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>Podlahový EPS 150</t>
+          <t>Kročejová EPS nad ocelobeton</t>
         </is>
       </c>
       <c r="D101" s="27" t="inlineStr">
@@ -15542,7 +15506,7 @@
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>Podlahový EPS 150 λ=0.035 tl. 120 mm — pod betonový potěr 1.NP a 3.NP</t>
+          <t>Kročejová EPS 150 / 30 dB tl. 40 mm nad ocelobetonovým stropem 2.NP/3.NP</t>
         </is>
       </c>
       <c r="F101" s="20" t="inlineStr">
@@ -15551,7 +15515,7 @@
         </is>
       </c>
       <c r="G101" s="22" t="n">
-        <v>177.5</v>
+        <v>104.4</v>
       </c>
       <c r="H101" s="10" t="n"/>
       <c r="I101" s="10" t="n"/>
@@ -15561,7 +15525,7 @@
         </is>
       </c>
       <c r="K101" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L101" s="20" t="inlineStr">
         <is>
@@ -15570,12 +15534,12 @@
       </c>
       <c r="M101" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — EPS 150 λ=0.035 tl. 120 mm</t>
+          <t>TZ ARS dům §4 — kročejová EPS shora ocelobeton</t>
         </is>
       </c>
       <c r="N101" s="20" t="inlineStr">
         <is>
-          <t>#4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O101" s="26" t="inlineStr">
@@ -15583,10 +15547,14 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P101" s="41" t="n"/>
+      <c r="P101" s="41" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
       <c r="Q101" s="41" t="inlineStr">
         <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+          <t>D2_KROCEJOVA_30_to_40_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -15596,41 +15564,41 @@
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace TI</t>
+          <t>PSV-76 Klempíř</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>Kročejová EPS nad ocelobeton</t>
-        </is>
-      </c>
-      <c r="D102" s="27" t="inlineStr">
-        <is>
-          <t>713121??? ?</t>
+          <t>Oplechování krytiny</t>
+        </is>
+      </c>
+      <c r="D102" s="20" t="inlineStr">
+        <is>
+          <t>764312235</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>Kročejová EPS 150 / 30 dB tl. 40 mm nad ocelobetonovým stropem 2.NP/3.NP</t>
+          <t>Klempířské oplechování krytiny — úžlabí, hřeben, štítové lemy (Al / Pzn lakovaný 0.55 mm)</t>
         </is>
       </c>
       <c r="F102" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G102" s="22" t="n">
-        <v>104.4</v>
+        <v>69.5</v>
       </c>
       <c r="H102" s="10" t="n"/>
       <c r="I102" s="10" t="n"/>
       <c r="J102" s="8" t="inlineStr">
         <is>
-          <t>izolater_TI</t>
+          <t>klempir</t>
         </is>
       </c>
       <c r="K102" s="24" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="L102" s="20" t="inlineStr">
         <is>
@@ -15639,12 +15607,12 @@
       </c>
       <c r="M102" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — kročejová EPS shora ocelobeton</t>
+          <t>DXF MA_klempíř (75.4 m) + SM__ klempířina (98.4 m) total = 173.8 m × 0.40 split heuristic — Path C Tier 3</t>
         </is>
       </c>
       <c r="N102" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O102" s="26" t="inlineStr">
@@ -15652,14 +15620,15 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P102" s="41" t="inlineStr">
-        <is>
-          <t>S09</t>
-        </is>
-      </c>
+      <c r="P102" s="41" t="n"/>
       <c r="Q102" s="41" t="inlineStr">
         <is>
-          <t>D2_KROCEJOVA_30_to_40_2026-06-01</t>
+          <t>URS_PHASE5B_FAMILY_VERIFIED_CHAPTER_MATCH</t>
+        </is>
+      </c>
+      <c r="R102" s="41" t="inlineStr">
+        <is>
+          <t>PSV-76 Klempíř items sum 159.9 m vs DXF MA_klempíř + SM__ klempířina total 173.8 m, Δ -8.0 % (-13.9 m). Within ±15 % tolerance per CEV Matrix D.4 verdict (gate-3). FLAG for Karel site walkthrough — possible missing klempíř segment (small). Source: outputs/cev_matrix_d_cross_doc_consistency.json D.4.</t>
         </is>
       </c>
     </row>
@@ -15674,17 +15643,17 @@
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>Oplechování krytiny</t>
+          <t>Venkovní parapety oken</t>
         </is>
       </c>
       <c r="D103" s="20" t="inlineStr">
         <is>
-          <t>764312235</t>
+          <t>764218201</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>Klempířské oplechování krytiny — úžlabí, hřeben, štítové lemy (Al / Pzn lakovaný 0.55 mm)</t>
+          <t>Venkovní parapety oken — Pzn plech lakovaný 250 mm × tl. 0.55 mm × 16 ks oken</t>
         </is>
       </c>
       <c r="F103" s="20" t="inlineStr">
@@ -15693,7 +15662,7 @@
         </is>
       </c>
       <c r="G103" s="22" t="n">
-        <v>69.5</v>
+        <v>20.8</v>
       </c>
       <c r="H103" s="10" t="n"/>
       <c r="I103" s="10" t="n"/>
@@ -15703,7 +15672,7 @@
         </is>
       </c>
       <c r="K103" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L103" s="20" t="inlineStr">
         <is>
@@ -15712,12 +15681,12 @@
       </c>
       <c r="M103" s="8" t="inlineStr">
         <is>
-          <t>DXF MA_klempíř (75.4 m) + SM__ klempířina (98.4 m) total = 173.8 m × 0.40 split heuristic — Path C Tier 3</t>
+          <t>DXF okna 16 ks INSERT blocks + standard parapet width</t>
         </is>
       </c>
       <c r="N103" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O103" s="26" t="inlineStr">
@@ -15748,17 +15717,17 @@
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>Venkovní parapety oken</t>
+          <t>Dešťové svody + žlaby</t>
         </is>
       </c>
       <c r="D104" s="20" t="inlineStr">
         <is>
-          <t>764218201</t>
+          <t>764454802</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>Venkovní parapety oken — Pzn plech lakovaný 250 mm × tl. 0.55 mm × 16 ks oken</t>
+          <t>Dešťové svody Pzn 100 mm + žlaby — 4 svody × ~14 m + žlaby per obvod střechy</t>
         </is>
       </c>
       <c r="F104" s="20" t="inlineStr">
@@ -15767,7 +15736,7 @@
         </is>
       </c>
       <c r="G104" s="22" t="n">
-        <v>20.8</v>
+        <v>43.5</v>
       </c>
       <c r="H104" s="10" t="n"/>
       <c r="I104" s="10" t="n"/>
@@ -15777,7 +15746,7 @@
         </is>
       </c>
       <c r="K104" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L104" s="20" t="inlineStr">
         <is>
@@ -15786,7 +15755,7 @@
       </c>
       <c r="M104" s="8" t="inlineStr">
         <is>
-          <t>DXF okna 16 ks INSERT blocks + standard parapet width</t>
+          <t>DXF klempířina lengths split + TZ ARS dešťové svody</t>
         </is>
       </c>
       <c r="N104" s="20" t="inlineStr">
@@ -15822,17 +15791,17 @@
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>Dešťové svody + žlaby</t>
+          <t>Vikýře + atika + závětrné lemy</t>
         </is>
       </c>
       <c r="D105" s="20" t="inlineStr">
         <is>
-          <t>764454802</t>
+          <t>764315235</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>Dešťové svody Pzn 100 mm + žlaby — 4 svody × ~14 m + žlaby per obvod střechy</t>
+          <t>Klempířské doplňky vikýřů + atika + závětrné lemy (4 vikýře komplexní detail)</t>
         </is>
       </c>
       <c r="F105" s="20" t="inlineStr">
@@ -15841,7 +15810,7 @@
         </is>
       </c>
       <c r="G105" s="22" t="n">
-        <v>43.5</v>
+        <v>26.1</v>
       </c>
       <c r="H105" s="10" t="n"/>
       <c r="I105" s="10" t="n"/>
@@ -15860,7 +15829,7 @@
       </c>
       <c r="M105" s="8" t="inlineStr">
         <is>
-          <t>DXF klempířina lengths split + TZ ARS dešťové svody</t>
+          <t>DXF klempířina geometry split + TZ ARS 4 vikýře</t>
         </is>
       </c>
       <c r="N105" s="20" t="inlineStr">
@@ -15891,50 +15860,50 @@
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Klempíř</t>
+          <t>PSV-76 Truhlář</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>Vikýře + atika + závětrné lemy</t>
+          <t>Dřevěné stupně schodišť</t>
         </is>
       </c>
       <c r="D106" s="20" t="inlineStr">
         <is>
-          <t>764315235</t>
+          <t>766811111</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>Klempířské doplňky vikýřů + atika + závětrné lemy (4 vikýře komplexní detail)</t>
+          <t>Dřevěné stupně ocelových schodišť (truhlářské, dub masiv tl. 40 mm)</t>
         </is>
       </c>
       <c r="F106" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G106" s="22" t="n">
-        <v>26.1</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G106" s="23" t="n">
+        <v>16</v>
       </c>
       <c r="H106" s="10" t="n"/>
       <c r="I106" s="10" t="n"/>
       <c r="J106" s="8" t="inlineStr">
         <is>
-          <t>klempir</t>
+          <t>truhlar</t>
         </is>
       </c>
       <c r="K106" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L106" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M106" s="8" t="inlineStr">
         <is>
-          <t>DXF klempířina geometry split + TZ ARS 4 vikýře</t>
+          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni truhlářské</t>
         </is>
       </c>
       <c r="N106" s="20" t="inlineStr">
@@ -15948,16 +15917,7 @@
         </is>
       </c>
       <c r="P106" s="41" t="n"/>
-      <c r="Q106" s="41" t="inlineStr">
-        <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED_CHAPTER_MATCH</t>
-        </is>
-      </c>
-      <c r="R106" s="41" t="inlineStr">
-        <is>
-          <t>PSV-76 Klempíř items sum 159.9 m vs DXF MA_klempíř + SM__ klempířina total 173.8 m, Δ -8.0 % (-13.9 m). Within ±15 % tolerance per CEV Matrix D.4 verdict (gate-3). FLAG for Karel site walkthrough — possible missing klempíř segment (small). Source: outputs/cev_matrix_d_cross_doc_consistency.json D.4.</t>
-        </is>
-      </c>
+      <c r="Q106" s="41" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="20" t="n">
@@ -15970,26 +15930,26 @@
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t>Dřevěné stupně schodišť</t>
-        </is>
-      </c>
-      <c r="D107" s="20" t="inlineStr">
-        <is>
-          <t>766811111</t>
+          <t>Terasa garapa za opěrnou stěnou — dřevěná pochozí vrstva</t>
+        </is>
+      </c>
+      <c r="D107" s="27" t="inlineStr">
+        <is>
+          <t>762??? ?</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>Dřevěné stupně ocelových schodišť (truhlářské, dub masiv tl. 40 mm)</t>
+          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na dřevěném roštu z hranolů 50 mm na rektifikovatelných terčích (terče + podkladní skladba viz HSV1.005)</t>
         </is>
       </c>
       <c r="F107" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G107" s="23" t="n">
-        <v>16</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G107" s="22" t="n">
+        <v>9.23</v>
       </c>
       <c r="H107" s="10" t="n"/>
       <c r="I107" s="10" t="n"/>
@@ -15999,16 +15959,16 @@
         </is>
       </c>
       <c r="K107" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L107" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_762_leaf_lookup_required</t>
         </is>
       </c>
       <c r="M107" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni truhlářské</t>
+          <t>TZ ARS dům §4 + DXF dum_situace PLOT_DREVENY_04 (terasa, ne 3.NP); ŘEZ C-C potvrzuje dřevěný rošt z hranolů (NE hliníkový) + dřevěnou pochozí vrstvu</t>
         </is>
       </c>
       <c r="N107" s="20" t="inlineStr">
@@ -16022,7 +15982,11 @@
         </is>
       </c>
       <c r="P107" s="41" t="n"/>
-      <c r="Q107" s="41" t="n"/>
+      <c r="Q107" s="41" t="inlineStr">
+        <is>
+          <t>REZ_CC_TERASA_FIX_2026-05-29; SITUACE_AREA_FIX_2026-05-29</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="20" t="n">
@@ -16030,55 +15994,55 @@
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Truhlář</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>Terasa garapa za opěrnou stěnou — dřevěná pochozí vrstva</t>
-        </is>
-      </c>
-      <c r="D108" s="27" t="inlineStr">
-        <is>
-          <t>762??? ?</t>
+          <t>Plastové okno trojsklo — 'okno 1.NP' (ulice)</t>
+        </is>
+      </c>
+      <c r="D108" s="20" t="inlineStr">
+        <is>
+          <t>766621011</t>
         </is>
       </c>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na dřevěném roštu z hranolů 50 mm na rektifikovatelných terčích (terče + podkladní skladba viz HSV1.005)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP' velikost 1185×1600 mm × 2 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="F108" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G108" s="22" t="n">
-        <v>9.23</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G108" s="23" t="n">
+        <v>2</v>
       </c>
       <c r="H108" s="10" t="n"/>
       <c r="I108" s="10" t="n"/>
       <c r="J108" s="8" t="inlineStr">
         <is>
-          <t>truhlar</t>
+          <t>okennar</t>
         </is>
       </c>
       <c r="K108" s="24" t="n">
-        <v>0.95</v>
+        <v>0.99</v>
       </c>
       <c r="L108" s="20" t="inlineStr">
         <is>
-          <t>family_762_leaf_lookup_required</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M108" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 + DXF dum_situace PLOT_DREVENY_04 (terasa, ne 3.NP); ŘEZ C-C potvrzuje dřevěný rošt z hranolů (NE hliníkový) + dřevěnou pochozí vrstvu</t>
+          <t>DXF dum_DPZ INSERT block 'okno 1.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N108" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O108" s="26" t="inlineStr">
@@ -16087,11 +16051,7 @@
         </is>
       </c>
       <c r="P108" s="41" t="n"/>
-      <c r="Q108" s="41" t="inlineStr">
-        <is>
-          <t>REZ_CC_TERASA_FIX_2026-05-29; SITUACE_AREA_FIX_2026-05-29</t>
-        </is>
-      </c>
+      <c r="Q108" s="41" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="20" t="n">
@@ -16104,7 +16064,7 @@
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 1.NP' (ulice)</t>
+          <t>Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada)</t>
         </is>
       </c>
       <c r="D109" s="20" t="inlineStr">
@@ -16114,7 +16074,7 @@
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP' velikost 1185×1600 mm × 2 ks (fasáda ulice)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP vzadu' velikost 920×1600 mm × 3 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="F109" s="20" t="inlineStr">
@@ -16123,7 +16083,7 @@
         </is>
       </c>
       <c r="G109" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H109" s="10" t="n"/>
       <c r="I109" s="10" t="n"/>
@@ -16137,12 +16097,12 @@
       </c>
       <c r="L109" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M109" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 1.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 1.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N109" s="20" t="inlineStr">
@@ -16169,7 +16129,7 @@
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada)</t>
+          <t>Plastové okno trojsklo — 'okno 2.NP' (ulice)</t>
         </is>
       </c>
       <c r="D110" s="20" t="inlineStr">
@@ -16179,7 +16139,7 @@
       </c>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP vzadu' velikost 920×1600 mm × 3 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 2.NP' velikost 1160×1480 mm × 4 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="F110" s="20" t="inlineStr">
@@ -16188,7 +16148,7 @@
         </is>
       </c>
       <c r="G110" s="23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H110" s="10" t="n"/>
       <c r="I110" s="10" t="n"/>
@@ -16207,7 +16167,7 @@
       </c>
       <c r="M110" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 1.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 2.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N110" s="20" t="inlineStr">
@@ -16234,7 +16194,7 @@
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 2.NP' (ulice)</t>
+          <t>Plastové okno trojsklo — 'okno 3.NP' (ulice)</t>
         </is>
       </c>
       <c r="D111" s="20" t="inlineStr">
@@ -16244,7 +16204,7 @@
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 2.NP' velikost 1160×1480 mm × 4 ks (fasáda ulice)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP' velikost 1785×1241 mm × 3 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="F111" s="20" t="inlineStr">
@@ -16253,7 +16213,7 @@
         </is>
       </c>
       <c r="G111" s="23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H111" s="10" t="n"/>
       <c r="I111" s="10" t="n"/>
@@ -16272,7 +16232,7 @@
       </c>
       <c r="M111" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 2.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 3.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N111" s="20" t="inlineStr">
@@ -16299,7 +16259,7 @@
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 3.NP' (ulice)</t>
+          <t>Plastové okno trojsklo — 'okno 3.NP vzadu' (zahrada)</t>
         </is>
       </c>
       <c r="D112" s="20" t="inlineStr">
@@ -16309,7 +16269,7 @@
       </c>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP' velikost 1785×1241 mm × 3 ks (fasáda ulice)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP vzadu' velikost 2075×1241 mm × 1 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="F112" s="20" t="inlineStr">
@@ -16318,7 +16278,7 @@
         </is>
       </c>
       <c r="G112" s="23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H112" s="10" t="n"/>
       <c r="I112" s="10" t="n"/>
@@ -16337,7 +16297,7 @@
       </c>
       <c r="M112" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 3.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N112" s="20" t="inlineStr">
@@ -16364,7 +16324,7 @@
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 3.NP vzadu' (zahrada)</t>
+          <t>Plastové okno trojsklo — 'okno male 3.NP vzadu' (zahrada)</t>
         </is>
       </c>
       <c r="D113" s="20" t="inlineStr">
@@ -16374,7 +16334,7 @@
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP vzadu' velikost 2075×1241 mm × 1 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno male 3.NP vzadu' velikost 800×1241 mm × 1 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="F113" s="20" t="inlineStr">
@@ -16402,7 +16362,7 @@
       </c>
       <c r="M113" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno male 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N113" s="20" t="inlineStr">
@@ -16429,7 +16389,7 @@
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno male 3.NP vzadu' (zahrada)</t>
+          <t>Plastové okno trojsklo — 'okno malé vzadu' (zahrada)</t>
         </is>
       </c>
       <c r="D114" s="20" t="inlineStr">
@@ -16439,7 +16399,7 @@
       </c>
       <c r="E114" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno male 3.NP vzadu' velikost 800×1241 mm × 1 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno malé vzadu' velikost 700×800 mm × 2 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="F114" s="20" t="inlineStr">
@@ -16448,7 +16408,7 @@
         </is>
       </c>
       <c r="G114" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H114" s="10" t="n"/>
       <c r="I114" s="10" t="n"/>
@@ -16467,7 +16427,7 @@
       </c>
       <c r="M114" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno male 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno malé vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N114" s="20" t="inlineStr">
@@ -16494,17 +16454,17 @@
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno malé vzadu' (zahrada)</t>
+          <t>Žaluzie kastlík purenit</t>
         </is>
       </c>
       <c r="D115" s="20" t="inlineStr">
         <is>
-          <t>766621011</t>
+          <t>766631211</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno malé vzadu' velikost 700×800 mm × 2 ks (fasáda zahrada)</t>
+          <t>Integrované stínící venkovní žaluzie v kastlíku pod omítkou s purenitovou izolací — uliční fasáda Fibichova (9 ks)</t>
         </is>
       </c>
       <c r="F115" s="20" t="inlineStr">
@@ -16513,17 +16473,17 @@
         </is>
       </c>
       <c r="G115" s="23" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H115" s="10" t="n"/>
       <c r="I115" s="10" t="n"/>
       <c r="J115" s="8" t="inlineStr">
         <is>
-          <t>okennar</t>
+          <t>okenni_zaluzie_kastlik_purenit</t>
         </is>
       </c>
       <c r="K115" s="24" t="n">
-        <v>0.99</v>
+        <v>0.95</v>
       </c>
       <c r="L115" s="20" t="inlineStr">
         <is>
@@ -16532,7 +16492,7 @@
       </c>
       <c r="M115" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno malé vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>TZ ARS dům §3.2 — 'do ulice Fibichova s integrovanými stínícími žaluziemi v kastlíku pod omítkou s purenitovou izolací'</t>
         </is>
       </c>
       <c r="N115" s="20" t="inlineStr">
@@ -16559,17 +16519,17 @@
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>Žaluzie kastlík purenit</t>
+          <t>Vstupní plastové dveře</t>
         </is>
       </c>
       <c r="D116" s="20" t="inlineStr">
         <is>
-          <t>766631211</t>
+          <t>766682111</t>
         </is>
       </c>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t>Integrované stínící venkovní žaluzie v kastlíku pod omítkou s purenitovou izolací — uliční fasáda Fibichova (9 ks)</t>
+          <t>Plastové vstupní dveře (ulice + zahrada) — 2 ks</t>
         </is>
       </c>
       <c r="F116" s="20" t="inlineStr">
@@ -16578,17 +16538,17 @@
         </is>
       </c>
       <c r="G116" s="23" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H116" s="10" t="n"/>
       <c r="I116" s="10" t="n"/>
       <c r="J116" s="8" t="inlineStr">
         <is>
-          <t>okenni_zaluzie_kastlik_purenit</t>
+          <t>okennar</t>
         </is>
       </c>
       <c r="K116" s="24" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L116" s="20" t="inlineStr">
         <is>
@@ -16597,12 +16557,12 @@
       </c>
       <c r="M116" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — 'do ulice Fibichova s integrovanými stínícími žaluziemi v kastlíku pod omítkou s purenitovou izolací'</t>
+          <t>TZ ARS dům §4 — plastové vstupní dveře</t>
         </is>
       </c>
       <c r="N116" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O116" s="26" t="inlineStr">
@@ -16624,17 +16584,17 @@
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t>Vstupní plastové dveře</t>
+          <t>Vnitřní dveře DTD laminované</t>
         </is>
       </c>
       <c r="D117" s="20" t="inlineStr">
         <is>
-          <t>766682111</t>
+          <t>766660035</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>Plastové vstupní dveře (ulice + zahrada) — 2 ks</t>
+          <t>Vnitřní dveře DTD laminované s obložkovou zárubní — odhad 15 ks</t>
         </is>
       </c>
       <c r="F117" s="20" t="inlineStr">
@@ -16643,13 +16603,13 @@
         </is>
       </c>
       <c r="G117" s="23" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H117" s="10" t="n"/>
       <c r="I117" s="10" t="n"/>
       <c r="J117" s="8" t="inlineStr">
         <is>
-          <t>okennar</t>
+          <t>truhlar</t>
         </is>
       </c>
       <c r="K117" s="24" t="n">
@@ -16662,12 +16622,12 @@
       </c>
       <c r="M117" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — plastové vstupní dveře</t>
+          <t>TZ ARS dům §4 + DXF MTEXT room labels</t>
         </is>
       </c>
       <c r="N117" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O117" s="26" t="inlineStr">
@@ -16689,17 +16649,17 @@
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>Vnitřní dveře DTD laminované</t>
+          <t>Požárně odolné dveře EI 30 DP3</t>
         </is>
       </c>
       <c r="D118" s="20" t="inlineStr">
         <is>
-          <t>766660035</t>
+          <t>766694112</t>
         </is>
       </c>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t>Vnitřní dveře DTD laminované s obložkovou zárubní — odhad 15 ks</t>
+          <t>Požárně odolné jednokřídlové dveře EI 30 DP3 na vrcholu schodiště mezi 1.PP a 1.NP — uzavírá otvor v REI 90 stropu klenby sklepa (per PBŘ TUSPO § 'Požární uzávěry otvorů v požárních stěnách a požárních stropech: podzemní 30 DP1')</t>
         </is>
       </c>
       <c r="F118" s="20" t="inlineStr">
@@ -16708,17 +16668,17 @@
         </is>
       </c>
       <c r="G118" s="23" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H118" s="10" t="n"/>
       <c r="I118" s="10" t="n"/>
       <c r="J118" s="8" t="inlineStr">
         <is>
-          <t>truhlar</t>
+          <t>specialista_RC3_dvere</t>
         </is>
       </c>
       <c r="K118" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L118" s="20" t="inlineStr">
         <is>
@@ -16727,12 +16687,12 @@
       </c>
       <c r="M118" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 + DXF MTEXT room labels</t>
+          <t>PBŘ TUSPO § Požární uzávěry otvorů 'podzemní 30DP1'; DXF schodiště 1.PP→1.NP</t>
         </is>
       </c>
       <c r="N118" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O118" s="26" t="inlineStr">
@@ -16741,7 +16701,11 @@
         </is>
       </c>
       <c r="P118" s="41" t="n"/>
-      <c r="Q118" s="41" t="n"/>
+      <c r="Q118" s="41" t="inlineStr">
+        <is>
+          <t>GAP_008</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="20" t="n">
@@ -16754,17 +16718,17 @@
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t>Požárně odolné dveře EI 30 DP3</t>
+          <t>Oplechování venkovních parapetů Pzn — 16 ks</t>
         </is>
       </c>
       <c r="D119" s="20" t="inlineStr">
         <is>
-          <t>766694112</t>
+          <t>764811112</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>Požárně odolné jednokřídlové dveře EI 30 DP3 na vrcholu schodiště mezi 1.PP a 1.NP — uzavírá otvor v REI 90 stropu klenby sklepa (per PBŘ TUSPO § 'Požární uzávěry otvorů v požárních stěnách a požárních stropech: podzemní 30 DP1')</t>
+          <t>Oplechování venkovních parapetů Pzn plech lakovaný 250 mm × tl. 0.55 mm, vč. okapnice + boční zakončení — 16 ks (per DXF INSERT okno × 16)</t>
         </is>
       </c>
       <c r="F119" s="20" t="inlineStr">
@@ -16773,17 +16737,17 @@
         </is>
       </c>
       <c r="G119" s="23" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H119" s="10" t="n"/>
       <c r="I119" s="10" t="n"/>
       <c r="J119" s="8" t="inlineStr">
         <is>
-          <t>specialista_RC3_dvere</t>
+          <t>klempir</t>
         </is>
       </c>
       <c r="K119" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L119" s="20" t="inlineStr">
         <is>
@@ -16792,7 +16756,7 @@
       </c>
       <c r="M119" s="8" t="inlineStr">
         <is>
-          <t>PBŘ TUSPO § Požární uzávěry otvorů 'podzemní 30DP1'; DXF schodiště 1.PP→1.NP</t>
+          <t>DXF blocks okno* 16 ks + DXF klempir_parapet 16 ks (Path C Tier 4 INSERT discovery)</t>
         </is>
       </c>
       <c r="N119" s="20" t="inlineStr">
@@ -16808,7 +16772,7 @@
       <c r="P119" s="41" t="n"/>
       <c r="Q119" s="41" t="inlineStr">
         <is>
-          <t>GAP_008</t>
+          <t>GAP_004</t>
         </is>
       </c>
     </row>
@@ -16818,55 +16782,55 @@
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>Oplechování venkovních parapetů Pzn — 16 ks</t>
+          <t>Ocelové schodiště UPE200 ze zahrady</t>
         </is>
       </c>
       <c r="D120" s="20" t="inlineStr">
         <is>
-          <t>764811112</t>
+          <t>767531111</t>
         </is>
       </c>
       <c r="E120" s="8" t="inlineStr">
         <is>
-          <t>Oplechování venkovních parapetů Pzn plech lakovaný 250 mm × tl. 0.55 mm, vč. okapnice + boční zakončení — 16 ks (per DXF INSERT okno × 16)</t>
+          <t>Ocelové schodiště ze zahrady na mezipodestu — UPE200 schodnice + dřevěné nášlapy, kotvené do koruny opěrné stěny a zdiva (TZ statika §4)</t>
         </is>
       </c>
       <c r="F120" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G120" s="23" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H120" s="10" t="n"/>
       <c r="I120" s="10" t="n"/>
       <c r="J120" s="8" t="inlineStr">
         <is>
-          <t>klempir</t>
+          <t>zamecnik_PSV</t>
         </is>
       </c>
       <c r="K120" s="24" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="L120" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M120" s="8" t="inlineStr">
         <is>
-          <t>DXF blocks okno* 16 ks + DXF klempir_parapet 16 ks (Path C Tier 4 INSERT discovery)</t>
+          <t>TZ statika dům §4 — schodiště UPE200 + UPE100 podružné prvky</t>
         </is>
       </c>
       <c r="N120" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O120" s="26" t="inlineStr">
@@ -16877,7 +16841,7 @@
       <c r="P120" s="41" t="n"/>
       <c r="Q120" s="41" t="inlineStr">
         <is>
-          <t>GAP_004</t>
+          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
         </is>
       </c>
     </row>
@@ -16892,7 +16856,7 @@
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t>Ocelové schodiště UPE200 ze zahrady</t>
+          <t>Ocelové schodiště do spacího patra 3.NP</t>
         </is>
       </c>
       <c r="D121" s="20" t="inlineStr">
@@ -16902,7 +16866,7 @@
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>Ocelové schodiště ze zahrady na mezipodestu — UPE200 schodnice + dřevěné nášlapy, kotvené do koruny opěrné stěny a zdiva (TZ statika §4)</t>
+          <t>Interní ocelové schodiště do spacího patra v 3.NP s dřevěnými stupni (truhlářské)</t>
         </is>
       </c>
       <c r="F121" s="20" t="inlineStr">
@@ -16930,12 +16894,12 @@
       </c>
       <c r="M121" s="8" t="inlineStr">
         <is>
-          <t>TZ statika dům §4 — schodiště UPE200 + UPE100 podružné prvky</t>
+          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni</t>
         </is>
       </c>
       <c r="N121" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O121" s="26" t="inlineStr">
@@ -16961,26 +16925,26 @@
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>Ocelové schodiště do spacího patra 3.NP</t>
+          <t>Stříšky nad vstupy</t>
         </is>
       </c>
       <c r="D122" s="20" t="inlineStr">
         <is>
-          <t>767531111</t>
+          <t>767532111</t>
         </is>
       </c>
       <c r="E122" s="8" t="inlineStr">
         <is>
-          <t>Interní ocelové schodiště do spacího patra v 3.NP s dřevěnými stupni (truhlářské)</t>
+          <t>Stříšky nad vstupy z ocelové konstrukce + Cetris desky + falcovaná krytina — 2 ks (ulice + zahrada)</t>
         </is>
       </c>
       <c r="F122" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G122" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H122" s="10" t="n"/>
       <c r="I122" s="10" t="n"/>
@@ -16990,16 +16954,16 @@
         </is>
       </c>
       <c r="K122" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L122" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M122" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni</t>
+          <t>TZ ARS dům §4 — stříšky nad vstupy ocel+Cetris+plech</t>
         </is>
       </c>
       <c r="N122" s="20" t="inlineStr">
@@ -17013,11 +16977,7 @@
         </is>
       </c>
       <c r="P122" s="41" t="n"/>
-      <c r="Q122" s="41" t="inlineStr">
-        <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
-        </is>
-      </c>
+      <c r="Q122" s="41" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="20" t="n">
@@ -17030,26 +16990,26 @@
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t>Stříšky nad vstupy</t>
+          <t>Zábradlí z jeklů + nerez výplň</t>
         </is>
       </c>
       <c r="D123" s="20" t="inlineStr">
         <is>
-          <t>767532111</t>
+          <t>767163115</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>Stříšky nad vstupy z ocelové konstrukce + Cetris desky + falcovaná krytina — 2 ks (ulice + zahrada)</t>
+          <t>Ocelové zábradlí svařované z jeklů + nerez výplň pZn antracit — schodiště interier + venkovní terasa</t>
         </is>
       </c>
       <c r="F123" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G123" s="23" t="n">
-        <v>2</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G123" s="22" t="n">
+        <v>18</v>
       </c>
       <c r="H123" s="10" t="n"/>
       <c r="I123" s="10" t="n"/>
@@ -17068,7 +17028,7 @@
       </c>
       <c r="M123" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — stříšky nad vstupy ocel+Cetris+plech</t>
+          <t>TZ ARS dům §4 — zábradlí svařované z jeklů + nerez výplň</t>
         </is>
       </c>
       <c r="N123" s="20" t="inlineStr">
@@ -17090,55 +17050,55 @@
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnictví</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>Zábradlí z jeklů + nerez výplň</t>
+          <t>Nášlap vinyl obytné místnosti</t>
         </is>
       </c>
       <c r="D124" s="20" t="inlineStr">
         <is>
-          <t>767163115</t>
+          <t>776511820</t>
         </is>
       </c>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t>Ocelové zábradlí svařované z jeklů + nerez výplň pZn antracit — schodiště interier + venkovní terasa</t>
+          <t>Nášlapná vrstva vinyl tl. 4 mm na suchou skladbu — obytné místnosti (ložnice, obývák, kuchyně, chodby)</t>
         </is>
       </c>
       <c r="F124" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G124" s="22" t="n">
-        <v>18</v>
+        <v>171.5</v>
       </c>
       <c r="H124" s="10" t="n"/>
       <c r="I124" s="10" t="n"/>
       <c r="J124" s="8" t="inlineStr">
         <is>
-          <t>zamecnik_PSV</t>
+          <t>podlahar</t>
         </is>
       </c>
       <c r="K124" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L124" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M124" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — zábradlí svařované z jeklů + nerez výplň</t>
+          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (kuchyně/obytná/chodba = vinyl) + TZ ARS §3.2.4 nášlapná vrstva</t>
         </is>
       </c>
       <c r="N124" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#4</t>
         </is>
       </c>
       <c r="O124" s="26" t="inlineStr">
@@ -17147,7 +17107,11 @@
         </is>
       </c>
       <c r="P124" s="41" t="n"/>
-      <c r="Q124" s="41" t="n"/>
+      <c r="Q124" s="41" t="inlineStr">
+        <is>
+          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="20" t="n">
@@ -17160,17 +17124,17 @@
       </c>
       <c r="C125" s="8" t="inlineStr">
         <is>
-          <t>Nášlap vinyl obytné místnosti</t>
+          <t>Nášlap keramická dlažba — mokré zóny</t>
         </is>
       </c>
       <c r="D125" s="20" t="inlineStr">
         <is>
-          <t>776511820</t>
+          <t>771274102</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva vinyl tl. 4 mm na suchou skladbu — obytné místnosti (ložnice, obývák, kuchyně, chodby)</t>
+          <t>Nášlapná vrstva keramická dlažba lepená — koupelny + WC + spíž + komora (NÁDRŽ NP)</t>
         </is>
       </c>
       <c r="F125" s="20" t="inlineStr">
@@ -17179,13 +17143,13 @@
         </is>
       </c>
       <c r="G125" s="22" t="n">
-        <v>171.5</v>
+        <v>13.5</v>
       </c>
       <c r="H125" s="10" t="n"/>
       <c r="I125" s="10" t="n"/>
       <c r="J125" s="8" t="inlineStr">
         <is>
-          <t>podlahar</t>
+          <t>obkladac</t>
         </is>
       </c>
       <c r="K125" s="24" t="n">
@@ -17193,12 +17157,12 @@
       </c>
       <c r="L125" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M125" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (kuchyně/obytná/chodba = vinyl) + TZ ARS §3.2.4 nášlapná vrstva</t>
+          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (koupelna/WC/spíž = dlažba mokré) + TZ ARS skladba mokrá</t>
         </is>
       </c>
       <c r="N125" s="20" t="inlineStr">
@@ -17212,11 +17176,7 @@
         </is>
       </c>
       <c r="P125" s="41" t="n"/>
-      <c r="Q125" s="41" t="inlineStr">
-        <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
-        </is>
-      </c>
+      <c r="Q125" s="41" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="20" t="n">
@@ -17229,7 +17189,7 @@
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>Nášlap keramická dlažba — mokré zóny</t>
+          <t>Nášlap keramická dlažba — 1.PP sklep</t>
         </is>
       </c>
       <c r="D126" s="20" t="inlineStr">
@@ -17239,7 +17199,7 @@
       </c>
       <c r="E126" s="8" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva keramická dlažba lepená — koupelny + WC + spíž + komora (NÁDRŽ NP)</t>
+          <t>Nášlapná vrstva keramická dlažba — 1.PP technické místnosti (sušárna + sklepy + schodiště + chodba)</t>
         </is>
       </c>
       <c r="F126" s="20" t="inlineStr">
@@ -17248,7 +17208,7 @@
         </is>
       </c>
       <c r="G126" s="22" t="n">
-        <v>13.5</v>
+        <v>32.4</v>
       </c>
       <c r="H126" s="10" t="n"/>
       <c r="I126" s="10" t="n"/>
@@ -17267,7 +17227,7 @@
       </c>
       <c r="M126" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (koupelna/WC/spíž = dlažba mokré) + TZ ARS skladba mokrá</t>
+          <t>DXF km_tabulka místností MTEXT (návrh) — 1.PP all rooms = dlažba sklep zone</t>
         </is>
       </c>
       <c r="N126" s="20" t="inlineStr">
@@ -17294,17 +17254,17 @@
       </c>
       <c r="C127" s="8" t="inlineStr">
         <is>
-          <t>Nášlap keramická dlažba — 1.PP sklep</t>
+          <t>Nášlap biodeska 3.NP spací patro</t>
         </is>
       </c>
       <c r="D127" s="20" t="inlineStr">
         <is>
-          <t>771274102</t>
+          <t>766411111</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva keramická dlažba — 1.PP technické místnosti (sušárna + sklepy + schodiště + chodba)</t>
+          <t>Nášlapná vrstva biodeska (smrk masiv) nebo OSB v 3.NP spací části nad krovem</t>
         </is>
       </c>
       <c r="F127" s="20" t="inlineStr">
@@ -17313,17 +17273,17 @@
         </is>
       </c>
       <c r="G127" s="22" t="n">
-        <v>32.4</v>
+        <v>25</v>
       </c>
       <c r="H127" s="10" t="n"/>
       <c r="I127" s="10" t="n"/>
       <c r="J127" s="8" t="inlineStr">
         <is>
-          <t>obkladac</t>
+          <t>biodeska_konstrukcni</t>
         </is>
       </c>
       <c r="K127" s="24" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L127" s="20" t="inlineStr">
         <is>
@@ -17332,12 +17292,12 @@
       </c>
       <c r="M127" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT (návrh) — 1.PP all rooms = dlažba sklep zone</t>
+          <t>TZ ARS dům §3.2.3 — biodeska patro pro přespání</t>
         </is>
       </c>
       <c r="N127" s="20" t="inlineStr">
         <is>
-          <t>#4</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="O127" s="26" t="inlineStr">
@@ -17359,17 +17319,17 @@
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>Nášlap biodeska 3.NP spací patro</t>
+          <t>Betonový potěr s kari nad EPS</t>
         </is>
       </c>
       <c r="D128" s="20" t="inlineStr">
         <is>
-          <t>766411111</t>
+          <t>631321311</t>
         </is>
       </c>
       <c r="E128" s="8" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva biodeska (smrk masiv) nebo OSB v 3.NP spací části nad krovem</t>
+          <t>Mokrá podlahová skladba — betonový potěr s kari síťkou 4/100/100 tl. 50 mm + samonivelační stěrka</t>
         </is>
       </c>
       <c r="F128" s="20" t="inlineStr">
@@ -17378,17 +17338,17 @@
         </is>
       </c>
       <c r="G128" s="22" t="n">
-        <v>25</v>
+        <v>126.4</v>
       </c>
       <c r="H128" s="10" t="n"/>
       <c r="I128" s="10" t="n"/>
       <c r="J128" s="8" t="inlineStr">
         <is>
-          <t>biodeska_konstrukcni</t>
+          <t>podlahar</t>
         </is>
       </c>
       <c r="K128" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L128" s="20" t="inlineStr">
         <is>
@@ -17397,12 +17357,12 @@
       </c>
       <c r="M128" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2.3 — biodeska patro pro přespání</t>
+          <t>TZ ARS dům §3.2.4 + §3.2.x — 'kročejová izolace + betonový potěr s kari sítí'; DXF rooms areas</t>
         </is>
       </c>
       <c r="N128" s="20" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>#4</t>
         </is>
       </c>
       <c r="O128" s="26" t="inlineStr">
@@ -17424,26 +17384,26 @@
       </c>
       <c r="C129" s="8" t="inlineStr">
         <is>
-          <t>Betonový potěr s kari nad EPS</t>
+          <t>Soklíky vinyl</t>
         </is>
       </c>
       <c r="D129" s="20" t="inlineStr">
         <is>
-          <t>631321311</t>
+          <t>776511831</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t>Mokrá podlahová skladba — betonový potěr s kari síťkou 4/100/100 tl. 50 mm + samonivelační stěrka</t>
+          <t>Soklíky podlahové laminátové (dub) v obytných místnostech s vinyl podlahou</t>
         </is>
       </c>
       <c r="F129" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G129" s="22" t="n">
-        <v>126.4</v>
+        <v>72.03</v>
       </c>
       <c r="H129" s="10" t="n"/>
       <c r="I129" s="10" t="n"/>
@@ -17462,12 +17422,12 @@
       </c>
       <c r="M129" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2.4 + §3.2.x — 'kročejová izolace + betonový potěr s kari sítí'; DXF rooms areas</t>
+          <t>DXF rooms vinyl + standard ratio per RD geometry</t>
         </is>
       </c>
       <c r="N129" s="20" t="inlineStr">
         <is>
-          <t>#4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O129" s="26" t="inlineStr">
@@ -17489,17 +17449,17 @@
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>Soklíky vinyl</t>
+          <t>Soklíky keramické</t>
         </is>
       </c>
       <c r="D130" s="20" t="inlineStr">
         <is>
-          <t>776511831</t>
+          <t>771274107</t>
         </is>
       </c>
       <c r="E130" s="8" t="inlineStr">
         <is>
-          <t>Soklíky podlahové laminátové (dub) v obytných místnostech s vinyl podlahou</t>
+          <t>Soklíky keramické v místnostech s dlažbou (koupelny + WC + spíž + 1.PP)</t>
         </is>
       </c>
       <c r="F130" s="20" t="inlineStr">
@@ -17508,13 +17468,13 @@
         </is>
       </c>
       <c r="G130" s="22" t="n">
-        <v>72.03</v>
+        <v>19.28</v>
       </c>
       <c r="H130" s="10" t="n"/>
       <c r="I130" s="10" t="n"/>
       <c r="J130" s="8" t="inlineStr">
         <is>
-          <t>podlahar</t>
+          <t>obkladac</t>
         </is>
       </c>
       <c r="K130" s="24" t="n">
@@ -17527,7 +17487,7 @@
       </c>
       <c r="M130" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms vinyl + standard ratio per RD geometry</t>
+          <t>DXF rooms dlažba + standard ratio per RD geometry</t>
         </is>
       </c>
       <c r="N130" s="20" t="inlineStr">
@@ -17549,41 +17509,41 @@
       </c>
       <c r="B131" s="8" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="C131" s="8" t="inlineStr">
         <is>
-          <t>Soklíky keramické</t>
+          <t>Omítka jádrová + štuk 1.PP</t>
         </is>
       </c>
       <c r="D131" s="20" t="inlineStr">
         <is>
-          <t>771274107</t>
+          <t>612311311</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t>Soklíky keramické v místnostech s dlažbou (koupelny + WC + spíž + 1.PP)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.PP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="F131" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G131" s="22" t="n">
-        <v>19.28</v>
+        <v>78.2</v>
       </c>
       <c r="H131" s="10" t="n"/>
       <c r="I131" s="10" t="n"/>
       <c r="J131" s="8" t="inlineStr">
         <is>
-          <t>obkladac</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="K131" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L131" s="20" t="inlineStr">
         <is>
@@ -17592,12 +17552,12 @@
       </c>
       <c r="M131" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms dlažba + standard ratio per RD geometry</t>
+          <t>DXF rooms 1.PP obvod + výška podlaží 2.1 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="N131" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="O131" s="26" t="inlineStr">
@@ -17619,7 +17579,7 @@
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová + štuk 1.PP</t>
+          <t>Omítka jádrová + štuk 1.NP</t>
         </is>
       </c>
       <c r="D132" s="20" t="inlineStr">
@@ -17629,7 +17589,7 @@
       </c>
       <c r="E132" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.PP (stávající vyspravené + nové zděné)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="F132" s="20" t="inlineStr">
@@ -17638,7 +17598,7 @@
         </is>
       </c>
       <c r="G132" s="22" t="n">
-        <v>78.2</v>
+        <v>208.4</v>
       </c>
       <c r="H132" s="10" t="n"/>
       <c r="I132" s="10" t="n"/>
@@ -17657,7 +17617,7 @@
       </c>
       <c r="M132" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms 1.PP obvod + výška podlaží 2.1 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF rooms 1.NP obvod + výška podlaží 2.795 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="N132" s="20" t="inlineStr">
@@ -17684,7 +17644,7 @@
       </c>
       <c r="C133" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová + štuk 1.NP</t>
+          <t>Omítka jádrová + štuk 2.NP</t>
         </is>
       </c>
       <c r="D133" s="20" t="inlineStr">
@@ -17694,7 +17654,7 @@
       </c>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.NP (stávající vyspravené + nové zděné)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 2.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="F133" s="20" t="inlineStr">
@@ -17703,7 +17663,7 @@
         </is>
       </c>
       <c r="G133" s="22" t="n">
-        <v>208.4</v>
+        <v>201.6</v>
       </c>
       <c r="H133" s="10" t="n"/>
       <c r="I133" s="10" t="n"/>
@@ -17722,7 +17682,7 @@
       </c>
       <c r="M133" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms 1.NP obvod + výška podlaží 2.795 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF rooms 2.NP obvod + výška podlaží 2.865 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="N133" s="20" t="inlineStr">
@@ -17749,7 +17709,7 @@
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová + štuk 2.NP</t>
+          <t>Omítka jádrová + štuk 3.NP</t>
         </is>
       </c>
       <c r="D134" s="20" t="inlineStr">
@@ -17759,7 +17719,7 @@
       </c>
       <c r="E134" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 2.NP (stávající vyspravené + nové zděné)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 3.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="F134" s="20" t="inlineStr">
@@ -17768,7 +17728,7 @@
         </is>
       </c>
       <c r="G134" s="22" t="n">
-        <v>201.6</v>
+        <v>179.1</v>
       </c>
       <c r="H134" s="10" t="n"/>
       <c r="I134" s="10" t="n"/>
@@ -17787,7 +17747,7 @@
       </c>
       <c r="M134" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms 2.NP obvod + výška podlaží 2.865 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF rooms 3.NP obvod + výška podlaží 2.63 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="N134" s="20" t="inlineStr">
@@ -17814,17 +17774,17 @@
       </c>
       <c r="C135" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová + štuk 3.NP</t>
+          <t>SDK podhled — tmelení + úprava 1.NP</t>
         </is>
       </c>
       <c r="D135" s="20" t="inlineStr">
         <is>
-          <t>612311311</t>
+          <t>612471141</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 3.NP (stávající vyspravené + nové zděné)</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (1.NP)</t>
         </is>
       </c>
       <c r="F135" s="20" t="inlineStr">
@@ -17833,17 +17793,17 @@
         </is>
       </c>
       <c r="G135" s="22" t="n">
-        <v>179.1</v>
+        <v>59.5</v>
       </c>
       <c r="H135" s="10" t="n"/>
       <c r="I135" s="10" t="n"/>
       <c r="J135" s="8" t="inlineStr">
         <is>
-          <t>zednik</t>
+          <t>sadrokartonar</t>
         </is>
       </c>
       <c r="K135" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L135" s="20" t="inlineStr">
         <is>
@@ -17852,12 +17812,12 @@
       </c>
       <c r="M135" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms 3.NP obvod + výška podlaží 2.63 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF km_tabulka místností MTEXT — plocha 1.NP = plocha podhledu (flat ceiling assumption)</t>
         </is>
       </c>
       <c r="N135" s="20" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O135" s="26" t="inlineStr">
@@ -17879,7 +17839,7 @@
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled — tmelení + úprava 1.NP</t>
+          <t>SDK podhled — tmelení + úprava 2.NP</t>
         </is>
       </c>
       <c r="D136" s="20" t="inlineStr">
@@ -17889,7 +17849,7 @@
       </c>
       <c r="E136" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (1.NP)</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (2.NP)</t>
         </is>
       </c>
       <c r="F136" s="20" t="inlineStr">
@@ -17898,7 +17858,7 @@
         </is>
       </c>
       <c r="G136" s="22" t="n">
-        <v>59.5</v>
+        <v>61.1</v>
       </c>
       <c r="H136" s="10" t="n"/>
       <c r="I136" s="10" t="n"/>
@@ -17917,7 +17877,7 @@
       </c>
       <c r="M136" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT — plocha 1.NP = plocha podhledu (flat ceiling assumption)</t>
+          <t>DXF km_tabulka místností MTEXT — plocha 2.NP = plocha podhledu (flat ceiling assumption)</t>
         </is>
       </c>
       <c r="N136" s="20" t="inlineStr">
@@ -17944,7 +17904,7 @@
       </c>
       <c r="C137" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled — tmelení + úprava 2.NP</t>
+          <t>SDK podhled — tmelení + úprava 3.NP</t>
         </is>
       </c>
       <c r="D137" s="20" t="inlineStr">
@@ -17954,7 +17914,7 @@
       </c>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (2.NP)</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (3.NP)</t>
         </is>
       </c>
       <c r="F137" s="20" t="inlineStr">
@@ -17963,7 +17923,7 @@
         </is>
       </c>
       <c r="G137" s="22" t="n">
-        <v>61.1</v>
+        <v>64.5</v>
       </c>
       <c r="H137" s="10" t="n"/>
       <c r="I137" s="10" t="n"/>
@@ -17982,7 +17942,7 @@
       </c>
       <c r="M137" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT — plocha 2.NP = plocha podhledu (flat ceiling assumption)</t>
+          <t>DXF km_tabulka místností MTEXT — plocha 3.NP = plocha podhledu (flat ceiling assumption)</t>
         </is>
       </c>
       <c r="N137" s="20" t="inlineStr">
@@ -18009,17 +17969,17 @@
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled — tmelení + úprava 3.NP</t>
+          <t>Keramický obklad koupelna 1.05 (1.NP)</t>
         </is>
       </c>
       <c r="D138" s="20" t="inlineStr">
         <is>
-          <t>612471141</t>
+          <t>781447001</t>
         </is>
       </c>
       <c r="E138" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (3.NP)</t>
+          <t>Keramický obklad stěn koupelny 1.05 1.NP — výška obkladu 1.6 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="F138" s="20" t="inlineStr">
@@ -18028,17 +17988,17 @@
         </is>
       </c>
       <c r="G138" s="22" t="n">
-        <v>64.5</v>
+        <v>13.4</v>
       </c>
       <c r="H138" s="10" t="n"/>
       <c r="I138" s="10" t="n"/>
       <c r="J138" s="8" t="inlineStr">
         <is>
-          <t>sadrokartonar</t>
+          <t>obkladac</t>
         </is>
       </c>
       <c r="K138" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L138" s="20" t="inlineStr">
         <is>
@@ -18047,7 +18007,7 @@
       </c>
       <c r="M138" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT — plocha 3.NP = plocha podhledu (flat ceiling assumption)</t>
+          <t>DXF rooms PIP perimeter 1.05 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
         </is>
       </c>
       <c r="N138" s="20" t="inlineStr">
@@ -18074,7 +18034,7 @@
       </c>
       <c r="C139" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad koupelna 1.05 (1.NP)</t>
+          <t>Keramický obklad koupelna 2.03 (2.NP)</t>
         </is>
       </c>
       <c r="D139" s="20" t="inlineStr">
@@ -18084,7 +18044,7 @@
       </c>
       <c r="E139" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 1.05 1.NP — výška obkladu 1.6 m (z DXF km Obklady layer)</t>
+          <t>Keramický obklad stěn koupelny 2.03 2.NP — výška obkladu 2.45 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="F139" s="20" t="inlineStr">
@@ -18093,7 +18053,7 @@
         </is>
       </c>
       <c r="G139" s="22" t="n">
-        <v>13.4</v>
+        <v>15.2</v>
       </c>
       <c r="H139" s="10" t="n"/>
       <c r="I139" s="10" t="n"/>
@@ -18112,7 +18072,7 @@
       </c>
       <c r="M139" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms PIP perimeter 1.05 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
+          <t>DXF rooms PIP perimeter 2.03 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
         </is>
       </c>
       <c r="N139" s="20" t="inlineStr">
@@ -18139,7 +18099,7 @@
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad koupelna 2.03 (2.NP)</t>
+          <t>Keramický obklad koupelna 3.04 (3.NP)</t>
         </is>
       </c>
       <c r="D140" s="20" t="inlineStr">
@@ -18149,7 +18109,7 @@
       </c>
       <c r="E140" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 2.03 2.NP — výška obkladu 2.45 m (z DXF km Obklady layer)</t>
+          <t>Keramický obklad stěn koupelny 3.04 3.NP — výška obkladu 2.7 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="F140" s="20" t="inlineStr">
@@ -18158,7 +18118,7 @@
         </is>
       </c>
       <c r="G140" s="22" t="n">
-        <v>15.2</v>
+        <v>24.3</v>
       </c>
       <c r="H140" s="10" t="n"/>
       <c r="I140" s="10" t="n"/>
@@ -18177,7 +18137,7 @@
       </c>
       <c r="M140" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms PIP perimeter 2.03 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
+          <t>DXF rooms PIP perimeter 3.04 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
         </is>
       </c>
       <c r="N140" s="20" t="inlineStr">
@@ -18204,7 +18164,7 @@
       </c>
       <c r="C141" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad koupelna 3.04 (3.NP)</t>
+          <t>Obklad za kuchyňskou linkou</t>
         </is>
       </c>
       <c r="D141" s="20" t="inlineStr">
@@ -18214,7 +18174,7 @@
       </c>
       <c r="E141" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 3.04 3.NP — výška obkladu 2.7 m (z DXF km Obklady layer)</t>
+          <t>Keramický obklad za kuchyňskou linkou nad pracovní deskou — 2 kuchyně × ~5 m² (1.06 byt rodičů + 3.05 byt 3.NP)</t>
         </is>
       </c>
       <c r="F141" s="20" t="inlineStr">
@@ -18223,7 +18183,7 @@
         </is>
       </c>
       <c r="G141" s="22" t="n">
-        <v>24.3</v>
+        <v>10</v>
       </c>
       <c r="H141" s="10" t="n"/>
       <c r="I141" s="10" t="n"/>
@@ -18233,7 +18193,7 @@
         </is>
       </c>
       <c r="K141" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L141" s="20" t="inlineStr">
         <is>
@@ -18242,7 +18202,7 @@
       </c>
       <c r="M141" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms PIP perimeter 3.04 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
+          <t>DXF dum_DPZ 2× kuchyně MTEXT + TZ ARS</t>
         </is>
       </c>
       <c r="N141" s="20" t="inlineStr">
@@ -18269,17 +18229,17 @@
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>Obklad za kuchyňskou linkou</t>
+          <t>Interiérová výmalba</t>
         </is>
       </c>
       <c r="D142" s="20" t="inlineStr">
         <is>
-          <t>781447001</t>
+          <t>784121011</t>
         </is>
       </c>
       <c r="E142" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad za kuchyňskou linkou nad pracovní deskou — 2 kuchyně × ~5 m² (1.06 byt rodičů + 3.05 byt 3.NP)</t>
+          <t>Interiérová výmalba akrylátová bílá 2× — všechny stěny + podhledy mimo obklad</t>
         </is>
       </c>
       <c r="F142" s="20" t="inlineStr">
@@ -18288,17 +18248,17 @@
         </is>
       </c>
       <c r="G142" s="22" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H142" s="10" t="n"/>
       <c r="I142" s="10" t="n"/>
       <c r="J142" s="8" t="inlineStr">
         <is>
-          <t>obkladac</t>
+          <t>malir</t>
         </is>
       </c>
       <c r="K142" s="24" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L142" s="20" t="inlineStr">
         <is>
@@ -18307,7 +18267,7 @@
       </c>
       <c r="M142" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ 2× kuchyně MTEXT + TZ ARS</t>
+          <t>TZ ARS — interiérová výmalba (aggregate, no TZ per-room directive)</t>
         </is>
       </c>
       <c r="N142" s="20" t="inlineStr">
@@ -18321,7 +18281,11 @@
         </is>
       </c>
       <c r="P142" s="41" t="n"/>
-      <c r="Q142" s="41" t="n"/>
+      <c r="Q142" s="41" t="inlineStr">
+        <is>
+          <t>GAP_007_deprecated</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="20" t="n">
@@ -18334,7 +18298,7 @@
       </c>
       <c r="C143" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba</t>
+          <t>Interiérová výmalba 1.NP</t>
         </is>
       </c>
       <c r="D143" s="20" t="inlineStr">
@@ -18344,7 +18308,7 @@
       </c>
       <c r="E143" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba akrylátová bílá 2× — všechny stěny + podhledy mimo obklad</t>
+          <t>Interiérová výmalba 1.NP — stěny + SDK podhled − obklad koupelny 1.05 (1.6 m výška)</t>
         </is>
       </c>
       <c r="F143" s="20" t="inlineStr">
@@ -18353,7 +18317,7 @@
         </is>
       </c>
       <c r="G143" s="22" t="n">
-        <v>0</v>
+        <v>254.5</v>
       </c>
       <c r="H143" s="10" t="n"/>
       <c r="I143" s="10" t="n"/>
@@ -18363,7 +18327,7 @@
         </is>
       </c>
       <c r="K143" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L143" s="20" t="inlineStr">
         <is>
@@ -18372,7 +18336,7 @@
       </c>
       <c r="M143" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS — interiérová výmalba (aggregate, no TZ per-room directive)</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.002 + SDK podhled PSV78.005</t>
         </is>
       </c>
       <c r="N143" s="20" t="inlineStr">
@@ -18388,7 +18352,7 @@
       <c r="P143" s="41" t="n"/>
       <c r="Q143" s="41" t="inlineStr">
         <is>
-          <t>GAP_007_deprecated</t>
+          <t>GAP_007</t>
         </is>
       </c>
     </row>
@@ -18403,7 +18367,7 @@
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.NP</t>
+          <t>Interiérová výmalba 1.PP</t>
         </is>
       </c>
       <c r="D144" s="20" t="inlineStr">
@@ -18413,7 +18377,7 @@
       </c>
       <c r="E144" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.NP — stěny + SDK podhled − obklad koupelny 1.05 (1.6 m výška)</t>
+          <t>Interiérová výmalba 1.PP — sklep stěny + klenba bílá vápenná 2×</t>
         </is>
       </c>
       <c r="F144" s="20" t="inlineStr">
@@ -18422,7 +18386,7 @@
         </is>
       </c>
       <c r="G144" s="22" t="n">
-        <v>254.5</v>
+        <v>78.2</v>
       </c>
       <c r="H144" s="10" t="n"/>
       <c r="I144" s="10" t="n"/>
@@ -18441,7 +18405,7 @@
       </c>
       <c r="M144" s="8" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.002 + SDK podhled PSV78.005</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.001 + SDK podhled PSV78.—</t>
         </is>
       </c>
       <c r="N144" s="20" t="inlineStr">
@@ -18472,7 +18436,7 @@
       </c>
       <c r="C145" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.PP</t>
+          <t>Interiérová výmalba 2.NP</t>
         </is>
       </c>
       <c r="D145" s="20" t="inlineStr">
@@ -18482,7 +18446,7 @@
       </c>
       <c r="E145" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.PP — sklep stěny + klenba bílá vápenná 2×</t>
+          <t>Interiérová výmalba 2.NP — stěny + SDK podhled − obklad koupelny 2.03 (2.45 m výška)</t>
         </is>
       </c>
       <c r="F145" s="20" t="inlineStr">
@@ -18491,7 +18455,7 @@
         </is>
       </c>
       <c r="G145" s="22" t="n">
-        <v>78.2</v>
+        <v>247.5</v>
       </c>
       <c r="H145" s="10" t="n"/>
       <c r="I145" s="10" t="n"/>
@@ -18510,7 +18474,7 @@
       </c>
       <c r="M145" s="8" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.001 + SDK podhled PSV78.—</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.003 + SDK podhled PSV78.006</t>
         </is>
       </c>
       <c r="N145" s="20" t="inlineStr">
@@ -18541,7 +18505,7 @@
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 2.NP</t>
+          <t>Interiérová výmalba 3.NP</t>
         </is>
       </c>
       <c r="D146" s="20" t="inlineStr">
@@ -18551,7 +18515,7 @@
       </c>
       <c r="E146" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 2.NP — stěny + SDK podhled − obklad koupelny 2.03 (2.45 m výška)</t>
+          <t>Interiérová výmalba 3.NP — stěny + SDK podhled − obklad koupelny 3.04 (2.7 m výška)</t>
         </is>
       </c>
       <c r="F146" s="20" t="inlineStr">
@@ -18560,7 +18524,7 @@
         </is>
       </c>
       <c r="G146" s="22" t="n">
-        <v>247.5</v>
+        <v>219.3</v>
       </c>
       <c r="H146" s="10" t="n"/>
       <c r="I146" s="10" t="n"/>
@@ -18579,7 +18543,7 @@
       </c>
       <c r="M146" s="8" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.003 + SDK podhled PSV78.006</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.004 + SDK podhled PSV78.007</t>
         </is>
       </c>
       <c r="N146" s="20" t="inlineStr">
@@ -18605,37 +18569,37 @@
       </c>
       <c r="B147" s="8" t="inlineStr">
         <is>
-          <t>PSV-78 Povrchové úpravy</t>
+          <t>PSV-95 Detekce požární</t>
         </is>
       </c>
       <c r="C147" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 3.NP</t>
+          <t>Autonomní hlásič kouře</t>
         </is>
       </c>
       <c r="D147" s="20" t="inlineStr">
         <is>
-          <t>784121011</t>
+          <t>375211101</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 3.NP — stěny + SDK podhled − obklad koupelny 3.04 (2.7 m výška)</t>
+          <t>Autonomní hlásič kouře dle ČSN EN 14604 — 4 ks v místnostech 1.01, 1.02, 2.04, 3.03 dle PBŘ</t>
         </is>
       </c>
       <c r="F147" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G147" s="22" t="n">
-        <v>219.3</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G147" s="23" t="n">
+        <v>4</v>
       </c>
       <c r="H147" s="10" t="n"/>
       <c r="I147" s="10" t="n"/>
       <c r="J147" s="8" t="inlineStr">
         <is>
-          <t>malir</t>
+          <t>elektroinstalater</t>
         </is>
       </c>
       <c r="K147" s="24" t="n">
@@ -18643,12 +18607,12 @@
       </c>
       <c r="L147" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M147" s="8" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.004 + SDK podhled PSV78.007</t>
+          <t>TZ PBŘ dům — ČSN EN 14604 autonomní hlásič kouře 4 ks</t>
         </is>
       </c>
       <c r="N147" s="20" t="inlineStr">
@@ -18664,7 +18628,7 @@
       <c r="P147" s="41" t="n"/>
       <c r="Q147" s="41" t="inlineStr">
         <is>
-          <t>GAP_007</t>
+          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
         </is>
       </c>
     </row>
@@ -18679,17 +18643,17 @@
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>Autonomní hlásič kouře</t>
+          <t>Přenosný hasicí přístroj 34A</t>
         </is>
       </c>
       <c r="D148" s="20" t="inlineStr">
         <is>
-          <t>375211101</t>
+          <t>966067121</t>
         </is>
       </c>
       <c r="E148" s="8" t="inlineStr">
         <is>
-          <t>Autonomní hlásič kouře dle ČSN EN 14604 — 4 ks v místnostech 1.01, 1.02, 2.04, 3.03 dle PBŘ</t>
+          <t>Přenosný hasicí přístroj 34A dle PBŘ — min. 1 ks na společné chodbě</t>
         </is>
       </c>
       <c r="F148" s="20" t="inlineStr">
@@ -18698,13 +18662,13 @@
         </is>
       </c>
       <c r="G148" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H148" s="10" t="n"/>
       <c r="I148" s="10" t="n"/>
       <c r="J148" s="8" t="inlineStr">
         <is>
-          <t>elektroinstalater</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K148" s="24" t="n">
@@ -18712,12 +18676,12 @@
       </c>
       <c r="L148" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M148" s="8" t="inlineStr">
         <is>
-          <t>TZ PBŘ dům — ČSN EN 14604 autonomní hlásič kouře 4 ks</t>
+          <t>TZ PBŘ dům — PHP 34A 1 ks minimum</t>
         </is>
       </c>
       <c r="N148" s="20" t="inlineStr">
@@ -18731,11 +18695,7 @@
         </is>
       </c>
       <c r="P148" s="41" t="n"/>
-      <c r="Q148" s="41" t="inlineStr">
-        <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
-        </is>
-      </c>
+      <c r="Q148" s="41" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="20" t="n">
@@ -18748,22 +18708,22 @@
       </c>
       <c r="C149" s="8" t="inlineStr">
         <is>
-          <t>Přenosný hasicí přístroj 34A</t>
+          <t>Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
         </is>
       </c>
       <c r="D149" s="20" t="inlineStr">
         <is>
-          <t>966067121</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
         <is>
-          <t>Přenosný hasicí přístroj 34A dle PBŘ — min. 1 ks na společné chodbě</t>
+          <t>Předávací protokol krbu na tuhá paliva + kontrola bezpečných vzdáleností (800 mm směr sálání / 400 mm strany, nehořlavá zóna podlahy) dle PBŘ</t>
         </is>
       </c>
       <c r="F149" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>soubor</t>
         </is>
       </c>
       <c r="G149" s="23" t="n">
@@ -18773,11 +18733,11 @@
       <c r="I149" s="10" t="n"/>
       <c r="J149" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>topenar</t>
         </is>
       </c>
       <c r="K149" s="24" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="L149" s="20" t="inlineStr">
         <is>
@@ -18786,7 +18746,7 @@
       </c>
       <c r="M149" s="8" t="inlineStr">
         <is>
-          <t>TZ PBŘ dům — PHP 34A 1 ks minimum</t>
+          <t>PBŘ D.3</t>
         </is>
       </c>
       <c r="N149" s="20" t="inlineStr">
@@ -18799,8 +18759,12 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P149" s="41" t="n"/>
-      <c r="Q149" s="41" t="n"/>
+      <c r="P149" s="41" t="inlineStr"/>
+      <c r="Q149" s="41" t="inlineStr">
+        <is>
+          <t>DODATEK_PBR_GAPS_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="20" t="n">
@@ -18808,27 +18772,27 @@
       </c>
       <c r="B150" s="8" t="inlineStr">
         <is>
-          <t>PSV-95 Detekce požární</t>
+          <t>M-21 ELI silnoproud</t>
         </is>
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
+          <t>Demontáž stávající ELI</t>
         </is>
       </c>
       <c r="D150" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>210010011</t>
         </is>
       </c>
       <c r="E150" s="8" t="inlineStr">
         <is>
-          <t>Předávací protokol krbu na tuhá paliva + kontrola bezpečných vzdáleností (800 mm směr sálání / 400 mm strany, nehořlavá zóna podlahy) dle PBŘ</t>
+          <t>Demontáž stávající elektroinstalace v celém domě (vodiče, rozvaděč, zásuvky, svítidla) — recyklace mědi</t>
         </is>
       </c>
       <c r="F150" s="20" t="inlineStr">
         <is>
-          <t>soubor</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G150" s="23" t="n">
@@ -18838,11 +18802,11 @@
       <c r="I150" s="10" t="n"/>
       <c r="J150" s="8" t="inlineStr">
         <is>
-          <t>topenar</t>
+          <t>elektroinstalater</t>
         </is>
       </c>
       <c r="K150" s="24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L150" s="20" t="inlineStr">
         <is>
@@ -18851,12 +18815,12 @@
       </c>
       <c r="M150" s="8" t="inlineStr">
         <is>
-          <t>PBŘ D.3</t>
+          <t>TZ ARS dům §4 — kompletně nová ELI</t>
         </is>
       </c>
       <c r="N150" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#7</t>
         </is>
       </c>
       <c r="O150" s="26" t="inlineStr">
@@ -18864,12 +18828,8 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P150" s="41" t="inlineStr"/>
-      <c r="Q150" s="41" t="inlineStr">
-        <is>
-          <t>DODATEK_PBR_GAPS_2026-06-01</t>
-        </is>
-      </c>
+      <c r="P150" s="41" t="n"/>
+      <c r="Q150" s="41" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="20" t="n">
@@ -18882,26 +18842,26 @@
       </c>
       <c r="C151" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávající ELI</t>
+          <t>Pojistková skříň + 3× podružný rozvaděč</t>
         </is>
       </c>
       <c r="D151" s="20" t="inlineStr">
         <is>
-          <t>210010011</t>
+          <t>210110023</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávající elektroinstalace v celém domě (vodiče, rozvaděč, zásuvky, svítidla) — recyklace mědi</t>
+          <t>Nová pojistková skříň + 3× podružný rozvaděč pro každé patro (1.NP, 2.NP, 3.NP) s podružným měřením</t>
         </is>
       </c>
       <c r="F151" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G151" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H151" s="10" t="n"/>
       <c r="I151" s="10" t="n"/>
@@ -18920,7 +18880,7 @@
       </c>
       <c r="M151" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — kompletně nová ELI</t>
+          <t>TZ ARS dům §4 — 'nová pojistková skříň s podružným měřením pro každé patro'</t>
         </is>
       </c>
       <c r="N151" s="20" t="inlineStr">
@@ -18947,26 +18907,26 @@
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>Pojistková skříň + 3× podružný rozvaděč</t>
+          <t>Rozvody silnoproud</t>
         </is>
       </c>
       <c r="D152" s="20" t="inlineStr">
         <is>
-          <t>210110023</t>
+          <t>210800012</t>
         </is>
       </c>
       <c r="E152" s="8" t="inlineStr">
         <is>
-          <t>Nová pojistková skříň + 3× podružný rozvaděč pro každé patro (1.NP, 2.NP, 3.NP) s podružným měřením</t>
+          <t>Nové silnoproudé rozvody — vodiče CYKY 3×1.5 / 3×2.5 / 5×2.5 / 5×6 + krabice + instalační trubky</t>
         </is>
       </c>
       <c r="F152" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G152" s="23" t="n">
-        <v>4</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G152" s="22" t="n">
+        <v>700</v>
       </c>
       <c r="H152" s="10" t="n"/>
       <c r="I152" s="10" t="n"/>
@@ -18976,7 +18936,7 @@
         </is>
       </c>
       <c r="K152" s="24" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="L152" s="20" t="inlineStr">
         <is>
@@ -18985,7 +18945,7 @@
       </c>
       <c r="M152" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — 'nová pojistková skříň s podružným měřením pro každé patro'</t>
+          <t>TZ ARS + B4_productivity standard RD 3-byt. dispozice</t>
         </is>
       </c>
       <c r="N152" s="20" t="inlineStr">
@@ -19012,26 +18972,26 @@
       </c>
       <c r="C153" s="8" t="inlineStr">
         <is>
-          <t>Rozvody silnoproud</t>
+          <t>Zásuvky a vypínače</t>
         </is>
       </c>
       <c r="D153" s="20" t="inlineStr">
         <is>
-          <t>210800012</t>
+          <t>210810050</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
         <is>
-          <t>Nové silnoproudé rozvody — vodiče CYKY 3×1.5 / 3×2.5 / 5×2.5 / 5×6 + krabice + instalační trubky</t>
+          <t>Zásuvky a vypínače dodávka + montáž — ~70 ks (60-80 dle vyjasnění #7)</t>
         </is>
       </c>
       <c r="F153" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G153" s="22" t="n">
-        <v>700</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G153" s="23" t="n">
+        <v>70</v>
       </c>
       <c r="H153" s="10" t="n"/>
       <c r="I153" s="10" t="n"/>
@@ -19050,7 +19010,7 @@
       </c>
       <c r="M153" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD 3-byt. dispozice</t>
+          <t>TZ ARS + B4_productivity standard RD 220 m² 3-byt.</t>
         </is>
       </c>
       <c r="N153" s="20" t="inlineStr">
@@ -19077,17 +19037,17 @@
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>Zásuvky a vypínače</t>
+          <t>Svítidla</t>
         </is>
       </c>
       <c r="D154" s="20" t="inlineStr">
         <is>
-          <t>210810050</t>
+          <t>210820002</t>
         </is>
       </c>
       <c r="E154" s="8" t="inlineStr">
         <is>
-          <t>Zásuvky a vypínače dodávka + montáž — ~70 ks (60-80 dle vyjasnění #7)</t>
+          <t>Svítidla dodávka + montáž — ~35 ks (30-40 dle vyjasnění #7) interiér + venkovní u vstupů</t>
         </is>
       </c>
       <c r="F154" s="20" t="inlineStr">
@@ -19096,7 +19056,7 @@
         </is>
       </c>
       <c r="G154" s="23" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="H154" s="10" t="n"/>
       <c r="I154" s="10" t="n"/>
@@ -19115,7 +19075,7 @@
       </c>
       <c r="M154" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD 220 m² 3-byt.</t>
+          <t>TZ ARS + B4_productivity standard RD</t>
         </is>
       </c>
       <c r="N154" s="20" t="inlineStr">
@@ -19142,26 +19102,26 @@
       </c>
       <c r="C155" s="8" t="inlineStr">
         <is>
-          <t>Svítidla</t>
+          <t>Příprava FVE</t>
         </is>
       </c>
       <c r="D155" s="20" t="inlineStr">
         <is>
-          <t>210820002</t>
+          <t>210800099</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
         <is>
-          <t>Svítidla dodávka + montáž — ~35 ks (30-40 dle vyjasnění #7) interiér + venkovní u vstupů</t>
+          <t>Příprava na osazení FVE — rezerva v rozvaděči (jistič + zásuvka pro střídač) + trasy do střechy</t>
         </is>
       </c>
       <c r="F155" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G155" s="23" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="H155" s="10" t="n"/>
       <c r="I155" s="10" t="n"/>
@@ -19171,7 +19131,7 @@
         </is>
       </c>
       <c r="K155" s="24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L155" s="20" t="inlineStr">
         <is>
@@ -19180,7 +19140,7 @@
       </c>
       <c r="M155" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD</t>
+          <t>TZ ARS dům §4 — FVE příprava (bez panelů samotných)</t>
         </is>
       </c>
       <c r="N155" s="20" t="inlineStr">
@@ -19207,17 +19167,17 @@
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>Příprava FVE</t>
+          <t>Revize ELI při kolaudaci</t>
         </is>
       </c>
       <c r="D156" s="20" t="inlineStr">
         <is>
-          <t>210800099</t>
+          <t>996019011</t>
         </is>
       </c>
       <c r="E156" s="8" t="inlineStr">
         <is>
-          <t>Příprava na osazení FVE — rezerva v rozvaděči (jistič + zásuvka pro střídač) + trasy do střechy</t>
+          <t>Výchozí revize elektrické instalace dle ČSN 33 2000-6 + revizní zpráva pro kolaudaci</t>
         </is>
       </c>
       <c r="F156" s="20" t="inlineStr">
@@ -19232,11 +19192,11 @@
       <c r="I156" s="10" t="n"/>
       <c r="J156" s="8" t="inlineStr">
         <is>
-          <t>elektroinstalater</t>
+          <t>revize_specialista</t>
         </is>
       </c>
       <c r="K156" s="24" t="n">
-        <v>0.85</v>
+        <v>0.99</v>
       </c>
       <c r="L156" s="20" t="inlineStr">
         <is>
@@ -19245,12 +19205,12 @@
       </c>
       <c r="M156" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — FVE příprava (bez panelů samotných)</t>
+          <t>Povinná revize ELI dle ČSN 33 2000-6 + kolaudace</t>
         </is>
       </c>
       <c r="N156" s="20" t="inlineStr">
         <is>
-          <t>#7</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O156" s="26" t="inlineStr">
@@ -19267,22 +19227,22 @@
       </c>
       <c r="B157" s="8" t="inlineStr">
         <is>
-          <t>M-21 ELI silnoproud</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="C157" s="8" t="inlineStr">
         <is>
-          <t>Revize ELI při kolaudaci</t>
+          <t>Revize stávajících přípojek</t>
         </is>
       </c>
       <c r="D157" s="20" t="inlineStr">
         <is>
-          <t>996019011</t>
+          <t>722290515</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
         <is>
-          <t>Výchozí revize elektrické instalace dle ČSN 33 2000-6 + revizní zpráva pro kolaudaci</t>
+          <t>Revize stávajícího napojení vodovodu + kanalizace na pozemku — kontrola stavu, čištění, tlaková zkouška</t>
         </is>
       </c>
       <c r="F157" s="20" t="inlineStr">
@@ -19297,25 +19257,25 @@
       <c r="I157" s="10" t="n"/>
       <c r="J157" s="8" t="inlineStr">
         <is>
-          <t>revize_specialista</t>
+          <t>vodar</t>
         </is>
       </c>
       <c r="K157" s="24" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="L157" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M157" s="8" t="inlineStr">
         <is>
-          <t>Povinná revize ELI dle ČSN 33 2000-6 + kolaudace</t>
+          <t>TZ ARS dům §4 — vodovod + kanalizace stávající, bez změny</t>
         </is>
       </c>
       <c r="N157" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O157" s="26" t="inlineStr">
@@ -19324,7 +19284,11 @@
         </is>
       </c>
       <c r="P157" s="41" t="n"/>
-      <c r="Q157" s="41" t="n"/>
+      <c r="Q157" s="41" t="inlineStr">
+        <is>
+          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="20" t="n">
@@ -19337,26 +19301,26 @@
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>Revize stávajících přípojek</t>
+          <t>Nové rozvody vody do 3.NP</t>
         </is>
       </c>
       <c r="D158" s="20" t="inlineStr">
         <is>
-          <t>722290515</t>
+          <t>722172011</t>
         </is>
       </c>
       <c r="E158" s="8" t="inlineStr">
         <is>
-          <t>Revize stávajícího napojení vodovodu + kanalizace na pozemku — kontrola stavu, čištění, tlaková zkouška</t>
+          <t>Nové rozvody studené + teplé vody do koupelen 1.NP + 2.NP + 3.NP a kuchyní (PEX/Cu, dimenze DN15-25)</t>
         </is>
       </c>
       <c r="F158" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G158" s="23" t="n">
-        <v>1</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G158" s="22" t="n">
+        <v>80</v>
       </c>
       <c r="H158" s="10" t="n"/>
       <c r="I158" s="10" t="n"/>
@@ -19366,7 +19330,7 @@
         </is>
       </c>
       <c r="K158" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L158" s="20" t="inlineStr">
         <is>
@@ -19375,7 +19339,7 @@
       </c>
       <c r="M158" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — vodovod + kanalizace stávající, bez změny</t>
+          <t>TZ ARS dům §4 — nové koupelny + kuchyně, vyjasnění #6 working assumption</t>
         </is>
       </c>
       <c r="N158" s="20" t="inlineStr">
@@ -19406,17 +19370,17 @@
       </c>
       <c r="C159" s="8" t="inlineStr">
         <is>
-          <t>Nové rozvody vody do 3.NP</t>
+          <t>Nové odpadní rozvody</t>
         </is>
       </c>
       <c r="D159" s="20" t="inlineStr">
         <is>
-          <t>722172011</t>
+          <t>721174021</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
         <is>
-          <t>Nové rozvody studené + teplé vody do koupelen 1.NP + 2.NP + 3.NP a kuchyní (PEX/Cu, dimenze DN15-25)</t>
+          <t>Nové odpadní rozvody PVC-HT DN40-DN110 ke koupelnám 1.NP, 2.NP, 3.NP a kuchyním + napojení na stávající</t>
         </is>
       </c>
       <c r="F159" s="20" t="inlineStr">
@@ -19425,7 +19389,7 @@
         </is>
       </c>
       <c r="G159" s="22" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H159" s="10" t="n"/>
       <c r="I159" s="10" t="n"/>
@@ -19439,12 +19403,12 @@
       </c>
       <c r="L159" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M159" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — nové koupelny + kuchyně, vyjasnění #6 working assumption</t>
+          <t>TZ ARS dům §4 — nové koupelny + kuchyně, odpad do stávající kanalizace</t>
         </is>
       </c>
       <c r="N159" s="20" t="inlineStr">
@@ -19458,11 +19422,7 @@
         </is>
       </c>
       <c r="P159" s="41" t="n"/>
-      <c r="Q159" s="41" t="inlineStr">
-        <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
-        </is>
-      </c>
+      <c r="Q159" s="41" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="20" t="n">
@@ -19475,26 +19435,26 @@
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>Nové odpadní rozvody</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP)</t>
         </is>
       </c>
       <c r="D160" s="20" t="inlineStr">
         <is>
-          <t>721174021</t>
+          <t>725291131</t>
         </is>
       </c>
       <c r="E160" s="8" t="inlineStr">
         <is>
-          <t>Nové odpadní rozvody PVC-HT DN40-DN110 ke koupelnám 1.NP, 2.NP, 3.NP a kuchyním + napojení na stávající</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 1.05 1.NP: 1× vana (DXF) + 1× umyvadlo (DXF) + 1× WC (TZ standard)</t>
         </is>
       </c>
       <c r="F160" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>set</t>
         </is>
       </c>
       <c r="G160" s="22" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H160" s="10" t="n"/>
       <c r="I160" s="10" t="n"/>
@@ -19513,7 +19473,7 @@
       </c>
       <c r="M160" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — nové koupelny + kuchyně, odpad do stávající kanalizace</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 1.05 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="N160" s="20" t="inlineStr">
@@ -19527,7 +19487,11 @@
         </is>
       </c>
       <c r="P160" s="41" t="n"/>
-      <c r="Q160" s="41" t="n"/>
+      <c r="Q160" s="41" t="inlineStr">
+        <is>
+          <t>GAP_005_deprecated</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="20" t="n">
@@ -19540,26 +19504,26 @@
       </c>
       <c r="C161" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP)</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture A</t>
         </is>
       </c>
       <c r="D161" s="20" t="inlineStr">
         <is>
-          <t>725291131</t>
+          <t>725211101</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 1.05 1.NP: 1× vana (DXF) + 1× umyvadlo (DXF) + 1× WC (TZ standard)</t>
+          <t>Vana koupelnová obdélníková 170×70 cm — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="F161" s="20" t="inlineStr">
         <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="G161" s="22" t="n">
-        <v>0</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G161" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H161" s="10" t="n"/>
       <c r="I161" s="10" t="n"/>
@@ -19569,7 +19533,7 @@
         </is>
       </c>
       <c r="K161" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L161" s="20" t="inlineStr">
         <is>
@@ -19578,12 +19542,12 @@
       </c>
       <c r="M161" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 1.05 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>DXF dum_DPZ MTEXT room 1.05 1.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="N161" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O161" s="26" t="inlineStr">
@@ -19594,7 +19558,7 @@
       <c r="P161" s="41" t="n"/>
       <c r="Q161" s="41" t="inlineStr">
         <is>
-          <t>GAP_005_deprecated</t>
+          <t>GAP_005</t>
         </is>
       </c>
     </row>
@@ -19609,17 +19573,17 @@
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture A</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture B</t>
         </is>
       </c>
       <c r="D162" s="20" t="inlineStr">
         <is>
-          <t>725211101</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="E162" s="8" t="inlineStr">
         <is>
-          <t>Vana koupelnová obdélníková 170×70 cm — koupelna 1.05 1.NP</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="F162" s="20" t="inlineStr">
@@ -19678,17 +19642,17 @@
       </c>
       <c r="C163" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture B</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture C</t>
         </is>
       </c>
       <c r="D163" s="20" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="E163" s="8" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 1.05 1.NP</t>
+          <t>WC kombi keramické bílé — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="F163" s="20" t="inlineStr">
@@ -19747,26 +19711,26 @@
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture C</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP)</t>
         </is>
       </c>
       <c r="D164" s="20" t="inlineStr">
         <is>
-          <t>725111101</t>
+          <t>725291131</t>
         </is>
       </c>
       <c r="E164" s="8" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 1.05 1.NP</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 2.03 2.NP: 1× umyvadlo (DXF) + 1× WC (TZ standard) + 1× sprcha (TZ standard)</t>
         </is>
       </c>
       <c r="F164" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G164" s="23" t="n">
-        <v>1</v>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="G164" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H164" s="10" t="n"/>
       <c r="I164" s="10" t="n"/>
@@ -19776,7 +19740,7 @@
         </is>
       </c>
       <c r="K164" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L164" s="20" t="inlineStr">
         <is>
@@ -19785,12 +19749,12 @@
       </c>
       <c r="M164" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 1.05 1.NP + TZ ARS koupelna kompletace</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 2.03 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="N164" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O164" s="26" t="inlineStr">
@@ -19801,7 +19765,7 @@
       <c r="P164" s="41" t="n"/>
       <c r="Q164" s="41" t="inlineStr">
         <is>
-          <t>GAP_005</t>
+          <t>GAP_005_deprecated</t>
         </is>
       </c>
     </row>
@@ -19816,26 +19780,26 @@
       </c>
       <c r="C165" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP)</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture A</t>
         </is>
       </c>
       <c r="D165" s="20" t="inlineStr">
         <is>
-          <t>725291131</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 2.03 2.NP: 1× umyvadlo (DXF) + 1× WC (TZ standard) + 1× sprcha (TZ standard)</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="F165" s="20" t="inlineStr">
         <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="G165" s="22" t="n">
-        <v>0</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G165" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H165" s="10" t="n"/>
       <c r="I165" s="10" t="n"/>
@@ -19845,7 +19809,7 @@
         </is>
       </c>
       <c r="K165" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L165" s="20" t="inlineStr">
         <is>
@@ -19854,12 +19818,12 @@
       </c>
       <c r="M165" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 2.03 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>DXF dum_DPZ MTEXT room 2.03 2.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="N165" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O165" s="26" t="inlineStr">
@@ -19870,7 +19834,7 @@
       <c r="P165" s="41" t="n"/>
       <c r="Q165" s="41" t="inlineStr">
         <is>
-          <t>GAP_005_deprecated</t>
+          <t>GAP_005</t>
         </is>
       </c>
     </row>
@@ -19885,17 +19849,17 @@
       </c>
       <c r="C166" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture A</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture B</t>
         </is>
       </c>
       <c r="D166" s="20" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725221201</t>
         </is>
       </c>
       <c r="E166" s="8" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 2.03 2.NP</t>
+          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="F166" s="20" t="inlineStr">
@@ -19954,17 +19918,17 @@
       </c>
       <c r="C167" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture B</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture C</t>
         </is>
       </c>
       <c r="D167" s="20" t="inlineStr">
         <is>
-          <t>725221201</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="E167" s="8" t="inlineStr">
         <is>
-          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 2.03 2.NP</t>
+          <t>WC kombi keramické bílé — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="F167" s="20" t="inlineStr">
@@ -20023,26 +19987,26 @@
       </c>
       <c r="C168" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture C</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP)</t>
         </is>
       </c>
       <c r="D168" s="20" t="inlineStr">
         <is>
-          <t>725111101</t>
+          <t>725291131</t>
         </is>
       </c>
       <c r="E168" s="8" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 2.03 2.NP</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 3.04 3.NP: 1× WC (DXF) + 1× umyvadlo (TZ standard) + 1× sprcha (TZ standard)</t>
         </is>
       </c>
       <c r="F168" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G168" s="23" t="n">
-        <v>1</v>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="G168" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H168" s="10" t="n"/>
       <c r="I168" s="10" t="n"/>
@@ -20052,7 +20016,7 @@
         </is>
       </c>
       <c r="K168" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L168" s="20" t="inlineStr">
         <is>
@@ -20061,12 +20025,12 @@
       </c>
       <c r="M168" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 2.03 2.NP + TZ ARS koupelna kompletace</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 3.04 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="N168" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O168" s="26" t="inlineStr">
@@ -20077,7 +20041,7 @@
       <c r="P168" s="41" t="n"/>
       <c r="Q168" s="41" t="inlineStr">
         <is>
-          <t>GAP_005</t>
+          <t>GAP_005_deprecated</t>
         </is>
       </c>
     </row>
@@ -20092,26 +20056,26 @@
       </c>
       <c r="C169" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP)</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture A</t>
         </is>
       </c>
       <c r="D169" s="20" t="inlineStr">
         <is>
-          <t>725291131</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="E169" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 3.04 3.NP: 1× WC (DXF) + 1× umyvadlo (TZ standard) + 1× sprcha (TZ standard)</t>
+          <t>WC kombi keramické bílé — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="F169" s="20" t="inlineStr">
         <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="G169" s="22" t="n">
-        <v>0</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G169" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H169" s="10" t="n"/>
       <c r="I169" s="10" t="n"/>
@@ -20121,7 +20085,7 @@
         </is>
       </c>
       <c r="K169" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L169" s="20" t="inlineStr">
         <is>
@@ -20130,12 +20094,12 @@
       </c>
       <c r="M169" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 3.04 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>DXF dum_DPZ MTEXT room 3.04 3.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="N169" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O169" s="26" t="inlineStr">
@@ -20146,7 +20110,7 @@
       <c r="P169" s="41" t="n"/>
       <c r="Q169" s="41" t="inlineStr">
         <is>
-          <t>GAP_005_deprecated</t>
+          <t>GAP_005</t>
         </is>
       </c>
     </row>
@@ -20161,17 +20125,17 @@
       </c>
       <c r="C170" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture A</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture B</t>
         </is>
       </c>
       <c r="D170" s="20" t="inlineStr">
         <is>
-          <t>725111101</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="E170" s="8" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 3.04 3.NP</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="F170" s="20" t="inlineStr">
@@ -20230,17 +20194,17 @@
       </c>
       <c r="C171" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture B</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture C</t>
         </is>
       </c>
       <c r="D171" s="20" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725221201</t>
         </is>
       </c>
       <c r="E171" s="8" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 3.04 3.NP</t>
+          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="F171" s="20" t="inlineStr">
@@ -20299,17 +20263,17 @@
       </c>
       <c r="C172" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture C</t>
+          <t>Kuchyňský dřez 2 ks (1.06 + 3.05)</t>
         </is>
       </c>
       <c r="D172" s="20" t="inlineStr">
         <is>
-          <t>725221201</t>
+          <t>725840111</t>
         </is>
       </c>
       <c r="E172" s="8" t="inlineStr">
         <is>
-          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 3.04 3.NP</t>
+          <t>Kuchyňský dřez nerez + montáž — 2 ks (kuchyně 1.06 byt rodičů + kuchyně 3.05 byt 3.NP)</t>
         </is>
       </c>
       <c r="F172" s="20" t="inlineStr">
@@ -20318,7 +20282,7 @@
         </is>
       </c>
       <c r="G172" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H172" s="10" t="n"/>
       <c r="I172" s="10" t="n"/>
@@ -20328,7 +20292,7 @@
         </is>
       </c>
       <c r="K172" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L172" s="20" t="inlineStr">
         <is>
@@ -20337,12 +20301,12 @@
       </c>
       <c r="M172" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 3.04 3.NP + TZ ARS koupelna kompletace</t>
+          <t>DXF kuchyně MTEXT 2× + TZ ARS — dispozice byty</t>
         </is>
       </c>
       <c r="N172" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O172" s="26" t="inlineStr">
@@ -20351,11 +20315,7 @@
         </is>
       </c>
       <c r="P172" s="41" t="n"/>
-      <c r="Q172" s="41" t="inlineStr">
-        <is>
-          <t>GAP_005</t>
-        </is>
-      </c>
+      <c r="Q172" s="41" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="20" t="n">
@@ -20368,17 +20328,17 @@
       </c>
       <c r="C173" s="8" t="inlineStr">
         <is>
-          <t>Kuchyňský dřez 2 ks (1.06 + 3.05)</t>
+          <t>Vodovodní baterie + drobnosti</t>
         </is>
       </c>
       <c r="D173" s="20" t="inlineStr">
         <is>
-          <t>725840111</t>
+          <t>725822611</t>
         </is>
       </c>
       <c r="E173" s="8" t="inlineStr">
         <is>
-          <t>Kuchyňský dřez nerez + montáž — 2 ks (kuchyně 1.06 byt rodičů + kuchyně 3.05 byt 3.NP)</t>
+          <t>Vodovodní baterie (WC ventil + páková umyvadlová + sprchové + dřezové + termostat sprchové) — ~15 ks + drobné instalační materiály</t>
         </is>
       </c>
       <c r="F173" s="20" t="inlineStr">
@@ -20387,7 +20347,7 @@
         </is>
       </c>
       <c r="G173" s="23" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H173" s="10" t="n"/>
       <c r="I173" s="10" t="n"/>
@@ -20397,7 +20357,7 @@
         </is>
       </c>
       <c r="K173" s="24" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L173" s="20" t="inlineStr">
         <is>
@@ -20406,7 +20366,7 @@
       </c>
       <c r="M173" s="8" t="inlineStr">
         <is>
-          <t>DXF kuchyně MTEXT 2× + TZ ARS — dispozice byty</t>
+          <t>TZ ARS — kompletní baterie nové</t>
         </is>
       </c>
       <c r="N173" s="20" t="inlineStr">
@@ -20433,17 +20393,17 @@
       </c>
       <c r="C174" s="8" t="inlineStr">
         <is>
-          <t>Vodovodní baterie + drobnosti</t>
+          <t>Akumulační zásobník TUV v suterénu</t>
         </is>
       </c>
       <c r="D174" s="20" t="inlineStr">
         <is>
-          <t>725822611</t>
+          <t>732419411</t>
         </is>
       </c>
       <c r="E174" s="8" t="inlineStr">
         <is>
-          <t>Vodovodní baterie (WC ventil + páková umyvadlová + sprchové + dřezové + termostat sprchové) — ~15 ks + drobné instalační materiály</t>
+          <t>Akumulační zásobník TUV ~300 l v 1.PP napojený na topný systém (sporáková kamna + krb + elektrokotel) — nepřímotop</t>
         </is>
       </c>
       <c r="F174" s="20" t="inlineStr">
@@ -20452,17 +20412,17 @@
         </is>
       </c>
       <c r="G174" s="23" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H174" s="10" t="n"/>
       <c r="I174" s="10" t="n"/>
       <c r="J174" s="8" t="inlineStr">
         <is>
-          <t>vodar</t>
+          <t>instalater_TUV_akumulacni_zasobnik</t>
         </is>
       </c>
       <c r="K174" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L174" s="20" t="inlineStr">
         <is>
@@ -20471,7 +20431,7 @@
       </c>
       <c r="M174" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS — kompletní baterie nové</t>
+          <t>TZ ARS dům §4 — kombi akumulační zásobník napojený na multivariantní topný systém</t>
         </is>
       </c>
       <c r="N174" s="20" t="inlineStr">
@@ -20498,17 +20458,17 @@
       </c>
       <c r="C175" s="8" t="inlineStr">
         <is>
-          <t>Akumulační zásobník TUV v suterénu</t>
+          <t>Elektrický bojler 3.NP</t>
         </is>
       </c>
       <c r="D175" s="20" t="inlineStr">
         <is>
-          <t>732419411</t>
+          <t>732429211</t>
         </is>
       </c>
       <c r="E175" s="8" t="inlineStr">
         <is>
-          <t>Akumulační zásobník TUV ~300 l v 1.PP napojený na topný systém (sporáková kamna + krb + elektrokotel) — nepřímotop</t>
+          <t>Elektrický bojler ~80 l v koupelně 3.NP (nezávislý zdroj pro samostatný byt)</t>
         </is>
       </c>
       <c r="F175" s="20" t="inlineStr">
@@ -20523,7 +20483,7 @@
       <c r="I175" s="10" t="n"/>
       <c r="J175" s="8" t="inlineStr">
         <is>
-          <t>instalater_TUV_akumulacni_zasobnik</t>
+          <t>vodar</t>
         </is>
       </c>
       <c r="K175" s="24" t="n">
@@ -20536,7 +20496,7 @@
       </c>
       <c r="M175" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — kombi akumulační zásobník napojený na multivariantní topný systém</t>
+          <t>TZ ARS dům §4 — elektrický bojler v 3.NP koupelně, vyjasnění #6 odhad 80 l</t>
         </is>
       </c>
       <c r="N175" s="20" t="inlineStr">
@@ -20558,22 +20518,22 @@
       </c>
       <c r="B176" s="8" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>PSV-73 Vytápění</t>
         </is>
       </c>
       <c r="C176" s="8" t="inlineStr">
         <is>
-          <t>Elektrický bojler 3.NP</t>
+          <t>Sporáková kamna na tuhá paliva</t>
         </is>
       </c>
       <c r="D176" s="20" t="inlineStr">
         <is>
-          <t>732429211</t>
+          <t>733241011</t>
         </is>
       </c>
       <c r="E176" s="8" t="inlineStr">
         <is>
-          <t>Elektrický bojler ~80 l v koupelně 3.NP (nezávislý zdroj pro samostatný byt)</t>
+          <t>Sporáková kamna na tuhá paliva ~10 kW s akumulačním zásobníkem TUV — dodávka</t>
         </is>
       </c>
       <c r="F176" s="20" t="inlineStr">
@@ -20588,7 +20548,7 @@
       <c r="I176" s="10" t="n"/>
       <c r="J176" s="8" t="inlineStr">
         <is>
-          <t>vodar</t>
+          <t>topenar</t>
         </is>
       </c>
       <c r="K176" s="24" t="n">
@@ -20601,7 +20561,7 @@
       </c>
       <c r="M176" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — elektrický bojler v 3.NP koupelně, vyjasnění #6 odhad 80 l</t>
+          <t>TZ ARS dům §4 — primární zdroj 1.NP/2.NP, ~10 kW odhad standard RD</t>
         </is>
       </c>
       <c r="N176" s="20" t="inlineStr">
@@ -20628,22 +20588,22 @@
       </c>
       <c r="C177" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna na tuhá paliva</t>
+          <t>Sporáková kamna — montáž</t>
         </is>
       </c>
       <c r="D177" s="20" t="inlineStr">
         <is>
-          <t>733241011</t>
+          <t>733281011</t>
         </is>
       </c>
       <c r="E177" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna na tuhá paliva ~10 kW s akumulačním zásobníkem TUV — dodávka</t>
+          <t>Sporáková kamna — montáž vč. napojení na komín + akumulační zásobník (cca 8 Nh)</t>
         </is>
       </c>
       <c r="F177" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G177" s="23" t="n">
@@ -20657,7 +20617,7 @@
         </is>
       </c>
       <c r="K177" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L177" s="20" t="inlineStr">
         <is>
@@ -20666,12 +20626,12 @@
       </c>
       <c r="M177" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — primární zdroj 1.NP/2.NP, ~10 kW odhad standard RD</t>
+          <t>Standard montáž kamen s napojením na zásobník</t>
         </is>
       </c>
       <c r="N177" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O177" s="26" t="inlineStr">
@@ -20693,22 +20653,22 @@
       </c>
       <c r="C178" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna — montáž</t>
+          <t>Elektrokotel 3.NP</t>
         </is>
       </c>
       <c r="D178" s="20" t="inlineStr">
         <is>
-          <t>733281011</t>
+          <t>733131221</t>
         </is>
       </c>
       <c r="E178" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna — montáž vč. napojení na komín + akumulační zásobník (cca 8 Nh)</t>
+          <t>Elektrokotel ~8 kW pro 3.NP samostatný byt — dodávka + montáž + napojení</t>
         </is>
       </c>
       <c r="F178" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G178" s="23" t="n">
@@ -20722,7 +20682,7 @@
         </is>
       </c>
       <c r="K178" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L178" s="20" t="inlineStr">
         <is>
@@ -20731,12 +20691,12 @@
       </c>
       <c r="M178" s="8" t="inlineStr">
         <is>
-          <t>Standard montáž kamen s napojením na zásobník</t>
+          <t>TZ ARS dům §4 — 'Nově navržené 3.NP bude vytápěno elektrokotlem'; ~8 kW odhad</t>
         </is>
       </c>
       <c r="N178" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O178" s="26" t="inlineStr">
@@ -20758,17 +20718,17 @@
       </c>
       <c r="C179" s="8" t="inlineStr">
         <is>
-          <t>Elektrokotel 3.NP</t>
+          <t>Krb na tuhá paliva 3.NP</t>
         </is>
       </c>
       <c r="D179" s="20" t="inlineStr">
         <is>
-          <t>733131221</t>
+          <t>733241011</t>
         </is>
       </c>
       <c r="E179" s="8" t="inlineStr">
         <is>
-          <t>Elektrokotel ~8 kW pro 3.NP samostatný byt — dodávka + montáž + napojení</t>
+          <t>Krb na tuhá paliva v 3.NP ~6 kW — dodávka + montáž s napojením na samostatný komín</t>
         </is>
       </c>
       <c r="F179" s="20" t="inlineStr">
@@ -20796,7 +20756,7 @@
       </c>
       <c r="M179" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — 'Nově navržené 3.NP bude vytápěno elektrokotlem'; ~8 kW odhad</t>
+          <t>TZ ARS dům §4 — krb v 3.NP, ~6 kW odhad</t>
         </is>
       </c>
       <c r="N179" s="20" t="inlineStr">
@@ -20823,17 +20783,17 @@
       </c>
       <c r="C180" s="8" t="inlineStr">
         <is>
-          <t>Krb na tuhá paliva 3.NP</t>
+          <t>Multisplit TČ — venkovní jednotka</t>
         </is>
       </c>
       <c r="D180" s="20" t="inlineStr">
         <is>
-          <t>733241011</t>
+          <t>733425211</t>
         </is>
       </c>
       <c r="E180" s="8" t="inlineStr">
         <is>
-          <t>Krb na tuhá paliva v 3.NP ~6 kW — dodávka + montáž s napojením na samostatný komín</t>
+          <t>Multisplit tepelné čerpadlo vzduch-vzduch — 1× venkovní jednotka ~10 kW (silent mode hl. tlaku ≤49 dBA)</t>
         </is>
       </c>
       <c r="F180" s="20" t="inlineStr">
@@ -20848,7 +20808,7 @@
       <c r="I180" s="10" t="n"/>
       <c r="J180" s="8" t="inlineStr">
         <is>
-          <t>topenar</t>
+          <t>specialista_TC_multisplit</t>
         </is>
       </c>
       <c r="K180" s="24" t="n">
@@ -20861,7 +20821,7 @@
       </c>
       <c r="M180" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — krb v 3.NP, ~6 kW odhad</t>
+          <t>TZ ARS dům §4 — multisplit TČ s akustikou hl. tlaku ≤49 dBA, NV 272/2011</t>
         </is>
       </c>
       <c r="N180" s="20" t="inlineStr">
@@ -20888,17 +20848,17 @@
       </c>
       <c r="C181" s="8" t="inlineStr">
         <is>
-          <t>Multisplit TČ — venkovní jednotka</t>
+          <t>Multisplit TČ — vnitřní jednotky</t>
         </is>
       </c>
       <c r="D181" s="20" t="inlineStr">
         <is>
-          <t>733425211</t>
+          <t>733425221</t>
         </is>
       </c>
       <c r="E181" s="8" t="inlineStr">
         <is>
-          <t>Multisplit tepelné čerpadlo vzduch-vzduch — 1× venkovní jednotka ~10 kW (silent mode hl. tlaku ≤49 dBA)</t>
+          <t>Multisplit TČ — 5× vnitřní jednotka v obytných místnostech (1.NP, 2.NP, 3.NP — chlazení + vytápění)</t>
         </is>
       </c>
       <c r="F181" s="20" t="inlineStr">
@@ -20907,7 +20867,7 @@
         </is>
       </c>
       <c r="G181" s="23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H181" s="10" t="n"/>
       <c r="I181" s="10" t="n"/>
@@ -20917,7 +20877,7 @@
         </is>
       </c>
       <c r="K181" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L181" s="20" t="inlineStr">
         <is>
@@ -20926,7 +20886,7 @@
       </c>
       <c r="M181" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — multisplit TČ s akustikou hl. tlaku ≤49 dBA, NV 272/2011</t>
+          <t>TZ ARS dům §4 — vnitřní jednotky multisplit, vyjasnění #6 odhad 5 ks</t>
         </is>
       </c>
       <c r="N181" s="20" t="inlineStr">
@@ -20953,36 +20913,36 @@
       </c>
       <c r="C182" s="8" t="inlineStr">
         <is>
-          <t>Multisplit TČ — vnitřní jednotky</t>
+          <t>Revize komínu</t>
         </is>
       </c>
       <c r="D182" s="20" t="inlineStr">
         <is>
-          <t>733425221</t>
+          <t>734262122</t>
         </is>
       </c>
       <c r="E182" s="8" t="inlineStr">
         <is>
-          <t>Multisplit TČ — 5× vnitřní jednotka v obytných místnostech (1.NP, 2.NP, 3.NP — chlazení + vytápění)</t>
+          <t>Revize stávajícího komínu — kontrola, čištění, vystrojení vložkou nerez DN160 pro kamna + krb 3.NP</t>
         </is>
       </c>
       <c r="F182" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G182" s="23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H182" s="10" t="n"/>
       <c r="I182" s="10" t="n"/>
       <c r="J182" s="8" t="inlineStr">
         <is>
-          <t>specialista_TC_multisplit</t>
+          <t>kominik</t>
         </is>
       </c>
       <c r="K182" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L182" s="20" t="inlineStr">
         <is>
@@ -20991,7 +20951,7 @@
       </c>
       <c r="M182" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — vnitřní jednotky multisplit, vyjasnění #6 odhad 5 ks</t>
+          <t>TZ ARS dům §4 — komín stávající, vystrojení vložkou pro kamna + krb</t>
         </is>
       </c>
       <c r="N182" s="20" t="inlineStr">
@@ -21018,36 +20978,36 @@
       </c>
       <c r="C183" s="8" t="inlineStr">
         <is>
-          <t>Revize komínu</t>
+          <t>Rozvody otopné soustavy</t>
         </is>
       </c>
       <c r="D183" s="20" t="inlineStr">
         <is>
-          <t>734262122</t>
+          <t>733111021</t>
         </is>
       </c>
       <c r="E183" s="8" t="inlineStr">
         <is>
-          <t>Revize stávajícího komínu — kontrola, čištění, vystrojení vložkou nerez DN160 pro kamna + krb 3.NP</t>
+          <t>Rozvody otopné soustavy Cu/PEX k vnitřním jednotkám TČ + radiátorům pro doplňkové (cca 100 bm odhad)</t>
         </is>
       </c>
       <c r="F183" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G183" s="23" t="n">
-        <v>1</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G183" s="22" t="n">
+        <v>100</v>
       </c>
       <c r="H183" s="10" t="n"/>
       <c r="I183" s="10" t="n"/>
       <c r="J183" s="8" t="inlineStr">
         <is>
-          <t>kominik</t>
+          <t>topenar</t>
         </is>
       </c>
       <c r="K183" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L183" s="20" t="inlineStr">
         <is>
@@ -21056,7 +21016,7 @@
       </c>
       <c r="M183" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — komín stávající, vystrojení vložkou pro kamna + krb</t>
+          <t>TZ ARS dům §4 — rozvody otopné soustavy</t>
         </is>
       </c>
       <c r="N183" s="20" t="inlineStr">
@@ -21078,41 +21038,41 @@
       </c>
       <c r="B184" s="8" t="inlineStr">
         <is>
-          <t>PSV-73 Vytápění</t>
+          <t>VRN — BOZP</t>
         </is>
       </c>
       <c r="C184" s="8" t="inlineStr">
         <is>
-          <t>Rozvody otopné soustavy</t>
+          <t>Koordinace BOZP</t>
         </is>
       </c>
       <c r="D184" s="20" t="inlineStr">
         <is>
-          <t>733111021</t>
+          <t>030091000</t>
         </is>
       </c>
       <c r="E184" s="8" t="inlineStr">
         <is>
-          <t>Rozvody otopné soustavy Cu/PEX k vnitřním jednotkám TČ + radiátorům pro doplňkové (cca 100 bm odhad)</t>
+          <t>Koordinátor BOZP na staveništi dle zákona 309/2006 Sb. — pro stavbu s více než jedním zhotovitelem</t>
         </is>
       </c>
       <c r="F184" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G184" s="22" t="n">
-        <v>100</v>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G184" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H184" s="10" t="n"/>
       <c r="I184" s="10" t="n"/>
       <c r="J184" s="8" t="inlineStr">
         <is>
-          <t>topenar</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K184" s="24" t="n">
-        <v>0.75</v>
+        <v>0.99</v>
       </c>
       <c r="L184" s="20" t="inlineStr">
         <is>
@@ -21121,12 +21081,12 @@
       </c>
       <c r="M184" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — rozvody otopné soustavy</t>
+          <t>Zákon 309/2006 Sb. — povinný BOZP koordinátor pro vícezhotovitelskou stavbu</t>
         </is>
       </c>
       <c r="N184" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>#10</t>
         </is>
       </c>
       <c r="O184" s="26" t="inlineStr">
@@ -21143,22 +21103,22 @@
       </c>
       <c r="B185" s="8" t="inlineStr">
         <is>
-          <t>VRN — BOZP</t>
+          <t>VRN — Dokumentace</t>
         </is>
       </c>
       <c r="C185" s="8" t="inlineStr">
         <is>
-          <t>Koordinace BOZP</t>
+          <t>Předávací protokoly + DSP</t>
         </is>
       </c>
       <c r="D185" s="20" t="inlineStr">
         <is>
-          <t>030091000</t>
+          <t>030151000</t>
         </is>
       </c>
       <c r="E185" s="8" t="inlineStr">
         <is>
-          <t>Koordinátor BOZP na staveništi dle zákona 309/2006 Sb. — pro stavbu s více než jedním zhotovitelem</t>
+          <t>Předávací protokoly + Dokumentace skutečného provedení (DSP) — sestavení, vázání, dodávka 2× tiskem + elektronická verze</t>
         </is>
       </c>
       <c r="F185" s="20" t="inlineStr">
@@ -21186,12 +21146,12 @@
       </c>
       <c r="M185" s="8" t="inlineStr">
         <is>
-          <t>Zákon 309/2006 Sb. — povinný BOZP koordinátor pro vícezhotovitelskou stavbu</t>
+          <t>Vyhláška 499/2006 Sb. + ČKAIT — DSP povinná pro kolaudaci</t>
         </is>
       </c>
       <c r="N185" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O185" s="26" t="inlineStr">
@@ -21208,41 +21168,41 @@
       </c>
       <c r="B186" s="8" t="inlineStr">
         <is>
-          <t>VRN — Dokumentace</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="C186" s="8" t="inlineStr">
         <is>
-          <t>Předávací protokoly + DSP</t>
+          <t>Kontejnery suti tříděné</t>
         </is>
       </c>
       <c r="D186" s="20" t="inlineStr">
         <is>
-          <t>030151000</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="E186" s="8" t="inlineStr">
         <is>
-          <t>Předávací protokoly + Dokumentace skutečného provedení (DSP) — sestavení, vázání, dodávka 2× tiskem + elektronická verze</t>
+          <t>Kontejnery na suť tříděnou velkoobjemové (beton/cihly, dřevo, kovy, EPS, sádra, směs) — pronájem + svozy</t>
         </is>
       </c>
       <c r="F186" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G186" s="23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H186" s="10" t="n"/>
       <c r="I186" s="10" t="n"/>
       <c r="J186" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="K186" s="24" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="L186" s="20" t="inlineStr">
         <is>
@@ -21251,12 +21211,12 @@
       </c>
       <c r="M186" s="8" t="inlineStr">
         <is>
-          <t>Vyhláška 499/2006 Sb. + ČKAIT — DSP povinná pro kolaudaci</t>
+          <t>TZ B m.10.e: beton/cihly 46 t + dřevo 9 t + kovy 0.1 + EPS 0.1 + sádra 0.2 + směs 1.0</t>
         </is>
       </c>
       <c r="N186" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#9, #10</t>
         </is>
       </c>
       <c r="O186" s="26" t="inlineStr">
@@ -21278,36 +21238,36 @@
       </c>
       <c r="C187" s="8" t="inlineStr">
         <is>
-          <t>Kontejnery suti tříděné</t>
+          <t>Doprava materiálu</t>
         </is>
       </c>
       <c r="D187" s="20" t="inlineStr">
         <is>
-          <t>997013211</t>
+          <t>031031000</t>
         </is>
       </c>
       <c r="E187" s="8" t="inlineStr">
         <is>
-          <t>Kontejnery na suť tříděnou velkoobjemové (beton/cihly, dřevo, kovy, EPS, sádra, směs) — pronájem + svozy</t>
+          <t>Doprava materiálu na stavbu (centrální koordinace) — paušál ~2-3 % z PN materiál</t>
         </is>
       </c>
       <c r="F187" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>paušál</t>
         </is>
       </c>
       <c r="G187" s="23" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H187" s="10" t="n"/>
       <c r="I187" s="10" t="n"/>
       <c r="J187" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K187" s="24" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="L187" s="20" t="inlineStr">
         <is>
@@ -21316,12 +21276,12 @@
       </c>
       <c r="M187" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10.e: beton/cihly 46 t + dřevo 9 t + kovy 0.1 + EPS 0.1 + sádra 0.2 + směs 1.0</t>
+          <t>B4_productivity — standard doprava RD městská zástavba</t>
         </is>
       </c>
       <c r="N187" s="20" t="inlineStr">
         <is>
-          <t>#9, #10</t>
+          <t>#10</t>
         </is>
       </c>
       <c r="O187" s="26" t="inlineStr">
@@ -21343,36 +21303,36 @@
       </c>
       <c r="C188" s="8" t="inlineStr">
         <is>
-          <t>Doprava materiálu</t>
+          <t>Likvidace odpadů 56.9 t</t>
         </is>
       </c>
       <c r="D188" s="20" t="inlineStr">
         <is>
-          <t>031031000</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="E188" s="8" t="inlineStr">
         <is>
-          <t>Doprava materiálu na stavbu (centrální koordinace) — paušál ~2-3 % z PN materiál</t>
+          <t>Likvidace stavební suti dle vyhl. 8/2021 Sb. — skládkovné + recyklace + třídění (56.9 t celkem per TZ B m.10.e)</t>
         </is>
       </c>
       <c r="F188" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
-        </is>
-      </c>
-      <c r="G188" s="23" t="n">
-        <v>1</v>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G188" s="22" t="n">
+        <v>56.9</v>
       </c>
       <c r="H188" s="10" t="n"/>
       <c r="I188" s="10" t="n"/>
       <c r="J188" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="K188" s="24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L188" s="20" t="inlineStr">
         <is>
@@ -21381,12 +21341,12 @@
       </c>
       <c r="M188" s="8" t="inlineStr">
         <is>
-          <t>B4_productivity — standard doprava RD městská zástavba</t>
+          <t>TZ B m.10.e bilance odpadů celkem dům</t>
         </is>
       </c>
       <c r="N188" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>#9, #10</t>
         </is>
       </c>
       <c r="O188" s="26" t="inlineStr">
@@ -21403,41 +21363,41 @@
       </c>
       <c r="B189" s="8" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>VRN — Geodet</t>
         </is>
       </c>
       <c r="C189" s="8" t="inlineStr">
         <is>
-          <t>Likvidace odpadů 56.9 t</t>
+          <t>Geodetické zaměření před + po realizaci</t>
         </is>
       </c>
       <c r="D189" s="20" t="inlineStr">
         <is>
-          <t>997013211</t>
+          <t>030141000</t>
         </is>
       </c>
       <c r="E189" s="8" t="inlineStr">
         <is>
-          <t>Likvidace stavební suti dle vyhl. 8/2021 Sb. — skládkovné + recyklace + třídění (56.9 t celkem per TZ B m.10.e)</t>
+          <t>Geodetické zaměření před realizací (verifikace polohopis + výškopis) + po dokončení (zaměření skutečného provedení pro kolaudaci)</t>
         </is>
       </c>
       <c r="F189" s="20" t="inlineStr">
         <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="G189" s="22" t="n">
-        <v>56.9</v>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G189" s="23" t="n">
+        <v>2</v>
       </c>
       <c r="H189" s="10" t="n"/>
       <c r="I189" s="10" t="n"/>
       <c r="J189" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>geodet</t>
         </is>
       </c>
       <c r="K189" s="24" t="n">
-        <v>0.85</v>
+        <v>0.99</v>
       </c>
       <c r="L189" s="20" t="inlineStr">
         <is>
@@ -21446,12 +21406,12 @@
       </c>
       <c r="M189" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10.e bilance odpadů celkem dům</t>
+          <t>Standard — geodet před+po pro každou stavbu</t>
         </is>
       </c>
       <c r="N189" s="20" t="inlineStr">
         <is>
-          <t>#9, #10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O189" s="26" t="inlineStr">
@@ -21468,37 +21428,37 @@
       </c>
       <c r="B190" s="8" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>VRN — Kolaudace</t>
         </is>
       </c>
       <c r="C190" s="8" t="inlineStr">
         <is>
-          <t>Geodetické zaměření před + po realizaci</t>
+          <t>Kolaudační řízení</t>
         </is>
       </c>
       <c r="D190" s="20" t="inlineStr">
         <is>
-          <t>030141000</t>
+          <t>030171000</t>
         </is>
       </c>
       <c r="E190" s="8" t="inlineStr">
         <is>
-          <t>Geodetické zaměření před realizací (verifikace polohopis + výškopis) + po dokončení (zaměření skutečného provedení pro kolaudaci)</t>
+          <t>Kolaudační řízení — paušál (správní poplatky + součinnost) dle zákona 183/2006 Sb.</t>
         </is>
       </c>
       <c r="F190" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>paušál</t>
         </is>
       </c>
       <c r="G190" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H190" s="10" t="n"/>
       <c r="I190" s="10" t="n"/>
       <c r="J190" s="8" t="inlineStr">
         <is>
-          <t>geodet</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K190" s="24" t="n">
@@ -21511,7 +21471,7 @@
       </c>
       <c r="M190" s="8" t="inlineStr">
         <is>
-          <t>Standard — geodet před+po pro každou stavbu</t>
+          <t>Zákon 183/2006 Sb. + vyhl. 499/2006 Sb.</t>
         </is>
       </c>
       <c r="N190" s="20" t="inlineStr">
@@ -21533,31 +21493,31 @@
       </c>
       <c r="B191" s="8" t="inlineStr">
         <is>
-          <t>VRN — Kolaudace</t>
+          <t>VRN — Lešení</t>
         </is>
       </c>
       <c r="C191" s="8" t="inlineStr">
         <is>
-          <t>Kolaudační řízení</t>
+          <t>Fasádní lešení (ETICS + krov + klempířina)</t>
         </is>
       </c>
       <c r="D191" s="20" t="inlineStr">
         <is>
-          <t>030171000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E191" s="8" t="inlineStr">
         <is>
-          <t>Kolaudační řízení — paušál (správní poplatky + součinnost) dle zákona 183/2006 Sb.</t>
+          <t>Fasádní lešení trubkové/rámové vč. montáže + pronájmu + demontáže — pro provedení ETICS fasády, krovu a klempířiny po obvodu domu (výška 13 m)</t>
         </is>
       </c>
       <c r="F191" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
-        </is>
-      </c>
-      <c r="G191" s="23" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G191" s="22" t="n">
+        <v>503.1</v>
       </c>
       <c r="H191" s="10" t="n"/>
       <c r="I191" s="10" t="n"/>
@@ -21567,7 +21527,7 @@
         </is>
       </c>
       <c r="K191" s="24" t="n">
-        <v>0.99</v>
+        <v>0.8</v>
       </c>
       <c r="L191" s="20" t="inlineStr">
         <is>
@@ -21576,7 +21536,7 @@
       </c>
       <c r="M191" s="8" t="inlineStr">
         <is>
-          <t>Zákon 183/2006 Sb. + vyhl. 499/2006 Sb.</t>
+          <t>anchor checklist PM02 — technical necessity (ETICS 276.7 m² nelze provést bez lešení, 941xxx URS família) + DXF obvod 38.7 m + řez výška 13 m</t>
         </is>
       </c>
       <c r="N191" s="20" t="inlineStr">
@@ -21590,7 +21550,11 @@
         </is>
       </c>
       <c r="P191" s="41" t="n"/>
-      <c r="Q191" s="41" t="n"/>
+      <c r="Q191" s="41" t="inlineStr">
+        <is>
+          <t>ANCHOR_CHECKLIST_PM02</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="20" t="n">
@@ -21598,31 +21562,31 @@
       </c>
       <c r="B192" s="8" t="inlineStr">
         <is>
-          <t>VRN — Lešení</t>
+          <t>VRN — Pojištění + zábory</t>
         </is>
       </c>
       <c r="C192" s="8" t="inlineStr">
         <is>
-          <t>Fasádní lešení (ETICS + krov + klempířina)</t>
+          <t>Pojištění stavby (montážní + odpovědnostní)</t>
         </is>
       </c>
       <c r="D192" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>030081000</t>
         </is>
       </c>
       <c r="E192" s="8" t="inlineStr">
         <is>
-          <t>Fasádní lešení trubkové/rámové vč. montáže + pronájmu + demontáže — pro provedení ETICS fasády, krovu a klempířiny po obvodu domu (výška 13 m)</t>
+          <t>Montážní pojištění stavby (CAR) + pojištění odpovědnosti za škodu (zhotovitel) — paušál cca 0.3-0.5 % z PN</t>
         </is>
       </c>
       <c r="F192" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G192" s="22" t="n">
-        <v>503.1</v>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="G192" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H192" s="10" t="n"/>
       <c r="I192" s="10" t="n"/>
@@ -21632,7 +21596,7 @@
         </is>
       </c>
       <c r="K192" s="24" t="n">
-        <v>0.8</v>
+        <v>0.99</v>
       </c>
       <c r="L192" s="20" t="inlineStr">
         <is>
@@ -21641,12 +21605,12 @@
       </c>
       <c r="M192" s="8" t="inlineStr">
         <is>
-          <t>anchor checklist PM02 — technical necessity (ETICS 276.7 m² nelze provést bez lešení, 941xxx URS família) + DXF obvod 38.7 m + řez výška 13 m</t>
+          <t>Standard zhotovitel — pojistná povinnost</t>
         </is>
       </c>
       <c r="N192" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#10</t>
         </is>
       </c>
       <c r="O192" s="26" t="inlineStr">
@@ -21655,11 +21619,7 @@
         </is>
       </c>
       <c r="P192" s="41" t="n"/>
-      <c r="Q192" s="41" t="inlineStr">
-        <is>
-          <t>ANCHOR_CHECKLIST_PM02</t>
-        </is>
-      </c>
+      <c r="Q192" s="41" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="20" t="n">
@@ -21672,22 +21632,22 @@
       </c>
       <c r="C193" s="8" t="inlineStr">
         <is>
-          <t>Pojištění stavby (montážní + odpovědnostní)</t>
+          <t>Krátkodobé zábory ul. Fibichova</t>
         </is>
       </c>
       <c r="D193" s="20" t="inlineStr">
         <is>
-          <t>030081000</t>
+          <t>030083000</t>
         </is>
       </c>
       <c r="E193" s="8" t="inlineStr">
         <is>
-          <t>Montážní pojištění stavby (CAR) + pojištění odpovědnosti za škodu (zhotovitel) — paušál cca 0.3-0.5 % z PN</t>
+          <t>Krátkodobé zábory ulice Fibichova pro materiál a kontejnery (povolení MU Jáchymov + DI) — odhad 30 dnů kumulativně</t>
         </is>
       </c>
       <c r="F193" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G193" s="23" t="n">
@@ -21701,7 +21661,7 @@
         </is>
       </c>
       <c r="K193" s="24" t="n">
-        <v>0.99</v>
+        <v>0.75</v>
       </c>
       <c r="L193" s="20" t="inlineStr">
         <is>
@@ -21710,7 +21670,7 @@
       </c>
       <c r="M193" s="8" t="inlineStr">
         <is>
-          <t>Standard zhotovitel — pojistná povinnost</t>
+          <t>TZ B m.10 + situace — řadovka ul. Fibichova</t>
         </is>
       </c>
       <c r="N193" s="20" t="inlineStr">
@@ -21732,22 +21692,22 @@
       </c>
       <c r="B194" s="8" t="inlineStr">
         <is>
-          <t>VRN — Pojištění + zábory</t>
+          <t>VRN — Průzkumy</t>
         </is>
       </c>
       <c r="C194" s="8" t="inlineStr">
         <is>
-          <t>Krátkodobé zábory ul. Fibichova</t>
+          <t>Mykologický průzkum dřeva při bourání</t>
         </is>
       </c>
       <c r="D194" s="20" t="inlineStr">
         <is>
-          <t>030083000</t>
+          <t>030131000</t>
         </is>
       </c>
       <c r="E194" s="8" t="inlineStr">
         <is>
-          <t>Krátkodobé zábory ulice Fibichova pro materiál a kontejnery (povolení MU Jáchymov + DI) — odhad 30 dnů kumulativně</t>
+          <t>Mykologický průzkum + průzkum výskytu dřevokazného hmyzu stávajícího krovu a dřevěných trámů zhlaví — pro vyloučení narušení dřevěných konstrukcí; provádí autorizovaný mykolog při bourání</t>
         </is>
       </c>
       <c r="F194" s="20" t="inlineStr">
@@ -21762,11 +21722,11 @@
       <c r="I194" s="10" t="n"/>
       <c r="J194" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>mykolog</t>
         </is>
       </c>
       <c r="K194" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L194" s="20" t="inlineStr">
         <is>
@@ -21775,7 +21735,7 @@
       </c>
       <c r="M194" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10 + situace — řadovka ul. Fibichova</t>
+          <t>TZ ARS dům §3.2.3 + POZN.2.05 z půdorysů návrh + řez A-A návrh (explicit dřevokazný hmyz scope per drawing wording)</t>
         </is>
       </c>
       <c r="N194" s="20" t="inlineStr">
@@ -21789,7 +21749,11 @@
         </is>
       </c>
       <c r="P194" s="41" t="n"/>
-      <c r="Q194" s="41" t="n"/>
+      <c r="Q194" s="41" t="inlineStr">
+        <is>
+          <t>PER_DRAWING_ENRICHMENT_POZN_2_05</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="20" t="n">
@@ -21802,17 +21766,17 @@
       </c>
       <c r="C195" s="8" t="inlineStr">
         <is>
-          <t>Mykologický průzkum dřeva při bourání</t>
+          <t>Azbestový průzkum podrobný před demolicí</t>
         </is>
       </c>
       <c r="D195" s="20" t="inlineStr">
         <is>
-          <t>030131000</t>
+          <t>030133000</t>
         </is>
       </c>
       <c r="E195" s="8" t="inlineStr">
         <is>
-          <t>Mykologický průzkum + průzkum výskytu dřevokazného hmyzu stávajícího krovu a dřevěných trámů zhlaví — pro vyloučení narušení dřevěných konstrukcí; provádí autorizovaný mykolog při bourání</t>
+          <t>Azbestový průzkum podrobný před demolicí — laboratorní vzorky a posudek (B kap. m.7.a předběžně negativní, ale podrobný před bouráním povinný)</t>
         </is>
       </c>
       <c r="F195" s="20" t="inlineStr">
@@ -21827,7 +21791,7 @@
       <c r="I195" s="10" t="n"/>
       <c r="J195" s="8" t="inlineStr">
         <is>
-          <t>mykolog</t>
+          <t>azbestovy_specialista</t>
         </is>
       </c>
       <c r="K195" s="24" t="n">
@@ -21840,7 +21804,7 @@
       </c>
       <c r="M195" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2.3 + POZN.2.05 z půdorysů návrh + řez A-A návrh (explicit dřevokazný hmyz scope per drawing wording)</t>
+          <t>TZ B m.7.a + ARS §3.2 — azbestový průzkum povinný před demolicí</t>
         </is>
       </c>
       <c r="N195" s="20" t="inlineStr">
@@ -21854,11 +21818,7 @@
         </is>
       </c>
       <c r="P195" s="41" t="n"/>
-      <c r="Q195" s="41" t="inlineStr">
-        <is>
-          <t>PER_DRAWING_ENRICHMENT_POZN_2_05</t>
-        </is>
-      </c>
+      <c r="Q195" s="41" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="20" t="n">
@@ -21866,41 +21826,41 @@
       </c>
       <c r="B196" s="8" t="inlineStr">
         <is>
-          <t>VRN — Průzkumy</t>
+          <t>VRN — Přesun hmot</t>
         </is>
       </c>
       <c r="C196" s="8" t="inlineStr">
         <is>
-          <t>Azbestový průzkum podrobný před demolicí</t>
+          <t>Přesun hmot pro budovu</t>
         </is>
       </c>
       <c r="D196" s="20" t="inlineStr">
         <is>
-          <t>030133000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E196" s="8" t="inlineStr">
         <is>
-          <t>Azbestový průzkum podrobný před demolicí — laboratorní vzorky a posudek (B kap. m.7.a předběžně negativní, ale podrobný před bouráním povinný)</t>
+          <t>Přesun hmot pro budovu — vnitrostaveništní vertikální + horizontální doprava materiálu a hmot (rekonstrukce vícepodlažní RD + nástavba 3.NP)</t>
         </is>
       </c>
       <c r="F196" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G196" s="23" t="n">
-        <v>1</v>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G196" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H196" s="10" t="n"/>
       <c r="I196" s="10" t="n"/>
       <c r="J196" s="8" t="inlineStr">
         <is>
-          <t>azbestovy_specialista</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K196" s="24" t="n">
-        <v>0.85</v>
+        <v>0.6</v>
       </c>
       <c r="L196" s="20" t="inlineStr">
         <is>
@@ -21909,12 +21869,12 @@
       </c>
       <c r="M196" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.7.a + ARS §3.2 — azbestový průzkum povinný před demolicí</t>
+          <t>anchor checklist PM01 — technical necessity (povinná položka každého rozpočtu, 998xxx URS família)</t>
         </is>
       </c>
       <c r="N196" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O196" s="26" t="inlineStr">
@@ -21923,7 +21883,11 @@
         </is>
       </c>
       <c r="P196" s="41" t="n"/>
-      <c r="Q196" s="41" t="n"/>
+      <c r="Q196" s="41" t="inlineStr">
+        <is>
+          <t>ANCHOR_CHECKLIST_PM01</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="20" t="n">
@@ -21931,41 +21895,41 @@
       </c>
       <c r="B197" s="8" t="inlineStr">
         <is>
-          <t>VRN — Přesun hmot</t>
+          <t>VRN — Revize</t>
         </is>
       </c>
       <c r="C197" s="8" t="inlineStr">
         <is>
-          <t>Přesun hmot pro budovu</t>
+          <t>Revize hydrantu vnějšího</t>
         </is>
       </c>
       <c r="D197" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>030161000</t>
         </is>
       </c>
       <c r="E197" s="8" t="inlineStr">
         <is>
-          <t>Přesun hmot pro budovu — vnitrostaveništní vertikální + horizontální doprava materiálu a hmot (rekonstrukce vícepodlažní RD + nástavba 3.NP)</t>
+          <t>Revize vnějšího hydrantu pro požární zabezpečení (DN min. 80, vzdálenost 100 m dle TZ PBŘ) — periodická kontrola</t>
         </is>
       </c>
       <c r="F197" s="20" t="inlineStr">
         <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="G197" s="22" t="n">
-        <v>0</v>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G197" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H197" s="10" t="n"/>
       <c r="I197" s="10" t="n"/>
       <c r="J197" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>revize_specialista</t>
         </is>
       </c>
       <c r="K197" s="24" t="n">
-        <v>0.6</v>
+        <v>0.85</v>
       </c>
       <c r="L197" s="20" t="inlineStr">
         <is>
@@ -21974,7 +21938,7 @@
       </c>
       <c r="M197" s="8" t="inlineStr">
         <is>
-          <t>anchor checklist PM01 — technical necessity (povinná položka každého rozpočtu, 998xxx URS família)</t>
+          <t>TZ PBŘ dům — vnější odběrné místo požární vody, revize před kolaudací</t>
         </is>
       </c>
       <c r="N197" s="20" t="inlineStr">
@@ -21988,11 +21952,7 @@
         </is>
       </c>
       <c r="P197" s="41" t="n"/>
-      <c r="Q197" s="41" t="inlineStr">
-        <is>
-          <t>ANCHOR_CHECKLIST_PM01</t>
-        </is>
-      </c>
+      <c r="Q197" s="41" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="20" t="n">
@@ -22000,41 +21960,41 @@
       </c>
       <c r="B198" s="8" t="inlineStr">
         <is>
-          <t>VRN — Revize</t>
+          <t>VRN — Zařízení staveniště</t>
         </is>
       </c>
       <c r="C198" s="8" t="inlineStr">
         <is>
-          <t>Revize hydrantu vnějšího</t>
+          <t>Buňky kancelář + sociální</t>
         </is>
       </c>
       <c r="D198" s="20" t="inlineStr">
         <is>
-          <t>030161000</t>
+          <t>030011000</t>
         </is>
       </c>
       <c r="E198" s="8" t="inlineStr">
         <is>
-          <t>Revize vnějšího hydrantu pro požární zabezpečení (DN min. 80, vzdálenost 100 m dle TZ PBŘ) — periodická kontrola</t>
+          <t>Zařízení staveniště — buňka kancelář + sociální buňka (WC + šatna), pronájem ~8 měsíců</t>
         </is>
       </c>
       <c r="F198" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>kpl-měs</t>
         </is>
       </c>
       <c r="G198" s="23" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H198" s="10" t="n"/>
       <c r="I198" s="10" t="n"/>
       <c r="J198" s="8" t="inlineStr">
         <is>
-          <t>revize_specialista</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K198" s="24" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="L198" s="20" t="inlineStr">
         <is>
@@ -22043,12 +22003,12 @@
       </c>
       <c r="M198" s="8" t="inlineStr">
         <is>
-          <t>TZ PBŘ dům — vnější odběrné místo požární vody, revize před kolaudací</t>
+          <t>TZ B m.1.m realizace 2026-2027 + standard staveniště RD městská zástavba</t>
         </is>
       </c>
       <c r="N198" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#10</t>
         </is>
       </c>
       <c r="O198" s="26" t="inlineStr">
@@ -22070,22 +22030,22 @@
       </c>
       <c r="C199" s="8" t="inlineStr">
         <is>
-          <t>Buňky kancelář + sociální</t>
+          <t>Mobilní WC</t>
         </is>
       </c>
       <c r="D199" s="20" t="inlineStr">
         <is>
-          <t>030011000</t>
+          <t>030013000</t>
         </is>
       </c>
       <c r="E199" s="8" t="inlineStr">
         <is>
-          <t>Zařízení staveniště — buňka kancelář + sociální buňka (WC + šatna), pronájem ~8 měsíců</t>
+          <t>Mobilní chemické WC TOI TOI pro pracovníky — pronájem ~8 měsíců</t>
         </is>
       </c>
       <c r="F199" s="20" t="inlineStr">
         <is>
-          <t>kpl-měs</t>
+          <t>ks-měs</t>
         </is>
       </c>
       <c r="G199" s="23" t="n">
@@ -22108,7 +22068,7 @@
       </c>
       <c r="M199" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.1.m realizace 2026-2027 + standard staveniště RD městská zástavba</t>
+          <t>BOZP — mobilní WC povinné pro stavbu RD</t>
         </is>
       </c>
       <c r="N199" s="20" t="inlineStr">
@@ -22135,26 +22095,26 @@
       </c>
       <c r="C200" s="8" t="inlineStr">
         <is>
-          <t>Mobilní WC</t>
+          <t>El. odběr + vodovodní odběr stavby</t>
         </is>
       </c>
       <c r="D200" s="20" t="inlineStr">
         <is>
-          <t>030013000</t>
+          <t>031011000</t>
         </is>
       </c>
       <c r="E200" s="8" t="inlineStr">
         <is>
-          <t>Mobilní chemické WC TOI TOI pro pracovníky — pronájem ~8 měsíců</t>
+          <t>El. odběr stavby (zřízení staveništního rozvaděče + měřič) + vodovodní odběr (zřízení staveništní přípojky + vodoměr) — ~8 měsíců</t>
         </is>
       </c>
       <c r="F200" s="20" t="inlineStr">
         <is>
-          <t>ks-měs</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G200" s="23" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H200" s="10" t="n"/>
       <c r="I200" s="10" t="n"/>
@@ -22173,7 +22133,7 @@
       </c>
       <c r="M200" s="8" t="inlineStr">
         <is>
-          <t>BOZP — mobilní WC povinné pro stavbu RD</t>
+          <t>Standard staveniště — el. + voda zřízení a odběr po dobu stavby</t>
         </is>
       </c>
       <c r="N200" s="20" t="inlineStr">
@@ -22200,17 +22160,17 @@
       </c>
       <c r="C201" s="8" t="inlineStr">
         <is>
-          <t>El. odběr + vodovodní odběr stavby</t>
+          <t>Voda staveniště</t>
         </is>
       </c>
       <c r="D201" s="20" t="inlineStr">
         <is>
-          <t>031011000</t>
+          <t>012103101</t>
         </is>
       </c>
       <c r="E201" s="8" t="inlineStr">
         <is>
-          <t>El. odběr stavby (zřízení staveništního rozvaděče + měřič) + vodovodní odběr (zřízení staveništní přípojky + vodoměr) — ~8 měsíců</t>
+          <t>Voda staveniště — napojení na stávající vodovodní přípojku, dočasné rozvody na staveništi (mísení malt, čištění, soc. zázemí), paušál pro dobu výstavby ~18 měs.</t>
         </is>
       </c>
       <c r="F201" s="20" t="inlineStr">
@@ -22229,7 +22189,7 @@
         </is>
       </c>
       <c r="K201" s="24" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L201" s="20" t="inlineStr">
         <is>
@@ -22238,12 +22198,12 @@
       </c>
       <c r="M201" s="8" t="inlineStr">
         <is>
-          <t>Standard staveniště — el. + voda zřízení a odběr po dobu stavby</t>
+          <t>TZ B Souhrnná m.5 — 'Stávající vodovodní přípojka z veřejného vodovodu'</t>
         </is>
       </c>
       <c r="N201" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O201" s="26" t="inlineStr">
@@ -22252,7 +22212,11 @@
         </is>
       </c>
       <c r="P201" s="41" t="n"/>
-      <c r="Q201" s="41" t="n"/>
+      <c r="Q201" s="41" t="inlineStr">
+        <is>
+          <t>GAP_003</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="20" t="n">
@@ -22260,27 +22224,27 @@
       </c>
       <c r="B202" s="8" t="inlineStr">
         <is>
-          <t>VRN — Zařízení staveniště</t>
+          <t>M-21 ELI silnoproud</t>
         </is>
       </c>
       <c r="C202" s="8" t="inlineStr">
         <is>
-          <t>Voda staveniště</t>
+          <t>Hlavní vypínač TOTAL STOP + požární značení</t>
         </is>
       </c>
       <c r="D202" s="20" t="inlineStr">
         <is>
-          <t>012103101</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E202" s="8" t="inlineStr">
         <is>
-          <t>Voda staveniště — napojení na stávající vodovodní přípojku, dočasné rozvody na staveništi (mísení malt, čištění, soc. zázemí), paušál pro dobu výstavby ~18 měs.</t>
+          <t>Hlavní vypínač elektrické energie TOTAL STOP + požární značení rozvodného zařízení a uzávěrů (voda/elektro)</t>
         </is>
       </c>
       <c r="F202" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>soubor</t>
         </is>
       </c>
       <c r="G202" s="23" t="n">
@@ -22290,11 +22254,11 @@
       <c r="I202" s="10" t="n"/>
       <c r="J202" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>elektrikar</t>
         </is>
       </c>
       <c r="K202" s="24" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="L202" s="20" t="inlineStr">
         <is>
@@ -22303,7 +22267,7 @@
       </c>
       <c r="M202" s="8" t="inlineStr">
         <is>
-          <t>TZ B Souhrnná m.5 — 'Stávající vodovodní přípojka z veřejného vodovodu'</t>
+          <t>PBŘ D.3 §16.05/16.06</t>
         </is>
       </c>
       <c r="N202" s="20" t="inlineStr">
@@ -22316,10 +22280,10 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P202" s="41" t="n"/>
+      <c r="P202" s="41" t="inlineStr"/>
       <c r="Q202" s="41" t="inlineStr">
         <is>
-          <t>GAP_003</t>
+          <t>DODATEK_PBR_GAPS_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -22329,12 +22293,12 @@
       </c>
       <c r="B203" s="8" t="inlineStr">
         <is>
-          <t>M-21 ELI silnoproud</t>
+          <t>M-24 VZT</t>
         </is>
       </c>
       <c r="C203" s="8" t="inlineStr">
         <is>
-          <t>Hlavní vypínač TOTAL STOP + požární značení</t>
+          <t>Lokální odtah digestoří kuchyní</t>
         </is>
       </c>
       <c r="D203" s="20" t="inlineStr">
@@ -22344,26 +22308,26 @@
       </c>
       <c r="E203" s="8" t="inlineStr">
         <is>
-          <t>Hlavní vypínač elektrické energie TOTAL STOP + požární značení rozvodného zařízení a uzávěrů (voda/elektro)</t>
+          <t>Lokální odtah digestoří kuchyní (1.NP + 3.NP) — dodávka + montáž digestoře + prostup fasádou/střechou + zpětná klapka</t>
         </is>
       </c>
       <c r="F203" s="20" t="inlineStr">
         <is>
-          <t>soubor</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G203" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H203" s="10" t="n"/>
       <c r="I203" s="10" t="n"/>
       <c r="J203" s="8" t="inlineStr">
         <is>
-          <t>elektrikar</t>
+          <t>vzduchotechnik</t>
         </is>
       </c>
       <c r="K203" s="24" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="L203" s="20" t="inlineStr">
         <is>
@@ -22372,7 +22336,7 @@
       </c>
       <c r="M203" s="8" t="inlineStr">
         <is>
-          <t>PBŘ D.3 §16.05/16.06</t>
+          <t>B zpráva — VZT: obytné místnosti větrání okny, kuchyně lokální odtah digestoří</t>
         </is>
       </c>
       <c r="N203" s="20" t="inlineStr">
@@ -22392,78 +22356,9 @@
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="20" t="n">
-        <v>203</v>
-      </c>
-      <c r="B204" s="8" t="inlineStr">
-        <is>
-          <t>M-24 VZT</t>
-        </is>
-      </c>
-      <c r="C204" s="8" t="inlineStr">
-        <is>
-          <t>Lokální odtah digestoří kuchyní</t>
-        </is>
-      </c>
-      <c r="D204" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E204" s="8" t="inlineStr">
-        <is>
-          <t>Lokální odtah digestoří kuchyní (1.NP + 3.NP) — dodávka + montáž digestoře + prostup fasádou/střechou + zpětná klapka</t>
-        </is>
-      </c>
-      <c r="F204" s="20" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G204" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="H204" s="10" t="n"/>
-      <c r="I204" s="10" t="n"/>
-      <c r="J204" s="8" t="inlineStr">
-        <is>
-          <t>vzduchotechnik</t>
-        </is>
-      </c>
-      <c r="K204" s="24" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L204" s="20" t="inlineStr">
-        <is>
-          <t>needs_production_lookup</t>
-        </is>
-      </c>
-      <c r="M204" s="8" t="inlineStr">
-        <is>
-          <t>B zpráva — VZT: obytné místnosti větrání okny, kuchyně lokální odtah digestoří</t>
-        </is>
-      </c>
-      <c r="N204" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O204" s="26" t="inlineStr">
-        <is>
-          <t>ANO</t>
-        </is>
-      </c>
-      <c r="P204" s="41" t="inlineStr"/>
-      <c r="Q204" s="41" t="inlineStr">
-        <is>
-          <t>DODATEK_PBR_GAPS_2026-06-01</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O204"/>
-  <conditionalFormatting sqref="K2:K204">
+  <autoFilter ref="A1:O203"/>
+  <conditionalFormatting sqref="K2:K203">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0" stopIfTrue="1">
       <formula>0.70</formula>
     </cfRule>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01_v2.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01_v2.xlsx
@@ -21,8 +21,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Var_A_Agregovany_Dum'!$A$1:$G$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Var_A_Agregovany_Sklad'!$A$1:$G$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$132</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Var_B_Polozkovy_Dum'!$A$1:$O$203</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$131</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Var_B_Polozkovy_Dum'!$A$1:$O$202</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Var_B_Polozkovy_Sklad'!$A$1:$O$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Var_F_URS_Verification_Trail'!$A$1:$H$14</definedName>
   </definedNames>
@@ -1009,11 +1009,11 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>HSV položkově (118 ks) + PSV/TZB/VRN agregovaně (13 skupin) = 131 řádků.</t>
+          <t>HSV položkově (117 ks) + PSV/TZB/VRN agregovaně (13 skupin) = 130 řádků.</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D24" s="10" t="n"/>
       <c r="E24" s="10" t="n"/>
@@ -1027,11 +1027,11 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Plný detail (202 dum + 31 sklad = 233 položek). Cílový rozsah pro produkční pricing.</t>
+          <t>Plný detail (201 dum + 31 sklad = 232 položek). Cílový rozsah pro produkční pricing.</t>
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D25" s="10" t="n"/>
       <c r="E25" s="10" t="n"/>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>233 (202 dum + 31 sklad)</t>
+          <t>232 (201 dum + 31 sklad)</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>HSV 118 | M 2 | PSV 56 | TZB 34 | VRN 23</t>
+          <t>HSV 117 | M 2 | PSV 56 | TZB 34 | VRN 23</t>
         </is>
       </c>
     </row>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>0.99: 17 | 0.95: 32 | 0.90: 35 | 0.85: 41 | 0.80: 21 | 0.75: 71 | 0.70: 4 | 0.60: 3 | 0.50: 4 | 0.00: 5</t>
+          <t>0.99: 17 | 0.95: 32 | 0.90: 34 | 0.85: 41 | 0.80: 21 | 0.75: 71 | 0.70: 4 | 0.60: 3 | 0.50: 4 | 0.00: 5</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>8 WebSearch verified (3.4 %) ✓ | 5 wrong leaf flagged (2.1 %) ⚠ | 155 needs_production_lookup (66.5 %)</t>
+          <t>8 WebSearch verified (3.4 %) ✓ | 5 wrong leaf flagged (2.2 %) ⚠ | 155 needs_production_lookup (66.8 %)</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>30 items (viz Otazky_pro_Karla docx)</t>
+          <t>31 items (viz Otazky_pro_Karla docx)</t>
         </is>
       </c>
     </row>
@@ -1186,10 +1186,10 @@
       <c r="A43" s="12" t="inlineStr">
         <is>
           <t>Rozpočet generován STAVAGENT pipelinem z DSP dokumentace s DPS-grade DXF metadaty.
-233 položek celkem (202 dum + 31 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
-Confidence distribution: 17×0.99 · 32×0.95 · 35×0.90 · 41×0.85 · 21×0.80 · 71×0.75 · 4×0.70 · 3×0.60 · 4×0.50 · 5×0.00.
+232 položek celkem (201 dum + 31 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
+Confidence distribution: 17×0.99 · 32×0.95 · 34×0.90 · 41×0.85 · 21×0.80 · 71×0.75 · 4×0.70 · 3×0.60 · 4×0.50 · 5×0.00.
 25 položek vzniklo per-room expansion ze 9 aggregate parents (každá expanded položka tagged _expansion_origin).
-10 položek recalculated s exact external perimeter 38.70 m (DXF km_R_návrh_tlustá 2 closed polygon) vs prior fallback 41.0 m.
+9 položek recalculated s exact external perimeter 38.70 m (DXF km_R_návrh_tlustá 2 closed polygon) vs prior fallback 41.0 m.
 Skladby vrstev (Sheet 8 Var_E) pochází POUZE z TZ explicit text + DXF cross-validation HATCH patterns. ŽÁDNÉ generic 'standardní RD' assumption — kde TZ silent, explicit fallback flag s ČSN default.
 ÚRS kódy navrženy heuristikou. Part 5b WebSearch verified 12 codes / 8 unique families (viz Sheet 9 Var_F_URS_Verification_Trail). Wrong-leaf pattern identifikován: heuristika odhadne 6-cifernou rodinu správně v ~75 % případů, ale 9-cifrový leaf je chybný v ~63 % (odlišný distance band / materiál / geometrie / lokace). Produkční URS_MATCHER service (Perplexity-driven online lookup) nutný pro finální ověření zbývajících položek před cenotvorbou. Jednotkové ceny ponecháno k vyplnění zhotovitelem.</t>
         </is>
@@ -2626,11 +2626,11 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Příprava podkladu; ETICS EPS 70F grey 160 mm; ETICS sokl XPS; Špalety EPS; … (+5 dalších)</t>
+          <t>Příprava podkladu; ETICS EPS 70F grey 160 mm; Špalety EPS; Profilace fasády; … (+4 dalších)</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E8" s="10" t="n"/>
       <c r="F8" s="10" t="n"/>
@@ -3163,7 +3163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J132"/>
+  <dimension ref="A1:J131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6926,16 +6926,16 @@
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>ETICS sokl XPS — ETICS sokl — XPS λ=0.034 tl. 120 mm + soklový profil + cihelný obklad spárovaný</t>
+          <t>Špalety EPS — Špalety oken — EPS přesah 35-40 mm + síťka + omítka</t>
         </is>
       </c>
       <c r="E94" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="F94" s="22" t="n">
-        <v>13.5</v>
+        <v>82.2</v>
       </c>
       <c r="G94" s="10" t="n"/>
       <c r="H94" s="10" t="n"/>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="J94" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 622223111</t>
+          <t>URS-prop 622221221</t>
         </is>
       </c>
     </row>
@@ -6966,16 +6966,16 @@
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>Špalety EPS — Špalety oken — EPS přesah 35-40 mm + síťka + omítka</t>
+          <t>Profilace fasády — Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
         </is>
       </c>
       <c r="E95" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="F95" s="22" t="n">
-        <v>82.2</v>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="F95" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="G95" s="10" t="n"/>
       <c r="H95" s="10" t="n"/>
@@ -7006,16 +7006,16 @@
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>Profilace fasády — Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
+          <t>Tenkovrstvá omítka pastovitá — Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
         </is>
       </c>
       <c r="E96" s="20" t="inlineStr">
         <is>
-          <t>soubor</t>
-        </is>
-      </c>
-      <c r="F96" s="23" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F96" s="22" t="n">
+        <v>276.7</v>
       </c>
       <c r="G96" s="10" t="n"/>
       <c r="H96" s="10" t="n"/>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="J96" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 622221221</t>
+          <t>URS-prop 622521111</t>
         </is>
       </c>
     </row>
@@ -7041,32 +7041,32 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda ETICS</t>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>Tenkovrstvá omítka pastovitá — Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
+          <t>Demontáž oken — Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
         </is>
       </c>
       <c r="E97" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F97" s="22" t="n">
-        <v>290.2</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="F97" s="23" t="n">
+        <v>16</v>
       </c>
       <c r="G97" s="10" t="n"/>
       <c r="H97" s="10" t="n"/>
       <c r="I97" s="8" t="inlineStr">
         <is>
-          <t>fasadnik_etics</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="J97" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 622521111</t>
+          <t>URS-prop 978013181</t>
         </is>
       </c>
     </row>
@@ -7086,7 +7086,7 @@
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>Demontáž oken — Demontáž stávajících dřevěných oken vč. rámů a parapetů — 16 ks (návrh všechna okna nová plastová trojsklem)</t>
+          <t>Demontáž vstupních dveří venkovních — Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
         </is>
       </c>
       <c r="E98" s="20" t="inlineStr">
@@ -7095,7 +7095,7 @@
         </is>
       </c>
       <c r="F98" s="23" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G98" s="10" t="n"/>
       <c r="H98" s="10" t="n"/>
@@ -7126,7 +7126,7 @@
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>Demontáž vstupních dveří venkovních — Demontáž stávajících vstupních dveří + rámů — 2 ks (1× ulice Fibichova + 1× zahrada; návrh nové plastové vstupní dveře)</t>
+          <t>Demontáž vnitřních dveří vč. zárubní — Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
         </is>
       </c>
       <c r="E99" s="20" t="inlineStr">
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="F99" s="23" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="G99" s="10" t="n"/>
       <c r="H99" s="10" t="n"/>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="J99" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 978013181</t>
+          <t>URS-prop 968072456</t>
         </is>
       </c>
     </row>
@@ -7166,16 +7166,16 @@
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>Demontáž vnitřních dveří vč. zárubní — Demontáž stávajících vnitřních dveří vč. ocelových/dřevěných zárubní — odhad 15 ks (3 patra × ~5 dveří/patro per DXF SM__dveře layer)</t>
+          <t>Bourání zdiva komínu — Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
         </is>
       </c>
       <c r="E100" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="F100" s="23" t="n">
-        <v>15</v>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F100" s="22" t="n">
+        <v>0.6</v>
       </c>
       <c r="G100" s="10" t="n"/>
       <c r="H100" s="10" t="n"/>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="J100" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 968072456</t>
+          <t>URS-prop 962024141</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>Bourání zdiva komínu — Bourání vrchní části stávajícího komínu v posledním podlaží (cihelné zdivo, ručně), vč. likvidace cihelné suti</t>
+          <t>Bourání venkovních konstrukcí — Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
         </is>
       </c>
       <c r="E101" s="20" t="inlineStr">
@@ -7215,7 +7215,7 @@
         </is>
       </c>
       <c r="F101" s="22" t="n">
-        <v>0.6</v>
+        <v>8</v>
       </c>
       <c r="G101" s="10" t="n"/>
       <c r="H101" s="10" t="n"/>
@@ -7226,7 +7226,7 @@
       </c>
       <c r="J101" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 962024141</t>
+          <t>URS-prop 961044111</t>
         </is>
       </c>
     </row>
@@ -7241,32 +7241,32 @@
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>HSV-1 Zemní práce</t>
         </is>
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>Bourání venkovních konstrukcí — Bourání stávajících opěrných zídek a venkovního schodiště v zahradě/dvoře — částečné, dle vyznačení v půdorysech bourání</t>
+          <t>Drenáž za bílou vanou — Drenáž za opěrnou stěnou (bílou vanou) — drenážní trubka DN100 vlnitá perforovaná + štěrkový obsyp 16/32 + geotextilie + napojení do dešťové kanalizace, L po obvodu BV</t>
         </is>
       </c>
       <c r="E102" s="20" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F102" s="22" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G102" s="10" t="n"/>
       <c r="H102" s="10" t="n"/>
       <c r="I102" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="J102" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 961044111</t>
+          <t>URS-prop 877315111</t>
         </is>
       </c>
     </row>
@@ -7276,37 +7276,37 @@
       </c>
       <c r="B103" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>HSV-1 Zemní práce</t>
+          <t>HSV-5 Komunikace + schodiště</t>
         </is>
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>Drenáž za bílou vanou — Drenáž za opěrnou stěnou (bílou vanou) — drenážní trubka DN100 vlnitá perforovaná + štěrkový obsyp 16/32 + geotextilie + napojení do dešťové kanalizace, L po obvodu BV</t>
+          <t>Sklad mezipodesta schodiště prefa — Sklad mezipodesta schodiště — prefa betonové stupně (9 ks × 179.5×250 mm) + kladecí vrstva zavlhlého betonu nad ŽB podkladní deskou (S05 sklad skladba)</t>
         </is>
       </c>
       <c r="E103" s="20" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F103" s="22" t="n">
-        <v>12</v>
+        <v>5.5</v>
       </c>
       <c r="G103" s="10" t="n"/>
       <c r="H103" s="10" t="n"/>
       <c r="I103" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>betonar</t>
         </is>
       </c>
       <c r="J103" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 877315111</t>
+          <t>URS-prop 121301101</t>
         </is>
       </c>
     </row>
@@ -7316,37 +7316,37 @@
       </c>
       <c r="B104" s="20" t="inlineStr">
         <is>
-          <t>260217_sklad</t>
+          <t>260219_dum</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + schodiště</t>
+          <t>HSV-1 Zemní práce</t>
         </is>
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>Sklad mezipodesta schodiště prefa — Sklad mezipodesta schodiště — prefa betonové stupně (9 ks × 179.5×250 mm) + kladecí vrstva zavlhlého betonu nad ŽB podkladní deskou (S05 sklad skladba)</t>
+          <t>Venkovní schody na terénu (zahrada za opěrnou stěnou) — Venkovní schody na terénu z betonových dílců do betonového lože — rameno 1: 8×175×280 mm + rameno 2: 5×175×280 mm (13 stupňů), zahrada za opěrnou stěnou</t>
         </is>
       </c>
       <c r="E104" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F104" s="22" t="n">
-        <v>5.5</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="F104" s="23" t="n">
+        <v>13</v>
       </c>
       <c r="G104" s="10" t="n"/>
       <c r="H104" s="10" t="n"/>
       <c r="I104" s="8" t="inlineStr">
         <is>
-          <t>betonar</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="J104" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 121301101</t>
+          <t>URS-prop —</t>
         </is>
       </c>
     </row>
@@ -7361,12 +7361,12 @@
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>HSV-1 Zemní práce</t>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>Venkovní schody na terénu (zahrada za opěrnou stěnou) — Venkovní schody na terénu z betonových dílců do betonového lože — rameno 1: 8×175×280 mm + rameno 2: 5×175×280 mm (13 stupňů), zahrada za opěrnou stěnou</t>
+          <t>Spojovací prostředky krovu — svorníky tesařských spojů — Montáž svorníků / šroubů tesařských spojů krovu délky přes 150 do 300 mm — spojení kleštin 2×60/180 mm s krokvemi (svorník cca 250 mm, M12), vč. tyče závitové + matic + podložek</t>
         </is>
       </c>
       <c r="E105" s="20" t="inlineStr">
@@ -7375,18 +7375,18 @@
         </is>
       </c>
       <c r="F105" s="23" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="G105" s="10" t="n"/>
       <c r="H105" s="10" t="n"/>
       <c r="I105" s="8" t="inlineStr">
         <is>
-          <t>zednik</t>
+          <t>tesar</t>
         </is>
       </c>
       <c r="J105" s="8" t="inlineStr">
         <is>
-          <t>URS-prop —</t>
+          <t>URS-prop 762085112</t>
         </is>
       </c>
     </row>
@@ -7401,32 +7401,32 @@
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Krov + střecha</t>
+          <t>HSV-4 Vodorovné</t>
         </is>
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t>Spojovací prostředky krovu — svorníky tesařských spojů — Montáž svorníků / šroubů tesařských spojů krovu délky přes 150 do 300 mm — spojení kleštin 2×60/180 mm s krokvemi (svorník cca 250 mm, M12), vč. tyče závitové + matic + podložek</t>
+          <t>Strop 1.NP/2.NP — kročejová izolace (S07) — Desky kročejové izolace (Isover T-P) tl. 30 mm — trámový strop 1.NP/2.NP</t>
         </is>
       </c>
       <c r="E106" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="F106" s="23" t="n">
-        <v>50</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F106" s="22" t="n">
+        <v>59.5</v>
       </c>
       <c r="G106" s="10" t="n"/>
       <c r="H106" s="10" t="n"/>
       <c r="I106" s="8" t="inlineStr">
         <is>
-          <t>tesar</t>
+          <t>izolater_TI</t>
         </is>
       </c>
       <c r="J106" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 762085112</t>
+          <t>URS-prop 713191</t>
         </is>
       </c>
     </row>
@@ -7446,7 +7446,7 @@
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t>Strop 1.NP/2.NP — kročejová izolace (S07) — Desky kročejové izolace (Isover T-P) tl. 30 mm — trámový strop 1.NP/2.NP</t>
+          <t>Strop 1.NP/2.NP — separační geotextilie (S07) — Separační geotextilie pod suchý podsyp — trámový strop 1.NP/2.NP</t>
         </is>
       </c>
       <c r="E107" s="20" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="J107" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 713191</t>
+          <t>URS-prop —</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D108" s="8" t="inlineStr">
         <is>
-          <t>Strop 1.NP/2.NP — separační geotextilie (S07) — Separační geotextilie pod suchý podsyp — trámový strop 1.NP/2.NP</t>
+          <t>Strop 2.NP/3.NP — min. vata výplň mezi nosníky (S09) — Tepelná/akustická izolace minerální vata výplň mezi ocelové nosníky stropu 2.NP/3.NP, tl. 180/200 mm</t>
         </is>
       </c>
       <c r="E108" s="20" t="inlineStr">
@@ -7495,7 +7495,7 @@
         </is>
       </c>
       <c r="F108" s="22" t="n">
-        <v>59.5</v>
+        <v>104.4</v>
       </c>
       <c r="G108" s="10" t="n"/>
       <c r="H108" s="10" t="n"/>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="J108" s="8" t="inlineStr">
         <is>
-          <t>URS-prop —</t>
+          <t>URS-prop 713121</t>
         </is>
       </c>
     </row>
@@ -7526,7 +7526,7 @@
       </c>
       <c r="D109" s="8" t="inlineStr">
         <is>
-          <t>Strop 2.NP/3.NP — min. vata výplň mezi nosníky (S09) — Tepelná/akustická izolace minerální vata výplň mezi ocelové nosníky stropu 2.NP/3.NP, tl. 180/200 mm</t>
+          <t>Strop klemba mezi patry — Fermacell (S08) — Roznášecí sádrovláknité dílce Fermacell 2E22 tl. 25 mm — suchá skladba nad cihelnou klembou S08</t>
         </is>
       </c>
       <c r="E109" s="20" t="inlineStr">
@@ -7534,19 +7534,17 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="F109" s="22" t="n">
-        <v>104.4</v>
-      </c>
+      <c r="F109" s="22" t="n"/>
       <c r="G109" s="10" t="n"/>
       <c r="H109" s="10" t="n"/>
       <c r="I109" s="8" t="inlineStr">
         <is>
-          <t>izolater_TI</t>
+          <t>suchá_vystavba</t>
         </is>
       </c>
       <c r="J109" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 713121</t>
+          <t>URS-prop —</t>
         </is>
       </c>
     </row>
@@ -7566,7 +7564,7 @@
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
-          <t>Strop klemba mezi patry — Fermacell (S08) — Roznášecí sádrovláknité dílce Fermacell 2E22 tl. 25 mm — suchá skladba nad cihelnou klembou S08</t>
+          <t>Strop klemba mezi patry — kročejová izolace (S08) — Desky kročejové izolace (Isover T-P) tl. 30 mm — suchá skladba nad klembou S08</t>
         </is>
       </c>
       <c r="E110" s="20" t="inlineStr">
@@ -7579,12 +7577,12 @@
       <c r="H110" s="10" t="n"/>
       <c r="I110" s="8" t="inlineStr">
         <is>
-          <t>suchá_vystavba</t>
+          <t>izolater_TI</t>
         </is>
       </c>
       <c r="J110" s="8" t="inlineStr">
         <is>
-          <t>URS-prop —</t>
+          <t>URS-prop 713191</t>
         </is>
       </c>
     </row>
@@ -7604,7 +7602,7 @@
       </c>
       <c r="D111" s="8" t="inlineStr">
         <is>
-          <t>Strop klemba mezi patry — kročejová izolace (S08) — Desky kročejové izolace (Isover T-P) tl. 30 mm — suchá skladba nad klembou S08</t>
+          <t>Strop klemba mezi patry — suchý podsyp + dřevěný rošt (S08) — Vyrovnávací suchý podsyp keramzit/liapor + dřevěný rošt tl. 50 mm — nad klembou S08</t>
         </is>
       </c>
       <c r="E111" s="20" t="inlineStr">
@@ -7617,12 +7615,12 @@
       <c r="H111" s="10" t="n"/>
       <c r="I111" s="8" t="inlineStr">
         <is>
-          <t>izolater_TI</t>
+          <t>suchá_vystavba</t>
         </is>
       </c>
       <c r="J111" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 713191</t>
+          <t>URS-prop —</t>
         </is>
       </c>
     </row>
@@ -7642,7 +7640,7 @@
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
-          <t>Strop klemba mezi patry — suchý podsyp + dřevěný rošt (S08) — Vyrovnávací suchý podsyp keramzit/liapor + dřevěný rošt tl. 50 mm — nad klembou S08</t>
+          <t>Strop klemba mezi patry — separační vrstva (S08) — Separační vrstva pod suchý podsyp — nad cihelnou klembou S08</t>
         </is>
       </c>
       <c r="E112" s="20" t="inlineStr">
@@ -7675,12 +7673,12 @@
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t>HSV-4 Vodorovné</t>
+          <t>HSV-7 Fasáda + zateplení</t>
         </is>
       </c>
       <c r="D113" s="8" t="inlineStr">
         <is>
-          <t>Strop klemba mezi patry — separační vrstva (S08) — Separační vrstva pod suchý podsyp — nad cihelnou klembou S08</t>
+          <t>Sokl suterénu — sanační zateplení (S03) — Sanační zateplení soklu — sanační izolační deska Styrcon 200 + lepící tmel (Lepstyr plus) + armovací vrstva s tkaninou + penetrace</t>
         </is>
       </c>
       <c r="E113" s="20" t="inlineStr">
@@ -7688,12 +7686,14 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="F113" s="22" t="n"/>
+      <c r="F113" s="22" t="n">
+        <v>23</v>
+      </c>
       <c r="G113" s="10" t="n"/>
       <c r="H113" s="10" t="n"/>
       <c r="I113" s="8" t="inlineStr">
         <is>
-          <t>suchá_vystavba</t>
+          <t>fasader</t>
         </is>
       </c>
       <c r="J113" s="8" t="inlineStr">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t>Sokl suterénu — sanační zateplení (S03) — Sanační zateplení soklu — sanační izolační deska Styrcon 200 + lepící tmel (Lepstyr plus) + armovací vrstva s tkaninou + penetrace</t>
+          <t>Sokl pod terénem — drenážní nopová folie (S03a) — Drenážní vrstva — nopová folie tl. 20 mm na suterénní stěnu pod úrovní terénu</t>
         </is>
       </c>
       <c r="E114" s="20" t="inlineStr">
@@ -7733,7 +7733,7 @@
       <c r="H114" s="10" t="n"/>
       <c r="I114" s="8" t="inlineStr">
         <is>
-          <t>fasader</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="J114" s="8" t="inlineStr">
@@ -7758,7 +7758,7 @@
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
-          <t>Sokl pod terénem — drenážní nopová folie (S03a) — Drenážní vrstva — nopová folie tl. 20 mm na suterénní stěnu pod úrovní terénu</t>
+          <t>Sokl nad terénem — provětraný obklad (S03b) — Provětrávaná mezera s kotevním roštem 40 mm + keramický obklad 20 mm — sokl nad úrovní terénu</t>
         </is>
       </c>
       <c r="E115" s="20" t="inlineStr">
@@ -7773,7 +7773,7 @@
       <c r="H115" s="10" t="n"/>
       <c r="I115" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>obkladac</t>
         </is>
       </c>
       <c r="J115" s="8" t="inlineStr">
@@ -7793,12 +7793,12 @@
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda + zateplení</t>
+          <t>HSV-5 Krov + střecha</t>
         </is>
       </c>
       <c r="D116" s="8" t="inlineStr">
         <is>
-          <t>Sokl nad terénem — provětraný obklad (S03b) — Provětrávaná mezera s kotevním roštem 40 mm + keramický obklad 20 mm — sokl nad úrovní terénu</t>
+          <t>Střecha — pojistná HI folie pod Al krytinu (S10) — Pojistná hydroizolační folie pod hliníkovou falcovanou krytinu (nad celoplošným bedněním)</t>
         </is>
       </c>
       <c r="E116" s="20" t="inlineStr">
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="F116" s="22" t="n">
-        <v>23</v>
+        <v>140.94</v>
       </c>
       <c r="G116" s="10" t="n"/>
       <c r="H116" s="10" t="n"/>
       <c r="I116" s="8" t="inlineStr">
         <is>
-          <t>obkladac</t>
+          <t>pokryvac</t>
         </is>
       </c>
       <c r="J116" s="8" t="inlineStr">
@@ -7833,12 +7833,12 @@
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Krov + střecha</t>
+          <t>HSV-6 Bourací práce</t>
         </is>
       </c>
       <c r="D117" s="8" t="inlineStr">
         <is>
-          <t>Střecha — pojistná HI folie pod Al krytinu (S10) — Pojistná hydroizolační folie pod hliníkovou falcovanou krytinu (nad celoplošným bedněním)</t>
+          <t>Demontáž vnějšího keram. obkladu suterénu (S03 stávající) — Demontáž stávajícího vnějšího keramického obkladu suterénní stěny (sokl) tl. 20 mm</t>
         </is>
       </c>
       <c r="E117" s="20" t="inlineStr">
@@ -7847,13 +7847,13 @@
         </is>
       </c>
       <c r="F117" s="22" t="n">
-        <v>140.94</v>
+        <v>23</v>
       </c>
       <c r="G117" s="10" t="n"/>
       <c r="H117" s="10" t="n"/>
       <c r="I117" s="8" t="inlineStr">
         <is>
-          <t>pokryvac</t>
+          <t>bourac</t>
         </is>
       </c>
       <c r="J117" s="8" t="inlineStr">
@@ -7868,17 +7868,17 @@
       </c>
       <c r="B118" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>HSV-6 Bourací práce</t>
+          <t>HSV-5 Komunikace + vjezd</t>
         </is>
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t>Demontáž vnějšího keram. obkladu suterénu (S03 stávající) — Demontáž stávajícího vnějšího keramického obkladu suterénní stěny (sokl) tl. 20 mm</t>
+          <t>Vjezd Dvořákova — napojení na komunikaci — Napojení vjezdu na ulici Dvořákova — vydláždění z betonových dlaždic + spádování na pozemek investora + odvodnění dešťové vody na pozemek (ne na komunikaci)</t>
         </is>
       </c>
       <c r="E118" s="20" t="inlineStr">
@@ -7886,14 +7886,12 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="F118" s="22" t="n">
-        <v>23</v>
-      </c>
+      <c r="F118" s="22" t="n"/>
       <c r="G118" s="10" t="n"/>
       <c r="H118" s="10" t="n"/>
       <c r="I118" s="8" t="inlineStr">
         <is>
-          <t>bourac</t>
+          <t>komunikace</t>
         </is>
       </c>
       <c r="J118" s="8" t="inlineStr">
@@ -7911,32 +7909,34 @@
           <t>260217_sklad</t>
         </is>
       </c>
-      <c r="C119" s="8" t="inlineStr">
-        <is>
-          <t>HSV-5 Komunikace + vjezd</t>
+      <c r="C119" s="21" t="inlineStr">
+        <is>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D119" s="8" t="inlineStr">
         <is>
-          <t>Vjezd Dvořákova — napojení na komunikaci — Napojení vjezdu na ulici Dvořákova — vydláždění z betonových dlaždic + spádování na pozemek investora + odvodnění dešťové vody na pozemek (ne na komunikaci)</t>
+          <t>[agregát] 2 položek: Bezpečnostní dveře RC3 sklad; Vjezdová brána</t>
         </is>
       </c>
       <c r="E119" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F119" s="22" t="n"/>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F119" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="G119" s="10" t="n"/>
       <c r="H119" s="10" t="n"/>
       <c r="I119" s="8" t="inlineStr">
         <is>
-          <t>komunikace</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J119" s="8" t="inlineStr">
         <is>
-          <t>URS-prop —</t>
+          <t>agregát</t>
         </is>
       </c>
     </row>
@@ -7951,12 +7951,12 @@
       </c>
       <c r="C120" s="21" t="inlineStr">
         <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D120" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 2 položek: Bezpečnostní dveře RC3 sklad; Vjezdová brána</t>
+          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
         </is>
       </c>
       <c r="E120" s="20" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="C121" s="21" t="inlineStr">
         <is>
-          <t>PSV-77 — Podlahy</t>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
         </is>
       </c>
       <c r="D121" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
+          <t>[agregát] 5 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+2 dalších)</t>
         </is>
       </c>
       <c r="E121" s="20" t="inlineStr">
@@ -8026,17 +8026,17 @@
       </c>
       <c r="B122" s="20" t="inlineStr">
         <is>
-          <t>260217_sklad</t>
+          <t>260219_dum</t>
         </is>
       </c>
       <c r="C122" s="21" t="inlineStr">
         <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
+          <t>M-21 — Elektroinstalace silnoproudá</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 5 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+2 dalších)</t>
+          <t>[agregát] 8 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+5 dalších)</t>
         </is>
       </c>
       <c r="E122" s="20" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="C123" s="21" t="inlineStr">
         <is>
-          <t>M-21 — Elektroinstalace silnoproudá</t>
+          <t>M-24</t>
         </is>
       </c>
       <c r="D123" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 8 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+5 dalších)</t>
+          <t>[agregát] 1 položek: Lokální odtah digestoří kuchyní</t>
         </is>
       </c>
       <c r="E123" s="20" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="C124" s="21" t="inlineStr">
         <is>
-          <t>M-24</t>
+          <t>PSV-71 — Izolace HI + TI</t>
         </is>
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Lokální odtah digestoří kuchyní</t>
+          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
         </is>
       </c>
       <c r="E124" s="20" t="inlineStr">
@@ -8151,12 +8151,12 @@
       </c>
       <c r="C125" s="21" t="inlineStr">
         <is>
-          <t>PSV-71 — Izolace HI + TI</t>
+          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
         </is>
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
+          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
         </is>
       </c>
       <c r="E125" s="20" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="C126" s="21" t="inlineStr">
         <is>
-          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
+          <t>PSV-73 — Vytápění + komín</t>
         </is>
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
+          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
         </is>
       </c>
       <c r="E126" s="20" t="inlineStr">
@@ -8231,12 +8231,12 @@
       </c>
       <c r="C127" s="21" t="inlineStr">
         <is>
-          <t>PSV-73 — Vytápění + komín</t>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D127" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
+          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
         </is>
       </c>
       <c r="E127" s="20" t="inlineStr">
@@ -8271,12 +8271,12 @@
       </c>
       <c r="C128" s="21" t="inlineStr">
         <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
+          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
         </is>
       </c>
       <c r="E128" s="20" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="C129" s="21" t="inlineStr">
         <is>
-          <t>PSV-77 — Podlahy</t>
+          <t>PSV-78 — Povrchové úpravy</t>
         </is>
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
+          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
         </is>
       </c>
       <c r="E129" s="20" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="C130" s="21" t="inlineStr">
         <is>
-          <t>PSV-78 — Povrchové úpravy</t>
+          <t>PSV-95 — Detekce požární</t>
         </is>
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
+          <t>[agregát] 3 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A; Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
         </is>
       </c>
       <c r="E130" s="20" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="C131" s="21" t="inlineStr">
         <is>
-          <t>PSV-95 — Detekce požární</t>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
         </is>
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 3 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A; Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
+          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
         </is>
       </c>
       <c r="E131" s="20" t="inlineStr">
@@ -8420,48 +8420,8 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="20" t="n">
-        <v>131</v>
-      </c>
-      <c r="B132" s="20" t="inlineStr">
-        <is>
-          <t>260219_dum</t>
-        </is>
-      </c>
-      <c r="C132" s="21" t="inlineStr">
-        <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
-        </is>
-      </c>
-      <c r="D132" s="8" t="inlineStr">
-        <is>
-          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
-        </is>
-      </c>
-      <c r="E132" s="20" t="inlineStr">
-        <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F132" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G132" s="10" t="n"/>
-      <c r="H132" s="10" t="n"/>
-      <c r="I132" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J132" s="8" t="inlineStr">
-        <is>
-          <t>agregát</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J132"/>
+  <autoFilter ref="A1:J131"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8472,7 +8432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R203"/>
+  <dimension ref="A1:R202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -14618,7 +14578,7 @@
       </c>
       <c r="N88" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#35</t>
         </is>
       </c>
       <c r="O88" s="26" t="inlineStr">
@@ -14764,7 +14724,7 @@
       </c>
       <c r="N90" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#35</t>
         </is>
       </c>
       <c r="O90" s="26" t="inlineStr">
@@ -14936,26 +14896,26 @@
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>ETICS sokl XPS</t>
+          <t>Špalety EPS</t>
         </is>
       </c>
       <c r="D93" s="20" t="inlineStr">
         <is>
-          <t>622223111</t>
+          <t>622221221</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>ETICS sokl — XPS λ=0.034 tl. 120 mm + soklový profil + cihelný obklad spárovaný</t>
+          <t>Špalety oken — EPS přesah 35-40 mm + síťka + omítka</t>
         </is>
       </c>
       <c r="F93" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G93" s="22" t="n">
-        <v>13.5</v>
+        <v>82.2</v>
       </c>
       <c r="H93" s="10" t="n"/>
       <c r="I93" s="10" t="n"/>
@@ -14965,21 +14925,21 @@
         </is>
       </c>
       <c r="K93" s="24" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
       <c r="L93" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M93" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — sokl XPS + cihelný obklad + DXF perimeter</t>
+          <t>DXF okna per typ bbox + TZ ARS §3.2 EPS přesah na špaletách 35-40 mm</t>
         </is>
       </c>
       <c r="N93" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O93" s="26" t="inlineStr">
@@ -14989,14 +14949,10 @@
       </c>
       <c r="P93" s="41" t="inlineStr">
         <is>
-          <t>S01</t>
-        </is>
-      </c>
-      <c r="Q93" s="41" t="inlineStr">
-        <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
-        </is>
-      </c>
+          <t>S01, S12a</t>
+        </is>
+      </c>
+      <c r="Q93" s="41" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="20" t="n">
@@ -15009,7 +14965,7 @@
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>Špalety EPS</t>
+          <t>Profilace fasády</t>
         </is>
       </c>
       <c r="D94" s="20" t="inlineStr">
@@ -15019,16 +14975,16 @@
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>Špalety oken — EPS přesah 35-40 mm + síťka + omítka</t>
+          <t>Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
         </is>
       </c>
       <c r="F94" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G94" s="22" t="n">
-        <v>82.2</v>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="G94" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H94" s="10" t="n"/>
       <c r="I94" s="10" t="n"/>
@@ -15047,12 +15003,12 @@
       </c>
       <c r="M94" s="8" t="inlineStr">
         <is>
-          <t>DXF okna per typ bbox + TZ ARS §3.2 EPS přesah na špaletách 35-40 mm</t>
+          <t>TZ ARS dům §3.2 — profilace různými tl. EPS</t>
         </is>
       </c>
       <c r="N94" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O94" s="26" t="inlineStr">
@@ -15078,26 +15034,26 @@
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>Profilace fasády</t>
+          <t>Tenkovrstvá omítka pastovitá</t>
         </is>
       </c>
       <c r="D95" s="20" t="inlineStr">
         <is>
-          <t>622221221</t>
+          <t>622521111</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>Profilace fasády — různé tloušťky EPS (kordony, šambrány, rámování oken) — paušál podle pohledů</t>
+          <t>Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
         </is>
       </c>
       <c r="F95" s="20" t="inlineStr">
         <is>
-          <t>soubor</t>
-        </is>
-      </c>
-      <c r="G95" s="23" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G95" s="22" t="n">
+        <v>276.7</v>
       </c>
       <c r="H95" s="10" t="n"/>
       <c r="I95" s="10" t="n"/>
@@ -15107,16 +15063,16 @@
         </is>
       </c>
       <c r="K95" s="24" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
       <c r="L95" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M95" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — profilace různými tl. EPS</t>
+          <t>TZ ARS dům §3.2 — pastovitá probarvená lomená bílá + DXF perimeter</t>
         </is>
       </c>
       <c r="N95" s="20" t="inlineStr">
@@ -15131,10 +15087,14 @@
       </c>
       <c r="P95" s="41" t="inlineStr">
         <is>
-          <t>S01, S12a</t>
-        </is>
-      </c>
-      <c r="Q95" s="41" t="n"/>
+          <t>S01, S12a, S12b</t>
+        </is>
+      </c>
+      <c r="Q95" s="41" t="inlineStr">
+        <is>
+          <t>SOKL_RECONCILE_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="20" t="n">
@@ -15142,22 +15102,22 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>HSV-7 Fasáda ETICS</t>
+          <t>PSV-71 Izolace HI</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>Tenkovrstvá omítka pastovitá</t>
+          <t>HI pod ŽB deskou 1.NP</t>
         </is>
       </c>
       <c r="D96" s="20" t="inlineStr">
         <is>
-          <t>622521111</t>
+          <t>712311101</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>Tenkovrstvá pastovitá probarvená omítka, lomená bílá NCS NZÚ — finální vrstva ETICS</t>
+          <t>Hydroizolace pod ŽB deskou 1.NP — modifikované asfaltové pásy SBS 2× (zároveň protiradonová bariéra)</t>
         </is>
       </c>
       <c r="F96" s="20" t="inlineStr">
@@ -15166,17 +15126,17 @@
         </is>
       </c>
       <c r="G96" s="22" t="n">
-        <v>290.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="H96" s="10" t="n"/>
       <c r="I96" s="10" t="n"/>
       <c r="J96" s="8" t="inlineStr">
         <is>
-          <t>fasadnik_etics</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K96" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L96" s="20" t="inlineStr">
         <is>
@@ -15185,12 +15145,12 @@
       </c>
       <c r="M96" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — pastovitá probarvená lomená bílá + DXF perimeter</t>
+          <t>TZ ARS dům §4 + statika §5.5 — asfaltové pásy mod. proti radonu</t>
         </is>
       </c>
       <c r="N96" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="O96" s="26" t="inlineStr">
@@ -15198,14 +15158,10 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P96" s="41" t="inlineStr">
-        <is>
-          <t>S01, S12a, S12b</t>
-        </is>
-      </c>
+      <c r="P96" s="41" t="n"/>
       <c r="Q96" s="41" t="inlineStr">
         <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+          <t>URS_PHASE5B_FAMILY_VERIFIED; URS_PHASE5B_FAMILY_VERIFIED</t>
         </is>
       </c>
     </row>
@@ -15220,26 +15176,26 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>HI pod ŽB deskou 1.NP</t>
+          <t>Odvětrání radonu z podloží</t>
         </is>
       </c>
       <c r="D97" s="20" t="inlineStr">
         <is>
-          <t>712311101</t>
+          <t>712381111</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolace pod ŽB deskou 1.NP — modifikované asfaltové pásy SBS 2× (zároveň protiradonová bariéra)</t>
+          <t>Odvětrání radonu z podloží — perforované DN50 trubky v štěrkovém loži + výdech nad střechu</t>
         </is>
       </c>
       <c r="F97" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G97" s="22" t="n">
-        <v>80.40000000000001</v>
+        <v>12</v>
       </c>
       <c r="H97" s="10" t="n"/>
       <c r="I97" s="10" t="n"/>
@@ -15258,12 +15214,12 @@
       </c>
       <c r="M97" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 + statika §5.5 — asfaltové pásy mod. proti radonu</t>
+          <t>TZ statika §5.5 'ochrana proti radonu — modifikované asf. pásy + odvětrání'</t>
         </is>
       </c>
       <c r="N97" s="20" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O97" s="26" t="inlineStr">
@@ -15274,7 +15230,7 @@
       <c r="P97" s="41" t="n"/>
       <c r="Q97" s="41" t="inlineStr">
         <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED; URS_PHASE5B_FAMILY_VERIFIED</t>
+          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
         </is>
       </c>
     </row>
@@ -15289,26 +15245,26 @@
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>Odvětrání radonu z podloží</t>
-        </is>
-      </c>
-      <c r="D98" s="20" t="inlineStr">
-        <is>
-          <t>712381111</t>
+          <t>HI koupelny 1.NP + 2.NP + 3.NP</t>
+        </is>
+      </c>
+      <c r="D98" s="27" t="inlineStr">
+        <is>
+          <t>711??? ?</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>Odvětrání radonu z podloží — perforované DN50 trubky v štěrkovém loži + výdech nad střechu</t>
+          <t>Hydroizolační stěrka koupelen 3 ks — podlaha + sokl 200 mm + sprchový kout výška 2.0 m</t>
         </is>
       </c>
       <c r="F98" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G98" s="22" t="n">
-        <v>12</v>
+        <v>40.5</v>
       </c>
       <c r="H98" s="10" t="n"/>
       <c r="I98" s="10" t="n"/>
@@ -15318,7 +15274,7 @@
         </is>
       </c>
       <c r="K98" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L98" s="20" t="inlineStr">
         <is>
@@ -15327,12 +15283,12 @@
       </c>
       <c r="M98" s="8" t="inlineStr">
         <is>
-          <t>TZ statika §5.5 'ochrana proti radonu — modifikované asf. pásy + odvětrání'</t>
+          <t>DXF dum_DPZ MTEXT labels: 3× koupelna; TZ ARS — HI vana koupelny</t>
         </is>
       </c>
       <c r="N98" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#4</t>
         </is>
       </c>
       <c r="O98" s="26" t="inlineStr">
@@ -15353,22 +15309,22 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace HI</t>
+          <t>PSV-71 Izolace TI</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>HI koupelny 1.NP + 2.NP + 3.NP</t>
+          <t>Podlahový EPS 150</t>
         </is>
       </c>
       <c r="D99" s="27" t="inlineStr">
         <is>
-          <t>711??? ?</t>
+          <t>713121??? ?</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolační stěrka koupelen 3 ks — podlaha + sokl 200 mm + sprchový kout výška 2.0 m</t>
+          <t>Podlahový EPS 150 λ=0.035 tl. 120 mm — pod betonový potěr 1.NP a 3.NP</t>
         </is>
       </c>
       <c r="F99" s="20" t="inlineStr">
@@ -15377,17 +15333,17 @@
         </is>
       </c>
       <c r="G99" s="22" t="n">
-        <v>40.5</v>
+        <v>177.5</v>
       </c>
       <c r="H99" s="10" t="n"/>
       <c r="I99" s="10" t="n"/>
       <c r="J99" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>izolater_TI</t>
         </is>
       </c>
       <c r="K99" s="24" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L99" s="20" t="inlineStr">
         <is>
@@ -15396,7 +15352,7 @@
       </c>
       <c r="M99" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT labels: 3× koupelna; TZ ARS — HI vana koupelny</t>
+          <t>TZ ARS dům §4 — EPS 150 λ=0.035 tl. 120 mm</t>
         </is>
       </c>
       <c r="N99" s="20" t="inlineStr">
@@ -15427,7 +15383,7 @@
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>Podlahový EPS 150</t>
+          <t>Kročejová EPS nad ocelobeton</t>
         </is>
       </c>
       <c r="D100" s="27" t="inlineStr">
@@ -15437,7 +15393,7 @@
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>Podlahový EPS 150 λ=0.035 tl. 120 mm — pod betonový potěr 1.NP a 3.NP</t>
+          <t>Kročejová EPS 150 / 30 dB tl. 40 mm nad ocelobetonovým stropem 2.NP/3.NP</t>
         </is>
       </c>
       <c r="F100" s="20" t="inlineStr">
@@ -15446,7 +15402,7 @@
         </is>
       </c>
       <c r="G100" s="22" t="n">
-        <v>177.5</v>
+        <v>104.4</v>
       </c>
       <c r="H100" s="10" t="n"/>
       <c r="I100" s="10" t="n"/>
@@ -15456,7 +15412,7 @@
         </is>
       </c>
       <c r="K100" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L100" s="20" t="inlineStr">
         <is>
@@ -15465,12 +15421,12 @@
       </c>
       <c r="M100" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — EPS 150 λ=0.035 tl. 120 mm</t>
+          <t>TZ ARS dům §4 — kročejová EPS shora ocelobeton</t>
         </is>
       </c>
       <c r="N100" s="20" t="inlineStr">
         <is>
-          <t>#4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O100" s="26" t="inlineStr">
@@ -15478,10 +15434,14 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P100" s="41" t="n"/>
+      <c r="P100" s="41" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
       <c r="Q100" s="41" t="inlineStr">
         <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+          <t>D2_KROCEJOVA_30_to_40_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -15491,41 +15451,41 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>PSV-71 Izolace TI</t>
+          <t>PSV-76 Klempíř</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>Kročejová EPS nad ocelobeton</t>
-        </is>
-      </c>
-      <c r="D101" s="27" t="inlineStr">
-        <is>
-          <t>713121??? ?</t>
+          <t>Oplechování krytiny</t>
+        </is>
+      </c>
+      <c r="D101" s="20" t="inlineStr">
+        <is>
+          <t>764312235</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>Kročejová EPS 150 / 30 dB tl. 40 mm nad ocelobetonovým stropem 2.NP/3.NP</t>
+          <t>Klempířské oplechování krytiny — úžlabí, hřeben, štítové lemy (Al / Pzn lakovaný 0.55 mm)</t>
         </is>
       </c>
       <c r="F101" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G101" s="22" t="n">
-        <v>104.4</v>
+        <v>69.5</v>
       </c>
       <c r="H101" s="10" t="n"/>
       <c r="I101" s="10" t="n"/>
       <c r="J101" s="8" t="inlineStr">
         <is>
-          <t>izolater_TI</t>
+          <t>klempir</t>
         </is>
       </c>
       <c r="K101" s="24" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="L101" s="20" t="inlineStr">
         <is>
@@ -15534,12 +15494,12 @@
       </c>
       <c r="M101" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — kročejová EPS shora ocelobeton</t>
+          <t>DXF MA_klempíř (75.4 m) + SM__ klempířina (98.4 m) total = 173.8 m × 0.40 split heuristic — Path C Tier 3</t>
         </is>
       </c>
       <c r="N101" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O101" s="26" t="inlineStr">
@@ -15547,14 +15507,15 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P101" s="41" t="inlineStr">
-        <is>
-          <t>S09</t>
-        </is>
-      </c>
+      <c r="P101" s="41" t="n"/>
       <c r="Q101" s="41" t="inlineStr">
         <is>
-          <t>D2_KROCEJOVA_30_to_40_2026-06-01</t>
+          <t>URS_PHASE5B_FAMILY_VERIFIED_CHAPTER_MATCH</t>
+        </is>
+      </c>
+      <c r="R101" s="41" t="inlineStr">
+        <is>
+          <t>PSV-76 Klempíř items sum 159.9 m vs DXF MA_klempíř + SM__ klempířina total 173.8 m, Δ -8.0 % (-13.9 m). Within ±15 % tolerance per CEV Matrix D.4 verdict (gate-3). FLAG for Karel site walkthrough — possible missing klempíř segment (small). Source: outputs/cev_matrix_d_cross_doc_consistency.json D.4.</t>
         </is>
       </c>
     </row>
@@ -15569,17 +15530,17 @@
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>Oplechování krytiny</t>
+          <t>Venkovní parapety oken</t>
         </is>
       </c>
       <c r="D102" s="20" t="inlineStr">
         <is>
-          <t>764312235</t>
+          <t>764218201</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>Klempířské oplechování krytiny — úžlabí, hřeben, štítové lemy (Al / Pzn lakovaný 0.55 mm)</t>
+          <t>Venkovní parapety oken — Pzn plech lakovaný 250 mm × tl. 0.55 mm × 16 ks oken</t>
         </is>
       </c>
       <c r="F102" s="20" t="inlineStr">
@@ -15588,7 +15549,7 @@
         </is>
       </c>
       <c r="G102" s="22" t="n">
-        <v>69.5</v>
+        <v>20.8</v>
       </c>
       <c r="H102" s="10" t="n"/>
       <c r="I102" s="10" t="n"/>
@@ -15598,7 +15559,7 @@
         </is>
       </c>
       <c r="K102" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L102" s="20" t="inlineStr">
         <is>
@@ -15607,12 +15568,12 @@
       </c>
       <c r="M102" s="8" t="inlineStr">
         <is>
-          <t>DXF MA_klempíř (75.4 m) + SM__ klempířina (98.4 m) total = 173.8 m × 0.40 split heuristic — Path C Tier 3</t>
+          <t>DXF okna 16 ks INSERT blocks + standard parapet width</t>
         </is>
       </c>
       <c r="N102" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O102" s="26" t="inlineStr">
@@ -15643,17 +15604,17 @@
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>Venkovní parapety oken</t>
+          <t>Dešťové svody + žlaby</t>
         </is>
       </c>
       <c r="D103" s="20" t="inlineStr">
         <is>
-          <t>764218201</t>
+          <t>764454802</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>Venkovní parapety oken — Pzn plech lakovaný 250 mm × tl. 0.55 mm × 16 ks oken</t>
+          <t>Dešťové svody Pzn 100 mm + žlaby — 4 svody × ~14 m + žlaby per obvod střechy</t>
         </is>
       </c>
       <c r="F103" s="20" t="inlineStr">
@@ -15662,7 +15623,7 @@
         </is>
       </c>
       <c r="G103" s="22" t="n">
-        <v>20.8</v>
+        <v>43.5</v>
       </c>
       <c r="H103" s="10" t="n"/>
       <c r="I103" s="10" t="n"/>
@@ -15672,7 +15633,7 @@
         </is>
       </c>
       <c r="K103" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L103" s="20" t="inlineStr">
         <is>
@@ -15681,7 +15642,7 @@
       </c>
       <c r="M103" s="8" t="inlineStr">
         <is>
-          <t>DXF okna 16 ks INSERT blocks + standard parapet width</t>
+          <t>DXF klempířina lengths split + TZ ARS dešťové svody</t>
         </is>
       </c>
       <c r="N103" s="20" t="inlineStr">
@@ -15717,17 +15678,17 @@
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>Dešťové svody + žlaby</t>
+          <t>Vikýře + atika + závětrné lemy</t>
         </is>
       </c>
       <c r="D104" s="20" t="inlineStr">
         <is>
-          <t>764454802</t>
+          <t>764315235</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>Dešťové svody Pzn 100 mm + žlaby — 4 svody × ~14 m + žlaby per obvod střechy</t>
+          <t>Klempířské doplňky vikýřů + atika + závětrné lemy (4 vikýře komplexní detail)</t>
         </is>
       </c>
       <c r="F104" s="20" t="inlineStr">
@@ -15736,7 +15697,7 @@
         </is>
       </c>
       <c r="G104" s="22" t="n">
-        <v>43.5</v>
+        <v>26.1</v>
       </c>
       <c r="H104" s="10" t="n"/>
       <c r="I104" s="10" t="n"/>
@@ -15755,7 +15716,7 @@
       </c>
       <c r="M104" s="8" t="inlineStr">
         <is>
-          <t>DXF klempířina lengths split + TZ ARS dešťové svody</t>
+          <t>DXF klempířina geometry split + TZ ARS 4 vikýře</t>
         </is>
       </c>
       <c r="N104" s="20" t="inlineStr">
@@ -15786,50 +15747,50 @@
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Klempíř</t>
+          <t>PSV-76 Truhlář</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>Vikýře + atika + závětrné lemy</t>
+          <t>Dřevěné stupně schodišť</t>
         </is>
       </c>
       <c r="D105" s="20" t="inlineStr">
         <is>
-          <t>764315235</t>
+          <t>766811111</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>Klempířské doplňky vikýřů + atika + závětrné lemy (4 vikýře komplexní detail)</t>
+          <t>Dřevěné stupně ocelových schodišť (truhlářské, dub masiv tl. 40 mm)</t>
         </is>
       </c>
       <c r="F105" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G105" s="22" t="n">
-        <v>26.1</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G105" s="23" t="n">
+        <v>16</v>
       </c>
       <c r="H105" s="10" t="n"/>
       <c r="I105" s="10" t="n"/>
       <c r="J105" s="8" t="inlineStr">
         <is>
-          <t>klempir</t>
+          <t>truhlar</t>
         </is>
       </c>
       <c r="K105" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L105" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M105" s="8" t="inlineStr">
         <is>
-          <t>DXF klempířina geometry split + TZ ARS 4 vikýře</t>
+          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni truhlářské</t>
         </is>
       </c>
       <c r="N105" s="20" t="inlineStr">
@@ -15843,16 +15804,7 @@
         </is>
       </c>
       <c r="P105" s="41" t="n"/>
-      <c r="Q105" s="41" t="inlineStr">
-        <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED_CHAPTER_MATCH</t>
-        </is>
-      </c>
-      <c r="R105" s="41" t="inlineStr">
-        <is>
-          <t>PSV-76 Klempíř items sum 159.9 m vs DXF MA_klempíř + SM__ klempířina total 173.8 m, Δ -8.0 % (-13.9 m). Within ±15 % tolerance per CEV Matrix D.4 verdict (gate-3). FLAG for Karel site walkthrough — possible missing klempíř segment (small). Source: outputs/cev_matrix_d_cross_doc_consistency.json D.4.</t>
-        </is>
-      </c>
+      <c r="Q105" s="41" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="20" t="n">
@@ -15865,26 +15817,26 @@
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>Dřevěné stupně schodišť</t>
-        </is>
-      </c>
-      <c r="D106" s="20" t="inlineStr">
-        <is>
-          <t>766811111</t>
+          <t>Terasa garapa za opěrnou stěnou — dřevěná pochozí vrstva</t>
+        </is>
+      </c>
+      <c r="D106" s="27" t="inlineStr">
+        <is>
+          <t>762??? ?</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>Dřevěné stupně ocelových schodišť (truhlářské, dub masiv tl. 40 mm)</t>
+          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na dřevěném roštu z hranolů 50 mm na rektifikovatelných terčích (terče + podkladní skladba viz HSV1.005)</t>
         </is>
       </c>
       <c r="F106" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G106" s="23" t="n">
-        <v>16</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G106" s="22" t="n">
+        <v>9.23</v>
       </c>
       <c r="H106" s="10" t="n"/>
       <c r="I106" s="10" t="n"/>
@@ -15894,16 +15846,16 @@
         </is>
       </c>
       <c r="K106" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L106" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_762_leaf_lookup_required</t>
         </is>
       </c>
       <c r="M106" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni truhlářské</t>
+          <t>TZ ARS dům §4 + DXF dum_situace PLOT_DREVENY_04 (terasa, ne 3.NP); ŘEZ C-C potvrzuje dřevěný rošt z hranolů (NE hliníkový) + dřevěnou pochozí vrstvu</t>
         </is>
       </c>
       <c r="N106" s="20" t="inlineStr">
@@ -15917,7 +15869,11 @@
         </is>
       </c>
       <c r="P106" s="41" t="n"/>
-      <c r="Q106" s="41" t="n"/>
+      <c r="Q106" s="41" t="inlineStr">
+        <is>
+          <t>REZ_CC_TERASA_FIX_2026-05-29; SITUACE_AREA_FIX_2026-05-29</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="20" t="n">
@@ -15925,55 +15881,55 @@
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Truhlář</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t>Terasa garapa za opěrnou stěnou — dřevěná pochozí vrstva</t>
-        </is>
-      </c>
-      <c r="D107" s="27" t="inlineStr">
-        <is>
-          <t>762??? ?</t>
+          <t>Plastové okno trojsklo — 'okno 1.NP' (ulice)</t>
+        </is>
+      </c>
+      <c r="D107" s="20" t="inlineStr">
+        <is>
+          <t>766621011</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na dřevěném roštu z hranolů 50 mm na rektifikovatelných terčích (terče + podkladní skladba viz HSV1.005)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP' velikost 1185×1600 mm × 2 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="F107" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G107" s="22" t="n">
-        <v>9.23</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G107" s="23" t="n">
+        <v>2</v>
       </c>
       <c r="H107" s="10" t="n"/>
       <c r="I107" s="10" t="n"/>
       <c r="J107" s="8" t="inlineStr">
         <is>
-          <t>truhlar</t>
+          <t>okennar</t>
         </is>
       </c>
       <c r="K107" s="24" t="n">
-        <v>0.95</v>
+        <v>0.99</v>
       </c>
       <c r="L107" s="20" t="inlineStr">
         <is>
-          <t>family_762_leaf_lookup_required</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M107" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 + DXF dum_situace PLOT_DREVENY_04 (terasa, ne 3.NP); ŘEZ C-C potvrzuje dřevěný rošt z hranolů (NE hliníkový) + dřevěnou pochozí vrstvu</t>
+          <t>DXF dum_DPZ INSERT block 'okno 1.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N107" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O107" s="26" t="inlineStr">
@@ -15982,11 +15938,7 @@
         </is>
       </c>
       <c r="P107" s="41" t="n"/>
-      <c r="Q107" s="41" t="inlineStr">
-        <is>
-          <t>REZ_CC_TERASA_FIX_2026-05-29; SITUACE_AREA_FIX_2026-05-29</t>
-        </is>
-      </c>
+      <c r="Q107" s="41" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="20" t="n">
@@ -15999,7 +15951,7 @@
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 1.NP' (ulice)</t>
+          <t>Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada)</t>
         </is>
       </c>
       <c r="D108" s="20" t="inlineStr">
@@ -16009,7 +15961,7 @@
       </c>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP' velikost 1185×1600 mm × 2 ks (fasáda ulice)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP vzadu' velikost 920×1600 mm × 3 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="F108" s="20" t="inlineStr">
@@ -16018,7 +15970,7 @@
         </is>
       </c>
       <c r="G108" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H108" s="10" t="n"/>
       <c r="I108" s="10" t="n"/>
@@ -16032,12 +15984,12 @@
       </c>
       <c r="L108" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M108" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 1.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 1.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N108" s="20" t="inlineStr">
@@ -16064,7 +16016,7 @@
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada)</t>
+          <t>Plastové okno trojsklo — 'okno 2.NP' (ulice)</t>
         </is>
       </c>
       <c r="D109" s="20" t="inlineStr">
@@ -16074,7 +16026,7 @@
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 1.NP vzadu' velikost 920×1600 mm × 3 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 2.NP' velikost 1160×1480 mm × 4 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="F109" s="20" t="inlineStr">
@@ -16083,7 +16035,7 @@
         </is>
       </c>
       <c r="G109" s="23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H109" s="10" t="n"/>
       <c r="I109" s="10" t="n"/>
@@ -16102,7 +16054,7 @@
       </c>
       <c r="M109" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 1.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 2.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N109" s="20" t="inlineStr">
@@ -16129,7 +16081,7 @@
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 2.NP' (ulice)</t>
+          <t>Plastové okno trojsklo — 'okno 3.NP' (ulice)</t>
         </is>
       </c>
       <c r="D110" s="20" t="inlineStr">
@@ -16139,7 +16091,7 @@
       </c>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 2.NP' velikost 1160×1480 mm × 4 ks (fasáda ulice)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP' velikost 1785×1241 mm × 3 ks (fasáda ulice)</t>
         </is>
       </c>
       <c r="F110" s="20" t="inlineStr">
@@ -16148,7 +16100,7 @@
         </is>
       </c>
       <c r="G110" s="23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H110" s="10" t="n"/>
       <c r="I110" s="10" t="n"/>
@@ -16167,7 +16119,7 @@
       </c>
       <c r="M110" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 2.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 3.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N110" s="20" t="inlineStr">
@@ -16194,7 +16146,7 @@
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 3.NP' (ulice)</t>
+          <t>Plastové okno trojsklo — 'okno 3.NP vzadu' (zahrada)</t>
         </is>
       </c>
       <c r="D111" s="20" t="inlineStr">
@@ -16204,7 +16156,7 @@
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP' velikost 1785×1241 mm × 3 ks (fasáda ulice)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP vzadu' velikost 2075×1241 mm × 1 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="F111" s="20" t="inlineStr">
@@ -16213,7 +16165,7 @@
         </is>
       </c>
       <c r="G111" s="23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H111" s="10" t="n"/>
       <c r="I111" s="10" t="n"/>
@@ -16232,7 +16184,7 @@
       </c>
       <c r="M111" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 3.NP' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N111" s="20" t="inlineStr">
@@ -16259,7 +16211,7 @@
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno 3.NP vzadu' (zahrada)</t>
+          <t>Plastové okno trojsklo — 'okno male 3.NP vzadu' (zahrada)</t>
         </is>
       </c>
       <c r="D112" s="20" t="inlineStr">
@@ -16269,7 +16221,7 @@
       </c>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno 3.NP vzadu' velikost 2075×1241 mm × 1 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno male 3.NP vzadu' velikost 800×1241 mm × 1 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="F112" s="20" t="inlineStr">
@@ -16297,7 +16249,7 @@
       </c>
       <c r="M112" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno male 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N112" s="20" t="inlineStr">
@@ -16324,7 +16276,7 @@
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno male 3.NP vzadu' (zahrada)</t>
+          <t>Plastové okno trojsklo — 'okno malé vzadu' (zahrada)</t>
         </is>
       </c>
       <c r="D113" s="20" t="inlineStr">
@@ -16334,7 +16286,7 @@
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno male 3.NP vzadu' velikost 800×1241 mm × 1 ks (fasáda zahrada)</t>
+          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno malé vzadu' velikost 700×800 mm × 2 ks (fasáda zahrada)</t>
         </is>
       </c>
       <c r="F113" s="20" t="inlineStr">
@@ -16343,7 +16295,7 @@
         </is>
       </c>
       <c r="G113" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H113" s="10" t="n"/>
       <c r="I113" s="10" t="n"/>
@@ -16362,7 +16314,7 @@
       </c>
       <c r="M113" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno male 3.NP vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>DXF dum_DPZ INSERT block 'okno malé vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
         </is>
       </c>
       <c r="N113" s="20" t="inlineStr">
@@ -16389,17 +16341,17 @@
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno trojsklo — 'okno malé vzadu' (zahrada)</t>
+          <t>Žaluzie kastlík purenit</t>
         </is>
       </c>
       <c r="D114" s="20" t="inlineStr">
         <is>
-          <t>766621011</t>
+          <t>766631211</t>
         </is>
       </c>
       <c r="E114" s="8" t="inlineStr">
         <is>
-          <t>Plastové okno izolačním trojsklem Uw=0.85 W/m²K — typ 'okno malé vzadu' velikost 700×800 mm × 2 ks (fasáda zahrada)</t>
+          <t>Integrované stínící venkovní žaluzie v kastlíku pod omítkou s purenitovou izolací — uliční fasáda Fibichova (9 ks)</t>
         </is>
       </c>
       <c r="F114" s="20" t="inlineStr">
@@ -16408,17 +16360,17 @@
         </is>
       </c>
       <c r="G114" s="23" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H114" s="10" t="n"/>
       <c r="I114" s="10" t="n"/>
       <c r="J114" s="8" t="inlineStr">
         <is>
-          <t>okennar</t>
+          <t>okenni_zaluzie_kastlik_purenit</t>
         </is>
       </c>
       <c r="K114" s="24" t="n">
-        <v>0.99</v>
+        <v>0.95</v>
       </c>
       <c r="L114" s="20" t="inlineStr">
         <is>
@@ -16427,7 +16379,7 @@
       </c>
       <c r="M114" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT block 'okno malé vzadu' bbox z block definition + TZ ARS Uw=0.85 W/m²K</t>
+          <t>TZ ARS dům §3.2 — 'do ulice Fibichova s integrovanými stínícími žaluziemi v kastlíku pod omítkou s purenitovou izolací'</t>
         </is>
       </c>
       <c r="N114" s="20" t="inlineStr">
@@ -16454,17 +16406,17 @@
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t>Žaluzie kastlík purenit</t>
+          <t>Vstupní plastové dveře</t>
         </is>
       </c>
       <c r="D115" s="20" t="inlineStr">
         <is>
-          <t>766631211</t>
+          <t>766682111</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>Integrované stínící venkovní žaluzie v kastlíku pod omítkou s purenitovou izolací — uliční fasáda Fibichova (9 ks)</t>
+          <t>Plastové vstupní dveře (ulice + zahrada) — 2 ks</t>
         </is>
       </c>
       <c r="F115" s="20" t="inlineStr">
@@ -16473,17 +16425,17 @@
         </is>
       </c>
       <c r="G115" s="23" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H115" s="10" t="n"/>
       <c r="I115" s="10" t="n"/>
       <c r="J115" s="8" t="inlineStr">
         <is>
-          <t>okenni_zaluzie_kastlik_purenit</t>
+          <t>okennar</t>
         </is>
       </c>
       <c r="K115" s="24" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L115" s="20" t="inlineStr">
         <is>
@@ -16492,12 +16444,12 @@
       </c>
       <c r="M115" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2 — 'do ulice Fibichova s integrovanými stínícími žaluziemi v kastlíku pod omítkou s purenitovou izolací'</t>
+          <t>TZ ARS dům §4 — plastové vstupní dveře</t>
         </is>
       </c>
       <c r="N115" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O115" s="26" t="inlineStr">
@@ -16519,17 +16471,17 @@
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>Vstupní plastové dveře</t>
+          <t>Vnitřní dveře DTD laminované</t>
         </is>
       </c>
       <c r="D116" s="20" t="inlineStr">
         <is>
-          <t>766682111</t>
+          <t>766660035</t>
         </is>
       </c>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t>Plastové vstupní dveře (ulice + zahrada) — 2 ks</t>
+          <t>Vnitřní dveře DTD laminované s obložkovou zárubní — odhad 15 ks</t>
         </is>
       </c>
       <c r="F116" s="20" t="inlineStr">
@@ -16538,13 +16490,13 @@
         </is>
       </c>
       <c r="G116" s="23" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H116" s="10" t="n"/>
       <c r="I116" s="10" t="n"/>
       <c r="J116" s="8" t="inlineStr">
         <is>
-          <t>okennar</t>
+          <t>truhlar</t>
         </is>
       </c>
       <c r="K116" s="24" t="n">
@@ -16557,12 +16509,12 @@
       </c>
       <c r="M116" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — plastové vstupní dveře</t>
+          <t>TZ ARS dům §4 + DXF MTEXT room labels</t>
         </is>
       </c>
       <c r="N116" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O116" s="26" t="inlineStr">
@@ -16584,17 +16536,17 @@
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t>Vnitřní dveře DTD laminované</t>
+          <t>Požárně odolné dveře EI 30 DP3</t>
         </is>
       </c>
       <c r="D117" s="20" t="inlineStr">
         <is>
-          <t>766660035</t>
+          <t>766694112</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>Vnitřní dveře DTD laminované s obložkovou zárubní — odhad 15 ks</t>
+          <t>Požárně odolné jednokřídlové dveře EI 30 DP3 na vrcholu schodiště mezi 1.PP a 1.NP — uzavírá otvor v REI 90 stropu klenby sklepa (per PBŘ TUSPO § 'Požární uzávěry otvorů v požárních stěnách a požárních stropech: podzemní 30 DP1')</t>
         </is>
       </c>
       <c r="F117" s="20" t="inlineStr">
@@ -16603,17 +16555,17 @@
         </is>
       </c>
       <c r="G117" s="23" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H117" s="10" t="n"/>
       <c r="I117" s="10" t="n"/>
       <c r="J117" s="8" t="inlineStr">
         <is>
-          <t>truhlar</t>
+          <t>specialista_RC3_dvere</t>
         </is>
       </c>
       <c r="K117" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L117" s="20" t="inlineStr">
         <is>
@@ -16622,12 +16574,12 @@
       </c>
       <c r="M117" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 + DXF MTEXT room labels</t>
+          <t>PBŘ TUSPO § Požární uzávěry otvorů 'podzemní 30DP1'; DXF schodiště 1.PP→1.NP</t>
         </is>
       </c>
       <c r="N117" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O117" s="26" t="inlineStr">
@@ -16636,7 +16588,11 @@
         </is>
       </c>
       <c r="P117" s="41" t="n"/>
-      <c r="Q117" s="41" t="n"/>
+      <c r="Q117" s="41" t="inlineStr">
+        <is>
+          <t>GAP_008</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="20" t="n">
@@ -16649,17 +16605,17 @@
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>Požárně odolné dveře EI 30 DP3</t>
+          <t>Oplechování venkovních parapetů Pzn — 16 ks</t>
         </is>
       </c>
       <c r="D118" s="20" t="inlineStr">
         <is>
-          <t>766694112</t>
+          <t>764811112</t>
         </is>
       </c>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t>Požárně odolné jednokřídlové dveře EI 30 DP3 na vrcholu schodiště mezi 1.PP a 1.NP — uzavírá otvor v REI 90 stropu klenby sklepa (per PBŘ TUSPO § 'Požární uzávěry otvorů v požárních stěnách a požárních stropech: podzemní 30 DP1')</t>
+          <t>Oplechování venkovních parapetů Pzn plech lakovaný 250 mm × tl. 0.55 mm, vč. okapnice + boční zakončení — 16 ks (per DXF INSERT okno × 16)</t>
         </is>
       </c>
       <c r="F118" s="20" t="inlineStr">
@@ -16668,17 +16624,17 @@
         </is>
       </c>
       <c r="G118" s="23" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H118" s="10" t="n"/>
       <c r="I118" s="10" t="n"/>
       <c r="J118" s="8" t="inlineStr">
         <is>
-          <t>specialista_RC3_dvere</t>
+          <t>klempir</t>
         </is>
       </c>
       <c r="K118" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L118" s="20" t="inlineStr">
         <is>
@@ -16687,7 +16643,7 @@
       </c>
       <c r="M118" s="8" t="inlineStr">
         <is>
-          <t>PBŘ TUSPO § Požární uzávěry otvorů 'podzemní 30DP1'; DXF schodiště 1.PP→1.NP</t>
+          <t>DXF blocks okno* 16 ks + DXF klempir_parapet 16 ks (Path C Tier 4 INSERT discovery)</t>
         </is>
       </c>
       <c r="N118" s="20" t="inlineStr">
@@ -16703,7 +16659,7 @@
       <c r="P118" s="41" t="n"/>
       <c r="Q118" s="41" t="inlineStr">
         <is>
-          <t>GAP_008</t>
+          <t>GAP_004</t>
         </is>
       </c>
     </row>
@@ -16713,55 +16669,55 @@
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t>Oplechování venkovních parapetů Pzn — 16 ks</t>
+          <t>Ocelové schodiště UPE200 ze zahrady</t>
         </is>
       </c>
       <c r="D119" s="20" t="inlineStr">
         <is>
-          <t>764811112</t>
+          <t>767531111</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>Oplechování venkovních parapetů Pzn plech lakovaný 250 mm × tl. 0.55 mm, vč. okapnice + boční zakončení — 16 ks (per DXF INSERT okno × 16)</t>
+          <t>Ocelové schodiště ze zahrady na mezipodestu — UPE200 schodnice + dřevěné nášlapy, kotvené do koruny opěrné stěny a zdiva (TZ statika §4)</t>
         </is>
       </c>
       <c r="F119" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G119" s="23" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H119" s="10" t="n"/>
       <c r="I119" s="10" t="n"/>
       <c r="J119" s="8" t="inlineStr">
         <is>
-          <t>klempir</t>
+          <t>zamecnik_PSV</t>
         </is>
       </c>
       <c r="K119" s="24" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="L119" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M119" s="8" t="inlineStr">
         <is>
-          <t>DXF blocks okno* 16 ks + DXF klempir_parapet 16 ks (Path C Tier 4 INSERT discovery)</t>
+          <t>TZ statika dům §4 — schodiště UPE200 + UPE100 podružné prvky</t>
         </is>
       </c>
       <c r="N119" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#5</t>
         </is>
       </c>
       <c r="O119" s="26" t="inlineStr">
@@ -16772,7 +16728,7 @@
       <c r="P119" s="41" t="n"/>
       <c r="Q119" s="41" t="inlineStr">
         <is>
-          <t>GAP_004</t>
+          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
         </is>
       </c>
     </row>
@@ -16787,7 +16743,7 @@
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>Ocelové schodiště UPE200 ze zahrady</t>
+          <t>Ocelové schodiště do spacího patra 3.NP</t>
         </is>
       </c>
       <c r="D120" s="20" t="inlineStr">
@@ -16797,7 +16753,7 @@
       </c>
       <c r="E120" s="8" t="inlineStr">
         <is>
-          <t>Ocelové schodiště ze zahrady na mezipodestu — UPE200 schodnice + dřevěné nášlapy, kotvené do koruny opěrné stěny a zdiva (TZ statika §4)</t>
+          <t>Interní ocelové schodiště do spacího patra v 3.NP s dřevěnými stupni (truhlářské)</t>
         </is>
       </c>
       <c r="F120" s="20" t="inlineStr">
@@ -16825,12 +16781,12 @@
       </c>
       <c r="M120" s="8" t="inlineStr">
         <is>
-          <t>TZ statika dům §4 — schodiště UPE200 + UPE100 podružné prvky</t>
+          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni</t>
         </is>
       </c>
       <c r="N120" s="20" t="inlineStr">
         <is>
-          <t>#5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O120" s="26" t="inlineStr">
@@ -16856,26 +16812,26 @@
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t>Ocelové schodiště do spacího patra 3.NP</t>
+          <t>Stříšky nad vstupy</t>
         </is>
       </c>
       <c r="D121" s="20" t="inlineStr">
         <is>
-          <t>767531111</t>
+          <t>767532111</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>Interní ocelové schodiště do spacího patra v 3.NP s dřevěnými stupni (truhlářské)</t>
+          <t>Stříšky nad vstupy z ocelové konstrukce + Cetris desky + falcovaná krytina — 2 ks (ulice + zahrada)</t>
         </is>
       </c>
       <c r="F121" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G121" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H121" s="10" t="n"/>
       <c r="I121" s="10" t="n"/>
@@ -16885,16 +16841,16 @@
         </is>
       </c>
       <c r="K121" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L121" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M121" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — ocelové schodiště s dřevěnými stupni</t>
+          <t>TZ ARS dům §4 — stříšky nad vstupy ocel+Cetris+plech</t>
         </is>
       </c>
       <c r="N121" s="20" t="inlineStr">
@@ -16908,11 +16864,7 @@
         </is>
       </c>
       <c r="P121" s="41" t="n"/>
-      <c r="Q121" s="41" t="inlineStr">
-        <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
-        </is>
-      </c>
+      <c r="Q121" s="41" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="20" t="n">
@@ -16925,26 +16877,26 @@
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>Stříšky nad vstupy</t>
+          <t>Zábradlí z jeklů + nerez výplň</t>
         </is>
       </c>
       <c r="D122" s="20" t="inlineStr">
         <is>
-          <t>767532111</t>
+          <t>767163115</t>
         </is>
       </c>
       <c r="E122" s="8" t="inlineStr">
         <is>
-          <t>Stříšky nad vstupy z ocelové konstrukce + Cetris desky + falcovaná krytina — 2 ks (ulice + zahrada)</t>
+          <t>Ocelové zábradlí svařované z jeklů + nerez výplň pZn antracit — schodiště interier + venkovní terasa</t>
         </is>
       </c>
       <c r="F122" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G122" s="23" t="n">
-        <v>2</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G122" s="22" t="n">
+        <v>18</v>
       </c>
       <c r="H122" s="10" t="n"/>
       <c r="I122" s="10" t="n"/>
@@ -16963,7 +16915,7 @@
       </c>
       <c r="M122" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — stříšky nad vstupy ocel+Cetris+plech</t>
+          <t>TZ ARS dům §4 — zábradlí svařované z jeklů + nerez výplň</t>
         </is>
       </c>
       <c r="N122" s="20" t="inlineStr">
@@ -16985,55 +16937,55 @@
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnictví</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t>Zábradlí z jeklů + nerez výplň</t>
+          <t>Nášlap vinyl obytné místnosti</t>
         </is>
       </c>
       <c r="D123" s="20" t="inlineStr">
         <is>
-          <t>767163115</t>
+          <t>776511820</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>Ocelové zábradlí svařované z jeklů + nerez výplň pZn antracit — schodiště interier + venkovní terasa</t>
+          <t>Nášlapná vrstva vinyl tl. 4 mm na suchou skladbu — obytné místnosti (ložnice, obývák, kuchyně, chodby)</t>
         </is>
       </c>
       <c r="F123" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G123" s="22" t="n">
-        <v>18</v>
+        <v>171.5</v>
       </c>
       <c r="H123" s="10" t="n"/>
       <c r="I123" s="10" t="n"/>
       <c r="J123" s="8" t="inlineStr">
         <is>
-          <t>zamecnik_PSV</t>
+          <t>podlahar</t>
         </is>
       </c>
       <c r="K123" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L123" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M123" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — zábradlí svařované z jeklů + nerez výplň</t>
+          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (kuchyně/obytná/chodba = vinyl) + TZ ARS §3.2.4 nášlapná vrstva</t>
         </is>
       </c>
       <c r="N123" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#4</t>
         </is>
       </c>
       <c r="O123" s="26" t="inlineStr">
@@ -17042,7 +16994,11 @@
         </is>
       </c>
       <c r="P123" s="41" t="n"/>
-      <c r="Q123" s="41" t="n"/>
+      <c r="Q123" s="41" t="inlineStr">
+        <is>
+          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="20" t="n">
@@ -17055,17 +17011,17 @@
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>Nášlap vinyl obytné místnosti</t>
+          <t>Nášlap keramická dlažba — mokré zóny</t>
         </is>
       </c>
       <c r="D124" s="20" t="inlineStr">
         <is>
-          <t>776511820</t>
+          <t>771274102</t>
         </is>
       </c>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva vinyl tl. 4 mm na suchou skladbu — obytné místnosti (ložnice, obývák, kuchyně, chodby)</t>
+          <t>Nášlapná vrstva keramická dlažba lepená — koupelny + WC + spíž + komora (NÁDRŽ NP)</t>
         </is>
       </c>
       <c r="F124" s="20" t="inlineStr">
@@ -17074,13 +17030,13 @@
         </is>
       </c>
       <c r="G124" s="22" t="n">
-        <v>171.5</v>
+        <v>13.5</v>
       </c>
       <c r="H124" s="10" t="n"/>
       <c r="I124" s="10" t="n"/>
       <c r="J124" s="8" t="inlineStr">
         <is>
-          <t>podlahar</t>
+          <t>obkladac</t>
         </is>
       </c>
       <c r="K124" s="24" t="n">
@@ -17088,12 +17044,12 @@
       </c>
       <c r="L124" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M124" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (kuchyně/obytná/chodba = vinyl) + TZ ARS §3.2.4 nášlapná vrstva</t>
+          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (koupelna/WC/spíž = dlažba mokré) + TZ ARS skladba mokrá</t>
         </is>
       </c>
       <c r="N124" s="20" t="inlineStr">
@@ -17107,11 +17063,7 @@
         </is>
       </c>
       <c r="P124" s="41" t="n"/>
-      <c r="Q124" s="41" t="inlineStr">
-        <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
-        </is>
-      </c>
+      <c r="Q124" s="41" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="20" t="n">
@@ -17124,7 +17076,7 @@
       </c>
       <c r="C125" s="8" t="inlineStr">
         <is>
-          <t>Nášlap keramická dlažba — mokré zóny</t>
+          <t>Nášlap keramická dlažba — 1.PP sklep</t>
         </is>
       </c>
       <c r="D125" s="20" t="inlineStr">
@@ -17134,7 +17086,7 @@
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva keramická dlažba lepená — koupelny + WC + spíž + komora (NÁDRŽ NP)</t>
+          <t>Nášlapná vrstva keramická dlažba — 1.PP technické místnosti (sušárna + sklepy + schodiště + chodba)</t>
         </is>
       </c>
       <c r="F125" s="20" t="inlineStr">
@@ -17143,7 +17095,7 @@
         </is>
       </c>
       <c r="G125" s="22" t="n">
-        <v>13.5</v>
+        <v>32.4</v>
       </c>
       <c r="H125" s="10" t="n"/>
       <c r="I125" s="10" t="n"/>
@@ -17162,7 +17114,7 @@
       </c>
       <c r="M125" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT (návrh) — rooms classified per name (koupelna/WC/spíž = dlažba mokré) + TZ ARS skladba mokrá</t>
+          <t>DXF km_tabulka místností MTEXT (návrh) — 1.PP all rooms = dlažba sklep zone</t>
         </is>
       </c>
       <c r="N125" s="20" t="inlineStr">
@@ -17189,17 +17141,17 @@
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>Nášlap keramická dlažba — 1.PP sklep</t>
+          <t>Nášlap biodeska 3.NP spací patro</t>
         </is>
       </c>
       <c r="D126" s="20" t="inlineStr">
         <is>
-          <t>771274102</t>
+          <t>766411111</t>
         </is>
       </c>
       <c r="E126" s="8" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva keramická dlažba — 1.PP technické místnosti (sušárna + sklepy + schodiště + chodba)</t>
+          <t>Nášlapná vrstva biodeska (smrk masiv) nebo OSB v 3.NP spací části nad krovem</t>
         </is>
       </c>
       <c r="F126" s="20" t="inlineStr">
@@ -17208,17 +17160,17 @@
         </is>
       </c>
       <c r="G126" s="22" t="n">
-        <v>32.4</v>
+        <v>25</v>
       </c>
       <c r="H126" s="10" t="n"/>
       <c r="I126" s="10" t="n"/>
       <c r="J126" s="8" t="inlineStr">
         <is>
-          <t>obkladac</t>
+          <t>biodeska_konstrukcni</t>
         </is>
       </c>
       <c r="K126" s="24" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L126" s="20" t="inlineStr">
         <is>
@@ -17227,12 +17179,12 @@
       </c>
       <c r="M126" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT (návrh) — 1.PP all rooms = dlažba sklep zone</t>
+          <t>TZ ARS dům §3.2.3 — biodeska patro pro přespání</t>
         </is>
       </c>
       <c r="N126" s="20" t="inlineStr">
         <is>
-          <t>#4</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="O126" s="26" t="inlineStr">
@@ -17254,17 +17206,17 @@
       </c>
       <c r="C127" s="8" t="inlineStr">
         <is>
-          <t>Nášlap biodeska 3.NP spací patro</t>
+          <t>Betonový potěr s kari nad EPS</t>
         </is>
       </c>
       <c r="D127" s="20" t="inlineStr">
         <is>
-          <t>766411111</t>
+          <t>631321311</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>Nášlapná vrstva biodeska (smrk masiv) nebo OSB v 3.NP spací části nad krovem</t>
+          <t>Mokrá podlahová skladba — betonový potěr s kari síťkou 4/100/100 tl. 50 mm + samonivelační stěrka</t>
         </is>
       </c>
       <c r="F127" s="20" t="inlineStr">
@@ -17273,17 +17225,17 @@
         </is>
       </c>
       <c r="G127" s="22" t="n">
-        <v>25</v>
+        <v>126.4</v>
       </c>
       <c r="H127" s="10" t="n"/>
       <c r="I127" s="10" t="n"/>
       <c r="J127" s="8" t="inlineStr">
         <is>
-          <t>biodeska_konstrukcni</t>
+          <t>podlahar</t>
         </is>
       </c>
       <c r="K127" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L127" s="20" t="inlineStr">
         <is>
@@ -17292,12 +17244,12 @@
       </c>
       <c r="M127" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2.3 — biodeska patro pro přespání</t>
+          <t>TZ ARS dům §3.2.4 + §3.2.x — 'kročejová izolace + betonový potěr s kari sítí'; DXF rooms areas</t>
         </is>
       </c>
       <c r="N127" s="20" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>#4</t>
         </is>
       </c>
       <c r="O127" s="26" t="inlineStr">
@@ -17319,26 +17271,26 @@
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>Betonový potěr s kari nad EPS</t>
+          <t>Soklíky vinyl</t>
         </is>
       </c>
       <c r="D128" s="20" t="inlineStr">
         <is>
-          <t>631321311</t>
+          <t>776511831</t>
         </is>
       </c>
       <c r="E128" s="8" t="inlineStr">
         <is>
-          <t>Mokrá podlahová skladba — betonový potěr s kari síťkou 4/100/100 tl. 50 mm + samonivelační stěrka</t>
+          <t>Soklíky podlahové laminátové (dub) v obytných místnostech s vinyl podlahou</t>
         </is>
       </c>
       <c r="F128" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G128" s="22" t="n">
-        <v>126.4</v>
+        <v>72.03</v>
       </c>
       <c r="H128" s="10" t="n"/>
       <c r="I128" s="10" t="n"/>
@@ -17357,12 +17309,12 @@
       </c>
       <c r="M128" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2.4 + §3.2.x — 'kročejová izolace + betonový potěr s kari sítí'; DXF rooms areas</t>
+          <t>DXF rooms vinyl + standard ratio per RD geometry</t>
         </is>
       </c>
       <c r="N128" s="20" t="inlineStr">
         <is>
-          <t>#4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O128" s="26" t="inlineStr">
@@ -17384,17 +17336,17 @@
       </c>
       <c r="C129" s="8" t="inlineStr">
         <is>
-          <t>Soklíky vinyl</t>
+          <t>Soklíky keramické</t>
         </is>
       </c>
       <c r="D129" s="20" t="inlineStr">
         <is>
-          <t>776511831</t>
+          <t>771274107</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t>Soklíky podlahové laminátové (dub) v obytných místnostech s vinyl podlahou</t>
+          <t>Soklíky keramické v místnostech s dlažbou (koupelny + WC + spíž + 1.PP)</t>
         </is>
       </c>
       <c r="F129" s="20" t="inlineStr">
@@ -17403,13 +17355,13 @@
         </is>
       </c>
       <c r="G129" s="22" t="n">
-        <v>72.03</v>
+        <v>19.28</v>
       </c>
       <c r="H129" s="10" t="n"/>
       <c r="I129" s="10" t="n"/>
       <c r="J129" s="8" t="inlineStr">
         <is>
-          <t>podlahar</t>
+          <t>obkladac</t>
         </is>
       </c>
       <c r="K129" s="24" t="n">
@@ -17422,7 +17374,7 @@
       </c>
       <c r="M129" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms vinyl + standard ratio per RD geometry</t>
+          <t>DXF rooms dlažba + standard ratio per RD geometry</t>
         </is>
       </c>
       <c r="N129" s="20" t="inlineStr">
@@ -17444,41 +17396,41 @@
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-78 Povrchové úpravy</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>Soklíky keramické</t>
+          <t>Omítka jádrová + štuk 1.PP</t>
         </is>
       </c>
       <c r="D130" s="20" t="inlineStr">
         <is>
-          <t>771274107</t>
+          <t>612311311</t>
         </is>
       </c>
       <c r="E130" s="8" t="inlineStr">
         <is>
-          <t>Soklíky keramické v místnostech s dlažbou (koupelny + WC + spíž + 1.PP)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.PP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="F130" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G130" s="22" t="n">
-        <v>19.28</v>
+        <v>78.2</v>
       </c>
       <c r="H130" s="10" t="n"/>
       <c r="I130" s="10" t="n"/>
       <c r="J130" s="8" t="inlineStr">
         <is>
-          <t>obkladac</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="K130" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L130" s="20" t="inlineStr">
         <is>
@@ -17487,12 +17439,12 @@
       </c>
       <c r="M130" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms dlažba + standard ratio per RD geometry</t>
+          <t>DXF rooms 1.PP obvod + výška podlaží 2.1 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="N130" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#3</t>
         </is>
       </c>
       <c r="O130" s="26" t="inlineStr">
@@ -17514,7 +17466,7 @@
       </c>
       <c r="C131" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová + štuk 1.PP</t>
+          <t>Omítka jádrová + štuk 1.NP</t>
         </is>
       </c>
       <c r="D131" s="20" t="inlineStr">
@@ -17524,7 +17476,7 @@
       </c>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.PP (stávající vyspravené + nové zděné)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="F131" s="20" t="inlineStr">
@@ -17533,7 +17485,7 @@
         </is>
       </c>
       <c r="G131" s="22" t="n">
-        <v>78.2</v>
+        <v>208.4</v>
       </c>
       <c r="H131" s="10" t="n"/>
       <c r="I131" s="10" t="n"/>
@@ -17552,7 +17504,7 @@
       </c>
       <c r="M131" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms 1.PP obvod + výška podlaží 2.1 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF rooms 1.NP obvod + výška podlaží 2.795 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="N131" s="20" t="inlineStr">
@@ -17579,7 +17531,7 @@
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová + štuk 1.NP</t>
+          <t>Omítka jádrová + štuk 2.NP</t>
         </is>
       </c>
       <c r="D132" s="20" t="inlineStr">
@@ -17589,7 +17541,7 @@
       </c>
       <c r="E132" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 1.NP (stávající vyspravené + nové zděné)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 2.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="F132" s="20" t="inlineStr">
@@ -17598,7 +17550,7 @@
         </is>
       </c>
       <c r="G132" s="22" t="n">
-        <v>208.4</v>
+        <v>201.6</v>
       </c>
       <c r="H132" s="10" t="n"/>
       <c r="I132" s="10" t="n"/>
@@ -17617,7 +17569,7 @@
       </c>
       <c r="M132" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms 1.NP obvod + výška podlaží 2.795 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF rooms 2.NP obvod + výška podlaží 2.865 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="N132" s="20" t="inlineStr">
@@ -17644,7 +17596,7 @@
       </c>
       <c r="C133" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová + štuk 2.NP</t>
+          <t>Omítka jádrová + štuk 3.NP</t>
         </is>
       </c>
       <c r="D133" s="20" t="inlineStr">
@@ -17654,7 +17606,7 @@
       </c>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 2.NP (stávající vyspravené + nové zděné)</t>
+          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 3.NP (stávající vyspravené + nové zděné)</t>
         </is>
       </c>
       <c r="F133" s="20" t="inlineStr">
@@ -17663,7 +17615,7 @@
         </is>
       </c>
       <c r="G133" s="22" t="n">
-        <v>201.6</v>
+        <v>179.1</v>
       </c>
       <c r="H133" s="10" t="n"/>
       <c r="I133" s="10" t="n"/>
@@ -17682,7 +17634,7 @@
       </c>
       <c r="M133" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms 2.NP obvod + výška podlaží 2.865 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF rooms 3.NP obvod + výška podlaží 2.63 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
         </is>
       </c>
       <c r="N133" s="20" t="inlineStr">
@@ -17709,17 +17661,17 @@
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová + štuk 3.NP</t>
+          <t>SDK podhled — tmelení + úprava 1.NP</t>
         </is>
       </c>
       <c r="D134" s="20" t="inlineStr">
         <is>
-          <t>612311311</t>
+          <t>612471141</t>
         </is>
       </c>
       <c r="E134" s="8" t="inlineStr">
         <is>
-          <t>Omítka jádrová vápenocementová tl. 15 mm + štuková povrchová úprava na stěnách 3.NP (stávající vyspravené + nové zděné)</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (1.NP)</t>
         </is>
       </c>
       <c r="F134" s="20" t="inlineStr">
@@ -17728,17 +17680,17 @@
         </is>
       </c>
       <c r="G134" s="22" t="n">
-        <v>179.1</v>
+        <v>59.5</v>
       </c>
       <c r="H134" s="10" t="n"/>
       <c r="I134" s="10" t="n"/>
       <c r="J134" s="8" t="inlineStr">
         <is>
-          <t>zednik</t>
+          <t>sadrokartonar</t>
         </is>
       </c>
       <c r="K134" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L134" s="20" t="inlineStr">
         <is>
@@ -17747,12 +17699,12 @@
       </c>
       <c r="M134" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms 3.NP obvod + výška podlaží 2.63 m (DXF SM_kóty + řez A-A Path C Tier 1) − okenní plocha (DXF) − odpočet dveří 3%</t>
+          <t>DXF km_tabulka místností MTEXT — plocha 1.NP = plocha podhledu (flat ceiling assumption)</t>
         </is>
       </c>
       <c r="N134" s="20" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O134" s="26" t="inlineStr">
@@ -17774,7 +17726,7 @@
       </c>
       <c r="C135" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled — tmelení + úprava 1.NP</t>
+          <t>SDK podhled — tmelení + úprava 2.NP</t>
         </is>
       </c>
       <c r="D135" s="20" t="inlineStr">
@@ -17784,7 +17736,7 @@
       </c>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (1.NP)</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (2.NP)</t>
         </is>
       </c>
       <c r="F135" s="20" t="inlineStr">
@@ -17793,7 +17745,7 @@
         </is>
       </c>
       <c r="G135" s="22" t="n">
-        <v>59.5</v>
+        <v>61.1</v>
       </c>
       <c r="H135" s="10" t="n"/>
       <c r="I135" s="10" t="n"/>
@@ -17812,7 +17764,7 @@
       </c>
       <c r="M135" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT — plocha 1.NP = plocha podhledu (flat ceiling assumption)</t>
+          <t>DXF km_tabulka místností MTEXT — plocha 2.NP = plocha podhledu (flat ceiling assumption)</t>
         </is>
       </c>
       <c r="N135" s="20" t="inlineStr">
@@ -17839,7 +17791,7 @@
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled — tmelení + úprava 2.NP</t>
+          <t>SDK podhled — tmelení + úprava 3.NP</t>
         </is>
       </c>
       <c r="D136" s="20" t="inlineStr">
@@ -17849,7 +17801,7 @@
       </c>
       <c r="E136" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (2.NP)</t>
+          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (3.NP)</t>
         </is>
       </c>
       <c r="F136" s="20" t="inlineStr">
@@ -17858,7 +17810,7 @@
         </is>
       </c>
       <c r="G136" s="22" t="n">
-        <v>61.1</v>
+        <v>64.5</v>
       </c>
       <c r="H136" s="10" t="n"/>
       <c r="I136" s="10" t="n"/>
@@ -17877,7 +17829,7 @@
       </c>
       <c r="M136" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT — plocha 2.NP = plocha podhledu (flat ceiling assumption)</t>
+          <t>DXF km_tabulka místností MTEXT — plocha 3.NP = plocha podhledu (flat ceiling assumption)</t>
         </is>
       </c>
       <c r="N136" s="20" t="inlineStr">
@@ -17904,17 +17856,17 @@
       </c>
       <c r="C137" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled — tmelení + úprava 3.NP</t>
+          <t>Keramický obklad koupelna 1.05 (1.NP)</t>
         </is>
       </c>
       <c r="D137" s="20" t="inlineStr">
         <is>
-          <t>612471141</t>
+          <t>781447001</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>SDK podhled + případné předstěny — tmelení spojů Q3 + povrchová úprava před výmalbou (3.NP)</t>
+          <t>Keramický obklad stěn koupelny 1.05 1.NP — výška obkladu 1.6 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="F137" s="20" t="inlineStr">
@@ -17923,17 +17875,17 @@
         </is>
       </c>
       <c r="G137" s="22" t="n">
-        <v>64.5</v>
+        <v>13.4</v>
       </c>
       <c r="H137" s="10" t="n"/>
       <c r="I137" s="10" t="n"/>
       <c r="J137" s="8" t="inlineStr">
         <is>
-          <t>sadrokartonar</t>
+          <t>obkladac</t>
         </is>
       </c>
       <c r="K137" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L137" s="20" t="inlineStr">
         <is>
@@ -17942,7 +17894,7 @@
       </c>
       <c r="M137" s="8" t="inlineStr">
         <is>
-          <t>DXF km_tabulka místností MTEXT — plocha 3.NP = plocha podhledu (flat ceiling assumption)</t>
+          <t>DXF rooms PIP perimeter 1.05 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
         </is>
       </c>
       <c r="N137" s="20" t="inlineStr">
@@ -17969,7 +17921,7 @@
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad koupelna 1.05 (1.NP)</t>
+          <t>Keramický obklad koupelna 2.03 (2.NP)</t>
         </is>
       </c>
       <c r="D138" s="20" t="inlineStr">
@@ -17979,7 +17931,7 @@
       </c>
       <c r="E138" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 1.05 1.NP — výška obkladu 1.6 m (z DXF km Obklady layer)</t>
+          <t>Keramický obklad stěn koupelny 2.03 2.NP — výška obkladu 2.45 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="F138" s="20" t="inlineStr">
@@ -17988,7 +17940,7 @@
         </is>
       </c>
       <c r="G138" s="22" t="n">
-        <v>13.4</v>
+        <v>15.2</v>
       </c>
       <c r="H138" s="10" t="n"/>
       <c r="I138" s="10" t="n"/>
@@ -18007,7 +17959,7 @@
       </c>
       <c r="M138" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms PIP perimeter 1.05 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
+          <t>DXF rooms PIP perimeter 2.03 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
         </is>
       </c>
       <c r="N138" s="20" t="inlineStr">
@@ -18034,7 +17986,7 @@
       </c>
       <c r="C139" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad koupelna 2.03 (2.NP)</t>
+          <t>Keramický obklad koupelna 3.04 (3.NP)</t>
         </is>
       </c>
       <c r="D139" s="20" t="inlineStr">
@@ -18044,7 +17996,7 @@
       </c>
       <c r="E139" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 2.03 2.NP — výška obkladu 2.45 m (z DXF km Obklady layer)</t>
+          <t>Keramický obklad stěn koupelny 3.04 3.NP — výška obkladu 2.7 m (z DXF km Obklady layer)</t>
         </is>
       </c>
       <c r="F139" s="20" t="inlineStr">
@@ -18053,7 +18005,7 @@
         </is>
       </c>
       <c r="G139" s="22" t="n">
-        <v>15.2</v>
+        <v>24.3</v>
       </c>
       <c r="H139" s="10" t="n"/>
       <c r="I139" s="10" t="n"/>
@@ -18072,7 +18024,7 @@
       </c>
       <c r="M139" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms PIP perimeter 2.03 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
+          <t>DXF rooms PIP perimeter 3.04 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
         </is>
       </c>
       <c r="N139" s="20" t="inlineStr">
@@ -18099,7 +18051,7 @@
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad koupelna 3.04 (3.NP)</t>
+          <t>Obklad za kuchyňskou linkou</t>
         </is>
       </c>
       <c r="D140" s="20" t="inlineStr">
@@ -18109,7 +18061,7 @@
       </c>
       <c r="E140" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad stěn koupelny 3.04 3.NP — výška obkladu 2.7 m (z DXF km Obklady layer)</t>
+          <t>Keramický obklad za kuchyňskou linkou nad pracovní deskou — 2 kuchyně × ~5 m² (1.06 byt rodičů + 3.05 byt 3.NP)</t>
         </is>
       </c>
       <c r="F140" s="20" t="inlineStr">
@@ -18118,7 +18070,7 @@
         </is>
       </c>
       <c r="G140" s="22" t="n">
-        <v>24.3</v>
+        <v>10</v>
       </c>
       <c r="H140" s="10" t="n"/>
       <c r="I140" s="10" t="n"/>
@@ -18128,7 +18080,7 @@
         </is>
       </c>
       <c r="K140" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L140" s="20" t="inlineStr">
         <is>
@@ -18137,7 +18089,7 @@
       </c>
       <c r="M140" s="8" t="inlineStr">
         <is>
-          <t>DXF rooms PIP perimeter 3.04 + DXF km Obklady layer (11 LWPOLYLINE markers s bbox heights 1600/2450/2610-2715 mm) — Path C Tier 1</t>
+          <t>DXF dum_DPZ 2× kuchyně MTEXT + TZ ARS</t>
         </is>
       </c>
       <c r="N140" s="20" t="inlineStr">
@@ -18164,17 +18116,17 @@
       </c>
       <c r="C141" s="8" t="inlineStr">
         <is>
-          <t>Obklad za kuchyňskou linkou</t>
+          <t>Interiérová výmalba</t>
         </is>
       </c>
       <c r="D141" s="20" t="inlineStr">
         <is>
-          <t>781447001</t>
+          <t>784121011</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
         <is>
-          <t>Keramický obklad za kuchyňskou linkou nad pracovní deskou — 2 kuchyně × ~5 m² (1.06 byt rodičů + 3.05 byt 3.NP)</t>
+          <t>Interiérová výmalba akrylátová bílá 2× — všechny stěny + podhledy mimo obklad</t>
         </is>
       </c>
       <c r="F141" s="20" t="inlineStr">
@@ -18183,17 +18135,17 @@
         </is>
       </c>
       <c r="G141" s="22" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H141" s="10" t="n"/>
       <c r="I141" s="10" t="n"/>
       <c r="J141" s="8" t="inlineStr">
         <is>
-          <t>obkladac</t>
+          <t>malir</t>
         </is>
       </c>
       <c r="K141" s="24" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L141" s="20" t="inlineStr">
         <is>
@@ -18202,7 +18154,7 @@
       </c>
       <c r="M141" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ 2× kuchyně MTEXT + TZ ARS</t>
+          <t>TZ ARS — interiérová výmalba (aggregate, no TZ per-room directive)</t>
         </is>
       </c>
       <c r="N141" s="20" t="inlineStr">
@@ -18216,7 +18168,11 @@
         </is>
       </c>
       <c r="P141" s="41" t="n"/>
-      <c r="Q141" s="41" t="n"/>
+      <c r="Q141" s="41" t="inlineStr">
+        <is>
+          <t>GAP_007_deprecated</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="20" t="n">
@@ -18229,7 +18185,7 @@
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba</t>
+          <t>Interiérová výmalba 1.NP</t>
         </is>
       </c>
       <c r="D142" s="20" t="inlineStr">
@@ -18239,7 +18195,7 @@
       </c>
       <c r="E142" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba akrylátová bílá 2× — všechny stěny + podhledy mimo obklad</t>
+          <t>Interiérová výmalba 1.NP — stěny + SDK podhled − obklad koupelny 1.05 (1.6 m výška)</t>
         </is>
       </c>
       <c r="F142" s="20" t="inlineStr">
@@ -18248,7 +18204,7 @@
         </is>
       </c>
       <c r="G142" s="22" t="n">
-        <v>0</v>
+        <v>254.5</v>
       </c>
       <c r="H142" s="10" t="n"/>
       <c r="I142" s="10" t="n"/>
@@ -18258,7 +18214,7 @@
         </is>
       </c>
       <c r="K142" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L142" s="20" t="inlineStr">
         <is>
@@ -18267,7 +18223,7 @@
       </c>
       <c r="M142" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS — interiérová výmalba (aggregate, no TZ per-room directive)</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.002 + SDK podhled PSV78.005</t>
         </is>
       </c>
       <c r="N142" s="20" t="inlineStr">
@@ -18283,7 +18239,7 @@
       <c r="P142" s="41" t="n"/>
       <c r="Q142" s="41" t="inlineStr">
         <is>
-          <t>GAP_007_deprecated</t>
+          <t>GAP_007</t>
         </is>
       </c>
     </row>
@@ -18298,7 +18254,7 @@
       </c>
       <c r="C143" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.NP</t>
+          <t>Interiérová výmalba 1.PP</t>
         </is>
       </c>
       <c r="D143" s="20" t="inlineStr">
@@ -18308,7 +18264,7 @@
       </c>
       <c r="E143" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.NP — stěny + SDK podhled − obklad koupelny 1.05 (1.6 m výška)</t>
+          <t>Interiérová výmalba 1.PP — sklep stěny + klenba bílá vápenná 2×</t>
         </is>
       </c>
       <c r="F143" s="20" t="inlineStr">
@@ -18317,7 +18273,7 @@
         </is>
       </c>
       <c r="G143" s="22" t="n">
-        <v>254.5</v>
+        <v>78.2</v>
       </c>
       <c r="H143" s="10" t="n"/>
       <c r="I143" s="10" t="n"/>
@@ -18336,7 +18292,7 @@
       </c>
       <c r="M143" s="8" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.002 + SDK podhled PSV78.005</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.001 + SDK podhled PSV78.—</t>
         </is>
       </c>
       <c r="N143" s="20" t="inlineStr">
@@ -18367,7 +18323,7 @@
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.PP</t>
+          <t>Interiérová výmalba 2.NP</t>
         </is>
       </c>
       <c r="D144" s="20" t="inlineStr">
@@ -18377,7 +18333,7 @@
       </c>
       <c r="E144" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 1.PP — sklep stěny + klenba bílá vápenná 2×</t>
+          <t>Interiérová výmalba 2.NP — stěny + SDK podhled − obklad koupelny 2.03 (2.45 m výška)</t>
         </is>
       </c>
       <c r="F144" s="20" t="inlineStr">
@@ -18386,7 +18342,7 @@
         </is>
       </c>
       <c r="G144" s="22" t="n">
-        <v>78.2</v>
+        <v>247.5</v>
       </c>
       <c r="H144" s="10" t="n"/>
       <c r="I144" s="10" t="n"/>
@@ -18405,7 +18361,7 @@
       </c>
       <c r="M144" s="8" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.001 + SDK podhled PSV78.—</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.003 + SDK podhled PSV78.006</t>
         </is>
       </c>
       <c r="N144" s="20" t="inlineStr">
@@ -18436,7 +18392,7 @@
       </c>
       <c r="C145" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 2.NP</t>
+          <t>Interiérová výmalba 3.NP</t>
         </is>
       </c>
       <c r="D145" s="20" t="inlineStr">
@@ -18446,7 +18402,7 @@
       </c>
       <c r="E145" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 2.NP — stěny + SDK podhled − obklad koupelny 2.03 (2.45 m výška)</t>
+          <t>Interiérová výmalba 3.NP — stěny + SDK podhled − obklad koupelny 3.04 (2.7 m výška)</t>
         </is>
       </c>
       <c r="F145" s="20" t="inlineStr">
@@ -18455,7 +18411,7 @@
         </is>
       </c>
       <c r="G145" s="22" t="n">
-        <v>247.5</v>
+        <v>219.3</v>
       </c>
       <c r="H145" s="10" t="n"/>
       <c r="I145" s="10" t="n"/>
@@ -18474,7 +18430,7 @@
       </c>
       <c r="M145" s="8" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.003 + SDK podhled PSV78.006</t>
+          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.004 + SDK podhled PSV78.007</t>
         </is>
       </c>
       <c r="N145" s="20" t="inlineStr">
@@ -18500,37 +18456,37 @@
       </c>
       <c r="B146" s="8" t="inlineStr">
         <is>
-          <t>PSV-78 Povrchové úpravy</t>
+          <t>PSV-95 Detekce požární</t>
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 3.NP</t>
+          <t>Autonomní hlásič kouře</t>
         </is>
       </c>
       <c r="D146" s="20" t="inlineStr">
         <is>
-          <t>784121011</t>
+          <t>375211101</t>
         </is>
       </c>
       <c r="E146" s="8" t="inlineStr">
         <is>
-          <t>Interiérová výmalba 3.NP — stěny + SDK podhled − obklad koupelny 3.04 (2.7 m výška)</t>
+          <t>Autonomní hlásič kouře dle ČSN EN 14604 — 4 ks v místnostech 1.01, 1.02, 2.04, 3.03 dle PBŘ</t>
         </is>
       </c>
       <c r="F146" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G146" s="22" t="n">
-        <v>219.3</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G146" s="23" t="n">
+        <v>4</v>
       </c>
       <c r="H146" s="10" t="n"/>
       <c r="I146" s="10" t="n"/>
       <c r="J146" s="8" t="inlineStr">
         <is>
-          <t>malir</t>
+          <t>elektroinstalater</t>
         </is>
       </c>
       <c r="K146" s="24" t="n">
@@ -18538,12 +18494,12 @@
       </c>
       <c r="L146" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M146" s="8" t="inlineStr">
         <is>
-          <t>Per-podlaží split z PSV78.012 (audit v2 GAP_007 fix); omítka PSV78.004 + SDK podhled PSV78.007</t>
+          <t>TZ PBŘ dům — ČSN EN 14604 autonomní hlásič kouře 4 ks</t>
         </is>
       </c>
       <c r="N146" s="20" t="inlineStr">
@@ -18559,7 +18515,7 @@
       <c r="P146" s="41" t="n"/>
       <c r="Q146" s="41" t="inlineStr">
         <is>
-          <t>GAP_007</t>
+          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
         </is>
       </c>
     </row>
@@ -18574,17 +18530,17 @@
       </c>
       <c r="C147" s="8" t="inlineStr">
         <is>
-          <t>Autonomní hlásič kouře</t>
+          <t>Přenosný hasicí přístroj 34A</t>
         </is>
       </c>
       <c r="D147" s="20" t="inlineStr">
         <is>
-          <t>375211101</t>
+          <t>966067121</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
         <is>
-          <t>Autonomní hlásič kouře dle ČSN EN 14604 — 4 ks v místnostech 1.01, 1.02, 2.04, 3.03 dle PBŘ</t>
+          <t>Přenosný hasicí přístroj 34A dle PBŘ — min. 1 ks na společné chodbě</t>
         </is>
       </c>
       <c r="F147" s="20" t="inlineStr">
@@ -18593,13 +18549,13 @@
         </is>
       </c>
       <c r="G147" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H147" s="10" t="n"/>
       <c r="I147" s="10" t="n"/>
       <c r="J147" s="8" t="inlineStr">
         <is>
-          <t>elektroinstalater</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K147" s="24" t="n">
@@ -18607,12 +18563,12 @@
       </c>
       <c r="L147" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M147" s="8" t="inlineStr">
         <is>
-          <t>TZ PBŘ dům — ČSN EN 14604 autonomní hlásič kouře 4 ks</t>
+          <t>TZ PBŘ dům — PHP 34A 1 ks minimum</t>
         </is>
       </c>
       <c r="N147" s="20" t="inlineStr">
@@ -18626,11 +18582,7 @@
         </is>
       </c>
       <c r="P147" s="41" t="n"/>
-      <c r="Q147" s="41" t="inlineStr">
-        <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
-        </is>
-      </c>
+      <c r="Q147" s="41" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="20" t="n">
@@ -18643,22 +18595,22 @@
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>Přenosný hasicí přístroj 34A</t>
+          <t>Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
         </is>
       </c>
       <c r="D148" s="20" t="inlineStr">
         <is>
-          <t>966067121</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E148" s="8" t="inlineStr">
         <is>
-          <t>Přenosný hasicí přístroj 34A dle PBŘ — min. 1 ks na společné chodbě</t>
+          <t>Předávací protokol krbu na tuhá paliva + kontrola bezpečných vzdáleností (800 mm směr sálání / 400 mm strany, nehořlavá zóna podlahy) dle PBŘ</t>
         </is>
       </c>
       <c r="F148" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>soubor</t>
         </is>
       </c>
       <c r="G148" s="23" t="n">
@@ -18668,11 +18620,11 @@
       <c r="I148" s="10" t="n"/>
       <c r="J148" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>topenar</t>
         </is>
       </c>
       <c r="K148" s="24" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="L148" s="20" t="inlineStr">
         <is>
@@ -18681,7 +18633,7 @@
       </c>
       <c r="M148" s="8" t="inlineStr">
         <is>
-          <t>TZ PBŘ dům — PHP 34A 1 ks minimum</t>
+          <t>PBŘ D.3</t>
         </is>
       </c>
       <c r="N148" s="20" t="inlineStr">
@@ -18694,8 +18646,12 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P148" s="41" t="n"/>
-      <c r="Q148" s="41" t="n"/>
+      <c r="P148" s="41" t="inlineStr"/>
+      <c r="Q148" s="41" t="inlineStr">
+        <is>
+          <t>DODATEK_PBR_GAPS_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="20" t="n">
@@ -18703,27 +18659,27 @@
       </c>
       <c r="B149" s="8" t="inlineStr">
         <is>
-          <t>PSV-95 Detekce požární</t>
+          <t>M-21 ELI silnoproud</t>
         </is>
       </c>
       <c r="C149" s="8" t="inlineStr">
         <is>
-          <t>Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
+          <t>Demontáž stávající ELI</t>
         </is>
       </c>
       <c r="D149" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>210010011</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
         <is>
-          <t>Předávací protokol krbu na tuhá paliva + kontrola bezpečných vzdáleností (800 mm směr sálání / 400 mm strany, nehořlavá zóna podlahy) dle PBŘ</t>
+          <t>Demontáž stávající elektroinstalace v celém domě (vodiče, rozvaděč, zásuvky, svítidla) — recyklace mědi</t>
         </is>
       </c>
       <c r="F149" s="20" t="inlineStr">
         <is>
-          <t>soubor</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G149" s="23" t="n">
@@ -18733,11 +18689,11 @@
       <c r="I149" s="10" t="n"/>
       <c r="J149" s="8" t="inlineStr">
         <is>
-          <t>topenar</t>
+          <t>elektroinstalater</t>
         </is>
       </c>
       <c r="K149" s="24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L149" s="20" t="inlineStr">
         <is>
@@ -18746,12 +18702,12 @@
       </c>
       <c r="M149" s="8" t="inlineStr">
         <is>
-          <t>PBŘ D.3</t>
+          <t>TZ ARS dům §4 — kompletně nová ELI</t>
         </is>
       </c>
       <c r="N149" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#7</t>
         </is>
       </c>
       <c r="O149" s="26" t="inlineStr">
@@ -18759,12 +18715,8 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P149" s="41" t="inlineStr"/>
-      <c r="Q149" s="41" t="inlineStr">
-        <is>
-          <t>DODATEK_PBR_GAPS_2026-06-01</t>
-        </is>
-      </c>
+      <c r="P149" s="41" t="n"/>
+      <c r="Q149" s="41" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="20" t="n">
@@ -18777,26 +18729,26 @@
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávající ELI</t>
+          <t>Pojistková skříň + 3× podružný rozvaděč</t>
         </is>
       </c>
       <c r="D150" s="20" t="inlineStr">
         <is>
-          <t>210010011</t>
+          <t>210110023</t>
         </is>
       </c>
       <c r="E150" s="8" t="inlineStr">
         <is>
-          <t>Demontáž stávající elektroinstalace v celém domě (vodiče, rozvaděč, zásuvky, svítidla) — recyklace mědi</t>
+          <t>Nová pojistková skříň + 3× podružný rozvaděč pro každé patro (1.NP, 2.NP, 3.NP) s podružným měřením</t>
         </is>
       </c>
       <c r="F150" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G150" s="23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H150" s="10" t="n"/>
       <c r="I150" s="10" t="n"/>
@@ -18815,7 +18767,7 @@
       </c>
       <c r="M150" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — kompletně nová ELI</t>
+          <t>TZ ARS dům §4 — 'nová pojistková skříň s podružným měřením pro každé patro'</t>
         </is>
       </c>
       <c r="N150" s="20" t="inlineStr">
@@ -18842,26 +18794,26 @@
       </c>
       <c r="C151" s="8" t="inlineStr">
         <is>
-          <t>Pojistková skříň + 3× podružný rozvaděč</t>
+          <t>Rozvody silnoproud</t>
         </is>
       </c>
       <c r="D151" s="20" t="inlineStr">
         <is>
-          <t>210110023</t>
+          <t>210800012</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t>Nová pojistková skříň + 3× podružný rozvaděč pro každé patro (1.NP, 2.NP, 3.NP) s podružným měřením</t>
+          <t>Nové silnoproudé rozvody — vodiče CYKY 3×1.5 / 3×2.5 / 5×2.5 / 5×6 + krabice + instalační trubky</t>
         </is>
       </c>
       <c r="F151" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G151" s="23" t="n">
-        <v>4</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G151" s="22" t="n">
+        <v>700</v>
       </c>
       <c r="H151" s="10" t="n"/>
       <c r="I151" s="10" t="n"/>
@@ -18871,7 +18823,7 @@
         </is>
       </c>
       <c r="K151" s="24" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="L151" s="20" t="inlineStr">
         <is>
@@ -18880,7 +18832,7 @@
       </c>
       <c r="M151" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — 'nová pojistková skříň s podružným měřením pro každé patro'</t>
+          <t>TZ ARS + B4_productivity standard RD 3-byt. dispozice</t>
         </is>
       </c>
       <c r="N151" s="20" t="inlineStr">
@@ -18907,26 +18859,26 @@
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>Rozvody silnoproud</t>
+          <t>Zásuvky a vypínače</t>
         </is>
       </c>
       <c r="D152" s="20" t="inlineStr">
         <is>
-          <t>210800012</t>
+          <t>210810050</t>
         </is>
       </c>
       <c r="E152" s="8" t="inlineStr">
         <is>
-          <t>Nové silnoproudé rozvody — vodiče CYKY 3×1.5 / 3×2.5 / 5×2.5 / 5×6 + krabice + instalační trubky</t>
+          <t>Zásuvky a vypínače dodávka + montáž — ~70 ks (60-80 dle vyjasnění #7)</t>
         </is>
       </c>
       <c r="F152" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G152" s="22" t="n">
-        <v>700</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G152" s="23" t="n">
+        <v>70</v>
       </c>
       <c r="H152" s="10" t="n"/>
       <c r="I152" s="10" t="n"/>
@@ -18945,7 +18897,7 @@
       </c>
       <c r="M152" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD 3-byt. dispozice</t>
+          <t>TZ ARS + B4_productivity standard RD 220 m² 3-byt.</t>
         </is>
       </c>
       <c r="N152" s="20" t="inlineStr">
@@ -18972,17 +18924,17 @@
       </c>
       <c r="C153" s="8" t="inlineStr">
         <is>
-          <t>Zásuvky a vypínače</t>
+          <t>Svítidla</t>
         </is>
       </c>
       <c r="D153" s="20" t="inlineStr">
         <is>
-          <t>210810050</t>
+          <t>210820002</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
         <is>
-          <t>Zásuvky a vypínače dodávka + montáž — ~70 ks (60-80 dle vyjasnění #7)</t>
+          <t>Svítidla dodávka + montáž — ~35 ks (30-40 dle vyjasnění #7) interiér + venkovní u vstupů</t>
         </is>
       </c>
       <c r="F153" s="20" t="inlineStr">
@@ -18991,7 +18943,7 @@
         </is>
       </c>
       <c r="G153" s="23" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="H153" s="10" t="n"/>
       <c r="I153" s="10" t="n"/>
@@ -19010,7 +18962,7 @@
       </c>
       <c r="M153" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD 220 m² 3-byt.</t>
+          <t>TZ ARS + B4_productivity standard RD</t>
         </is>
       </c>
       <c r="N153" s="20" t="inlineStr">
@@ -19037,26 +18989,26 @@
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>Svítidla</t>
+          <t>Příprava FVE</t>
         </is>
       </c>
       <c r="D154" s="20" t="inlineStr">
         <is>
-          <t>210820002</t>
+          <t>210800099</t>
         </is>
       </c>
       <c r="E154" s="8" t="inlineStr">
         <is>
-          <t>Svítidla dodávka + montáž — ~35 ks (30-40 dle vyjasnění #7) interiér + venkovní u vstupů</t>
+          <t>Příprava na osazení FVE — rezerva v rozvaděči (jistič + zásuvka pro střídač) + trasy do střechy</t>
         </is>
       </c>
       <c r="F154" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G154" s="23" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="H154" s="10" t="n"/>
       <c r="I154" s="10" t="n"/>
@@ -19066,7 +19018,7 @@
         </is>
       </c>
       <c r="K154" s="24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L154" s="20" t="inlineStr">
         <is>
@@ -19075,7 +19027,7 @@
       </c>
       <c r="M154" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS + B4_productivity standard RD</t>
+          <t>TZ ARS dům §4 — FVE příprava (bez panelů samotných)</t>
         </is>
       </c>
       <c r="N154" s="20" t="inlineStr">
@@ -19102,17 +19054,17 @@
       </c>
       <c r="C155" s="8" t="inlineStr">
         <is>
-          <t>Příprava FVE</t>
+          <t>Revize ELI při kolaudaci</t>
         </is>
       </c>
       <c r="D155" s="20" t="inlineStr">
         <is>
-          <t>210800099</t>
+          <t>996019011</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
         <is>
-          <t>Příprava na osazení FVE — rezerva v rozvaděči (jistič + zásuvka pro střídač) + trasy do střechy</t>
+          <t>Výchozí revize elektrické instalace dle ČSN 33 2000-6 + revizní zpráva pro kolaudaci</t>
         </is>
       </c>
       <c r="F155" s="20" t="inlineStr">
@@ -19127,11 +19079,11 @@
       <c r="I155" s="10" t="n"/>
       <c r="J155" s="8" t="inlineStr">
         <is>
-          <t>elektroinstalater</t>
+          <t>revize_specialista</t>
         </is>
       </c>
       <c r="K155" s="24" t="n">
-        <v>0.85</v>
+        <v>0.99</v>
       </c>
       <c r="L155" s="20" t="inlineStr">
         <is>
@@ -19140,12 +19092,12 @@
       </c>
       <c r="M155" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — FVE příprava (bez panelů samotných)</t>
+          <t>Povinná revize ELI dle ČSN 33 2000-6 + kolaudace</t>
         </is>
       </c>
       <c r="N155" s="20" t="inlineStr">
         <is>
-          <t>#7</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O155" s="26" t="inlineStr">
@@ -19162,22 +19114,22 @@
       </c>
       <c r="B156" s="8" t="inlineStr">
         <is>
-          <t>M-21 ELI silnoproud</t>
+          <t>PSV-72 ZTI</t>
         </is>
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>Revize ELI při kolaudaci</t>
+          <t>Revize stávajících přípojek</t>
         </is>
       </c>
       <c r="D156" s="20" t="inlineStr">
         <is>
-          <t>996019011</t>
+          <t>722290515</t>
         </is>
       </c>
       <c r="E156" s="8" t="inlineStr">
         <is>
-          <t>Výchozí revize elektrické instalace dle ČSN 33 2000-6 + revizní zpráva pro kolaudaci</t>
+          <t>Revize stávajícího napojení vodovodu + kanalizace na pozemku — kontrola stavu, čištění, tlaková zkouška</t>
         </is>
       </c>
       <c r="F156" s="20" t="inlineStr">
@@ -19192,25 +19144,25 @@
       <c r="I156" s="10" t="n"/>
       <c r="J156" s="8" t="inlineStr">
         <is>
-          <t>revize_specialista</t>
+          <t>vodar</t>
         </is>
       </c>
       <c r="K156" s="24" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="L156" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M156" s="8" t="inlineStr">
         <is>
-          <t>Povinná revize ELI dle ČSN 33 2000-6 + kolaudace</t>
+          <t>TZ ARS dům §4 — vodovod + kanalizace stávající, bez změny</t>
         </is>
       </c>
       <c r="N156" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O156" s="26" t="inlineStr">
@@ -19219,7 +19171,11 @@
         </is>
       </c>
       <c r="P156" s="41" t="n"/>
-      <c r="Q156" s="41" t="n"/>
+      <c r="Q156" s="41" t="inlineStr">
+        <is>
+          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="20" t="n">
@@ -19232,26 +19188,26 @@
       </c>
       <c r="C157" s="8" t="inlineStr">
         <is>
-          <t>Revize stávajících přípojek</t>
+          <t>Nové rozvody vody do 3.NP</t>
         </is>
       </c>
       <c r="D157" s="20" t="inlineStr">
         <is>
-          <t>722290515</t>
+          <t>722172011</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
         <is>
-          <t>Revize stávajícího napojení vodovodu + kanalizace na pozemku — kontrola stavu, čištění, tlaková zkouška</t>
+          <t>Nové rozvody studené + teplé vody do koupelen 1.NP + 2.NP + 3.NP a kuchyní (PEX/Cu, dimenze DN15-25)</t>
         </is>
       </c>
       <c r="F157" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G157" s="23" t="n">
-        <v>1</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G157" s="22" t="n">
+        <v>80</v>
       </c>
       <c r="H157" s="10" t="n"/>
       <c r="I157" s="10" t="n"/>
@@ -19261,7 +19217,7 @@
         </is>
       </c>
       <c r="K157" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L157" s="20" t="inlineStr">
         <is>
@@ -19270,7 +19226,7 @@
       </c>
       <c r="M157" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — vodovod + kanalizace stávající, bez změny</t>
+          <t>TZ ARS dům §4 — nové koupelny + kuchyně, vyjasnění #6 working assumption</t>
         </is>
       </c>
       <c r="N157" s="20" t="inlineStr">
@@ -19301,17 +19257,17 @@
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>Nové rozvody vody do 3.NP</t>
+          <t>Nové odpadní rozvody</t>
         </is>
       </c>
       <c r="D158" s="20" t="inlineStr">
         <is>
-          <t>722172011</t>
+          <t>721174021</t>
         </is>
       </c>
       <c r="E158" s="8" t="inlineStr">
         <is>
-          <t>Nové rozvody studené + teplé vody do koupelen 1.NP + 2.NP + 3.NP a kuchyní (PEX/Cu, dimenze DN15-25)</t>
+          <t>Nové odpadní rozvody PVC-HT DN40-DN110 ke koupelnám 1.NP, 2.NP, 3.NP a kuchyním + napojení na stávající</t>
         </is>
       </c>
       <c r="F158" s="20" t="inlineStr">
@@ -19320,7 +19276,7 @@
         </is>
       </c>
       <c r="G158" s="22" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H158" s="10" t="n"/>
       <c r="I158" s="10" t="n"/>
@@ -19334,12 +19290,12 @@
       </c>
       <c r="L158" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M158" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — nové koupelny + kuchyně, vyjasnění #6 working assumption</t>
+          <t>TZ ARS dům §4 — nové koupelny + kuchyně, odpad do stávající kanalizace</t>
         </is>
       </c>
       <c r="N158" s="20" t="inlineStr">
@@ -19353,11 +19309,7 @@
         </is>
       </c>
       <c r="P158" s="41" t="n"/>
-      <c r="Q158" s="41" t="inlineStr">
-        <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
-        </is>
-      </c>
+      <c r="Q158" s="41" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="20" t="n">
@@ -19370,26 +19322,26 @@
       </c>
       <c r="C159" s="8" t="inlineStr">
         <is>
-          <t>Nové odpadní rozvody</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP)</t>
         </is>
       </c>
       <c r="D159" s="20" t="inlineStr">
         <is>
-          <t>721174021</t>
+          <t>725291131</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
         <is>
-          <t>Nové odpadní rozvody PVC-HT DN40-DN110 ke koupelnám 1.NP, 2.NP, 3.NP a kuchyním + napojení na stávající</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 1.05 1.NP: 1× vana (DXF) + 1× umyvadlo (DXF) + 1× WC (TZ standard)</t>
         </is>
       </c>
       <c r="F159" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>set</t>
         </is>
       </c>
       <c r="G159" s="22" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H159" s="10" t="n"/>
       <c r="I159" s="10" t="n"/>
@@ -19408,7 +19360,7 @@
       </c>
       <c r="M159" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — nové koupelny + kuchyně, odpad do stávající kanalizace</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 1.05 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="N159" s="20" t="inlineStr">
@@ -19422,7 +19374,11 @@
         </is>
       </c>
       <c r="P159" s="41" t="n"/>
-      <c r="Q159" s="41" t="n"/>
+      <c r="Q159" s="41" t="inlineStr">
+        <is>
+          <t>GAP_005_deprecated</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="20" t="n">
@@ -19435,26 +19391,26 @@
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP)</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture A</t>
         </is>
       </c>
       <c r="D160" s="20" t="inlineStr">
         <is>
-          <t>725291131</t>
+          <t>725211101</t>
         </is>
       </c>
       <c r="E160" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 1.05 1.NP: 1× vana (DXF) + 1× umyvadlo (DXF) + 1× WC (TZ standard)</t>
+          <t>Vana koupelnová obdélníková 170×70 cm — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="F160" s="20" t="inlineStr">
         <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="G160" s="22" t="n">
-        <v>0</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G160" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H160" s="10" t="n"/>
       <c r="I160" s="10" t="n"/>
@@ -19464,7 +19420,7 @@
         </is>
       </c>
       <c r="K160" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L160" s="20" t="inlineStr">
         <is>
@@ -19473,12 +19429,12 @@
       </c>
       <c r="M160" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 1.05 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>DXF dum_DPZ MTEXT room 1.05 1.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="N160" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O160" s="26" t="inlineStr">
@@ -19489,7 +19445,7 @@
       <c r="P160" s="41" t="n"/>
       <c r="Q160" s="41" t="inlineStr">
         <is>
-          <t>GAP_005_deprecated</t>
+          <t>GAP_005</t>
         </is>
       </c>
     </row>
@@ -19504,17 +19460,17 @@
       </c>
       <c r="C161" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture A</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture B</t>
         </is>
       </c>
       <c r="D161" s="20" t="inlineStr">
         <is>
-          <t>725211101</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
         <is>
-          <t>Vana koupelnová obdélníková 170×70 cm — koupelna 1.05 1.NP</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="F161" s="20" t="inlineStr">
@@ -19573,17 +19529,17 @@
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture B</t>
+          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture C</t>
         </is>
       </c>
       <c r="D162" s="20" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="E162" s="8" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 1.05 1.NP</t>
+          <t>WC kombi keramické bílé — koupelna 1.05 1.NP</t>
         </is>
       </c>
       <c r="F162" s="20" t="inlineStr">
@@ -19642,26 +19598,26 @@
       </c>
       <c r="C163" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 1.05 (1.NP) / fixture C</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP)</t>
         </is>
       </c>
       <c r="D163" s="20" t="inlineStr">
         <is>
-          <t>725111101</t>
+          <t>725291131</t>
         </is>
       </c>
       <c r="E163" s="8" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 1.05 1.NP</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 2.03 2.NP: 1× umyvadlo (DXF) + 1× WC (TZ standard) + 1× sprcha (TZ standard)</t>
         </is>
       </c>
       <c r="F163" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G163" s="23" t="n">
-        <v>1</v>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="G163" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H163" s="10" t="n"/>
       <c r="I163" s="10" t="n"/>
@@ -19671,7 +19627,7 @@
         </is>
       </c>
       <c r="K163" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L163" s="20" t="inlineStr">
         <is>
@@ -19680,12 +19636,12 @@
       </c>
       <c r="M163" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 1.05 1.NP + TZ ARS koupelna kompletace</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 2.03 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="N163" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O163" s="26" t="inlineStr">
@@ -19696,7 +19652,7 @@
       <c r="P163" s="41" t="n"/>
       <c r="Q163" s="41" t="inlineStr">
         <is>
-          <t>GAP_005</t>
+          <t>GAP_005_deprecated</t>
         </is>
       </c>
     </row>
@@ -19711,26 +19667,26 @@
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP)</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture A</t>
         </is>
       </c>
       <c r="D164" s="20" t="inlineStr">
         <is>
-          <t>725291131</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="E164" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 2.03 2.NP: 1× umyvadlo (DXF) + 1× WC (TZ standard) + 1× sprcha (TZ standard)</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="F164" s="20" t="inlineStr">
         <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="G164" s="22" t="n">
-        <v>0</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G164" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H164" s="10" t="n"/>
       <c r="I164" s="10" t="n"/>
@@ -19740,7 +19696,7 @@
         </is>
       </c>
       <c r="K164" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L164" s="20" t="inlineStr">
         <is>
@@ -19749,12 +19705,12 @@
       </c>
       <c r="M164" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 2.03 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>DXF dum_DPZ MTEXT room 2.03 2.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="N164" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O164" s="26" t="inlineStr">
@@ -19765,7 +19721,7 @@
       <c r="P164" s="41" t="n"/>
       <c r="Q164" s="41" t="inlineStr">
         <is>
-          <t>GAP_005_deprecated</t>
+          <t>GAP_005</t>
         </is>
       </c>
     </row>
@@ -19780,17 +19736,17 @@
       </c>
       <c r="C165" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture A</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture B</t>
         </is>
       </c>
       <c r="D165" s="20" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725221201</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 2.03 2.NP</t>
+          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="F165" s="20" t="inlineStr">
@@ -19849,17 +19805,17 @@
       </c>
       <c r="C166" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture B</t>
+          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture C</t>
         </is>
       </c>
       <c r="D166" s="20" t="inlineStr">
         <is>
-          <t>725221201</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="E166" s="8" t="inlineStr">
         <is>
-          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 2.03 2.NP</t>
+          <t>WC kombi keramické bílé — koupelna 2.03 2.NP</t>
         </is>
       </c>
       <c r="F166" s="20" t="inlineStr">
@@ -19918,26 +19874,26 @@
       </c>
       <c r="C167" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 2.03 (2.NP) / fixture C</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP)</t>
         </is>
       </c>
       <c r="D167" s="20" t="inlineStr">
         <is>
-          <t>725111101</t>
+          <t>725291131</t>
         </is>
       </c>
       <c r="E167" s="8" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 2.03 2.NP</t>
+          <t>Sanitární keramika dodávka + montáž v koupelně 3.04 3.NP: 1× WC (DXF) + 1× umyvadlo (TZ standard) + 1× sprcha (TZ standard)</t>
         </is>
       </c>
       <c r="F167" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G167" s="23" t="n">
-        <v>1</v>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="G167" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H167" s="10" t="n"/>
       <c r="I167" s="10" t="n"/>
@@ -19947,7 +19903,7 @@
         </is>
       </c>
       <c r="K167" s="24" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L167" s="20" t="inlineStr">
         <is>
@@ -19956,12 +19912,12 @@
       </c>
       <c r="M167" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 2.03 2.NP + TZ ARS koupelna kompletace</t>
+          <t>DXF dum_DPZ INSERT positions PIP do room 3.04 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
         </is>
       </c>
       <c r="N167" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O167" s="26" t="inlineStr">
@@ -19972,7 +19928,7 @@
       <c r="P167" s="41" t="n"/>
       <c r="Q167" s="41" t="inlineStr">
         <is>
-          <t>GAP_005</t>
+          <t>GAP_005_deprecated</t>
         </is>
       </c>
     </row>
@@ -19987,26 +19943,26 @@
       </c>
       <c r="C168" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP)</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture A</t>
         </is>
       </c>
       <c r="D168" s="20" t="inlineStr">
         <is>
-          <t>725291131</t>
+          <t>725111101</t>
         </is>
       </c>
       <c r="E168" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika dodávka + montáž v koupelně 3.04 3.NP: 1× WC (DXF) + 1× umyvadlo (TZ standard) + 1× sprcha (TZ standard)</t>
+          <t>WC kombi keramické bílé — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="F168" s="20" t="inlineStr">
         <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="G168" s="22" t="n">
-        <v>0</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G168" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H168" s="10" t="n"/>
       <c r="I168" s="10" t="n"/>
@@ -20016,7 +19972,7 @@
         </is>
       </c>
       <c r="K168" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L168" s="20" t="inlineStr">
         <is>
@@ -20025,12 +19981,12 @@
       </c>
       <c r="M168" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ INSERT positions PIP do room 3.04 polygon (partial — 4/13 fixtures matched celkem) + TZ ARS § koupelny standard pattern</t>
+          <t>DXF dum_DPZ MTEXT room 3.04 3.NP + TZ ARS koupelna kompletace</t>
         </is>
       </c>
       <c r="N168" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O168" s="26" t="inlineStr">
@@ -20041,7 +19997,7 @@
       <c r="P168" s="41" t="n"/>
       <c r="Q168" s="41" t="inlineStr">
         <is>
-          <t>GAP_005_deprecated</t>
+          <t>GAP_005</t>
         </is>
       </c>
     </row>
@@ -20056,17 +20012,17 @@
       </c>
       <c r="C169" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture A</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture B</t>
         </is>
       </c>
       <c r="D169" s="20" t="inlineStr">
         <is>
-          <t>725111101</t>
+          <t>725311111</t>
         </is>
       </c>
       <c r="E169" s="8" t="inlineStr">
         <is>
-          <t>WC kombi keramické bílé — koupelna 3.04 3.NP</t>
+          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="F169" s="20" t="inlineStr">
@@ -20125,17 +20081,17 @@
       </c>
       <c r="C170" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture B</t>
+          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture C</t>
         </is>
       </c>
       <c r="D170" s="20" t="inlineStr">
         <is>
-          <t>725311111</t>
+          <t>725221201</t>
         </is>
       </c>
       <c r="E170" s="8" t="inlineStr">
         <is>
-          <t>Umyvadlo bílé keramické se sloupcem 60 cm — koupelna 3.04 3.NP</t>
+          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 3.04 3.NP</t>
         </is>
       </c>
       <c r="F170" s="20" t="inlineStr">
@@ -20194,17 +20150,17 @@
       </c>
       <c r="C171" s="8" t="inlineStr">
         <is>
-          <t>Sanitární keramika koupelna 3.04 (3.NP) / fixture C</t>
+          <t>Kuchyňský dřez 2 ks (1.06 + 3.05)</t>
         </is>
       </c>
       <c r="D171" s="20" t="inlineStr">
         <is>
-          <t>725221201</t>
+          <t>725840111</t>
         </is>
       </c>
       <c r="E171" s="8" t="inlineStr">
         <is>
-          <t>Sprchový kout 90×90 cm vč. vaničky + skleněných dveří — koupelna 3.04 3.NP</t>
+          <t>Kuchyňský dřez nerez + montáž — 2 ks (kuchyně 1.06 byt rodičů + kuchyně 3.05 byt 3.NP)</t>
         </is>
       </c>
       <c r="F171" s="20" t="inlineStr">
@@ -20213,7 +20169,7 @@
         </is>
       </c>
       <c r="G171" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H171" s="10" t="n"/>
       <c r="I171" s="10" t="n"/>
@@ -20223,7 +20179,7 @@
         </is>
       </c>
       <c r="K171" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L171" s="20" t="inlineStr">
         <is>
@@ -20232,12 +20188,12 @@
       </c>
       <c r="M171" s="8" t="inlineStr">
         <is>
-          <t>DXF dum_DPZ MTEXT room 3.04 3.NP + TZ ARS koupelna kompletace</t>
+          <t>DXF kuchyně MTEXT 2× + TZ ARS — dispozice byty</t>
         </is>
       </c>
       <c r="N171" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O171" s="26" t="inlineStr">
@@ -20246,11 +20202,7 @@
         </is>
       </c>
       <c r="P171" s="41" t="n"/>
-      <c r="Q171" s="41" t="inlineStr">
-        <is>
-          <t>GAP_005</t>
-        </is>
-      </c>
+      <c r="Q171" s="41" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="20" t="n">
@@ -20263,17 +20215,17 @@
       </c>
       <c r="C172" s="8" t="inlineStr">
         <is>
-          <t>Kuchyňský dřez 2 ks (1.06 + 3.05)</t>
+          <t>Vodovodní baterie + drobnosti</t>
         </is>
       </c>
       <c r="D172" s="20" t="inlineStr">
         <is>
-          <t>725840111</t>
+          <t>725822611</t>
         </is>
       </c>
       <c r="E172" s="8" t="inlineStr">
         <is>
-          <t>Kuchyňský dřez nerez + montáž — 2 ks (kuchyně 1.06 byt rodičů + kuchyně 3.05 byt 3.NP)</t>
+          <t>Vodovodní baterie (WC ventil + páková umyvadlová + sprchové + dřezové + termostat sprchové) — ~15 ks + drobné instalační materiály</t>
         </is>
       </c>
       <c r="F172" s="20" t="inlineStr">
@@ -20282,7 +20234,7 @@
         </is>
       </c>
       <c r="G172" s="23" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H172" s="10" t="n"/>
       <c r="I172" s="10" t="n"/>
@@ -20292,7 +20244,7 @@
         </is>
       </c>
       <c r="K172" s="24" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="L172" s="20" t="inlineStr">
         <is>
@@ -20301,7 +20253,7 @@
       </c>
       <c r="M172" s="8" t="inlineStr">
         <is>
-          <t>DXF kuchyně MTEXT 2× + TZ ARS — dispozice byty</t>
+          <t>TZ ARS — kompletní baterie nové</t>
         </is>
       </c>
       <c r="N172" s="20" t="inlineStr">
@@ -20328,17 +20280,17 @@
       </c>
       <c r="C173" s="8" t="inlineStr">
         <is>
-          <t>Vodovodní baterie + drobnosti</t>
+          <t>Akumulační zásobník TUV v suterénu</t>
         </is>
       </c>
       <c r="D173" s="20" t="inlineStr">
         <is>
-          <t>725822611</t>
+          <t>732419411</t>
         </is>
       </c>
       <c r="E173" s="8" t="inlineStr">
         <is>
-          <t>Vodovodní baterie (WC ventil + páková umyvadlová + sprchové + dřezové + termostat sprchové) — ~15 ks + drobné instalační materiály</t>
+          <t>Akumulační zásobník TUV ~300 l v 1.PP napojený na topný systém (sporáková kamna + krb + elektrokotel) — nepřímotop</t>
         </is>
       </c>
       <c r="F173" s="20" t="inlineStr">
@@ -20347,17 +20299,17 @@
         </is>
       </c>
       <c r="G173" s="23" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H173" s="10" t="n"/>
       <c r="I173" s="10" t="n"/>
       <c r="J173" s="8" t="inlineStr">
         <is>
-          <t>vodar</t>
+          <t>instalater_TUV_akumulacni_zasobnik</t>
         </is>
       </c>
       <c r="K173" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L173" s="20" t="inlineStr">
         <is>
@@ -20366,7 +20318,7 @@
       </c>
       <c r="M173" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS — kompletní baterie nové</t>
+          <t>TZ ARS dům §4 — kombi akumulační zásobník napojený na multivariantní topný systém</t>
         </is>
       </c>
       <c r="N173" s="20" t="inlineStr">
@@ -20393,17 +20345,17 @@
       </c>
       <c r="C174" s="8" t="inlineStr">
         <is>
-          <t>Akumulační zásobník TUV v suterénu</t>
+          <t>Elektrický bojler 3.NP</t>
         </is>
       </c>
       <c r="D174" s="20" t="inlineStr">
         <is>
-          <t>732419411</t>
+          <t>732429211</t>
         </is>
       </c>
       <c r="E174" s="8" t="inlineStr">
         <is>
-          <t>Akumulační zásobník TUV ~300 l v 1.PP napojený na topný systém (sporáková kamna + krb + elektrokotel) — nepřímotop</t>
+          <t>Elektrický bojler ~80 l v koupelně 3.NP (nezávislý zdroj pro samostatný byt)</t>
         </is>
       </c>
       <c r="F174" s="20" t="inlineStr">
@@ -20418,7 +20370,7 @@
       <c r="I174" s="10" t="n"/>
       <c r="J174" s="8" t="inlineStr">
         <is>
-          <t>instalater_TUV_akumulacni_zasobnik</t>
+          <t>vodar</t>
         </is>
       </c>
       <c r="K174" s="24" t="n">
@@ -20431,7 +20383,7 @@
       </c>
       <c r="M174" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — kombi akumulační zásobník napojený na multivariantní topný systém</t>
+          <t>TZ ARS dům §4 — elektrický bojler v 3.NP koupelně, vyjasnění #6 odhad 80 l</t>
         </is>
       </c>
       <c r="N174" s="20" t="inlineStr">
@@ -20453,22 +20405,22 @@
       </c>
       <c r="B175" s="8" t="inlineStr">
         <is>
-          <t>PSV-72 ZTI</t>
+          <t>PSV-73 Vytápění</t>
         </is>
       </c>
       <c r="C175" s="8" t="inlineStr">
         <is>
-          <t>Elektrický bojler 3.NP</t>
+          <t>Sporáková kamna na tuhá paliva</t>
         </is>
       </c>
       <c r="D175" s="20" t="inlineStr">
         <is>
-          <t>732429211</t>
+          <t>733241011</t>
         </is>
       </c>
       <c r="E175" s="8" t="inlineStr">
         <is>
-          <t>Elektrický bojler ~80 l v koupelně 3.NP (nezávislý zdroj pro samostatný byt)</t>
+          <t>Sporáková kamna na tuhá paliva ~10 kW s akumulačním zásobníkem TUV — dodávka</t>
         </is>
       </c>
       <c r="F175" s="20" t="inlineStr">
@@ -20483,7 +20435,7 @@
       <c r="I175" s="10" t="n"/>
       <c r="J175" s="8" t="inlineStr">
         <is>
-          <t>vodar</t>
+          <t>topenar</t>
         </is>
       </c>
       <c r="K175" s="24" t="n">
@@ -20496,7 +20448,7 @@
       </c>
       <c r="M175" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — elektrický bojler v 3.NP koupelně, vyjasnění #6 odhad 80 l</t>
+          <t>TZ ARS dům §4 — primární zdroj 1.NP/2.NP, ~10 kW odhad standard RD</t>
         </is>
       </c>
       <c r="N175" s="20" t="inlineStr">
@@ -20523,22 +20475,22 @@
       </c>
       <c r="C176" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna na tuhá paliva</t>
+          <t>Sporáková kamna — montáž</t>
         </is>
       </c>
       <c r="D176" s="20" t="inlineStr">
         <is>
-          <t>733241011</t>
+          <t>733281011</t>
         </is>
       </c>
       <c r="E176" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna na tuhá paliva ~10 kW s akumulačním zásobníkem TUV — dodávka</t>
+          <t>Sporáková kamna — montáž vč. napojení na komín + akumulační zásobník (cca 8 Nh)</t>
         </is>
       </c>
       <c r="F176" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G176" s="23" t="n">
@@ -20552,7 +20504,7 @@
         </is>
       </c>
       <c r="K176" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L176" s="20" t="inlineStr">
         <is>
@@ -20561,12 +20513,12 @@
       </c>
       <c r="M176" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — primární zdroj 1.NP/2.NP, ~10 kW odhad standard RD</t>
+          <t>Standard montáž kamen s napojením na zásobník</t>
         </is>
       </c>
       <c r="N176" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O176" s="26" t="inlineStr">
@@ -20588,22 +20540,22 @@
       </c>
       <c r="C177" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna — montáž</t>
+          <t>Elektrokotel 3.NP</t>
         </is>
       </c>
       <c r="D177" s="20" t="inlineStr">
         <is>
-          <t>733281011</t>
+          <t>733131221</t>
         </is>
       </c>
       <c r="E177" s="8" t="inlineStr">
         <is>
-          <t>Sporáková kamna — montáž vč. napojení na komín + akumulační zásobník (cca 8 Nh)</t>
+          <t>Elektrokotel ~8 kW pro 3.NP samostatný byt — dodávka + montáž + napojení</t>
         </is>
       </c>
       <c r="F177" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G177" s="23" t="n">
@@ -20617,7 +20569,7 @@
         </is>
       </c>
       <c r="K177" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L177" s="20" t="inlineStr">
         <is>
@@ -20626,12 +20578,12 @@
       </c>
       <c r="M177" s="8" t="inlineStr">
         <is>
-          <t>Standard montáž kamen s napojením na zásobník</t>
+          <t>TZ ARS dům §4 — 'Nově navržené 3.NP bude vytápěno elektrokotlem'; ~8 kW odhad</t>
         </is>
       </c>
       <c r="N177" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#6</t>
         </is>
       </c>
       <c r="O177" s="26" t="inlineStr">
@@ -20653,17 +20605,17 @@
       </c>
       <c r="C178" s="8" t="inlineStr">
         <is>
-          <t>Elektrokotel 3.NP</t>
+          <t>Krb na tuhá paliva 3.NP</t>
         </is>
       </c>
       <c r="D178" s="20" t="inlineStr">
         <is>
-          <t>733131221</t>
+          <t>733241011</t>
         </is>
       </c>
       <c r="E178" s="8" t="inlineStr">
         <is>
-          <t>Elektrokotel ~8 kW pro 3.NP samostatný byt — dodávka + montáž + napojení</t>
+          <t>Krb na tuhá paliva v 3.NP ~6 kW — dodávka + montáž s napojením na samostatný komín</t>
         </is>
       </c>
       <c r="F178" s="20" t="inlineStr">
@@ -20691,7 +20643,7 @@
       </c>
       <c r="M178" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — 'Nově navržené 3.NP bude vytápěno elektrokotlem'; ~8 kW odhad</t>
+          <t>TZ ARS dům §4 — krb v 3.NP, ~6 kW odhad</t>
         </is>
       </c>
       <c r="N178" s="20" t="inlineStr">
@@ -20718,17 +20670,17 @@
       </c>
       <c r="C179" s="8" t="inlineStr">
         <is>
-          <t>Krb na tuhá paliva 3.NP</t>
+          <t>Multisplit TČ — venkovní jednotka</t>
         </is>
       </c>
       <c r="D179" s="20" t="inlineStr">
         <is>
-          <t>733241011</t>
+          <t>733425211</t>
         </is>
       </c>
       <c r="E179" s="8" t="inlineStr">
         <is>
-          <t>Krb na tuhá paliva v 3.NP ~6 kW — dodávka + montáž s napojením na samostatný komín</t>
+          <t>Multisplit tepelné čerpadlo vzduch-vzduch — 1× venkovní jednotka ~10 kW (silent mode hl. tlaku ≤49 dBA)</t>
         </is>
       </c>
       <c r="F179" s="20" t="inlineStr">
@@ -20743,7 +20695,7 @@
       <c r="I179" s="10" t="n"/>
       <c r="J179" s="8" t="inlineStr">
         <is>
-          <t>topenar</t>
+          <t>specialista_TC_multisplit</t>
         </is>
       </c>
       <c r="K179" s="24" t="n">
@@ -20756,7 +20708,7 @@
       </c>
       <c r="M179" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — krb v 3.NP, ~6 kW odhad</t>
+          <t>TZ ARS dům §4 — multisplit TČ s akustikou hl. tlaku ≤49 dBA, NV 272/2011</t>
         </is>
       </c>
       <c r="N179" s="20" t="inlineStr">
@@ -20783,17 +20735,17 @@
       </c>
       <c r="C180" s="8" t="inlineStr">
         <is>
-          <t>Multisplit TČ — venkovní jednotka</t>
+          <t>Multisplit TČ — vnitřní jednotky</t>
         </is>
       </c>
       <c r="D180" s="20" t="inlineStr">
         <is>
-          <t>733425211</t>
+          <t>733425221</t>
         </is>
       </c>
       <c r="E180" s="8" t="inlineStr">
         <is>
-          <t>Multisplit tepelné čerpadlo vzduch-vzduch — 1× venkovní jednotka ~10 kW (silent mode hl. tlaku ≤49 dBA)</t>
+          <t>Multisplit TČ — 5× vnitřní jednotka v obytných místnostech (1.NP, 2.NP, 3.NP — chlazení + vytápění)</t>
         </is>
       </c>
       <c r="F180" s="20" t="inlineStr">
@@ -20802,7 +20754,7 @@
         </is>
       </c>
       <c r="G180" s="23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H180" s="10" t="n"/>
       <c r="I180" s="10" t="n"/>
@@ -20812,7 +20764,7 @@
         </is>
       </c>
       <c r="K180" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L180" s="20" t="inlineStr">
         <is>
@@ -20821,7 +20773,7 @@
       </c>
       <c r="M180" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — multisplit TČ s akustikou hl. tlaku ≤49 dBA, NV 272/2011</t>
+          <t>TZ ARS dům §4 — vnitřní jednotky multisplit, vyjasnění #6 odhad 5 ks</t>
         </is>
       </c>
       <c r="N180" s="20" t="inlineStr">
@@ -20848,36 +20800,36 @@
       </c>
       <c r="C181" s="8" t="inlineStr">
         <is>
-          <t>Multisplit TČ — vnitřní jednotky</t>
+          <t>Revize komínu</t>
         </is>
       </c>
       <c r="D181" s="20" t="inlineStr">
         <is>
-          <t>733425221</t>
+          <t>734262122</t>
         </is>
       </c>
       <c r="E181" s="8" t="inlineStr">
         <is>
-          <t>Multisplit TČ — 5× vnitřní jednotka v obytných místnostech (1.NP, 2.NP, 3.NP — chlazení + vytápění)</t>
+          <t>Revize stávajícího komínu — kontrola, čištění, vystrojení vložkou nerez DN160 pro kamna + krb 3.NP</t>
         </is>
       </c>
       <c r="F181" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G181" s="23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H181" s="10" t="n"/>
       <c r="I181" s="10" t="n"/>
       <c r="J181" s="8" t="inlineStr">
         <is>
-          <t>specialista_TC_multisplit</t>
+          <t>kominik</t>
         </is>
       </c>
       <c r="K181" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L181" s="20" t="inlineStr">
         <is>
@@ -20886,7 +20838,7 @@
       </c>
       <c r="M181" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — vnitřní jednotky multisplit, vyjasnění #6 odhad 5 ks</t>
+          <t>TZ ARS dům §4 — komín stávající, vystrojení vložkou pro kamna + krb</t>
         </is>
       </c>
       <c r="N181" s="20" t="inlineStr">
@@ -20913,36 +20865,36 @@
       </c>
       <c r="C182" s="8" t="inlineStr">
         <is>
-          <t>Revize komínu</t>
+          <t>Rozvody otopné soustavy</t>
         </is>
       </c>
       <c r="D182" s="20" t="inlineStr">
         <is>
-          <t>734262122</t>
+          <t>733111021</t>
         </is>
       </c>
       <c r="E182" s="8" t="inlineStr">
         <is>
-          <t>Revize stávajícího komínu — kontrola, čištění, vystrojení vložkou nerez DN160 pro kamna + krb 3.NP</t>
+          <t>Rozvody otopné soustavy Cu/PEX k vnitřním jednotkám TČ + radiátorům pro doplňkové (cca 100 bm odhad)</t>
         </is>
       </c>
       <c r="F182" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G182" s="23" t="n">
-        <v>1</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G182" s="22" t="n">
+        <v>100</v>
       </c>
       <c r="H182" s="10" t="n"/>
       <c r="I182" s="10" t="n"/>
       <c r="J182" s="8" t="inlineStr">
         <is>
-          <t>kominik</t>
+          <t>topenar</t>
         </is>
       </c>
       <c r="K182" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L182" s="20" t="inlineStr">
         <is>
@@ -20951,7 +20903,7 @@
       </c>
       <c r="M182" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — komín stávající, vystrojení vložkou pro kamna + krb</t>
+          <t>TZ ARS dům §4 — rozvody otopné soustavy</t>
         </is>
       </c>
       <c r="N182" s="20" t="inlineStr">
@@ -20973,41 +20925,41 @@
       </c>
       <c r="B183" s="8" t="inlineStr">
         <is>
-          <t>PSV-73 Vytápění</t>
+          <t>VRN — BOZP</t>
         </is>
       </c>
       <c r="C183" s="8" t="inlineStr">
         <is>
-          <t>Rozvody otopné soustavy</t>
+          <t>Koordinace BOZP</t>
         </is>
       </c>
       <c r="D183" s="20" t="inlineStr">
         <is>
-          <t>733111021</t>
+          <t>030091000</t>
         </is>
       </c>
       <c r="E183" s="8" t="inlineStr">
         <is>
-          <t>Rozvody otopné soustavy Cu/PEX k vnitřním jednotkám TČ + radiátorům pro doplňkové (cca 100 bm odhad)</t>
+          <t>Koordinátor BOZP na staveništi dle zákona 309/2006 Sb. — pro stavbu s více než jedním zhotovitelem</t>
         </is>
       </c>
       <c r="F183" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G183" s="22" t="n">
-        <v>100</v>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G183" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H183" s="10" t="n"/>
       <c r="I183" s="10" t="n"/>
       <c r="J183" s="8" t="inlineStr">
         <is>
-          <t>topenar</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K183" s="24" t="n">
-        <v>0.75</v>
+        <v>0.99</v>
       </c>
       <c r="L183" s="20" t="inlineStr">
         <is>
@@ -21016,12 +20968,12 @@
       </c>
       <c r="M183" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — rozvody otopné soustavy</t>
+          <t>Zákon 309/2006 Sb. — povinný BOZP koordinátor pro vícezhotovitelskou stavbu</t>
         </is>
       </c>
       <c r="N183" s="20" t="inlineStr">
         <is>
-          <t>#6</t>
+          <t>#10</t>
         </is>
       </c>
       <c r="O183" s="26" t="inlineStr">
@@ -21038,22 +20990,22 @@
       </c>
       <c r="B184" s="8" t="inlineStr">
         <is>
-          <t>VRN — BOZP</t>
+          <t>VRN — Dokumentace</t>
         </is>
       </c>
       <c r="C184" s="8" t="inlineStr">
         <is>
-          <t>Koordinace BOZP</t>
+          <t>Předávací protokoly + DSP</t>
         </is>
       </c>
       <c r="D184" s="20" t="inlineStr">
         <is>
-          <t>030091000</t>
+          <t>030151000</t>
         </is>
       </c>
       <c r="E184" s="8" t="inlineStr">
         <is>
-          <t>Koordinátor BOZP na staveništi dle zákona 309/2006 Sb. — pro stavbu s více než jedním zhotovitelem</t>
+          <t>Předávací protokoly + Dokumentace skutečného provedení (DSP) — sestavení, vázání, dodávka 2× tiskem + elektronická verze</t>
         </is>
       </c>
       <c r="F184" s="20" t="inlineStr">
@@ -21081,12 +21033,12 @@
       </c>
       <c r="M184" s="8" t="inlineStr">
         <is>
-          <t>Zákon 309/2006 Sb. — povinný BOZP koordinátor pro vícezhotovitelskou stavbu</t>
+          <t>Vyhláška 499/2006 Sb. + ČKAIT — DSP povinná pro kolaudaci</t>
         </is>
       </c>
       <c r="N184" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O184" s="26" t="inlineStr">
@@ -21103,41 +21055,41 @@
       </c>
       <c r="B185" s="8" t="inlineStr">
         <is>
-          <t>VRN — Dokumentace</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="C185" s="8" t="inlineStr">
         <is>
-          <t>Předávací protokoly + DSP</t>
+          <t>Kontejnery suti tříděné</t>
         </is>
       </c>
       <c r="D185" s="20" t="inlineStr">
         <is>
-          <t>030151000</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="E185" s="8" t="inlineStr">
         <is>
-          <t>Předávací protokoly + Dokumentace skutečného provedení (DSP) — sestavení, vázání, dodávka 2× tiskem + elektronická verze</t>
+          <t>Kontejnery na suť tříděnou velkoobjemové (beton/cihly, dřevo, kovy, EPS, sádra, směs) — pronájem + svozy</t>
         </is>
       </c>
       <c r="F185" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G185" s="23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H185" s="10" t="n"/>
       <c r="I185" s="10" t="n"/>
       <c r="J185" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="K185" s="24" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="L185" s="20" t="inlineStr">
         <is>
@@ -21146,12 +21098,12 @@
       </c>
       <c r="M185" s="8" t="inlineStr">
         <is>
-          <t>Vyhláška 499/2006 Sb. + ČKAIT — DSP povinná pro kolaudaci</t>
+          <t>TZ B m.10.e: beton/cihly 46 t + dřevo 9 t + kovy 0.1 + EPS 0.1 + sádra 0.2 + směs 1.0</t>
         </is>
       </c>
       <c r="N185" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#9, #10</t>
         </is>
       </c>
       <c r="O185" s="26" t="inlineStr">
@@ -21173,36 +21125,36 @@
       </c>
       <c r="C186" s="8" t="inlineStr">
         <is>
-          <t>Kontejnery suti tříděné</t>
+          <t>Doprava materiálu</t>
         </is>
       </c>
       <c r="D186" s="20" t="inlineStr">
         <is>
-          <t>997013211</t>
+          <t>031031000</t>
         </is>
       </c>
       <c r="E186" s="8" t="inlineStr">
         <is>
-          <t>Kontejnery na suť tříděnou velkoobjemové (beton/cihly, dřevo, kovy, EPS, sádra, směs) — pronájem + svozy</t>
+          <t>Doprava materiálu na stavbu (centrální koordinace) — paušál ~2-3 % z PN materiál</t>
         </is>
       </c>
       <c r="F186" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>paušál</t>
         </is>
       </c>
       <c r="G186" s="23" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H186" s="10" t="n"/>
       <c r="I186" s="10" t="n"/>
       <c r="J186" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K186" s="24" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="L186" s="20" t="inlineStr">
         <is>
@@ -21211,12 +21163,12 @@
       </c>
       <c r="M186" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10.e: beton/cihly 46 t + dřevo 9 t + kovy 0.1 + EPS 0.1 + sádra 0.2 + směs 1.0</t>
+          <t>B4_productivity — standard doprava RD městská zástavba</t>
         </is>
       </c>
       <c r="N186" s="20" t="inlineStr">
         <is>
-          <t>#9, #10</t>
+          <t>#10</t>
         </is>
       </c>
       <c r="O186" s="26" t="inlineStr">
@@ -21238,36 +21190,36 @@
       </c>
       <c r="C187" s="8" t="inlineStr">
         <is>
-          <t>Doprava materiálu</t>
+          <t>Likvidace odpadů 56.9 t</t>
         </is>
       </c>
       <c r="D187" s="20" t="inlineStr">
         <is>
-          <t>031031000</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="E187" s="8" t="inlineStr">
         <is>
-          <t>Doprava materiálu na stavbu (centrální koordinace) — paušál ~2-3 % z PN materiál</t>
+          <t>Likvidace stavební suti dle vyhl. 8/2021 Sb. — skládkovné + recyklace + třídění (56.9 t celkem per TZ B m.10.e)</t>
         </is>
       </c>
       <c r="F187" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
-        </is>
-      </c>
-      <c r="G187" s="23" t="n">
-        <v>1</v>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G187" s="22" t="n">
+        <v>56.9</v>
       </c>
       <c r="H187" s="10" t="n"/>
       <c r="I187" s="10" t="n"/>
       <c r="J187" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="K187" s="24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L187" s="20" t="inlineStr">
         <is>
@@ -21276,12 +21228,12 @@
       </c>
       <c r="M187" s="8" t="inlineStr">
         <is>
-          <t>B4_productivity — standard doprava RD městská zástavba</t>
+          <t>TZ B m.10.e bilance odpadů celkem dům</t>
         </is>
       </c>
       <c r="N187" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>#9, #10</t>
         </is>
       </c>
       <c r="O187" s="26" t="inlineStr">
@@ -21298,41 +21250,41 @@
       </c>
       <c r="B188" s="8" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>VRN — Geodet</t>
         </is>
       </c>
       <c r="C188" s="8" t="inlineStr">
         <is>
-          <t>Likvidace odpadů 56.9 t</t>
+          <t>Geodetické zaměření před + po realizaci</t>
         </is>
       </c>
       <c r="D188" s="20" t="inlineStr">
         <is>
-          <t>997013211</t>
+          <t>030141000</t>
         </is>
       </c>
       <c r="E188" s="8" t="inlineStr">
         <is>
-          <t>Likvidace stavební suti dle vyhl. 8/2021 Sb. — skládkovné + recyklace + třídění (56.9 t celkem per TZ B m.10.e)</t>
+          <t>Geodetické zaměření před realizací (verifikace polohopis + výškopis) + po dokončení (zaměření skutečného provedení pro kolaudaci)</t>
         </is>
       </c>
       <c r="F188" s="20" t="inlineStr">
         <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="G188" s="22" t="n">
-        <v>56.9</v>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G188" s="23" t="n">
+        <v>2</v>
       </c>
       <c r="H188" s="10" t="n"/>
       <c r="I188" s="10" t="n"/>
       <c r="J188" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>geodet</t>
         </is>
       </c>
       <c r="K188" s="24" t="n">
-        <v>0.85</v>
+        <v>0.99</v>
       </c>
       <c r="L188" s="20" t="inlineStr">
         <is>
@@ -21341,12 +21293,12 @@
       </c>
       <c r="M188" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10.e bilance odpadů celkem dům</t>
+          <t>Standard — geodet před+po pro každou stavbu</t>
         </is>
       </c>
       <c r="N188" s="20" t="inlineStr">
         <is>
-          <t>#9, #10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O188" s="26" t="inlineStr">
@@ -21363,37 +21315,37 @@
       </c>
       <c r="B189" s="8" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>VRN — Kolaudace</t>
         </is>
       </c>
       <c r="C189" s="8" t="inlineStr">
         <is>
-          <t>Geodetické zaměření před + po realizaci</t>
+          <t>Kolaudační řízení</t>
         </is>
       </c>
       <c r="D189" s="20" t="inlineStr">
         <is>
-          <t>030141000</t>
+          <t>030171000</t>
         </is>
       </c>
       <c r="E189" s="8" t="inlineStr">
         <is>
-          <t>Geodetické zaměření před realizací (verifikace polohopis + výškopis) + po dokončení (zaměření skutečného provedení pro kolaudaci)</t>
+          <t>Kolaudační řízení — paušál (správní poplatky + součinnost) dle zákona 183/2006 Sb.</t>
         </is>
       </c>
       <c r="F189" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>paušál</t>
         </is>
       </c>
       <c r="G189" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H189" s="10" t="n"/>
       <c r="I189" s="10" t="n"/>
       <c r="J189" s="8" t="inlineStr">
         <is>
-          <t>geodet</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K189" s="24" t="n">
@@ -21406,7 +21358,7 @@
       </c>
       <c r="M189" s="8" t="inlineStr">
         <is>
-          <t>Standard — geodet před+po pro každou stavbu</t>
+          <t>Zákon 183/2006 Sb. + vyhl. 499/2006 Sb.</t>
         </is>
       </c>
       <c r="N189" s="20" t="inlineStr">
@@ -21428,31 +21380,31 @@
       </c>
       <c r="B190" s="8" t="inlineStr">
         <is>
-          <t>VRN — Kolaudace</t>
+          <t>VRN — Lešení</t>
         </is>
       </c>
       <c r="C190" s="8" t="inlineStr">
         <is>
-          <t>Kolaudační řízení</t>
+          <t>Fasádní lešení (ETICS + krov + klempířina)</t>
         </is>
       </c>
       <c r="D190" s="20" t="inlineStr">
         <is>
-          <t>030171000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E190" s="8" t="inlineStr">
         <is>
-          <t>Kolaudační řízení — paušál (správní poplatky + součinnost) dle zákona 183/2006 Sb.</t>
+          <t>Fasádní lešení trubkové/rámové vč. montáže + pronájmu + demontáže — pro provedení ETICS fasády, krovu a klempířiny po obvodu domu (výška 13 m)</t>
         </is>
       </c>
       <c r="F190" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
-        </is>
-      </c>
-      <c r="G190" s="23" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G190" s="22" t="n">
+        <v>503.1</v>
       </c>
       <c r="H190" s="10" t="n"/>
       <c r="I190" s="10" t="n"/>
@@ -21462,7 +21414,7 @@
         </is>
       </c>
       <c r="K190" s="24" t="n">
-        <v>0.99</v>
+        <v>0.8</v>
       </c>
       <c r="L190" s="20" t="inlineStr">
         <is>
@@ -21471,7 +21423,7 @@
       </c>
       <c r="M190" s="8" t="inlineStr">
         <is>
-          <t>Zákon 183/2006 Sb. + vyhl. 499/2006 Sb.</t>
+          <t>anchor checklist PM02 — technical necessity (ETICS 276.7 m² nelze provést bez lešení, 941xxx URS família) + DXF obvod 38.7 m + řez výška 13 m</t>
         </is>
       </c>
       <c r="N190" s="20" t="inlineStr">
@@ -21485,7 +21437,11 @@
         </is>
       </c>
       <c r="P190" s="41" t="n"/>
-      <c r="Q190" s="41" t="n"/>
+      <c r="Q190" s="41" t="inlineStr">
+        <is>
+          <t>ANCHOR_CHECKLIST_PM02</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="20" t="n">
@@ -21493,31 +21449,31 @@
       </c>
       <c r="B191" s="8" t="inlineStr">
         <is>
-          <t>VRN — Lešení</t>
+          <t>VRN — Pojištění + zábory</t>
         </is>
       </c>
       <c r="C191" s="8" t="inlineStr">
         <is>
-          <t>Fasádní lešení (ETICS + krov + klempířina)</t>
+          <t>Pojištění stavby (montážní + odpovědnostní)</t>
         </is>
       </c>
       <c r="D191" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>030081000</t>
         </is>
       </c>
       <c r="E191" s="8" t="inlineStr">
         <is>
-          <t>Fasádní lešení trubkové/rámové vč. montáže + pronájmu + demontáže — pro provedení ETICS fasády, krovu a klempířiny po obvodu domu (výška 13 m)</t>
+          <t>Montážní pojištění stavby (CAR) + pojištění odpovědnosti za škodu (zhotovitel) — paušál cca 0.3-0.5 % z PN</t>
         </is>
       </c>
       <c r="F191" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G191" s="22" t="n">
-        <v>503.1</v>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="G191" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H191" s="10" t="n"/>
       <c r="I191" s="10" t="n"/>
@@ -21527,7 +21483,7 @@
         </is>
       </c>
       <c r="K191" s="24" t="n">
-        <v>0.8</v>
+        <v>0.99</v>
       </c>
       <c r="L191" s="20" t="inlineStr">
         <is>
@@ -21536,12 +21492,12 @@
       </c>
       <c r="M191" s="8" t="inlineStr">
         <is>
-          <t>anchor checklist PM02 — technical necessity (ETICS 276.7 m² nelze provést bez lešení, 941xxx URS família) + DXF obvod 38.7 m + řez výška 13 m</t>
+          <t>Standard zhotovitel — pojistná povinnost</t>
         </is>
       </c>
       <c r="N191" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#10</t>
         </is>
       </c>
       <c r="O191" s="26" t="inlineStr">
@@ -21550,11 +21506,7 @@
         </is>
       </c>
       <c r="P191" s="41" t="n"/>
-      <c r="Q191" s="41" t="inlineStr">
-        <is>
-          <t>ANCHOR_CHECKLIST_PM02</t>
-        </is>
-      </c>
+      <c r="Q191" s="41" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="20" t="n">
@@ -21567,22 +21519,22 @@
       </c>
       <c r="C192" s="8" t="inlineStr">
         <is>
-          <t>Pojištění stavby (montážní + odpovědnostní)</t>
+          <t>Krátkodobé zábory ul. Fibichova</t>
         </is>
       </c>
       <c r="D192" s="20" t="inlineStr">
         <is>
-          <t>030081000</t>
+          <t>030083000</t>
         </is>
       </c>
       <c r="E192" s="8" t="inlineStr">
         <is>
-          <t>Montážní pojištění stavby (CAR) + pojištění odpovědnosti za škodu (zhotovitel) — paušál cca 0.3-0.5 % z PN</t>
+          <t>Krátkodobé zábory ulice Fibichova pro materiál a kontejnery (povolení MU Jáchymov + DI) — odhad 30 dnů kumulativně</t>
         </is>
       </c>
       <c r="F192" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G192" s="23" t="n">
@@ -21596,7 +21548,7 @@
         </is>
       </c>
       <c r="K192" s="24" t="n">
-        <v>0.99</v>
+        <v>0.75</v>
       </c>
       <c r="L192" s="20" t="inlineStr">
         <is>
@@ -21605,7 +21557,7 @@
       </c>
       <c r="M192" s="8" t="inlineStr">
         <is>
-          <t>Standard zhotovitel — pojistná povinnost</t>
+          <t>TZ B m.10 + situace — řadovka ul. Fibichova</t>
         </is>
       </c>
       <c r="N192" s="20" t="inlineStr">
@@ -21627,22 +21579,22 @@
       </c>
       <c r="B193" s="8" t="inlineStr">
         <is>
-          <t>VRN — Pojištění + zábory</t>
+          <t>VRN — Průzkumy</t>
         </is>
       </c>
       <c r="C193" s="8" t="inlineStr">
         <is>
-          <t>Krátkodobé zábory ul. Fibichova</t>
+          <t>Mykologický průzkum dřeva při bourání</t>
         </is>
       </c>
       <c r="D193" s="20" t="inlineStr">
         <is>
-          <t>030083000</t>
+          <t>030131000</t>
         </is>
       </c>
       <c r="E193" s="8" t="inlineStr">
         <is>
-          <t>Krátkodobé zábory ulice Fibichova pro materiál a kontejnery (povolení MU Jáchymov + DI) — odhad 30 dnů kumulativně</t>
+          <t>Mykologický průzkum + průzkum výskytu dřevokazného hmyzu stávajícího krovu a dřevěných trámů zhlaví — pro vyloučení narušení dřevěných konstrukcí; provádí autorizovaný mykolog při bourání</t>
         </is>
       </c>
       <c r="F193" s="20" t="inlineStr">
@@ -21657,11 +21609,11 @@
       <c r="I193" s="10" t="n"/>
       <c r="J193" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>mykolog</t>
         </is>
       </c>
       <c r="K193" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L193" s="20" t="inlineStr">
         <is>
@@ -21670,7 +21622,7 @@
       </c>
       <c r="M193" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.10 + situace — řadovka ul. Fibichova</t>
+          <t>TZ ARS dům §3.2.3 + POZN.2.05 z půdorysů návrh + řez A-A návrh (explicit dřevokazný hmyz scope per drawing wording)</t>
         </is>
       </c>
       <c r="N193" s="20" t="inlineStr">
@@ -21684,7 +21636,11 @@
         </is>
       </c>
       <c r="P193" s="41" t="n"/>
-      <c r="Q193" s="41" t="n"/>
+      <c r="Q193" s="41" t="inlineStr">
+        <is>
+          <t>PER_DRAWING_ENRICHMENT_POZN_2_05</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="20" t="n">
@@ -21697,17 +21653,17 @@
       </c>
       <c r="C194" s="8" t="inlineStr">
         <is>
-          <t>Mykologický průzkum dřeva při bourání</t>
+          <t>Azbestový průzkum podrobný před demolicí</t>
         </is>
       </c>
       <c r="D194" s="20" t="inlineStr">
         <is>
-          <t>030131000</t>
+          <t>030133000</t>
         </is>
       </c>
       <c r="E194" s="8" t="inlineStr">
         <is>
-          <t>Mykologický průzkum + průzkum výskytu dřevokazného hmyzu stávajícího krovu a dřevěných trámů zhlaví — pro vyloučení narušení dřevěných konstrukcí; provádí autorizovaný mykolog při bourání</t>
+          <t>Azbestový průzkum podrobný před demolicí — laboratorní vzorky a posudek (B kap. m.7.a předběžně negativní, ale podrobný před bouráním povinný)</t>
         </is>
       </c>
       <c r="F194" s="20" t="inlineStr">
@@ -21722,7 +21678,7 @@
       <c r="I194" s="10" t="n"/>
       <c r="J194" s="8" t="inlineStr">
         <is>
-          <t>mykolog</t>
+          <t>azbestovy_specialista</t>
         </is>
       </c>
       <c r="K194" s="24" t="n">
@@ -21735,7 +21691,7 @@
       </c>
       <c r="M194" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §3.2.3 + POZN.2.05 z půdorysů návrh + řez A-A návrh (explicit dřevokazný hmyz scope per drawing wording)</t>
+          <t>TZ B m.7.a + ARS §3.2 — azbestový průzkum povinný před demolicí</t>
         </is>
       </c>
       <c r="N194" s="20" t="inlineStr">
@@ -21749,11 +21705,7 @@
         </is>
       </c>
       <c r="P194" s="41" t="n"/>
-      <c r="Q194" s="41" t="inlineStr">
-        <is>
-          <t>PER_DRAWING_ENRICHMENT_POZN_2_05</t>
-        </is>
-      </c>
+      <c r="Q194" s="41" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="20" t="n">
@@ -21761,41 +21713,41 @@
       </c>
       <c r="B195" s="8" t="inlineStr">
         <is>
-          <t>VRN — Průzkumy</t>
+          <t>VRN — Přesun hmot</t>
         </is>
       </c>
       <c r="C195" s="8" t="inlineStr">
         <is>
-          <t>Azbestový průzkum podrobný před demolicí</t>
+          <t>Přesun hmot pro budovu</t>
         </is>
       </c>
       <c r="D195" s="20" t="inlineStr">
         <is>
-          <t>030133000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E195" s="8" t="inlineStr">
         <is>
-          <t>Azbestový průzkum podrobný před demolicí — laboratorní vzorky a posudek (B kap. m.7.a předběžně negativní, ale podrobný před bouráním povinný)</t>
+          <t>Přesun hmot pro budovu — vnitrostaveništní vertikální + horizontální doprava materiálu a hmot (rekonstrukce vícepodlažní RD + nástavba 3.NP)</t>
         </is>
       </c>
       <c r="F195" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G195" s="23" t="n">
-        <v>1</v>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G195" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H195" s="10" t="n"/>
       <c r="I195" s="10" t="n"/>
       <c r="J195" s="8" t="inlineStr">
         <is>
-          <t>azbestovy_specialista</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K195" s="24" t="n">
-        <v>0.85</v>
+        <v>0.6</v>
       </c>
       <c r="L195" s="20" t="inlineStr">
         <is>
@@ -21804,12 +21756,12 @@
       </c>
       <c r="M195" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.7.a + ARS §3.2 — azbestový průzkum povinný před demolicí</t>
+          <t>anchor checklist PM01 — technical necessity (povinná položka každého rozpočtu, 998xxx URS família)</t>
         </is>
       </c>
       <c r="N195" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O195" s="26" t="inlineStr">
@@ -21818,7 +21770,11 @@
         </is>
       </c>
       <c r="P195" s="41" t="n"/>
-      <c r="Q195" s="41" t="n"/>
+      <c r="Q195" s="41" t="inlineStr">
+        <is>
+          <t>ANCHOR_CHECKLIST_PM01</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="20" t="n">
@@ -21826,41 +21782,41 @@
       </c>
       <c r="B196" s="8" t="inlineStr">
         <is>
-          <t>VRN — Přesun hmot</t>
+          <t>VRN — Revize</t>
         </is>
       </c>
       <c r="C196" s="8" t="inlineStr">
         <is>
-          <t>Přesun hmot pro budovu</t>
+          <t>Revize hydrantu vnějšího</t>
         </is>
       </c>
       <c r="D196" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>030161000</t>
         </is>
       </c>
       <c r="E196" s="8" t="inlineStr">
         <is>
-          <t>Přesun hmot pro budovu — vnitrostaveništní vertikální + horizontální doprava materiálu a hmot (rekonstrukce vícepodlažní RD + nástavba 3.NP)</t>
+          <t>Revize vnějšího hydrantu pro požární zabezpečení (DN min. 80, vzdálenost 100 m dle TZ PBŘ) — periodická kontrola</t>
         </is>
       </c>
       <c r="F196" s="20" t="inlineStr">
         <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="G196" s="22" t="n">
-        <v>0</v>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G196" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H196" s="10" t="n"/>
       <c r="I196" s="10" t="n"/>
       <c r="J196" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>revize_specialista</t>
         </is>
       </c>
       <c r="K196" s="24" t="n">
-        <v>0.6</v>
+        <v>0.85</v>
       </c>
       <c r="L196" s="20" t="inlineStr">
         <is>
@@ -21869,7 +21825,7 @@
       </c>
       <c r="M196" s="8" t="inlineStr">
         <is>
-          <t>anchor checklist PM01 — technical necessity (povinná položka každého rozpočtu, 998xxx URS família)</t>
+          <t>TZ PBŘ dům — vnější odběrné místo požární vody, revize před kolaudací</t>
         </is>
       </c>
       <c r="N196" s="20" t="inlineStr">
@@ -21883,11 +21839,7 @@
         </is>
       </c>
       <c r="P196" s="41" t="n"/>
-      <c r="Q196" s="41" t="inlineStr">
-        <is>
-          <t>ANCHOR_CHECKLIST_PM01</t>
-        </is>
-      </c>
+      <c r="Q196" s="41" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="20" t="n">
@@ -21895,41 +21847,41 @@
       </c>
       <c r="B197" s="8" t="inlineStr">
         <is>
-          <t>VRN — Revize</t>
+          <t>VRN — Zařízení staveniště</t>
         </is>
       </c>
       <c r="C197" s="8" t="inlineStr">
         <is>
-          <t>Revize hydrantu vnějšího</t>
+          <t>Buňky kancelář + sociální</t>
         </is>
       </c>
       <c r="D197" s="20" t="inlineStr">
         <is>
-          <t>030161000</t>
+          <t>030011000</t>
         </is>
       </c>
       <c r="E197" s="8" t="inlineStr">
         <is>
-          <t>Revize vnějšího hydrantu pro požární zabezpečení (DN min. 80, vzdálenost 100 m dle TZ PBŘ) — periodická kontrola</t>
+          <t>Zařízení staveniště — buňka kancelář + sociální buňka (WC + šatna), pronájem ~8 měsíců</t>
         </is>
       </c>
       <c r="F197" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>kpl-měs</t>
         </is>
       </c>
       <c r="G197" s="23" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H197" s="10" t="n"/>
       <c r="I197" s="10" t="n"/>
       <c r="J197" s="8" t="inlineStr">
         <is>
-          <t>revize_specialista</t>
+          <t>VRN_management</t>
         </is>
       </c>
       <c r="K197" s="24" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="L197" s="20" t="inlineStr">
         <is>
@@ -21938,12 +21890,12 @@
       </c>
       <c r="M197" s="8" t="inlineStr">
         <is>
-          <t>TZ PBŘ dům — vnější odběrné místo požární vody, revize před kolaudací</t>
+          <t>TZ B m.1.m realizace 2026-2027 + standard staveniště RD městská zástavba</t>
         </is>
       </c>
       <c r="N197" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#10</t>
         </is>
       </c>
       <c r="O197" s="26" t="inlineStr">
@@ -21965,22 +21917,22 @@
       </c>
       <c r="C198" s="8" t="inlineStr">
         <is>
-          <t>Buňky kancelář + sociální</t>
+          <t>Mobilní WC</t>
         </is>
       </c>
       <c r="D198" s="20" t="inlineStr">
         <is>
-          <t>030011000</t>
+          <t>030013000</t>
         </is>
       </c>
       <c r="E198" s="8" t="inlineStr">
         <is>
-          <t>Zařízení staveniště — buňka kancelář + sociální buňka (WC + šatna), pronájem ~8 měsíců</t>
+          <t>Mobilní chemické WC TOI TOI pro pracovníky — pronájem ~8 měsíců</t>
         </is>
       </c>
       <c r="F198" s="20" t="inlineStr">
         <is>
-          <t>kpl-měs</t>
+          <t>ks-měs</t>
         </is>
       </c>
       <c r="G198" s="23" t="n">
@@ -22003,7 +21955,7 @@
       </c>
       <c r="M198" s="8" t="inlineStr">
         <is>
-          <t>TZ B m.1.m realizace 2026-2027 + standard staveniště RD městská zástavba</t>
+          <t>BOZP — mobilní WC povinné pro stavbu RD</t>
         </is>
       </c>
       <c r="N198" s="20" t="inlineStr">
@@ -22030,26 +21982,26 @@
       </c>
       <c r="C199" s="8" t="inlineStr">
         <is>
-          <t>Mobilní WC</t>
+          <t>El. odběr + vodovodní odběr stavby</t>
         </is>
       </c>
       <c r="D199" s="20" t="inlineStr">
         <is>
-          <t>030013000</t>
+          <t>031011000</t>
         </is>
       </c>
       <c r="E199" s="8" t="inlineStr">
         <is>
-          <t>Mobilní chemické WC TOI TOI pro pracovníky — pronájem ~8 měsíců</t>
+          <t>El. odběr stavby (zřízení staveništního rozvaděče + měřič) + vodovodní odběr (zřízení staveništní přípojky + vodoměr) — ~8 měsíců</t>
         </is>
       </c>
       <c r="F199" s="20" t="inlineStr">
         <is>
-          <t>ks-měs</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G199" s="23" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H199" s="10" t="n"/>
       <c r="I199" s="10" t="n"/>
@@ -22068,7 +22020,7 @@
       </c>
       <c r="M199" s="8" t="inlineStr">
         <is>
-          <t>BOZP — mobilní WC povinné pro stavbu RD</t>
+          <t>Standard staveniště — el. + voda zřízení a odběr po dobu stavby</t>
         </is>
       </c>
       <c r="N199" s="20" t="inlineStr">
@@ -22095,17 +22047,17 @@
       </c>
       <c r="C200" s="8" t="inlineStr">
         <is>
-          <t>El. odběr + vodovodní odběr stavby</t>
+          <t>Voda staveniště</t>
         </is>
       </c>
       <c r="D200" s="20" t="inlineStr">
         <is>
-          <t>031011000</t>
+          <t>012103101</t>
         </is>
       </c>
       <c r="E200" s="8" t="inlineStr">
         <is>
-          <t>El. odběr stavby (zřízení staveništního rozvaděče + měřič) + vodovodní odběr (zřízení staveništní přípojky + vodoměr) — ~8 měsíců</t>
+          <t>Voda staveniště — napojení na stávající vodovodní přípojku, dočasné rozvody na staveništi (mísení malt, čištění, soc. zázemí), paušál pro dobu výstavby ~18 měs.</t>
         </is>
       </c>
       <c r="F200" s="20" t="inlineStr">
@@ -22124,7 +22076,7 @@
         </is>
       </c>
       <c r="K200" s="24" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L200" s="20" t="inlineStr">
         <is>
@@ -22133,12 +22085,12 @@
       </c>
       <c r="M200" s="8" t="inlineStr">
         <is>
-          <t>Standard staveniště — el. + voda zřízení a odběr po dobu stavby</t>
+          <t>TZ B Souhrnná m.5 — 'Stávající vodovodní přípojka z veřejného vodovodu'</t>
         </is>
       </c>
       <c r="N200" s="20" t="inlineStr">
         <is>
-          <t>#10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O200" s="26" t="inlineStr">
@@ -22147,7 +22099,11 @@
         </is>
       </c>
       <c r="P200" s="41" t="n"/>
-      <c r="Q200" s="41" t="n"/>
+      <c r="Q200" s="41" t="inlineStr">
+        <is>
+          <t>GAP_003</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="20" t="n">
@@ -22155,27 +22111,27 @@
       </c>
       <c r="B201" s="8" t="inlineStr">
         <is>
-          <t>VRN — Zařízení staveniště</t>
+          <t>M-21 ELI silnoproud</t>
         </is>
       </c>
       <c r="C201" s="8" t="inlineStr">
         <is>
-          <t>Voda staveniště</t>
+          <t>Hlavní vypínač TOTAL STOP + požární značení</t>
         </is>
       </c>
       <c r="D201" s="20" t="inlineStr">
         <is>
-          <t>012103101</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E201" s="8" t="inlineStr">
         <is>
-          <t>Voda staveniště — napojení na stávající vodovodní přípojku, dočasné rozvody na staveništi (mísení malt, čištění, soc. zázemí), paušál pro dobu výstavby ~18 měs.</t>
+          <t>Hlavní vypínač elektrické energie TOTAL STOP + požární značení rozvodného zařízení a uzávěrů (voda/elektro)</t>
         </is>
       </c>
       <c r="F201" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>soubor</t>
         </is>
       </c>
       <c r="G201" s="23" t="n">
@@ -22185,11 +22141,11 @@
       <c r="I201" s="10" t="n"/>
       <c r="J201" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>elektrikar</t>
         </is>
       </c>
       <c r="K201" s="24" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="L201" s="20" t="inlineStr">
         <is>
@@ -22198,7 +22154,7 @@
       </c>
       <c r="M201" s="8" t="inlineStr">
         <is>
-          <t>TZ B Souhrnná m.5 — 'Stávající vodovodní přípojka z veřejného vodovodu'</t>
+          <t>PBŘ D.3 §16.05/16.06</t>
         </is>
       </c>
       <c r="N201" s="20" t="inlineStr">
@@ -22211,10 +22167,10 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P201" s="41" t="n"/>
+      <c r="P201" s="41" t="inlineStr"/>
       <c r="Q201" s="41" t="inlineStr">
         <is>
-          <t>GAP_003</t>
+          <t>DODATEK_PBR_GAPS_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -22224,12 +22180,12 @@
       </c>
       <c r="B202" s="8" t="inlineStr">
         <is>
-          <t>M-21 ELI silnoproud</t>
+          <t>M-24 VZT</t>
         </is>
       </c>
       <c r="C202" s="8" t="inlineStr">
         <is>
-          <t>Hlavní vypínač TOTAL STOP + požární značení</t>
+          <t>Lokální odtah digestoří kuchyní</t>
         </is>
       </c>
       <c r="D202" s="20" t="inlineStr">
@@ -22239,26 +22195,26 @@
       </c>
       <c r="E202" s="8" t="inlineStr">
         <is>
-          <t>Hlavní vypínač elektrické energie TOTAL STOP + požární značení rozvodného zařízení a uzávěrů (voda/elektro)</t>
+          <t>Lokální odtah digestoří kuchyní (1.NP + 3.NP) — dodávka + montáž digestoře + prostup fasádou/střechou + zpětná klapka</t>
         </is>
       </c>
       <c r="F202" s="20" t="inlineStr">
         <is>
-          <t>soubor</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G202" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H202" s="10" t="n"/>
       <c r="I202" s="10" t="n"/>
       <c r="J202" s="8" t="inlineStr">
         <is>
-          <t>elektrikar</t>
+          <t>vzduchotechnik</t>
         </is>
       </c>
       <c r="K202" s="24" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="L202" s="20" t="inlineStr">
         <is>
@@ -22267,7 +22223,7 @@
       </c>
       <c r="M202" s="8" t="inlineStr">
         <is>
-          <t>PBŘ D.3 §16.05/16.06</t>
+          <t>B zpráva — VZT: obytné místnosti větrání okny, kuchyně lokální odtah digestoří</t>
         </is>
       </c>
       <c r="N202" s="20" t="inlineStr">
@@ -22287,78 +22243,9 @@
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="20" t="n">
-        <v>202</v>
-      </c>
-      <c r="B203" s="8" t="inlineStr">
-        <is>
-          <t>M-24 VZT</t>
-        </is>
-      </c>
-      <c r="C203" s="8" t="inlineStr">
-        <is>
-          <t>Lokální odtah digestoří kuchyní</t>
-        </is>
-      </c>
-      <c r="D203" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E203" s="8" t="inlineStr">
-        <is>
-          <t>Lokální odtah digestoří kuchyní (1.NP + 3.NP) — dodávka + montáž digestoře + prostup fasádou/střechou + zpětná klapka</t>
-        </is>
-      </c>
-      <c r="F203" s="20" t="inlineStr">
-        <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G203" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="H203" s="10" t="n"/>
-      <c r="I203" s="10" t="n"/>
-      <c r="J203" s="8" t="inlineStr">
-        <is>
-          <t>vzduchotechnik</t>
-        </is>
-      </c>
-      <c r="K203" s="24" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L203" s="20" t="inlineStr">
-        <is>
-          <t>needs_production_lookup</t>
-        </is>
-      </c>
-      <c r="M203" s="8" t="inlineStr">
-        <is>
-          <t>B zpráva — VZT: obytné místnosti větrání okny, kuchyně lokální odtah digestoří</t>
-        </is>
-      </c>
-      <c r="N203" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O203" s="26" t="inlineStr">
-        <is>
-          <t>ANO</t>
-        </is>
-      </c>
-      <c r="P203" s="41" t="inlineStr"/>
-      <c r="Q203" s="41" t="inlineStr">
-        <is>
-          <t>DODATEK_PBR_GAPS_2026-06-01</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O203"/>
-  <conditionalFormatting sqref="K2:K203">
+  <autoFilter ref="A1:O202"/>
+  <conditionalFormatting sqref="K2:K202">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0" stopIfTrue="1">
       <formula>0.70</formula>
     </cfRule>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01_v2.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01_v2.xlsx
@@ -21,9 +21,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Var_A_Agregovany_Dum'!$A$1:$G$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Var_A_Agregovany_Sklad'!$A$1:$G$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$131</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$133</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Var_B_Polozkovy_Dum'!$A$1:$O$202</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Var_B_Polozkovy_Sklad'!$A$1:$O$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Var_B_Polozkovy_Sklad'!$A$1:$O$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Var_F_URS_Verification_Trail'!$A$1:$H$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1009,11 +1009,11 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>HSV položkově (117 ks) + PSV/TZB/VRN agregovaně (13 skupin) = 130 řádků.</t>
+          <t>HSV položkově (119 ks) + PSV/TZB/VRN agregovaně (13 skupin) = 132 řádků.</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D24" s="10" t="n"/>
       <c r="E24" s="10" t="n"/>
@@ -1027,11 +1027,11 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Plný detail (201 dum + 31 sklad = 232 položek). Cílový rozsah pro produkční pricing.</t>
+          <t>Plný detail (201 dum + 33 sklad = 234 položek). Cílový rozsah pro produkční pricing.</t>
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D25" s="10" t="n"/>
       <c r="E25" s="10" t="n"/>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>232 (201 dum + 31 sklad)</t>
+          <t>234 (201 dum + 33 sklad)</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>HSV 117 | M 2 | PSV 56 | TZB 34 | VRN 23</t>
+          <t>HSV 119 | M 2 | PSV 56 | TZB 34 | VRN 23</t>
         </is>
       </c>
     </row>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>0.99: 17 | 0.95: 32 | 0.90: 34 | 0.85: 41 | 0.80: 21 | 0.75: 71 | 0.70: 4 | 0.60: 3 | 0.50: 4 | 0.00: 5</t>
+          <t>0.99: 17 | 0.95: 32 | 0.90: 34 | 0.85: 41 | 0.80: 21 | 0.75: 71 | 0.70: 4 | 0.60: 3 | 0.50: 6 | 0.00: 5</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>8 WebSearch verified (3.4 %) ✓ | 5 wrong leaf flagged (2.2 %) ⚠ | 155 needs_production_lookup (66.8 %)</t>
+          <t>8 WebSearch verified (3.4 %) ✓ | 5 wrong leaf flagged (2.1 %) ⚠ | 157 needs_production_lookup (67.1 %)</t>
         </is>
       </c>
     </row>
@@ -1186,8 +1186,8 @@
       <c r="A43" s="12" t="inlineStr">
         <is>
           <t>Rozpočet generován STAVAGENT pipelinem z DSP dokumentace s DPS-grade DXF metadaty.
-232 položek celkem (201 dum + 31 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
-Confidence distribution: 17×0.99 · 32×0.95 · 34×0.90 · 41×0.85 · 21×0.80 · 71×0.75 · 4×0.70 · 3×0.60 · 4×0.50 · 5×0.00.
+234 položek celkem (201 dum + 33 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
+Confidence distribution: 17×0.99 · 32×0.95 · 34×0.90 · 41×0.85 · 21×0.80 · 71×0.75 · 4×0.70 · 3×0.60 · 6×0.50 · 5×0.00.
 25 položek vzniklo per-room expansion ze 9 aggregate parents (každá expanded položka tagged _expansion_origin).
 9 položek recalculated s exact external perimeter 38.70 m (DXF km_R_návrh_tlustá 2 closed polygon) vs prior fallback 41.0 m.
 Skladby vrstev (Sheet 8 Var_E) pochází POUZE z TZ explicit text + DXF cross-validation HATCH patterns. ŽÁDNÉ generic 'standardní RD' assumption — kde TZ silent, explicit fallback flag s ČSN default.
@@ -3012,11 +3012,11 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>H-BLOK opěrná stěna; Tvarovky ZB obvod skladu; Výztuž ZB tvarovek</t>
+          <t>H-BLOK opěrná stěna; Tvarovky ZB obvod skladu; Výztuž ZB tvarovek; Hydroizolace + protiradon stěn pod terénem (S03a+S04); … (+1 dalších)</t>
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E4" s="10" t="n"/>
       <c r="F4" s="10" t="n"/>
@@ -3163,7 +3163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J131"/>
+  <dimension ref="A1:J133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3735,7 +3735,7 @@
         </is>
       </c>
       <c r="F14" s="22" t="n">
-        <v>3.2</v>
+        <v>2.64</v>
       </c>
       <c r="G14" s="10" t="n"/>
       <c r="H14" s="10" t="n"/>
@@ -4495,7 +4495,7 @@
         </is>
       </c>
       <c r="F33" s="22" t="n">
-        <v>2.12</v>
+        <v>1.76</v>
       </c>
       <c r="G33" s="10" t="n"/>
       <c r="H33" s="10" t="n"/>
@@ -5535,7 +5535,7 @@
         </is>
       </c>
       <c r="F59" s="22" t="n">
-        <v>33.9</v>
+        <v>36.74</v>
       </c>
       <c r="G59" s="10" t="n"/>
       <c r="H59" s="10" t="n"/>
@@ -7687,7 +7687,7 @@
         </is>
       </c>
       <c r="F113" s="22" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G113" s="10" t="n"/>
       <c r="H113" s="10" t="n"/>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="F114" s="22" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G114" s="10" t="n"/>
       <c r="H114" s="10" t="n"/>
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="F115" s="22" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G115" s="10" t="n"/>
       <c r="H115" s="10" t="n"/>
@@ -7847,7 +7847,7 @@
         </is>
       </c>
       <c r="F117" s="22" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G117" s="10" t="n"/>
       <c r="H117" s="10" t="n"/>
@@ -7909,34 +7909,34 @@
           <t>260217_sklad</t>
         </is>
       </c>
-      <c r="C119" s="21" t="inlineStr">
-        <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+      <c r="C119" s="8" t="inlineStr">
+        <is>
+          <t>HSV-3 Svislé konstrukce</t>
         </is>
       </c>
       <c r="D119" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 2 položek: Bezpečnostní dveře RC3 sklad; Vjezdová brána</t>
+          <t>Hydroizolace + protiradon stěn pod terénem (S03a+S04) — Hydroizolace + protiradonová ochrana obvodových stěn (S03a) + opěrné stěny (S04) pod úrovní terénu — asfaltová penetrace + 2× HI a protiradonový pás z modif. asfaltu 2×4 mm</t>
         </is>
       </c>
       <c r="E119" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F119" s="9" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F119" s="22" t="n">
+        <v>33</v>
       </c>
       <c r="G119" s="10" t="n"/>
       <c r="H119" s="10" t="n"/>
       <c r="I119" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="J119" s="8" t="inlineStr">
         <is>
-          <t>agregát</t>
+          <t>URS-prop —</t>
         </is>
       </c>
     </row>
@@ -7949,34 +7949,34 @@
           <t>260217_sklad</t>
         </is>
       </c>
-      <c r="C120" s="21" t="inlineStr">
-        <is>
-          <t>PSV-77 — Podlahy</t>
+      <c r="C120" s="8" t="inlineStr">
+        <is>
+          <t>HSV-3 Svislé konstrukce</t>
         </is>
       </c>
       <c r="D120" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
+          <t>Drenáž nopová folie stěn pod terénem (S03a+S04) — Drenážní vrstva — nopová folie tl. 20 mm na obvodové stěny (S03a) + opěrnou stěnu (S04) pod úrovní terénu</t>
         </is>
       </c>
       <c r="E120" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F120" s="9" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F120" s="22" t="n">
+        <v>33</v>
       </c>
       <c r="G120" s="10" t="n"/>
       <c r="H120" s="10" t="n"/>
       <c r="I120" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="J120" s="8" t="inlineStr">
         <is>
-          <t>agregát</t>
+          <t>URS-prop —</t>
         </is>
       </c>
     </row>
@@ -7991,12 +7991,12 @@
       </c>
       <c r="C121" s="21" t="inlineStr">
         <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D121" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 5 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+2 dalších)</t>
+          <t>[agregát] 2 položek: Bezpečnostní dveře RC3 sklad; Vjezdová brána</t>
         </is>
       </c>
       <c r="E121" s="20" t="inlineStr">
@@ -8026,17 +8026,17 @@
       </c>
       <c r="B122" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="C122" s="21" t="inlineStr">
         <is>
-          <t>M-21 — Elektroinstalace silnoproudá</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 8 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+5 dalších)</t>
+          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
         </is>
       </c>
       <c r="E122" s="20" t="inlineStr">
@@ -8066,17 +8066,17 @@
       </c>
       <c r="B123" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="C123" s="21" t="inlineStr">
         <is>
-          <t>M-24</t>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
         </is>
       </c>
       <c r="D123" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Lokální odtah digestoří kuchyní</t>
+          <t>[agregát] 5 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+2 dalších)</t>
         </is>
       </c>
       <c r="E123" s="20" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="C124" s="21" t="inlineStr">
         <is>
-          <t>PSV-71 — Izolace HI + TI</t>
+          <t>M-21 — Elektroinstalace silnoproudá</t>
         </is>
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
+          <t>[agregát] 8 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+5 dalších)</t>
         </is>
       </c>
       <c r="E124" s="20" t="inlineStr">
@@ -8151,12 +8151,12 @@
       </c>
       <c r="C125" s="21" t="inlineStr">
         <is>
-          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
+          <t>M-24</t>
         </is>
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
+          <t>[agregát] 1 položek: Lokální odtah digestoří kuchyní</t>
         </is>
       </c>
       <c r="E125" s="20" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="C126" s="21" t="inlineStr">
         <is>
-          <t>PSV-73 — Vytápění + komín</t>
+          <t>PSV-71 — Izolace HI + TI</t>
         </is>
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
+          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
         </is>
       </c>
       <c r="E126" s="20" t="inlineStr">
@@ -8231,12 +8231,12 @@
       </c>
       <c r="C127" s="21" t="inlineStr">
         <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
         </is>
       </c>
       <c r="D127" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
+          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
         </is>
       </c>
       <c r="E127" s="20" t="inlineStr">
@@ -8271,12 +8271,12 @@
       </c>
       <c r="C128" s="21" t="inlineStr">
         <is>
-          <t>PSV-77 — Podlahy</t>
+          <t>PSV-73 — Vytápění + komín</t>
         </is>
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
+          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
         </is>
       </c>
       <c r="E128" s="20" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="C129" s="21" t="inlineStr">
         <is>
-          <t>PSV-78 — Povrchové úpravy</t>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
+          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
         </is>
       </c>
       <c r="E129" s="20" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="C130" s="21" t="inlineStr">
         <is>
-          <t>PSV-95 — Detekce požární</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 3 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A; Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
+          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
         </is>
       </c>
       <c r="E130" s="20" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="C131" s="21" t="inlineStr">
         <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
+          <t>PSV-78 — Povrchové úpravy</t>
         </is>
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
+          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
         </is>
       </c>
       <c r="E131" s="20" t="inlineStr">
@@ -8420,8 +8420,88 @@
         </is>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" s="20" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C132" s="21" t="inlineStr">
+        <is>
+          <t>PSV-95 — Detekce požární</t>
+        </is>
+      </c>
+      <c r="D132" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 3 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A; Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
+        </is>
+      </c>
+      <c r="E132" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F132" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G132" s="10" t="n"/>
+      <c r="H132" s="10" t="n"/>
+      <c r="I132" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J132" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="20" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C133" s="21" t="inlineStr">
+        <is>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
+        </is>
+      </c>
+      <c r="D133" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
+        </is>
+      </c>
+      <c r="E133" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F133" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G133" s="10" t="n"/>
+      <c r="H133" s="10" t="n"/>
+      <c r="I133" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J133" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J131"/>
+  <autoFilter ref="A1:J133"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14481,7 +14561,7 @@
         </is>
       </c>
       <c r="G87" s="22" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H87" s="10" t="n"/>
       <c r="I87" s="10" t="n"/>
@@ -14520,7 +14600,7 @@
       </c>
       <c r="Q87" s="41" t="inlineStr">
         <is>
-          <t>SKLADBY_GAPS_2026-06-01</t>
+          <t>W2_SOKL_23to16_RADOVKA_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -14554,7 +14634,7 @@
         </is>
       </c>
       <c r="G88" s="22" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H88" s="10" t="n"/>
       <c r="I88" s="10" t="n"/>
@@ -14593,7 +14673,7 @@
       </c>
       <c r="Q88" s="41" t="inlineStr">
         <is>
-          <t>SKLADBY_GAPS_2026-06-01</t>
+          <t>W2_SOKL_23to16_RADOVKA_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -14627,7 +14707,7 @@
         </is>
       </c>
       <c r="G89" s="22" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H89" s="10" t="n"/>
       <c r="I89" s="10" t="n"/>
@@ -14666,7 +14746,7 @@
       </c>
       <c r="Q89" s="41" t="inlineStr">
         <is>
-          <t>SKLADBY_GAPS_2026-06-01</t>
+          <t>W2_SOKL_23to16_RADOVKA_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -14700,7 +14780,7 @@
         </is>
       </c>
       <c r="G90" s="22" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H90" s="10" t="n"/>
       <c r="I90" s="10" t="n"/>
@@ -14739,7 +14819,7 @@
       </c>
       <c r="Q90" s="41" t="inlineStr">
         <is>
-          <t>SKLADBY_GAPS_2026-06-01</t>
+          <t>W2_SOKL_23to16_RADOVKA_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -22263,12 +22343,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R32"/>
+  <dimension ref="A1:R34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
@@ -22672,7 +22752,7 @@
         </is>
       </c>
       <c r="G6" s="22" t="n">
-        <v>3.2</v>
+        <v>2.64</v>
       </c>
       <c r="H6" s="10" t="n"/>
       <c r="I6" s="10" t="n"/>
@@ -22709,7 +22789,11 @@
           <t>S01_sklad</t>
         </is>
       </c>
-      <c r="Q6" s="41" t="n"/>
+      <c r="Q6" s="41" t="inlineStr">
+        <is>
+          <t>W1_PODLAHA_17.6_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="n">
@@ -23073,7 +23157,7 @@
         </is>
       </c>
       <c r="G12" s="22" t="n">
-        <v>2.12</v>
+        <v>1.76</v>
       </c>
       <c r="H12" s="10" t="n"/>
       <c r="I12" s="10" t="n"/>
@@ -23112,7 +23196,7 @@
       </c>
       <c r="Q12" s="41" t="inlineStr">
         <is>
-          <t>URS_PHASE5B_CROSS_DISCIPLINE_OK</t>
+          <t>W1_PODLAHA_17.6_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -23402,41 +23486,41 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>HSV-4 Vodorovné</t>
+          <t>HSV-3 Svislé konstrukce</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Dřevěné stropnice skladu</t>
+          <t>Hydroizolace + protiradon stěn pod terénem (S03a+S04)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
         <is>
-          <t>762341110</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>Dřevěné stropnice 100/160 mm á 625 mm primární zastřešení skladu — rezivo C24 fungicidní</t>
+          <t>Hydroizolace + protiradonová ochrana obvodových stěn (S03a) + opěrné stěny (S04) pod úrovní terénu — asfaltová penetrace + 2× HI a protiradonový pás z modif. asfaltu 2×4 mm</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G17" s="22" t="n">
-        <v>33.9</v>
+        <v>33</v>
       </c>
       <c r="H17" s="10" t="n"/>
       <c r="I17" s="10" t="n"/>
       <c r="J17" s="8" t="inlineStr">
         <is>
-          <t>krov_tesarsky_kompletni</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K17" s="24" t="n">
-        <v>0.95</v>
+        <v>0.5</v>
       </c>
       <c r="L17" s="20" t="inlineStr">
         <is>
@@ -23445,7 +23529,7 @@
       </c>
       <c r="M17" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 + DXF DIMENSION</t>
+          <t>skladba S03a+S04 řez D.1.1.03/04 + legenda materiálu</t>
         </is>
       </c>
       <c r="N17" s="20" t="inlineStr">
@@ -23460,10 +23544,14 @@
       </c>
       <c r="P17" s="41" t="inlineStr">
         <is>
-          <t>S02_sklad</t>
-        </is>
-      </c>
-      <c r="Q17" s="41" t="n"/>
+          <t>S03a, S04</t>
+        </is>
+      </c>
+      <c r="Q17" s="41" t="inlineStr">
+        <is>
+          <t>SKLAD_WALL_HI_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n">
@@ -23471,22 +23559,22 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>HSV-4 Vodorovné</t>
+          <t>HSV-3 Svislé konstrukce</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Prkenný záklop stropu skladu</t>
+          <t>Drenáž nopová folie stěn pod terénem (S03a+S04)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>762331110</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>Prkenný záklop stropnic skladu tl. 20 mm + impregnace</t>
+          <t>Drenážní vrstva — nopová folie tl. 20 mm na obvodové stěny (S03a) + opěrnou stěnu (S04) pod úrovní terénu</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -23495,17 +23583,17 @@
         </is>
       </c>
       <c r="G18" s="22" t="n">
-        <v>21.209</v>
+        <v>33</v>
       </c>
       <c r="H18" s="10" t="n"/>
       <c r="I18" s="10" t="n"/>
       <c r="J18" s="8" t="inlineStr">
         <is>
-          <t>krov_tesarsky_kompletni</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K18" s="24" t="n">
-        <v>0.95</v>
+        <v>0.5</v>
       </c>
       <c r="L18" s="20" t="inlineStr">
         <is>
@@ -23514,7 +23602,7 @@
       </c>
       <c r="M18" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 + DXF</t>
+          <t>skladba S03a+S04 řez D.1.1.03/04</t>
         </is>
       </c>
       <c r="N18" s="20" t="inlineStr">
@@ -23529,10 +23617,14 @@
       </c>
       <c r="P18" s="41" t="inlineStr">
         <is>
-          <t>S02_sklad</t>
-        </is>
-      </c>
-      <c r="Q18" s="41" t="n"/>
+          <t>S03a, S04</t>
+        </is>
+      </c>
+      <c r="Q18" s="41" t="inlineStr">
+        <is>
+          <t>SKLAD_WALL_HI_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="20" t="n">
@@ -23545,32 +23637,32 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolační střešní souvrství skladu</t>
+          <t>Dřevěné stropnice skladu</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
         <is>
-          <t>712331101</t>
+          <t>762341110</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolační střešní souvrství skladu (modifikovaný asfaltový pás SBS + ochranná vrstva)</t>
+          <t>Dřevěné stropnice 100/160 mm á 625 mm primární zastřešení skladu — rezivo C24 fungicidní</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G19" s="22" t="n">
-        <v>22.26945</v>
+        <v>36.74</v>
       </c>
       <c r="H19" s="10" t="n"/>
       <c r="I19" s="10" t="n"/>
       <c r="J19" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>krov_tesarsky_kompletni</t>
         </is>
       </c>
       <c r="K19" s="24" t="n">
@@ -23583,7 +23675,7 @@
       </c>
       <c r="M19" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 — HI souvrství</t>
+          <t>TZ statika sklad §4 + DXF DIMENSION</t>
         </is>
       </c>
       <c r="N19" s="20" t="inlineStr">
@@ -23601,7 +23693,11 @@
           <t>S02_sklad</t>
         </is>
       </c>
-      <c r="Q19" s="41" t="n"/>
+      <c r="Q19" s="41" t="inlineStr">
+        <is>
+          <t>DS3_STROPNICE_11_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="n">
@@ -23614,36 +23710,36 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>IPE180 parking — sekundární</t>
+          <t>Prkenný záklop stropu skladu</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>411321414</t>
+          <t>762331110</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>Sekundární zastřešení parkingu — IPE180 v rozteči 1000 mm × délka 7 m × 7 ks</t>
+          <t>Prkenný záklop stropnic skladu tl. 20 mm + impregnace</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G20" s="22" t="n">
-        <v>921</v>
+        <v>21.209</v>
       </c>
       <c r="H20" s="10" t="n"/>
       <c r="I20" s="10" t="n"/>
       <c r="J20" s="8" t="inlineStr">
         <is>
-          <t>ocel_zamecnik_konstrukce</t>
+          <t>krov_tesarsky_kompletni</t>
         </is>
       </c>
       <c r="K20" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L20" s="20" t="inlineStr">
         <is>
@@ -23652,12 +23748,12 @@
       </c>
       <c r="M20" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §1.4 + DXF LWPOLYLINE 7000 mm + rozteč 1000 mm</t>
+          <t>TZ statika sklad §4 + DXF</t>
         </is>
       </c>
       <c r="N20" s="20" t="inlineStr">
         <is>
-          <t>#18</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O20" s="26" t="inlineStr">
@@ -23683,17 +23779,17 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Pojezdové ocelové pororošty</t>
+          <t>Hydroizolační střešní souvrství skladu</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
         <is>
-          <t>411321515</t>
+          <t>712331101</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>Pojezdové ocelové pororošty demontovatelné — povrch parkingu (žárově zinkováno)</t>
+          <t>Hydroizolační střešní souvrství skladu (modifikovaný asfaltový pás SBS + ochranná vrstva)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -23702,26 +23798,26 @@
         </is>
       </c>
       <c r="G21" s="22" t="n">
-        <v>44.6</v>
+        <v>22.26945</v>
       </c>
       <c r="H21" s="10" t="n"/>
       <c r="I21" s="10" t="n"/>
       <c r="J21" s="8" t="inlineStr">
         <is>
-          <t>ocel_zamecnik_konstrukce</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K21" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L21" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M21" s="8" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ km_tabulka místností + Phase 3.5 sklad qty crosscheck (Pattern 17 Phase 0a Layer 2 + Pattern 31 CEV Matrix D.2)</t>
+          <t>TZ statika sklad §4 — HI souvrství</t>
         </is>
       </c>
       <c r="N21" s="20" t="inlineStr">
@@ -23739,11 +23835,7 @@
           <t>S02_sklad</t>
         </is>
       </c>
-      <c r="Q21" s="41" t="inlineStr">
-        <is>
-          <t>PHASE_3_5_SKLAD_QTY_DXF_VERIFY; URS_PHASE5B_FAMILY_VERIFIED</t>
-        </is>
-      </c>
+      <c r="Q21" s="41" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="20" t="n">
@@ -23756,17 +23848,17 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Žárový zinek IPE + pororošty</t>
+          <t>IPE180 parking — sekundární</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>783201001</t>
+          <t>411321414</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>Žárově zinková povrchová úprava IPE180 + pororoštů dle ČSN EN ISO 12944 (C3 prostředí)</t>
+          <t>Sekundární zastřešení parkingu — IPE180 v rozteči 1000 mm × délka 7 m × 7 ks</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -23775,7 +23867,7 @@
         </is>
       </c>
       <c r="G22" s="22" t="n">
-        <v>1551</v>
+        <v>921</v>
       </c>
       <c r="H22" s="10" t="n"/>
       <c r="I22" s="10" t="n"/>
@@ -23785,7 +23877,7 @@
         </is>
       </c>
       <c r="K22" s="24" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L22" s="20" t="inlineStr">
         <is>
@@ -23794,12 +23886,12 @@
       </c>
       <c r="M22" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §1.4 + ČSN EN ISO 12944 — žárový zinek pro pojezdové ocel</t>
+          <t>TZ statika sklad §1.4 + DXF LWPOLYLINE 7000 mm + rozteč 1000 mm</t>
         </is>
       </c>
       <c r="N22" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#18</t>
         </is>
       </c>
       <c r="O22" s="26" t="inlineStr">
@@ -23820,22 +23912,22 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + schodiště</t>
+          <t>HSV-4 Vodorovné</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Sklad mezipodesta schodiště prefa</t>
+          <t>Pojezdové ocelové pororošty</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
         <is>
-          <t>121301101</t>
+          <t>411321515</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>Sklad mezipodesta schodiště — prefa betonové stupně (9 ks × 179.5×250 mm) + kladecí vrstva zavlhlého betonu nad ŽB podkladní deskou (S05 sklad skladba)</t>
+          <t>Pojezdové ocelové pororošty demontovatelné — povrch parkingu (žárově zinkováno)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -23844,26 +23936,26 @@
         </is>
       </c>
       <c r="G23" s="22" t="n">
-        <v>5.5</v>
+        <v>44.6</v>
       </c>
       <c r="H23" s="10" t="n"/>
       <c r="I23" s="10" t="n"/>
       <c r="J23" s="8" t="inlineStr">
         <is>
-          <t>betonar</t>
+          <t>ocel_zamecnik_konstrukce</t>
         </is>
       </c>
       <c r="K23" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L23" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M23" s="8" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ km_tabulka místností room 1.02 + DXF dimension 9×179.5×250 mm + Phase 3.5 sklad S-code mapping (S05 sklad schodiště skladba)</t>
+          <t>DXF sklad_DPZ km_tabulka místností + Phase 3.5 sklad qty crosscheck (Pattern 17 Phase 0a Layer 2 + Pattern 31 CEV Matrix D.2)</t>
         </is>
       </c>
       <c r="N23" s="20" t="inlineStr">
@@ -23878,12 +23970,12 @@
       </c>
       <c r="P23" s="41" t="inlineStr">
         <is>
-          <t>S05_sklad</t>
+          <t>S02_sklad</t>
         </is>
       </c>
       <c r="Q23" s="41" t="inlineStr">
         <is>
-          <t>PHASE_3_5_SKLAD_MEZIPODESTA_GAP</t>
+          <t>PHASE_3_5_SKLAD_QTY_DXF_VERIFY; URS_PHASE5B_FAMILY_VERIFIED</t>
         </is>
       </c>
     </row>
@@ -23893,39 +23985,41 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + vjezd</t>
+          <t>HSV-4 Vodorovné</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Vjezd Dvořákova — napojení na komunikaci</t>
+          <t>Žárový zinek IPE + pororošty</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>783201001</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>Napojení vjezdu na ulici Dvořákova — vydláždění z betonových dlaždic + spádování na pozemek investora + odvodnění dešťové vody na pozemek (ne na komunikaci)</t>
+          <t>Žárově zinková povrchová úprava IPE180 + pororoštů dle ČSN EN ISO 12944 (C3 prostředí)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G24" s="22" t="n"/>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="n">
+        <v>1551</v>
+      </c>
       <c r="H24" s="10" t="n"/>
       <c r="I24" s="10" t="n"/>
       <c r="J24" s="8" t="inlineStr">
         <is>
-          <t>komunikace</t>
+          <t>ocel_zamecnik_konstrukce</t>
         </is>
       </c>
       <c r="K24" s="24" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L24" s="20" t="inlineStr">
         <is>
@@ -23934,7 +24028,7 @@
       </c>
       <c r="M24" s="8" t="inlineStr">
         <is>
-          <t>Dodatek PD č.1 (E.01) / DI PČR požadavek</t>
+          <t>TZ statika sklad §1.4 + ČSN EN ISO 12944 — žárový zinek pro pojezdové ocel</t>
         </is>
       </c>
       <c r="N24" s="20" t="inlineStr">
@@ -23947,12 +24041,12 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P24" s="41" t="inlineStr"/>
-      <c r="Q24" s="41" t="inlineStr">
-        <is>
-          <t>DODATEK_PBR_GAPS_2026-06-01</t>
-        </is>
-      </c>
+      <c r="P24" s="41" t="inlineStr">
+        <is>
+          <t>S02_sklad</t>
+        </is>
+      </c>
+      <c r="Q24" s="41" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="20" t="n">
@@ -23960,41 +24054,41 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>HSV-5 Komunikace + schodiště</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Bezpečnostní dveře RC3 sklad</t>
+          <t>Sklad mezipodesta schodiště prefa</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
         <is>
-          <t>766682111</t>
+          <t>121301101</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
+          <t>Sklad mezipodesta schodiště — prefa betonové stupně (9 ks × 179.5×250 mm) + kladecí vrstva zavlhlého betonu nad ŽB podkladní deskou (S05 sklad skladba)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G25" s="23" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="n">
+        <v>5.5</v>
       </c>
       <c r="H25" s="10" t="n"/>
       <c r="I25" s="10" t="n"/>
       <c r="J25" s="8" t="inlineStr">
         <is>
-          <t>specialista_RC3_dvere</t>
+          <t>betonar</t>
         </is>
       </c>
       <c r="K25" s="24" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="L25" s="20" t="inlineStr">
         <is>
@@ -24003,7 +24097,7 @@
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §1.4 — RC3 bezpečnostní dveře v ocelové zárubni</t>
+          <t>DXF sklad_DPZ km_tabulka místností room 1.02 + DXF dimension 9×179.5×250 mm + Phase 3.5 sklad S-code mapping (S05 sklad schodiště skladba)</t>
         </is>
       </c>
       <c r="N25" s="20" t="inlineStr">
@@ -24016,8 +24110,16 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P25" s="41" t="n"/>
-      <c r="Q25" s="41" t="n"/>
+      <c r="P25" s="41" t="inlineStr">
+        <is>
+          <t>S05_sklad</t>
+        </is>
+      </c>
+      <c r="Q25" s="41" t="inlineStr">
+        <is>
+          <t>PHASE_3_5_SKLAD_MEZIPODESTA_GAP</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="20" t="n">
@@ -24025,12 +24127,12 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnictví</t>
+          <t>HSV-5 Komunikace + vjezd</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Vjezdová brána</t>
+          <t>Vjezd Dvořákova — napojení na komunikaci</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -24040,26 +24142,24 @@
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>Vjezdová brána na pozemku investora (ocelová) — dodávka + montáž</t>
+          <t>Napojení vjezdu na ulici Dvořákova — vydláždění z betonových dlaždic + spádování na pozemek investora + odvodnění dešťové vody na pozemek (ne na komunikaci)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G26" s="23" t="n">
-        <v>1</v>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="n"/>
       <c r="H26" s="10" t="n"/>
       <c r="I26" s="10" t="n"/>
       <c r="J26" s="8" t="inlineStr">
         <is>
-          <t>zamecnik</t>
+          <t>komunikace</t>
         </is>
       </c>
       <c r="K26" s="24" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="L26" s="20" t="inlineStr">
         <is>
@@ -24068,7 +24168,7 @@
       </c>
       <c r="M26" s="8" t="inlineStr">
         <is>
-          <t>Dodatek PD č.1 (E.01)</t>
+          <t>Dodatek PD č.1 (E.01) / DI PČR požadavek</t>
         </is>
       </c>
       <c r="N26" s="20" t="inlineStr">
@@ -24094,50 +24194,50 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Betonová dlažba sklad</t>
-        </is>
-      </c>
-      <c r="D27" s="27" t="inlineStr">
-        <is>
-          <t>596??? ?</t>
+          <t>Bezpečnostní dveře RC3 sklad</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>766682111</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>Betonová dlažba do pískového lože — povrch podlahy skladu (~21 m²)</t>
+          <t>Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G27" s="22" t="n">
-        <v>17.6</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G27" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H27" s="10" t="n"/>
       <c r="I27" s="10" t="n"/>
       <c r="J27" s="8" t="inlineStr">
         <is>
-          <t>podlahar</t>
+          <t>specialista_RC3_dvere</t>
         </is>
       </c>
       <c r="K27" s="24" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="L27" s="20" t="inlineStr">
         <is>
-          <t>wrong_leaf_disambiguation_needed</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M27" s="8" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ km_tabulka místností + Phase 3.5 sklad qty crosscheck (Pattern 17 Phase 0a Layer 2 + Pattern 31 CEV Matrix D.2)</t>
+          <t>TZ statika sklad §1.4 — RC3 bezpečnostní dveře v ocelové zárubni</t>
         </is>
       </c>
       <c r="N27" s="20" t="inlineStr">
@@ -24145,21 +24245,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O27" s="28" t="inlineStr">
-        <is>
-          <t>LEAF CHYBNÝ — viz alternatives</t>
-        </is>
-      </c>
-      <c r="P27" s="41" t="inlineStr">
-        <is>
-          <t>S01_sklad</t>
-        </is>
-      </c>
-      <c r="Q27" s="41" t="inlineStr">
-        <is>
-          <t>PHASE_3_5_SKLAD_QTY_DXF_VERIFY</t>
-        </is>
-      </c>
+      <c r="O27" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P27" s="41" t="n"/>
+      <c r="Q27" s="41" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="20" t="n">
@@ -24167,27 +24259,27 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Doprava prefa H-BLOK auto s hyd. rukou</t>
+          <t>Vjezdová brána</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>031032000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>Doprava prefa H-BLOK Standard z výrobny Herkul (Obrnice) auto s hydraulickou rukou — celkem ~60 ks bloků</t>
+          <t>Vjezdová brána na pozemku investora (ocelová) — dodávka + montáž</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G28" s="23" t="n">
@@ -24197,11 +24289,11 @@
       <c r="I28" s="10" t="n"/>
       <c r="J28" s="8" t="inlineStr">
         <is>
-          <t>prefa_bloky_specialista</t>
+          <t>zamecnik</t>
         </is>
       </c>
       <c r="K28" s="24" t="n">
-        <v>0.85</v>
+        <v>0.6</v>
       </c>
       <c r="L28" s="20" t="inlineStr">
         <is>
@@ -24210,7 +24302,7 @@
       </c>
       <c r="M28" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 + ARS — auto s hyd. rukou pro osazení H-BLOK</t>
+          <t>Dodatek PD č.1 (E.01)</t>
         </is>
       </c>
       <c r="N28" s="20" t="inlineStr">
@@ -24223,8 +24315,12 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P28" s="41" t="n"/>
-      <c r="Q28" s="41" t="n"/>
+      <c r="P28" s="41" t="inlineStr"/>
+      <c r="Q28" s="41" t="inlineStr">
+        <is>
+          <t>DODATEK_PBR_GAPS_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="20" t="n">
@@ -24232,50 +24328,50 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Likvidace odpadu sklad</t>
-        </is>
-      </c>
-      <c r="D29" s="20" t="inlineStr">
-        <is>
-          <t>997013211</t>
+          <t>Betonová dlažba sklad</t>
+        </is>
+      </c>
+      <c r="D29" s="27" t="inlineStr">
+        <is>
+          <t>596??? ?</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
+          <t>Betonová dlažba do pískového lože — povrch podlahy skladu (~21 m²)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G29" s="22" t="n">
-        <v>8</v>
+        <v>17.6</v>
       </c>
       <c r="H29" s="10" t="n"/>
       <c r="I29" s="10" t="n"/>
       <c r="J29" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>podlahar</t>
         </is>
       </c>
       <c r="K29" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L29" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>wrong_leaf_disambiguation_needed</t>
         </is>
       </c>
       <c r="M29" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS sklad §3 — kamenné zídky + schodiště odstraneny</t>
+          <t>DXF sklad_DPZ km_tabulka místností + Phase 3.5 sklad qty crosscheck (Pattern 17 Phase 0a Layer 2 + Pattern 31 CEV Matrix D.2)</t>
         </is>
       </c>
       <c r="N29" s="20" t="inlineStr">
@@ -24283,13 +24379,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O29" s="26" t="inlineStr">
-        <is>
-          <t>ANO</t>
-        </is>
-      </c>
-      <c r="P29" s="41" t="n"/>
-      <c r="Q29" s="41" t="n"/>
+      <c r="O29" s="28" t="inlineStr">
+        <is>
+          <t>LEAF CHYBNÝ — viz alternatives</t>
+        </is>
+      </c>
+      <c r="P29" s="41" t="inlineStr">
+        <is>
+          <t>S01_sklad</t>
+        </is>
+      </c>
+      <c r="Q29" s="41" t="inlineStr">
+        <is>
+          <t>PHASE_3_5_SKLAD_QTY_DXF_VERIFY</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="20" t="n">
@@ -24297,22 +24401,22 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Geodetické vytýčení sklad</t>
+          <t>Doprava prefa H-BLOK auto s hyd. rukou</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
         <is>
-          <t>030141000</t>
+          <t>031032000</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
+          <t>Doprava prefa H-BLOK Standard z výrobny Herkul (Obrnice) auto s hydraulickou rukou — celkem ~60 ks bloků</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
@@ -24327,11 +24431,11 @@
       <c r="I30" s="10" t="n"/>
       <c r="J30" s="8" t="inlineStr">
         <is>
-          <t>geodet</t>
+          <t>prefa_bloky_specialista</t>
         </is>
       </c>
       <c r="K30" s="24" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="L30" s="20" t="inlineStr">
         <is>
@@ -24340,7 +24444,7 @@
       </c>
       <c r="M30" s="8" t="inlineStr">
         <is>
-          <t>Standard — geodet vytýčení pro každý nový objekt</t>
+          <t>TZ statika sklad §4 + ARS — auto s hyd. rukou pro osazení H-BLOK</t>
         </is>
       </c>
       <c r="N30" s="20" t="inlineStr">
@@ -24362,41 +24466,41 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>VRN — Geodet / PČR</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>Rozhledové trojúhelníky — vytyčení + kontrola</t>
+          <t>Likvidace odpadu sklad</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>Vytyčení + kontrola rozhledových trojúhelníků (Vn=40 km/h, Dz=25 m) dle požadavku DI PČR</t>
+          <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
         <is>
-          <t>soubor</t>
-        </is>
-      </c>
-      <c r="G31" s="23" t="n">
-        <v>1</v>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G31" s="22" t="n">
+        <v>8</v>
       </c>
       <c r="H31" s="10" t="n"/>
       <c r="I31" s="10" t="n"/>
       <c r="J31" s="8" t="inlineStr">
         <is>
-          <t>geodet</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="K31" s="24" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="L31" s="20" t="inlineStr">
         <is>
@@ -24405,7 +24509,7 @@
       </c>
       <c r="M31" s="8" t="inlineStr">
         <is>
-          <t>Dodatek PD č.1 (E.01) / DI PČR</t>
+          <t>TZ ARS sklad §3 — kamenné zídky + schodiště odstraneny</t>
         </is>
       </c>
       <c r="N31" s="20" t="inlineStr">
@@ -24418,12 +24522,8 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P31" s="41" t="inlineStr"/>
-      <c r="Q31" s="41" t="inlineStr">
-        <is>
-          <t>DODATEK_PBR_GAPS_2026-06-01</t>
-        </is>
-      </c>
+      <c r="P31" s="41" t="n"/>
+      <c r="Q31" s="41" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="20" t="n">
@@ -24431,27 +24531,27 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>VRN — Společné</t>
+          <t>VRN — Geodet</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Podíl na obecných VRN dům</t>
+          <t>Geodetické vytýčení sklad</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
         <is>
-          <t>030001000</t>
+          <t>030141000</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+          <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G32" s="23" t="n">
@@ -24461,11 +24561,11 @@
       <c r="I32" s="10" t="n"/>
       <c r="J32" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>geodet</t>
         </is>
       </c>
       <c r="K32" s="24" t="n">
-        <v>0.8</v>
+        <v>0.99</v>
       </c>
       <c r="L32" s="20" t="inlineStr">
         <is>
@@ -24474,7 +24574,7 @@
       </c>
       <c r="M32" s="8" t="inlineStr">
         <is>
-          <t>Standard zhotovitel — alokace VRN pro paralelně realizovaný sklad</t>
+          <t>Standard — geodet vytýčení pro každý nový objekt</t>
         </is>
       </c>
       <c r="N32" s="20" t="inlineStr">
@@ -24490,9 +24590,143 @@
       <c r="P32" s="41" t="n"/>
       <c r="Q32" s="41" t="n"/>
     </row>
+    <row r="33">
+      <c r="A33" s="20" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Geodet / PČR</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Rozhledové trojúhelníky — vytyčení + kontrola</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>Vytyčení + kontrola rozhledových trojúhelníků (Vn=40 km/h, Dz=25 m) dle požadavku DI PČR</t>
+        </is>
+      </c>
+      <c r="F33" s="20" t="inlineStr">
+        <is>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="G33" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="10" t="n"/>
+      <c r="I33" s="10" t="n"/>
+      <c r="J33" s="8" t="inlineStr">
+        <is>
+          <t>geodet</t>
+        </is>
+      </c>
+      <c r="K33" s="24" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L33" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M33" s="8" t="inlineStr">
+        <is>
+          <t>Dodatek PD č.1 (E.01) / DI PČR</t>
+        </is>
+      </c>
+      <c r="N33" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O33" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P33" s="41" t="inlineStr"/>
+      <c r="Q33" s="41" t="inlineStr">
+        <is>
+          <t>DODATEK_PBR_GAPS_2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="20" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Společné</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>Podíl na obecných VRN dům</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="inlineStr">
+        <is>
+          <t>030001000</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+        </is>
+      </c>
+      <c r="F34" s="20" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="G34" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="10" t="n"/>
+      <c r="I34" s="10" t="n"/>
+      <c r="J34" s="8" t="inlineStr">
+        <is>
+          <t>VRN_management</t>
+        </is>
+      </c>
+      <c r="K34" s="24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L34" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M34" s="8" t="inlineStr">
+        <is>
+          <t>Standard zhotovitel — alokace VRN pro paralelně realizovaný sklad</t>
+        </is>
+      </c>
+      <c r="N34" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O34" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P34" s="41" t="n"/>
+      <c r="Q34" s="41" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O32"/>
-  <conditionalFormatting sqref="K2:K32">
+  <autoFilter ref="A1:O34"/>
+  <conditionalFormatting sqref="K2:K34">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0" stopIfTrue="1">
       <formula>0.70</formula>
     </cfRule>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01_v2.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01_v2.xlsx
@@ -23544,7 +23544,7 @@
       </c>
       <c r="P17" s="41" t="inlineStr">
         <is>
-          <t>S03a, S04</t>
+          <t>S03a_sklad, S04_sklad</t>
         </is>
       </c>
       <c r="Q17" s="41" t="inlineStr">
@@ -23617,7 +23617,7 @@
       </c>
       <c r="P18" s="41" t="inlineStr">
         <is>
-          <t>S03a, S04</t>
+          <t>S03a_sklad, S04_sklad</t>
         </is>
       </c>
       <c r="Q18" s="41" t="inlineStr">

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01_v2.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01_v2.xlsx
@@ -23318,7 +23318,7 @@
       </c>
       <c r="M14" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 + ARS — Herkul H-BLOK, montáž auto s hyd. rukou</t>
+          <t>TZ statika sklad §[19] tech. list H-BLOK Standard Herkul a.s. (Obrnice) + řez A-A výška 3000</t>
         </is>
       </c>
       <c r="N14" s="20" t="inlineStr">
@@ -23336,7 +23336,11 @@
           <t>S04_sklad</t>
         </is>
       </c>
-      <c r="Q14" s="41" t="n"/>
+      <c r="Q14" s="41" t="inlineStr">
+        <is>
+          <t>PREFA_HEIGHT3.0_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="20" t="n">

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01_v2.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01_v2.xlsx
@@ -1097,7 +1097,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>0.99: 17 | 0.95: 32 | 0.90: 34 | 0.85: 41 | 0.80: 21 | 0.75: 71 | 0.70: 4 | 0.60: 3 | 0.50: 6 | 0.00: 5</t>
+          <t>0.99: 17 | 0.95: 32 | 0.90: 34 | 0.85: 41 | 0.82: 1 | 0.80: 21 | 0.75: 70 | 0.70: 4 | 0.60: 3 | 0.50: 6 | 0.00: 5</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
         <is>
           <t>Rozpočet generován STAVAGENT pipelinem z DSP dokumentace s DPS-grade DXF metadaty.
 234 položek celkem (201 dum + 33 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
-Confidence distribution: 17×0.99 · 32×0.95 · 34×0.90 · 41×0.85 · 21×0.80 · 71×0.75 · 4×0.70 · 3×0.60 · 6×0.50 · 5×0.00.
+Confidence distribution: 17×0.99 · 32×0.95 · 34×0.90 · 41×0.85 · 1×0.82 · 21×0.80 · 70×0.75 · 4×0.70 · 3×0.60 · 6×0.50 · 5×0.00.
 25 položek vzniklo per-room expansion ze 9 aggregate parents (každá expanded položka tagged _expansion_origin).
 9 položek recalculated s exact external perimeter 38.70 m (DXF km_R_návrh_tlustá 2 closed polygon) vs prior fallback 41.0 m.
 Skladby vrstev (Sheet 8 Var_E) pochází POUZE z TZ explicit text + DXF cross-validation HATCH patterns. ŽÁDNÉ generic 'standardní RD' assumption — kde TZ silent, explicit fallback flag s ČSN default.
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="F42" s="23" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="G42" s="10" t="n"/>
       <c r="H42" s="10" t="n"/>
@@ -23299,7 +23299,7 @@
         </is>
       </c>
       <c r="G14" s="23" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="H14" s="10" t="n"/>
       <c r="I14" s="10" t="n"/>
@@ -23309,7 +23309,7 @@
         </is>
       </c>
       <c r="K14" s="24" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="L14" s="20" t="inlineStr">
         <is>
@@ -23318,7 +23318,7 @@
       </c>
       <c r="M14" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §[19] tech. list H-BLOK Standard Herkul a.s. (Obrnice) + řez A-A výška 3000</t>
+          <t>TZ statika sklad §[19] + web: H-BLOK Standard Herkul (Obrnice) líc 1800×600 mm = 1.08 m²/blok; ověřit definitiv z tech. listu dodavatele</t>
         </is>
       </c>
       <c r="N14" s="20" t="inlineStr">
@@ -23338,7 +23338,7 @@
       </c>
       <c r="Q14" s="41" t="inlineStr">
         <is>
-          <t>PREFA_HEIGHT3.0_2026-06-01</t>
+          <t>HBLOK_ROZMERY_2026-06-01</t>
         </is>
       </c>
     </row>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01_v2.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01_v2.xlsx
@@ -23318,7 +23318,7 @@
       </c>
       <c r="M14" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §[19] + web: H-BLOK Standard Herkul (Obrnice) líc 1800×600 mm = 1.08 m²/blok; ověřit definitiv z tech. listu dodavatele</t>
+          <t>TZ statika sklad §[19] H-BLOK Standard Herkul (Obrnice). Rozměr bloku NEověřen z tech. listu — odhad 1800×600 mm z web-analogie (BB6 stejný gabarit). Plocha líce 19.05 m² je measured (řez A-A); count 18 ks je estimate závislý na rozměru bloku.</t>
         </is>
       </c>
       <c r="N14" s="20" t="inlineStr">
@@ -23338,7 +23338,7 @@
       </c>
       <c r="Q14" s="41" t="inlineStr">
         <is>
-          <t>HBLOK_ROZMERY_2026-06-01</t>
+          <t>HBLOK_ROZMERY_ESTIMATE_2026-06-01</t>
         </is>
       </c>
     </row>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01_v2.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-01_v2.xlsx
@@ -1097,7 +1097,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>0.99: 17 | 0.95: 32 | 0.90: 34 | 0.85: 41 | 0.80: 21 | 0.75: 71 | 0.70: 4 | 0.60: 3 | 0.50: 6 | 0.00: 5</t>
+          <t>0.99: 17 | 0.95: 32 | 0.90: 34 | 0.85: 41 | 0.82: 1 | 0.80: 21 | 0.75: 70 | 0.70: 4 | 0.60: 3 | 0.50: 6 | 0.00: 5</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
         <is>
           <t>Rozpočet generován STAVAGENT pipelinem z DSP dokumentace s DPS-grade DXF metadaty.
 234 položek celkem (201 dum + 33 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
-Confidence distribution: 17×0.99 · 32×0.95 · 34×0.90 · 41×0.85 · 21×0.80 · 71×0.75 · 4×0.70 · 3×0.60 · 6×0.50 · 5×0.00.
+Confidence distribution: 17×0.99 · 32×0.95 · 34×0.90 · 41×0.85 · 1×0.82 · 21×0.80 · 70×0.75 · 4×0.70 · 3×0.60 · 6×0.50 · 5×0.00.
 25 položek vzniklo per-room expansion ze 9 aggregate parents (každá expanded položka tagged _expansion_origin).
 9 položek recalculated s exact external perimeter 38.70 m (DXF km_R_návrh_tlustá 2 closed polygon) vs prior fallback 41.0 m.
 Skladby vrstev (Sheet 8 Var_E) pochází POUZE z TZ explicit text + DXF cross-validation HATCH patterns. ŽÁDNÉ generic 'standardní RD' assumption — kde TZ silent, explicit fallback flag s ČSN default.
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="F42" s="23" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="G42" s="10" t="n"/>
       <c r="H42" s="10" t="n"/>
@@ -23299,7 +23299,7 @@
         </is>
       </c>
       <c r="G14" s="23" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="H14" s="10" t="n"/>
       <c r="I14" s="10" t="n"/>
@@ -23309,7 +23309,7 @@
         </is>
       </c>
       <c r="K14" s="24" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="L14" s="20" t="inlineStr">
         <is>
@@ -23318,7 +23318,7 @@
       </c>
       <c r="M14" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §[19] tech. list H-BLOK Standard Herkul a.s. (Obrnice) + řez A-A výška 3000</t>
+          <t>TZ statika sklad §[19] H-BLOK Standard Herkul (Obrnice). Rozměr bloku NEověřen z tech. listu — odhad 1800×600 mm z web-analogie (BB6 stejný gabarit). Plocha líce 19.05 m² je measured (řez A-A); count 18 ks je estimate závislý na rozměru bloku.</t>
         </is>
       </c>
       <c r="N14" s="20" t="inlineStr">
@@ -23338,7 +23338,7 @@
       </c>
       <c r="Q14" s="41" t="inlineStr">
         <is>
-          <t>PREFA_HEIGHT3.0_2026-06-01</t>
+          <t>HBLOK_ROZMERY_ESTIMATE_2026-06-01</t>
         </is>
       </c>
     </row>
